--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -3683,17 +3683,17 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Clients who stopped guessing</t>
+          <t>Tangible results</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>კლიენტები, რომლებმაც ვარაუდი სისტემით ჩაანაცვლეს</t>
+          <t>ხელშესახები შედეგები</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Клиенты, которые перестали гадать</t>
+          <t>Ощутимые результаты</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -4079,17 +4079,17 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>20 minutes closes every question</t>
+          <t>20 minutes to save 30+ hours</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>20 წუთი ყველა კითხვას პასუხს გაგცემს</t>
+          <t>20 წუთი, 30+ საათის დასაზოგად</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>20 минут закрывают любой вопрос</t>
+          <t>20 минут, чтобы сэкономить 30+ часов</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
           <t>Цены</t>
         </is>
       </c>
-      <c r="G126" s="3" t="inlineStr"/>
+      <c r="G126" s="3" t="n"/>
       <c r="H126" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -5768,7 +5768,7 @@
           <t>Три модели сотрудничества</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr"/>
+      <c r="G127" s="3" t="n"/>
       <c r="H127" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -5806,7 +5806,7 @@
           <t>В зависимости от того, сколько нашего ресурса вам нужно, мы предлагаем три модели сотрудничества. Выберите самую удобную.</t>
         </is>
       </c>
-      <c r="G128" s="3" t="inlineStr"/>
+      <c r="G128" s="3" t="n"/>
       <c r="H128" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -5831,23 +5831,23 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Already have a system?</t>
+          <t>We share our tools and experience</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>უკვე გაქვს სისტემა?</t>
+          <t>გიზიარებთ ინსტრუმენტებს და გამოცდილებას</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Уже есть система?</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="inlineStr"/>
+          <t>Делимся инструментами и опытом</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n"/>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -5869,23 +5869,23 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>ADVISOR</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>STARTER</t>
+          <t>ADVISOR</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>STARTER</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr"/>
+          <t>ADVISOR</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n"/>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
           <t>1-2 конкретных решения из нашего каталога, внедрённых в вашу систему. Быстро, точно, без переделки.</t>
         </is>
       </c>
-      <c r="G131" s="3" t="inlineStr"/>
+      <c r="G131" s="3" t="n"/>
       <c r="H131" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -5945,23 +5945,23 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>€990-1,490</t>
+          <t>€990+</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>€990-1,490</t>
+          <t>€990+</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>€990-1,490</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr"/>
+          <t>€990+</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n"/>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
           <t>+ НДС · разово</t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="n"/>
       <c r="H133" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6021,23 +6021,23 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>3-5 working days</t>
+          <t>3+ working days</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>3-5 სამუშაო დღე</t>
+          <t>3+ სამუშაო დღე</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>3-5 рабочих дней</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr"/>
+          <t>3+ рабочих дня</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n"/>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
           <t>1-2 решения из каталога</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="n"/>
       <c r="H135" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6110,7 +6110,7 @@
           <t>Интеграция в существующую систему</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr"/>
+      <c r="G136" s="3" t="n"/>
       <c r="H136" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6148,7 +6148,7 @@
           <t>30-минутное обучение команды</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr"/>
+      <c r="G137" s="3" t="n"/>
       <c r="H137" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6173,23 +6173,23 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>14-day post-launch support</t>
+          <t>Consulting sessions</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>14-დღიანი დანერგვის შემდგომი მხარდაჭერა</t>
+          <t>საკონსულტაციო შეხვედრები</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>14-дневная поддержка после запуска</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr"/>
+          <t>Консультационные встречи</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n"/>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6211,23 +6211,23 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Request Starter</t>
+          <t>Request Advisor</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე Starter</t>
+          <t>მოითხოვე Advisor</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Запросить Starter</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr"/>
+          <t>Запросить Advisor</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n"/>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
           <t>⭐ Самый популярный</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr"/>
+      <c r="G140" s="3" t="n"/>
       <c r="H140" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6287,23 +6287,23 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Build it right, from scratch</t>
+          <t>We help you implement step by step</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>ააშენე სწორად, თავიდან</t>
+          <t>გეხმარებით ეტაპობრივად დანერგვაში</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Построить правильно, с нуля</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr"/>
+          <t>Помогаем внедрять поэтапно</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n"/>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6325,23 +6325,23 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>SPRINT</t>
+          <t>SPRINTER</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>SPRINT</t>
+          <t>SPRINTER</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>SPRINT</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="inlineStr"/>
+          <t>SPRINTER</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n"/>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
           <t>Построение полной системы или решение главной боли. За 2 недели, команда обучена, всё ваше.</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr"/>
+      <c r="G143" s="3" t="n"/>
       <c r="H143" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6414,7 +6414,7 @@
           <t>€2,990</t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr"/>
+      <c r="G144" s="3" t="n"/>
       <c r="H144" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6452,7 +6452,7 @@
           <t>+ НДС · разово</t>
         </is>
       </c>
-      <c r="G145" s="3" t="inlineStr"/>
+      <c r="G145" s="3" t="n"/>
       <c r="H145" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6490,7 +6490,7 @@
           <t>10-15 рабочих дней</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr"/>
+      <c r="G146" s="3" t="n"/>
       <c r="H146" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6528,7 +6528,7 @@
           <t>Полный спринт Data Foundation или Sharpest Pain</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="n"/>
       <c r="H147" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6566,7 +6566,7 @@
           <t>До 6 решений из каталога</t>
         </is>
       </c>
-      <c r="G148" s="3" t="inlineStr"/>
+      <c r="G148" s="3" t="n"/>
       <c r="H148" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6604,7 +6604,7 @@
           <t>Автоматизация + 1 интеграция</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr"/>
+      <c r="G149" s="3" t="n"/>
       <c r="H149" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6642,7 +6642,7 @@
           <t>Миграция данных (1 источник)</t>
         </is>
       </c>
-      <c r="G150" s="3" t="inlineStr"/>
+      <c r="G150" s="3" t="n"/>
       <c r="H150" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6680,7 +6680,7 @@
           <t>1-часовое обучение команды</t>
         </is>
       </c>
-      <c r="G151" s="3" t="inlineStr"/>
+      <c r="G151" s="3" t="n"/>
       <c r="H151" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6700,28 +6700,28 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>pricing.2.feature.6</t>
+          <t>pricing.2.cta</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>30-day post-launch tuning</t>
+          <t>Request Sprinter</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>30-დღიანი დანერგვის შემდგომი დახვეწა</t>
+          <t>მოითხოვე Sprinter</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>30-дневная настройка после запуска</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr"/>
+          <t>Запросить Sprinter</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n"/>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6738,28 +6738,28 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>pricing.2.cta</t>
+          <t>pricing.3.tag</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Request Sprint</t>
+          <t>We keep your growth moving, continuously</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე Sprint</t>
+          <t>მუდმივად ვზრუნავთ განვითარებაზე</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Запросить Sprint</t>
-        </is>
-      </c>
-      <c r="G153" s="3" t="inlineStr"/>
+          <t>Постоянно заботимся о развитии</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n"/>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6776,28 +6776,28 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.tag</t>
+          <t>pricing.3.name</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Need a digital team on tap?</t>
+          <t>PRIORITY</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>ციფრული გუნდი მუდმივად გჭირდება?</t>
+          <t>PRIORITY</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Нужна цифровая команда на связи?</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr"/>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n"/>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6814,25 +6814,25 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.name</t>
+          <t>pricing.3.pitch</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>PARTNERSHIP</t>
+          <t>Multi-sprint build + ongoing managed services. Priority queue, direct line to our CEO + Tech Lead.</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>PARTNERSHIP</t>
+          <t>მრავალ-სპრინტიანი აწყობა + მუდმივი managed services. პრიორიტეტული რიგი, პირდაპირი კავშირი CEO-სთან და Tech Lead-სთან.</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>PARTNERSHIP</t>
-        </is>
-      </c>
-      <c r="G155" s="3" t="inlineStr"/>
+          <t>Многоспринтовое построение + постоянные managed services. Приоритетная очередь, прямая связь с CEO и Tech Lead.</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n"/>
       <c r="H155" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6852,25 +6852,25 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.pitch</t>
+          <t>pricing.3.price</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Multi-sprint build + ongoing managed services. Priority queue, direct line to our CEO + Tech Lead.</t>
+          <t>€7,990 + €790/mo</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>მრავალ-სპრინტიანი აწყობა + მუდმივი managed services. პრიორიტეტული რიგი, პირდაპირი კავშირი CEO-სთან და Tech Lead-სთან.</t>
+          <t>€7,990 + €790/თვე</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Многоспринтовое построение + постоянные managed services. Приоритетная очередь, прямая связь с CEO и Tech Lead.</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="inlineStr"/>
+          <t>€7,990 + €790/мес</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n"/>
       <c r="H156" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6890,25 +6890,25 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.price</t>
+          <t>pricing.3.priceUnit</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>€7,990 + €790/mo</t>
+          <t>+ VAT · 6-month minimum</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>€7,990 + €790/თვე</t>
+          <t>+ დღგ · 6 თვე მინ.</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>€7,990 + €790/мес</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr"/>
+          <t>+ НДС · минимум 6 месяцев</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n"/>
       <c r="H157" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6928,25 +6928,25 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.priceUnit</t>
+          <t>pricing.3.timeline</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>+ VAT · 6-month minimum</t>
+          <t>90-day engagement</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>+ დღგ · 6 თვე მინ.</t>
+          <t>90-დღიანი ჩართულობა</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>+ НДС · минимум 6 месяцев</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="inlineStr"/>
+          <t>90-дневное взаимодействие</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n"/>
       <c r="H158" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6966,28 +6966,28 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.timeline</t>
+          <t>pricing.3.feature.1</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>90-day engagement</t>
+          <t>Everything included in Sprinter</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>90-დღიანი ჩართულობა</t>
+          <t>ყველაფერი, რასაც Sprinter მოიცავს</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>90-дневное взаимодействие</t>
-        </is>
-      </c>
-      <c r="G159" s="3" t="inlineStr"/>
+          <t>Всё, что входит в Sprinter</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n"/>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -7004,25 +7004,25 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.feature.1</t>
+          <t>pricing.3.feature.2</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Sprint 1 + Sprint 2 pre-planned</t>
+          <t>Priority dev queue</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Sprint 1 + Sprint 2 წინასწარ ჩაგეგმილი</t>
+          <t>პრიორიტეტული dev-ის რიგი</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Спринт 1 + Спринт 2 запланированы</t>
-        </is>
-      </c>
-      <c r="G160" s="3" t="inlineStr"/>
+          <t>Приоритетная очередь разработки</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n"/>
       <c r="H160" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7042,28 +7042,28 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.feature.2</t>
+          <t>pricing.3.feature.3</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Priority dev queue</t>
+          <t>A dedicated specialist from our team</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>პრიორიტეტული dev-ის რიგი</t>
+          <t>გამოყოფილი სპეციალისტი გუნდიდან</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Приоритетная очередь разработки</t>
-        </is>
-      </c>
-      <c r="G161" s="3" t="inlineStr"/>
+          <t>Выделенный специалист из команды</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n"/>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -7080,25 +7080,25 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.feature.3</t>
+          <t>pricing.3.feature.4</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Direct WhatsApp with CEO + Tech Lead</t>
+          <t>Managed services (ongoing optimization)</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>პირდაპირი WhatsApp CEO-სთან + Tech Lead-სთან</t>
+          <t>Managed services (მუდმივი ოპტიმიზაცია)</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Прямой WhatsApp с CEO + Tech Lead</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="inlineStr"/>
+          <t>Managed services (постоянная оптимизация)</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n"/>
       <c r="H162" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.feature.4</t>
+          <t>pricing.3.feature.5</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Managed services (ongoing optimization)</t>
+          <t>Monthly strategy review (CEO level)</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Managed services (მუდმივი ოპტიმიზაცია)</t>
+          <t>თვიური სტრატეგიული შეხვედრა (CEO)</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Managed services (постоянная оптимизация)</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr"/>
+          <t>Ежемесячная стратегическая встреча (CEO)</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n"/>
       <c r="H163" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7156,28 +7156,28 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.feature.5</t>
+          <t>pricing.3.cta</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Monthly strategy review (CEO level)</t>
+          <t>Request Priority</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>თვიური სტრატეგიული შეხვედრა (CEO)</t>
+          <t>მოითხოვე Priority</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Ежемесячная стратегическая встреча (CEO)</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr"/>
+          <t>Запросить Priority</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -7194,28 +7194,28 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>pricing.3.cta</t>
+          <t>pricing.blueprint.title</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Request Partnership</t>
+          <t>Need more flexibility? Use our resource - by the hour</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე Partnership</t>
+          <t>მეტი მოქნილობა გჭირდება? გამოიყენე ჩვენი რესურსი - საათობრივად</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Запросить Partnership</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr"/>
+          <t>Нужно больше гибкости? Используйте наш ресурс - почасово</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n"/>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -7232,25 +7232,25 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>pricing.blueprint.title</t>
+          <t>pricing.blueprint.body</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Need help with your existing system?</t>
+          <t>Order technical and expert support by the hour. Our team helps with implementation, know-how, and years of experience - exactly when you need it. €69/h + VAT, no minimum commitment.</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>გჭირდება მხარდაჭერა შენი არსებული სისტემისთვის?</t>
+          <t>შეუკვეთე ტექნიკური და საექსპერტო მხარდაჭერა საათობრივად. ჩვენი გუნდი დაგეხმარება ტექნიკური დანერგვით, ცოდნითა და წლების გამოცდილებით - ზუსტად მაშინ, როცა გჭირდება. €69/სთ + დღგ, არანაირი მინიმალური ვალდებულება.</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Нужна поддержка существующей системы?</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr"/>
+          <t>Закажите техническую и экспертную поддержку почасово. Наша команда поможет с технической реализацией, знаниями и многолетним опытом - именно тогда, когда это нужно. €69/ч + НДС, без минимальных обязательств.</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n"/>
       <c r="H166" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7270,25 +7270,25 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>pricing.blueprint.body</t>
+          <t>pricing.blueprint.cta</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Order technical and expert support by the hour. Our team helps with implementation, know-how, and years of experience - exactly when you need it. €69/h + VAT, no minimum commitment.</t>
+          <t>Request support →</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>შეუკვეთე ტექნიკური და საექსპერტო მხარდაჭერა საათობრივად. ჩვენი გუნდი დაგეხმარება ტექნიკური დანერგვით, ცოდნითა და წლების გამოცდილებით - ზუსტად მაშინ, როცა გჭირდება. €69/სთ + დღგ, არანაირი მინიმალური ვალდებულება.</t>
+          <t>მოითხოვე მხარდაჭერა →</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Закажите техническую и экспертную поддержку почасово. Наша команда поможет с технической реализацией, знаниями и многолетним опытом - именно тогда, когда это нужно. €69/ч + НДС, без минимальных обязательств.</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr"/>
+          <t>Запросить поддержку →</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n"/>
       <c r="H167" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7303,30 +7303,34 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>Form</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>pricing.blueprint.cta</t>
+          <t>form.fullName</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Request support →</t>
+          <t>Full Name</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე მხარდაჭერა →</t>
+          <t>სახელი და გვარი</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Запросить поддержку →</t>
-        </is>
-      </c>
-      <c r="G168" s="3" t="inlineStr"/>
+          <t>Имя и фамилия</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>Single "Full Name" field. CRM: 1 word -&gt; Last Name; 2+ words -&gt; first = First Name, rest = Last Name</t>
+        </is>
+      </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7346,27 +7350,27 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>form.fullName</t>
+          <t>form.consent</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Full Name</t>
+          <t>By submitting this form, I consent to Unity LLC (unitty.io) processing my data for communication and direct marketing. I can withdraw consent or have my data corrected or deleted at any time by writing to digital@unitty.io.</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>სახელი და გვარი</t>
+          <t>ფორმის გაგზავნით ვეთანხმები შპს „იუნითის“ (unitty.io) მიერ ჩემი მონაცემების დამუშავებას კომუნიკაციისა და პირდაპირი მარკეტინგის მიზნით. თანხმობის გაუქმება ან მონაცემების გასწორება/წაშლა შესაძლებელია ნებისმიერ დროს: digital@unitty.io მიმართვით.</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Имя и фамилия</t>
+          <t>Отправляя форму, я соглашаюсь на обработку моих данных ООО «Юнити» (unitty.io) в целях коммуникации и прямого маркетинга. Отозвать согласие или исправить/удалить данные можно в любое время, написав на digital@unitty.io.</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>Single "Full Name" field. CRM: 1 word -&gt; Last Name; 2+ words -&gt; first = First Name, rest = Last Name</t>
+          <t>Consent text under the lead form (personal data + direct marketing)</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
@@ -7383,32 +7387,32 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>Nav</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>form.consent</t>
+          <t>nav.call</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>By submitting this form, I consent to Unity LLC (unitty.io) processing my data for communication and direct marketing. I can withdraw consent or have my data corrected or deleted at any time by writing to digital@unitty.io.</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>ფორმის გაგზავნით ვეთანხმები შპს „იუნითის“ (unitty.io) მიერ ჩემი მონაცემების დამუშავებას კომუნიკაციისა და პირდაპირი მარკეტინგის მიზნით. თანხმობის გაუქმება ან მონაცემების გასწორება/წაშლა შესაძლებელია ნებისმიერ დროს: digital@unitty.io მიმართვით.</t>
+          <t>დარეკვა</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Отправляя форму, я соглашаюсь на обработку моих данных ООО «Юнити» (unitty.io) в целях коммуникации и прямого маркетинга. Отозвать согласие или исправить/удалить данные можно в любое время, написав на digital@unitty.io.</t>
+          <t>Позвонить</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>Consent text under the lead form (personal data + direct marketing)</t>
+          <t>Header call button (shown Mon-Fri 10:00-19:00 Tbilisi time)</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
@@ -7425,32 +7429,32 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Nav</t>
+          <t>Pricing</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>nav.call</t>
+          <t>pricing.note</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>These packages describe the collaboration model and its minimum thresholds. The exact cost and details are agreed individually.</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>დარეკვა</t>
+          <t>ეს პაკეტები ასახავს თანამშრომლობის მოდელს და მინიმალურ ზღვრებს. უშუალოდ ღირებულების და დეტალების შეთანხმება ხდება ინდივიდუალურად.</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Позвонить</t>
+          <t>Эти пакеты описывают модель сотрудничества и минимальные пороги. Точная стоимость и детали согласовываются индивидуально.</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>Header call button (shown Mon-Fri 10:00-19:00 Tbilisi time)</t>
+          <t>Note under the three packages</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
@@ -8666,7 +8670,7 @@
           <t>Выберите удобное время</t>
         </is>
       </c>
-      <c r="G200" s="3" t="inlineStr"/>
+      <c r="G200" s="3" t="n"/>
       <c r="H200" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -8704,7 +8708,7 @@
           <t>Подтверждение и ссылка на Google Meet придут на почту сразу.</t>
         </is>
       </c>
-      <c r="G201" s="3" t="inlineStr"/>
+      <c r="G201" s="3" t="n"/>
       <c r="H201" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -8742,7 +8746,7 @@
           <t>Календарь не загружается? Откройте в новой вкладке</t>
         </is>
       </c>
-      <c r="G202" s="3" t="inlineStr"/>
+      <c r="G202" s="3" t="n"/>
       <c r="H202" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -8850,7 +8854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -9399,6 +9403,44 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>pricing.2.feature.6</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>30-day post-launch tuning</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>30-დღიანი დანერგვის შემდგომი დახვეწა</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>30-дневная настройка после запуска</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -827,17 +827,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>After 500+ successful deployments across multiple industries, we'll show you the exact 1-3 tools that solve your challenges - all in one call. Free if you book now.</t>
+          <t>With 500+ successful implementations behind us, in 20 minutes I'll walk you through the exact 1-3 tools that will handle your challenges. Free if you book now.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>სხვადასხვა ინდუსტრიაში 500+ წარმატებული დანერგვის გამოცდილებით, 20 წუთში გაგიჩვენებთ ზუსტად იმ 1-3 ხელსაწყოს, რომელიც შენ გამოწვევებს გაუმკლავდება. უფასოდ - თუ ახლავე დაჯავშნი.</t>
+          <t>500+ წარმატებული დანერგვის გამოცდილებით, 20 წუთში, მოგიყვები ზუსტად იმ 1-3 ინსტრუმენტის შესახებ, რომლებიც შენს გამოწვევებს გაუმკლავდება. უფასოდ - თუ ახლავე დაჯავშნი.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>После более 500 успешных внедрений в разных отраслях мы за один звонок покажем вам ровно те 1-3 инструмента, которые решают ваши задачи. Бесплатно - если бронируете сейчас.</t>
+          <t>Опираясь на 500+ успешных внедрений, за 20 минут расскажу о тех 1-3 инструментах, которые справятся с вашими задачами. Бесплатно - если бронируете сейчас.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -7985,17 +7985,17 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>PDF · 12 pages · personal picks</t>
+          <t>PDF · 3 pages · personal picks</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>PDF · 12 გვერდი · პირადი რეკომენდაციები</t>
+          <t>PDF · 3 გვერდი · პირადი რეკომენდაციები</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>PDF · 12 страниц · личный выбор</t>
+          <t>PDF · 3 страницы · личные рекомендации</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -8,7 +8,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed keys" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Untitled'!$A$1:$H$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Untitled'!$A$1:$H$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z204"/>
+  <dimension ref="A1:Z201"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -743,17 +743,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>30+ hours</t>
+          <t>100+ hours</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>30+ საათიან</t>
+          <t>100+ საათიან</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>30+ часов</t>
+          <t>100+ часов</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -953,17 +953,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a Call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -1583,17 +1583,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Years · Market Expert</t>
+          <t>years of experience</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>წელი · ბაზრის ექსპერტი</t>
+          <t>წლიანი გამოცდილება</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>лет · Эксперт рынка</t>
+          <t>лет опыта</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -3683,17 +3683,17 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Tangible results</t>
+          <t>What our clients say</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>ხელშესახები შედეგები</t>
+          <t>რას ამბობენ კლიენტები</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Ощутимые результаты</t>
+          <t>Что говорят клиенты</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4079,17 +4079,17 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>20 minutes to save 30+ hours</t>
+          <t>20 minutes to save 100+ hours</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>20 წუთი, 30+ საათის დასაზოგად</t>
+          <t>20 წუთი, 100+ საათის დასაზოგად</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>20 минут, чтобы сэкономить 30+ часов</t>
+          <t>20 минут, чтобы сэкономить 100+ часов</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -5717,23 +5717,23 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>ფასი</t>
+          <t>თანამშრომლობა</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Цены</t>
+          <t>Сотрудничество</t>
         </is>
       </c>
       <c r="G126" s="3" t="n"/>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -5869,17 +5869,17 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>ADVISOR</t>
+          <t>CONSULTING</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>ADVISOR</t>
+          <t>კონსულტაცია</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>ADVISOR</t>
+          <t>КОНСУЛЬТАЦИЯ</t>
         </is>
       </c>
       <c r="G130" s="3" t="n"/>
@@ -6059,23 +6059,23 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>1-2 solutions from our catalog</t>
+          <t>1-2 specific solutions</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>1-2 გადაწყვეტა კატალოგიდან</t>
+          <t>1-2 კონკრეტული გადაწყვეტა</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>1-2 решения из каталога</t>
+          <t>1-2 конкретных решения</t>
         </is>
       </c>
       <c r="G135" s="3" t="n"/>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6211,17 +6211,17 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Request Advisor</t>
+          <t>Request consulting</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე Advisor</t>
+          <t>მოითხოვე კონსულტაცია</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Запросить Advisor</t>
+          <t>Запросить консультацию</t>
         </is>
       </c>
       <c r="G139" s="3" t="n"/>
@@ -6325,17 +6325,17 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>SPRINTER</t>
+          <t>IMPLEMENTATION</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>SPRINTER</t>
+          <t>დანერგვა</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>SPRINTER</t>
+          <t>ВНЕДРЕНИЕ</t>
         </is>
       </c>
       <c r="G142" s="3" t="n"/>
@@ -6553,23 +6553,23 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Up to 6 solutions from catalog</t>
+          <t>Up to 6 solutions</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>6-მდე გადაწყვეტა კატალოგიდან</t>
+          <t>6-მდე გადაწყვეტა</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>До 6 решений из каталога</t>
+          <t>До 6 решений</t>
         </is>
       </c>
       <c r="G148" s="3" t="n"/>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6705,17 +6705,17 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Request Sprinter</t>
+          <t>Request implementation</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე Sprinter</t>
+          <t>მოითხოვე დანერგვა</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Запросить Sprinter</t>
+          <t>Запросить внедрение</t>
         </is>
       </c>
       <c r="G152" s="3" t="n"/>
@@ -6781,17 +6781,17 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>PRIORITY</t>
+          <t>PARTNERSHIP</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>PRIORITY</t>
+          <t>პარტნიორობა</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>PRIORITY</t>
+          <t>ПАРТНЁРСТВО</t>
         </is>
       </c>
       <c r="G154" s="3" t="n"/>
@@ -6971,17 +6971,17 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Everything included in Sprinter</t>
+          <t>Everything included in Implementation</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>ყველაფერი, რასაც Sprinter მოიცავს</t>
+          <t>ყველაფერი, რასაც დანერგვა მოიცავს</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Всё, что входит в Sprinter</t>
+          <t>Всё, что входит во Внедрение</t>
         </is>
       </c>
       <c r="G159" s="3" t="n"/>
@@ -7085,23 +7085,23 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Managed services (ongoing optimization)</t>
+          <t>Ongoing optimization</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Managed services (მუდმივი ოპტიმიზაცია)</t>
+          <t>მუდმივი ოპტიმიზაცია</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Managed services (постоянная оптимизация)</t>
+          <t>Постоянная оптимизация</t>
         </is>
       </c>
       <c r="G162" s="3" t="n"/>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -7161,17 +7161,17 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Request Priority</t>
+          <t>Request partnership</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე Priority</t>
+          <t>მოითხოვე პარტნიორობა</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Запросить Priority</t>
+          <t>Запросить партнёрство</t>
         </is>
       </c>
       <c r="G164" s="3" t="n"/>
@@ -7439,17 +7439,17 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>These packages describe the collaboration model and its minimum thresholds. The exact cost and details are agreed individually.</t>
+          <t>These packages describe our ways of working together. The cost is set individually and starts from 2,990 GEL (prices exclude VAT).</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>ეს პაკეტები ასახავს თანამშრომლობის მოდელს და მინიმალურ ზღვრებს. უშუალოდ ღირებულების და დეტალების შეთანხმება ხდება ინდივიდუალურად.</t>
+          <t>ეს პაკეტები ასახავს თანამშრომლობის მიდგომებს. ღირებულება ინდივიდუალურად განისაზღვრება და იწყება 2990 ლარიდან (ფასები არ მოიცავს დღგ-ს).</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Эти пакеты описывают модель сотрудничества и минимальные пороги. Точная стоимость и детали согласовываются индивидуально.</t>
+          <t>Эти пакеты описывают подходы к сотрудничеству. Стоимость определяется индивидуально и начинается от 2990 лари (цены без НДС).</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -7459,175 +7459,159 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>Thank-you</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Gain</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>ty.confirm.title</t>
+          <t>gain.title</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Thank you {name}, your request has been received.</t>
+          <t>What you get from this call</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>მადლობა {name}, თქვენი მოთხოვნა მიღებულია.</t>
+          <t>რას მიიღებ ამ ზარით</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Спасибо, {name}, ваш запрос получен.</t>
-        </is>
-      </c>
-      <c r="G172" s="3" t="inlineStr">
-        <is>
-          <t>Thank-you headline. Keep {name} - it is replaced with the visitor's first name</t>
-        </is>
-      </c>
+          <t>Что вы получите от этого звонка</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr"/>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>Thank-you</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>SelfBook</t>
+          <t>Gain</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>ty.selfbook.eyebrow</t>
+          <t>gain.1</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Prefer to pick a time yourself?</t>
+          <t>You save a lot of time - and with it, money.</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>გირჩევნია დრო თავად შეარჩიო?</t>
+          <t>დაზოგავ უამრავ დროს, შესაბამისად ფულსაც.</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Хотите выбрать время сами?</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>Lime eyebrow</t>
-        </is>
-      </c>
+          <t>Сэкономите массу времени, а значит и денег.</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr"/>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>Thank-you</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>SelfBook</t>
+          <t>Gain</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>ty.selfbook.title</t>
+          <t>gain.2</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Skip the wait - book a 20-minute slot directly on my calendar</t>
+          <t>You'll know the concrete next steps to take.</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>ნუ დაელოდები ზარს - დაჯავშნე 20-წუთიანი სლოტი პირდაპირ ჩემს კალენდარში</t>
+          <t>გეცოდინება კონკრეტული გადასადგმელი ნაბიჯები.</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Не ждите - забронируйте 20-минутный слот прямо в моём календаре</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>Self-book card title</t>
-        </is>
-      </c>
+          <t>Будете знать конкретные следующие шаги.</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr"/>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>Thank-you</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>SelfBook</t>
+          <t>Gain</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>ty.selfbook.note</t>
+          <t>gain.3</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Pick a time that works for you. The confirmation and the Google Meet link will be sent to your email.</t>
+          <t>You'll set realistic expectations for results, timelines and budget.</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>შეარჩიე შენთვის მოსახერხებელი დრო. დადასტურება და Google Meet-ის ბმული გამოიგზავნება შენს ელ.ფოსტაზე.</t>
+          <t>შეიქმნი ადეკვატურ მოლოდინს შედეგზე, ვადებზე და ბიუჯეტზე.</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Выберите удобное время. Подтверждение и ссылка на Google Meet придут на вашу почту.</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>Self-book card note</t>
-        </is>
-      </c>
+          <t>Сформируете реалистичные ожидания по результату, срокам и бюджету.</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr"/>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -7639,37 +7623,37 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>SelfBook</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>ty.selfbook.cta</t>
+          <t>ty.confirm.title</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Book a Call</t>
+          <t>Thank you {name}, your request has been received.</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>დაჯავშნე შეხვედრა</t>
+          <t>მადლობა {name}, თქვენი მოთხოვნა მიღებულია.</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Забронировать звонок</t>
+          <t>Спасибо, {name}, ваш запрос получен.</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>Primary CTA button</t>
+          <t>Thank-you headline. Keep {name} - it is replaced with the visitor's first name</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -7686,27 +7670,27 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>ty.selfbook.meta</t>
+          <t>ty.selfbook.eyebrow</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>⏱ 20 min · 🖥 Google Meet · Free</t>
+          <t>Prefer to pick a time yourself?</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>⏱ 20 წთ · 🖥 Google Meet · უფასო</t>
+          <t>გირჩევნია დრო თავად შეარჩიო?</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>⏱ 20 мин · 🖥 Google Meet · Бесплатно</t>
+          <t>Хотите выбрать время сами?</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>Meta line under CTA</t>
+          <t>Lime eyebrow</t>
         </is>
       </c>
       <c r="H177" s="3" t="inlineStr">
@@ -7723,32 +7707,32 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>SelfBook</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>ty.video.eyebrow</t>
+          <t>ty.selfbook.title</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Before we talk</t>
+          <t>Skip the wait - book a 20-minute slot directly on my calendar</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>სანამ ვისაუბრებთ</t>
+          <t>ნუ დაელოდები ზარს - დაჯავშნე 20-წუთიანი სლოტი პირდაპირ ჩემს კალენდარში</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Прежде чем поговорим</t>
+          <t>Не ждите - забронируйте 20-минутный слот прямо в моём календаре</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>Section eyebrow</t>
+          <t>Self-book card title</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
@@ -7765,37 +7749,37 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>SelfBook</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>ty.video.title</t>
+          <t>ty.selfbook.cta</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>A 60-second note from Giorgi</t>
+          <t>Book a Call</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>60-წამიანი მიმართვა გიორგისგან</t>
+          <t>დაჯავშნე შეხვედრა</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>60-секундное обращение от Георгия</t>
+          <t>Забронировать звонок</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>Section title</t>
+          <t>Primary CTA button</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7807,32 +7791,32 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>SelfBook</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>ty.video.caption</t>
+          <t>ty.selfbook.meta</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Welcome from Giorgi</t>
+          <t>⏱ 20 min · 🖥 Google Meet · Free</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>მოკლე ვიდეო გიორგისგან</t>
+          <t>⏱ 20 წთ · 🖥 Google Meet · უფასო</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Приветствие от Георгия</t>
+          <t>⏱ 20 мин · 🖥 Google Meet · Бесплатно</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>Video poster caption</t>
+          <t>Meta line under CTA</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
@@ -7849,27 +7833,27 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>ty.gift.eyebrow</t>
+          <t>ty.video.eyebrow</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>A gift from me</t>
+          <t>Before we talk</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>საჩუქარი ჩემგან</t>
+          <t>სანამ ვისაუბრებთ</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Подарок от меня</t>
+          <t>Прежде чем поговорим</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -7891,32 +7875,32 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>ty.gift.title</t>
+          <t>ty.video.title</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>10 tools we use every day to run faster</t>
+          <t>A 60-second note from Giorgi</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>10 ინსტრუმენტი, რომელსაც ყოველდღიურად ვიყენებთ ეფექტურობის გასაზრდელად</t>
+          <t>60-წამიანი მიმართვა გიორგისგან</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>10 инструментов, которыми мы пользуемся каждый день, чтобы работать быстрее</t>
+          <t>60-секундное обращение от Георгия</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>Gift section title</t>
+          <t>Section title</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
@@ -7933,37 +7917,37 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>ty.gift.sub</t>
+          <t>ty.video.caption</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>An opinionated PDF - the exact stack we rely on for research, writing, scheduling, note-taking, and keeping my own team sharp. Yours, free, no strings.</t>
+          <t>Welcome from Giorgi</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>პრაქტიკული PDF გზამკვლევი - ინსტრუმენტები, რომლებსაც ყოველდღე ვიყენებთ კვლევისთვის, ტექსტების დასაწერად, შეხვედრების დასაგეგმად და გუნდის ეფექტურობისთვის. სრულიად უფასოდ, ჩამოტვირთე.</t>
+          <t>მოკლე ვიდეო გიორგისგან</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Личный PDF с подборкой - точный стек, которым мы пользуемся для исследований, писанины, планирования встреч, заметок и чтобы держать команду в тонусе. Ваше, бесплатно, без условий.</t>
+          <t>Приветствие от Георгия</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>Gift section subtitle</t>
+          <t>Video poster caption</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7975,37 +7959,37 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Prep</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>ty.gift.tag</t>
+          <t>ty.prep.eyebrow</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>PDF · 3 pages · personal picks</t>
+          <t>Optional - if you want to go deeper</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>PDF · 3 გვერდი · პირადი რეკომენდაციები</t>
+          <t>სურვილისამებრ - თუ გსურს უფრო სიღრმისეულად მომზადება</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>PDF · 3 страницы · личные рекомендации</t>
+          <t>По желанию - если хотите углубиться</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>Small tag above gift card title</t>
+          <t>Section eyebrow</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8017,37 +8001,37 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Prep</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>ty.gift.card.title</t>
+          <t>ty.prep.title</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Unitty's Productivity Stack 2026</t>
+          <t>Five questions to think about beforehand</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Unitty-ის პროდუქტიულობის ნაკრები 2026</t>
+          <t>5 კითხვა, რომელზეც შეგიძლია წინასწარ დაფიქრდე</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Стек продуктивности Unitty 2026</t>
+          <t>Пять вопросов, о которых подумать заранее</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>Gift card title</t>
+          <t>Section title</t>
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8059,37 +8043,37 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Prep</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>ty.gift.card.desc</t>
+          <t>ty.prep.sub</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Each tool with what we use it for, why it beats the alternatives I tried, and the one setting most people miss. Takes 8 minutes to read, saves hours a week.</t>
+          <t>Not required. But if you want our 20 minutes to cut straight to the answer, these are the places I usually start.</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>თითოეული ხელსაწყოს დეტალური აღწერა: რისთვის ვიყენებთ, რით ჯობია ალტერნატივებს და რომელია ის მთავარი ფუნქცია, რაც უმეტესობას გამორჩება ხოლმე. წასაკითხად საჭიროა 8 წუთი - გიზოგავს კვირაში რამდენიმე საათს.</t>
+          <t>არ არის სავალდებულო. მაგრამ თუ გსურს, ჩვენი 20 წუთი პირდაპირ გადაწყვეტაზე ორიენტირებული იყოს, ეს ის კითხვებია, რითაც ყოველთვის ვიწყებ.</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>О каждом инструменте: для чего используем, почему он лучше альтернатив, которые пробовали, и та одна настройка, которую большинство упускает. Читается 8 минут, экономит часы в неделю.</t>
+          <t>Не обязательно. Но если хотите, чтобы наши 20 минут сразу вышли на ответ - вот откуда я обычно начинаю.</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>Gift card description</t>
+          <t>Section subtitle</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -8101,32 +8085,32 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Prep</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>ty.gift.card.cta</t>
+          <t>ty.prep.q1</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Download the PDF</t>
+          <t>How does the work you want to improve happen today - who does it, in which tool, and where does it break?</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>ჩამოტვირთე PDF</t>
+          <t>როგორ სრულდება ის პროცესი დღეს, რომლის გაუმჯობესებაც გსურს - ვინ აკეთებს, სად, და რა იწვევს შეფერხებას?</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Скачать PDF</t>
+          <t>Как сейчас происходит работа, которую вы хотите улучшить - кто её делает, в каком инструменте и где всё ломается?</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>Gift card CTA button</t>
+          <t>Prep Q1</t>
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr">
@@ -8148,27 +8132,27 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>ty.prep.eyebrow</t>
+          <t>ty.prep.q2</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Optional - if you want to go deeper</t>
+          <t>What have you already tried, and what specifically didn't work about it?</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>სურვილისამებრ - თუ გსურს უფრო სიღრმისეულად მომზადება</t>
+          <t>რა გზები სცადეთ უკვე და კონკრეტულად რატომ არ გაამართლა?</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>По желанию - если хотите углубиться</t>
+          <t>Что вы уже пробовали, и что конкретно не сработало?</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>Section eyebrow</t>
+          <t>Prep Q2</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr">
@@ -8190,27 +8174,27 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>ty.prep.title</t>
+          <t>ty.prep.q3</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Five questions to think about beforehand</t>
+          <t>If this problem were solved three months from now, what would be different about your day?</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>5 კითხვა, რომელზეც შეგიძლია წინასწარ დაფიქრდე</t>
+          <t>ეს პრობლემა 3 თვეში რომ სრულად მოგვარდეს, რა შეიცვლებოდა შენს ყოველდღიურ საქმიანობაში?</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Пять вопросов, о которых подумать заранее</t>
+          <t>Если бы эта проблема была решена через три месяца, что в вашем дне стало бы другим?</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>Section title</t>
+          <t>Prep Q3</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
@@ -8232,27 +8216,27 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>ty.prep.sub</t>
+          <t>ty.prep.q4</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Not required. But if you want our 20 minutes to cut straight to the answer, these are the places I usually start.</t>
+          <t>Who in your team will own the new process - a specific person, or still deciding?</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>არ არის სავალდებულო. მაგრამ თუ გსურს, ჩვენი 20 წუთი პირდაპირ გადაწყვეტაზე ორიენტირებული იყოს, ეს ის კითხვებია, რითაც ყოველთვის ვიწყებ.</t>
+          <t>ვინ იქნება შენს გუნდში ახალი პროცესის პასუხისმგებელი პირი - კონკრეტული თანამშრომელი, თუ ჯერ გადასაწყვეტია?</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Не обязательно. Но если хотите, чтобы наши 20 минут сразу вышли на ответ - вот откуда я обычно начинаю.</t>
+          <t>Кто в вашей команде будет владельцем нового процесса - конкретный человек или ещё решаете?</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Section subtitle</t>
+          <t>Prep Q4</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
@@ -8274,32 +8258,32 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>ty.prep.q1</t>
+          <t>ty.prep.q5</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>How does the work you want to improve happen today - who does it, in which tool, and where does it break?</t>
+          <t>What's your rough budget range - not a commitment, just so we don't propose something that doesn't fit?</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>როგორ სრულდება ის პროცესი დღეს, რომლის გაუმჯობესებაც გსურს - ვინ აკეთებს, სად, და რა იწვევს შეფერხებას?</t>
+          <t>რა არის შენი სავარაუდო საორიენტაციო ბიუჯეტი? (ეს არ არის ვალდებულება, უბრალოდ იმისთვის, რომ არ შემოგთავაზოთ ისეთი რამ, რაც შენს შესაძლებლობებს არ შეესაბამება).</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Как сейчас происходит работа, которую вы хотите улучшить - кто её делает, в каком инструменте и где всё ломается?</t>
+          <t>Какой у вас примерный бюджетный диапазон - не обязательство, просто чтобы мы не предложили что-то, что не вписывается?</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>Prep Q1</t>
+          <t>Prep Q5</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -8311,32 +8295,32 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>ty.prep.q2</t>
+          <t>ty.social.eyebrow</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>What have you already tried, and what specifically didn't work about it?</t>
+          <t>Follow my work</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>რა გზები სცადეთ უკვე და კონკრეტულად რატომ არ გაამართლა?</t>
+          <t>თვალი ადევნე ჩემს საქმიანობას</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Что вы уже пробовали, и что конкретно не сработало?</t>
+          <t>Следите за моей работой</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>Prep Q2</t>
+          <t>Section eyebrow</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr">
@@ -8353,32 +8337,32 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>ty.prep.q3</t>
+          <t>ty.social.title</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>If this problem were solved three months from now, what would be different about your day?</t>
+          <t>Follow for daily videos on productivity tools worth your time</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>ეს პრობლემა 3 თვეში რომ სრულად მოგვარდეს, რა შეიცვლებოდა შენს ყოველდღიურ საქმიანობაში?</t>
+          <t>გამოიწერე ჩემი არხები ყოველდღიური სასარგებლო ვიდეოებისთვის იმ ციფრულ ხელსაწყოებზე, რომლებიც შენს დროს ნამდვილად იმსახურებს</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Если бы эта проблема была решена через три месяца, что в вашем дне стало бы другим?</t>
+          <t>Подпишитесь, чтобы каждый день получать видео о продуктивных инструментах, которые стоят вашего времени</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>Prep Q3</t>
+          <t>Social section title</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
@@ -8395,37 +8379,37 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>ty.prep.q4</t>
+          <t>ty.social.sub</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Who in your team will own the new process - a specific person, or still deciding?</t>
+          <t>Short breakdowns of the tools we actually use with clients - what works, what doesn't, and how to set it up without the sales pitch.</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>ვინ იქნება შენს გუნდში ახალი პროცესის პასუხისმგებელი პირი - კონკრეტული თანამშრომელი, თუ ჯერ გადასაწყვეტია?</t>
+          <t>მოკლე პრაქტიკული მიმოხილვები ხელსაწყოებზე, რომლებსაც რეალურად ვიყენებთ კლიენტებთან — რა მუშაობს, რა არა და როგორ გამართო მარტივად, ზედმეტი სარეკლამო ხმაურის გარეშე.</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Кто в вашей команде будет владельцем нового процесса - конкретный человек или ещё решаете?</t>
+          <t>Короткие разборы инструментов, которые мы реально используем с клиентами - что работает, что нет, и как настроить без продажного пафоса.</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>Prep Q4</t>
+          <t>Social section subtitle</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -8437,37 +8421,37 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>Bookings</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>ty.prep.q5</t>
+          <t>ty.bookings.eyebrow</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>What's your rough budget range - not a commitment, just so we don't propose something that doesn't fit?</t>
+          <t>Pick a time now</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>რა არის შენი სავარაუდო საორიენტაციო ბიუჯეტი? (ეს არ არის ვალდებულება, უბრალოდ იმისთვის, რომ არ შემოგთავაზოთ ისეთი რამ, რაც შენს შესაძლებლობებს არ შეესაბამება).</t>
+          <t>აირჩიე დრო ახლავე</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Какой у вас примерный бюджетный диапазон - не обязательство, просто чтобы мы не предложили что-то, что не вписывается?</t>
+          <t>Выберите время сейчас</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>Prep Q5</t>
+          <t>Booking calendar section</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -8479,37 +8463,33 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Bookings</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>ty.social.eyebrow</t>
+          <t>ty.bookings.title</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Follow my work</t>
+          <t>Choose a slot that works for you</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>თვალი ადევნე ჩემს საქმიანობას</t>
+          <t>აირჩიე შენთვის მოსახერხებელი დრო</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Следите за моей работой</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="inlineStr">
-        <is>
-          <t>Section eyebrow</t>
-        </is>
-      </c>
+          <t>Выберите удобное время</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="n"/>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -8521,37 +8501,33 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Bookings</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>ty.social.title</t>
+          <t>ty.bookings.note</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Follow for daily videos on productivity tools worth your time</t>
+          <t>Confirmation and the Google Meet link land in your inbox immediately.</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>გამოიწერე ჩემი არხები ყოველდღიური სასარგებლო ვიდეოებისთვის იმ ციფრულ ხელსაწყოებზე, რომლებიც შენს დროს ნამდვილად იმსახურებს</t>
+          <t>დადასტურება და Google Meet-ის ბმული მაშინვე მოგივა ელფოსტაზე.</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Подпишитесь, чтобы каждый день получать видео о продуктивных инструментах, которые стоят вашего времени</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>Social section title</t>
-        </is>
-      </c>
+          <t>Подтверждение и ссылка на Google Meet придут на почту сразу.</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="n"/>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -8563,37 +8539,33 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Bookings</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>ty.social.sub</t>
+          <t>ty.bookings.fallback</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Short breakdowns of the tools we actually use with clients - what works, what doesn't, and how to set it up without the sales pitch.</t>
+          <t>Calendar not loading? Open it in a new tab</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>მოკლე პრაქტიკული მიმოხილვები ხელსაწყოებზე, რომლებსაც რეალურად ვიყენებთ კლიენტებთან — რა მუშაობს, რა არა და როგორ გამართო მარტივად, ზედმეტი სარეკლამო ხმაურის გარეშე.</t>
+          <t>კალენდარი არ იტვირთება? გახსენი ახალ ფანჯარაში</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Короткие разборы инструментов, которые мы реально используем с клиентами - что работает, что нет, и как настроить без продажного пафоса.</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>Social section subtitle</t>
-        </is>
-      </c>
+          <t>Календарь не загружается? Откройте в новой вкладке</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="n"/>
       <c r="H198" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -8605,32 +8577,32 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Bookings</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>ty.bookings.eyebrow</t>
+          <t>ty.confirm.title.noname</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Pick a time now</t>
+          <t>Thank you, your request has been received.</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>აირჩიე დრო ახლავე</t>
+          <t>მადლობა, თქვენი მოთხოვნა მიღებულია.</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Выберите время сейчас</t>
+          <t>Спасибо, ваш запрос получен.</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>Booking calendar section</t>
+          <t>Thank-you headline when no name is known</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
@@ -8647,30 +8619,34 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Bookings</t>
+          <t>Nav</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>ty.bookings.title</t>
+          <t>nav.call</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Choose a slot that works for you</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>აირჩიე შენთვის მოსახერხებელი დრო</t>
+          <t>დარეკვა</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Выберите удобное время</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="n"/>
+          <t>Позвонить</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Same text as on the landing - change both rows together</t>
+        </is>
+      </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -8685,160 +8661,38 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Bookings</t>
+          <t>Ty</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>ty.bookings.note</t>
+          <t>ty.bonus.cta</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Confirmation and the Google Meet link land in your inbox immediately.</t>
+          <t>Download the bonus PDF</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>დადასტურება და Google Meet-ის ბმული მაშინვე მოგივა ელფოსტაზე.</t>
+          <t>ჩამოტვირთე PDF ბონუსად</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Подтверждение и ссылка на Google Meet придут на почту сразу.</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="n"/>
+          <t>Скачать бонусный PDF</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr"/>
       <c r="H201" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>Thank-you</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>Bookings</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr">
-        <is>
-          <t>ty.bookings.fallback</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>Calendar not loading? Open it in a new tab</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>კალენდარი არ იტვირთება? გახსენი ახალ ფანჯარაში</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>Календарь не загружается? Откройте в новой вкладке</t>
-        </is>
-      </c>
-      <c r="G202" s="3" t="n"/>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>Thank-you</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>ty.confirm.title.noname</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>Thank you, your request has been received.</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>მადლობა, თქვენი მოთხოვნა მიღებულია.</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>Спасибо, ваш запрос получен.</t>
-        </is>
-      </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>Thank-you headline when no name is known</t>
-        </is>
-      </c>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>Thank-you</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Nav</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>nav.call</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>Call</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>დარეკვა</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>Позвонить</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>Same text as on the landing - change both rows together</t>
-        </is>
-      </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H204"/>
+  <autoFilter ref="A1:H201"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
@@ -8854,7 +8708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -9441,6 +9295,342 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>SelfBook</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>ty.selfbook.note</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Pick a time that works for you. The confirmation and the Google Meet link will be sent to your email.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>შეარჩიე შენთვის მოსახერხებელი დრო. დადასტურება და Google Meet-ის ბმული გამოიგზავნება შენს ელ.ფოსტაზე.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Выберите удобное время. Подтверждение и ссылка на Google Meet придут на вашу почту.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Self-book card note</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>ty.gift.eyebrow</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>A gift from me</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>საჩუქარი ჩემგან</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Подарок от меня</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Section eyebrow</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>ty.gift.title</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>10 tools we use every day to run faster</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>10 ინსტრუმენტი, რომელსაც ყოველდღიურად ვიყენებთ ეფექტურობის გასაზრდელად</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>10 инструментов, которыми мы пользуемся каждый день, чтобы работать быстрее</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Gift section title</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>ty.gift.sub</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>An opinionated PDF - the exact stack we rely on for research, writing, scheduling, note-taking, and keeping my own team sharp. Yours, free, no strings.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>პრაქტიკული PDF გზამკვლევი - ინსტრუმენტები, რომლებსაც ყოველდღე ვიყენებთ კვლევისთვის, ტექსტების დასაწერად, შეხვედრების დასაგეგმად და გუნდის ეფექტურობისთვის. სრულიად უფასოდ, ჩამოტვირთე.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Личный PDF с подборкой - точный стек, которым мы пользуемся для исследований, писанины, планирования встреч, заметок и чтобы держать команду в тонусе. Ваше, бесплатно, без условий.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Gift section subtitle</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>ty.gift.tag</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>PDF · 3 pages · personal picks</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>PDF · 3 გვერდი · პირადი რეკომენდაციები</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>PDF · 3 страницы · личные рекомендации</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Small tag above gift card title</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>ty.gift.card.title</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Unitty's Productivity Stack 2026</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Unitty-ის პროდუქტიულობის ნაკრები 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Стек продуктивности Unitty 2026</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Gift card title</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>ty.gift.card.desc</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Each tool with what we use it for, why it beats the alternatives I tried, and the one setting most people miss. Takes 8 minutes to read, saves hours a week.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>თითოეული ხელსაწყოს დეტალური აღწერა: რისთვის ვიყენებთ, რით ჯობია ალტერნატივებს და რომელია ის მთავარი ფუნქცია, რაც უმეტესობას გამორჩება ხოლმე. წასაკითხად საჭიროა 8 წუთი - გიზოგავს კვირაში რამდენიმე საათს.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>О каждом инструменте: для чего используем, почему он лучше альтернатив, которые пробовали, и та одна настройка, которую большинство упускает. Читается 8 минут, экономит часы в неделю.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Gift card description</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>ty.gift.card.cta</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Download the PDF</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ჩამოტვირთე PDF</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Скачать PDF</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Gift card CTA button</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Removed 2026-10-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed keys" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$205</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$205</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$165</definedName>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -5515,27 +5515,27 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>pain.title</t>
+          <t>hero.v.manager.a</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Sound familiar?</t>
+          <t>Your manager left.</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>ნაცნობია?</t>
+          <t>მენეჯერი წავიდა.</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Знакомо?</t>
+          <t>Менеджер ушёл.</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr"/>
@@ -5553,27 +5553,27 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>pain.sub</t>
+          <t>hero.v.manager.b</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>We see these situations every day. One call shows you how to fix yours.</t>
+          <t>With your clients?</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>ასეთ სიტუაციებს ყოველდღე ვხედავთ. ერთი ზარი გაჩვენებს, როგორ მოაგვარო შენი.</t>
+          <t>კლიენტებიც თან წაიყვანა?</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Мы видим такие ситуации каждый день. Один звонок покажет, как решить вашу.</t>
+          <t>Вместе с клиентами?</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr"/>
@@ -5591,27 +5591,27 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>pain.cta</t>
+          <t>hero.v.28.a</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Request a free call</t>
+          <t>Only 28% of sales time</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე უფასო ზარი</t>
+          <t>გაყიდვების დროის მხოლოდ</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный звонок</t>
+          <t>Только 28% времени</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
@@ -5629,27 +5629,27 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>pain.fix.label</t>
+          <t>hero.v.28.b</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>The fix:</t>
+          <t>goes to selling</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>გამოსავალი:</t>
+          <t>28% მიდის გაყიდვაზე</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Решение:</t>
+          <t>уходит на продажи</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr"/>
@@ -5667,27 +5667,27 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.from</t>
+          <t>hero.v.owner.a</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Ana · Sales manager</t>
+          <t>Business owner</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>ანა · გაყიდვების მენეჯერი</t>
+          <t>ბიზნესის მფლობელი ხარ</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Анна · менеджер по продажам</t>
+          <t>Владелец бизнеса</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr"/>
@@ -5705,27 +5705,27 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.msg</t>
+          <t>hero.v.owner.b</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>I'm not coming in from tomorrow. Good luck!</t>
+          <t>or manager of everything?</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>ხვალიდან აღარ მოვდივარ. წარმატებები!</t>
+          <t>თუ ყველაფრის მენეჯერი?</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>С завтрашнего дня я больше не выхожу. Удачи!</t>
+          <t>или менеджер всего?</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr"/>
@@ -5743,27 +5743,27 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.lost1</t>
+          <t>hero.v.excel.a</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Client base</t>
+          <t>Still searching Excel</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>კლიენტების ბაზა</t>
+          <t>ისევ Excel-ში ეძებ,</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>База клиентов</t>
+          <t>Всё ещё ищете в Excel,</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr"/>
@@ -5781,27 +5781,27 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.lost2</t>
+          <t>hero.v.excel.b</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Chat history</t>
+          <t>for who bought what?</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>მიმოწერის ისტორია</t>
+          <t>ვის რა მიჰყიდე?</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>История переписки</t>
+          <t>кому что продали?</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr"/>
@@ -5819,27 +5819,27 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.lost3</t>
+          <t>hero.v.chats.a</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Agreed prices</t>
+          <t>A client messaged you.</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>შეთანხმებული ფასები</t>
+          <t>კლიენტმა მოგწერა.</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Согласованные цены</t>
+          <t>Клиент написал.</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr"/>
@@ -5857,27 +5857,27 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.title</t>
+          <t>hero.v.chats.b</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Your manager left. And took the clients along.</t>
+          <t>Who replied?</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>მენეჯერი წავიდა. კლიენტებიც თან წაიყვანა.</t>
+          <t>ვინ უპასუხა?</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Менеджер ушёл. И забрал клиентов с собой.</t>
+          <t>Кто ответил?</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr"/>
@@ -5895,27 +5895,27 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.fix</t>
+          <t>process.eyebrow</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>In the right CRM, client history stays with the company, not on an employee's phone.</t>
+          <t>How we work</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>სწორ CRM-ში კლიენტის ისტორია კომპანიას რჩება და არა თანამშრომლის ტელეფონს.</t>
+          <t>როგორ ვმუშაობთ</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>В правильной CRM история клиента остаётся у компании, а не в телефоне сотрудника.</t>
+          <t>Как мы работаем</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr"/>
@@ -5933,27 +5933,27 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>pain.28.sell</t>
+          <t>process.title</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Selling</t>
+          <t>Three steps to results</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>გაყიდვა</t>
+          <t>სამი ნაბიჯი შედეგამდე</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Три шага к результату</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr"/>
@@ -5971,33 +5971,33 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>pain.28.rest</t>
+          <t>process.sub</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Everything else</t>
+          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>დანარჩენი</t>
+          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Всё остальное</t>
+          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6009,27 +6009,27 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>pain.28.title</t>
+          <t>process.1.name</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Only 28% of a sales rep's time goes to selling</t>
+          <t>Consultation</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>გაყიდვების მენეჯერის დროის მხოლოდ 28% მიდის გაყიდვაზე</t>
+          <t>კონსულტაცია</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Только 28% времени менеджера уходит на продажи</t>
+          <t>Консультация</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr"/>
@@ -6047,27 +6047,27 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>pain.28.body</t>
+          <t>process.1.desc</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>The rest goes to spreadsheets, calls and messaging.</t>
+          <t>We find the real problem and pick the right tool.</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>დანარჩენი ცხრილებს, ზარებსა და მიმოწერას ეხარჯება.</t>
+          <t>ვიგებთ რეალურ პრობლემას და ვარჩევთ სწორ ინსტრუმენტს.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Остальное уходит на таблицы, звонки и переписку.</t>
+          <t>Находим реальную проблему и подбираем правильный инструмент.</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr"/>
@@ -6085,27 +6085,27 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>pain.28.fix</t>
+          <t>process.1.item.1</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Automation takes the routine away and gives the rep back to selling.</t>
+          <t>Review of your processes and current systems</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>ავტომატიზაცია რუტინას აშორებს და მენეჯერს გაყიდვას უბრუნებს.</t>
+          <t>პროცესებისა და არსებული სისტემების ანალიზი</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Автоматизация убирает рутину и возвращает менеджера к продажам.</t>
+          <t>Анализ процессов и текущих систем</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr"/>
@@ -6123,27 +6123,27 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>pain.28.source</t>
+          <t>process.1.item.2</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Source: Salesforce, State of Sales</t>
+          <t>1-3 tools that fit (and what you don't need)</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>წყარო: Salesforce, State of Sales</t>
+          <t>1-3 ინსტრუმენტის შერჩევა (და რა არ გჭირდება)</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Источник: Salesforce, State of Sales</t>
+          <t>1-3 подходящих инструмента (и что вам не нужно)</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr"/>
@@ -6161,27 +6161,27 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.c1</t>
+          <t>process.1.item.3</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Call the client!</t>
+          <t>Implementation plan, budget and timeline</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>კლიენტს დაურეკე!</t>
+          <t>დანერგვის გეგმა, ბიუჯეტი და ვადები</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Позвони клиенту!</t>
+          <t>План внедрения, бюджет и сроки</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr"/>
@@ -6199,27 +6199,27 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.c2</t>
+          <t>process.1.time</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Invoice on rs.ge</t>
+          <t>First call · 20 min · free</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>ინვოისი rs.ge-ზე</t>
+          <t>პირველი ზარი · 20 წთ · უფასო</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Счёт на rs.ge</t>
+          <t>Первый звонок · 20 мин · бесплатно</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr"/>
@@ -6237,27 +6237,27 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.c3</t>
+          <t>process.2.name</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Who replied on Instagram?</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Instagram-ზე ვინ უპასუხა?</t>
+          <t>დანერგვა</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Кто ответил в Instagram?</t>
+          <t>Внедрение</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr"/>
@@ -6275,27 +6275,27 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.c4</t>
+          <t>process.2.desc</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Did you send the price?</t>
+          <t>We build the system in short sprints. You see the first result in 1-2 weeks.</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>ფასი გაუგზავნე?</t>
+          <t>ვაწყობთ სისტემას მოკლე სპრინტებით. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Цену отправил?</t>
+          <t>Строим систему короткими спринтами. Первый результат - через 1-2 недели.</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr"/>
@@ -6313,27 +6313,27 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.c5</t>
+          <t>process.2.item.1</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Manager is off today</t>
+          <t>System setup and data migration</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>მენეჯერი დღეს არ მოვა</t>
+          <t>სისტემის აწყობა და მონაცემების გადატანა</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Менеджер сегодня не придёт</t>
+          <t>Настройка системы и перенос данных</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr"/>
@@ -6351,27 +6351,27 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.c6</t>
+          <t>process.2.item.2</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Report tomorrow!!</t>
+          <t>Automations and integrations</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>ანგარიში ხვალ!!</t>
+          <t>ავტომატიზაციები და ინტეგრაციები</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Отчёт завтра!!</t>
+          <t>Автоматизации и интеграции</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr"/>
@@ -6389,27 +6389,27 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.title</t>
+          <t>process.2.item.3</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Business owner or the manager of everything?</t>
+          <t>Team training</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>ბიზნესის მფლობელი ხარ თუ ყველაფრის მენეჯერი?</t>
+          <t>გუნდის ტრენინგი</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Владелец бизнеса или менеджер всего подряд?</t>
+          <t>Обучение команды</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr"/>
@@ -6427,27 +6427,27 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.body</t>
+          <t>process.2.time</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Every question lands on you, every task is on your mind.</t>
+          <t>Sprint · 1-2 weeks</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>ყველა კითხვა შენთან მოდის, ყველა დავალება შენ გახსოვს.</t>
+          <t>სპრინტი · 1-2 კვირა</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Все вопросы идут к вам, все задачи держите в голове вы.</t>
+          <t>Спринт · 1-2 недели</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr"/>
@@ -6465,27 +6465,27 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.fix</t>
+          <t>process.3.name</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>The system reminds the team who owes what, so you can run the business.</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>სისტემა თვითონ ახსენებს გუნდს, ვის რა ევალება, შენ კი ბიზნესს მართავ.</t>
+          <t>მხარდაჭერა</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Система сама напоминает команде, кто что должен, а вы управляете бизнесом.</t>
+          <t>Поддержка</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr"/>
@@ -6503,27 +6503,27 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.h1</t>
+          <t>process.3.desc</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>The system keeps working after launch and grows with your business.</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>კლიენტი</t>
+          <t>სისტემა გაშვების შემდეგაც მუშაობს და იზრდება ბიზნესთან ერთად.</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Клиент</t>
+          <t>Система продолжает работать после запуска и растёт вместе с бизнесом.</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr"/>
@@ -6541,27 +6541,27 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.h2</t>
+          <t>process.3.item.1</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Technical support when you need it</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>ტელეფონი</t>
+          <t>ტექნიკური მხარდაჭერა, როცა გჭირდება</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Телефон</t>
+          <t>Техническая поддержка, когда она нужна</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr"/>
@@ -6579,27 +6579,27 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.h3</t>
+          <t>process.3.item.2</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Ongoing optimization and improvements</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>სტატუსი</t>
+          <t>მუდმივი ოპტიმიზაცია და განვითარება</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Постоянная оптимизация и развитие</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr"/>
@@ -6617,27 +6617,27 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.sticky</t>
+          <t>process.3.item.3</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Who deleted column C?!</t>
+          <t>New tools added as you need them</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>ვინ წაშალა მე-3 სვეტი?!</t>
+          <t>ახალი ინსტრუმენტების დამატება საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Кто удалил третий столбец?!</t>
+          <t>Новые инструменты - по мере необходимости</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr"/>
@@ -6655,27 +6655,27 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.title</t>
+          <t>process.3.time</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Still searching Excel for who bought what?</t>
+          <t>Ongoing · as needed</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>ისევ Excel-ში ეძებ, ვის რა მიჰყიდე?</t>
+          <t>მუდმივად · საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Всё ещё ищете в Excel, кому что продали?</t>
+          <t>Постоянно · по необходимости</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr"/>
@@ -6693,33 +6693,33 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.body</t>
+          <t>process.note</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Clients spread across files, notebooks and phones.</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>კლიენტები ფაილებში, რვეულებსა და ტელეფონში.</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Клиенты в файлах, тетрадях и телефонах.</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -6731,27 +6731,27 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.fix</t>
+          <t>process.cta</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>In one system every client, sale and agreement is one search away.</t>
+          <t>Start with a free consultation</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>ერთ სისტემაში ყველა კლიენტი, გაყიდვა და შეთანხმება ერთი ძებნით ჩანს.</t>
+          <t>დაიწყე უფასო კონსულტაციით</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>В одной системе каждый клиент, продажа и договорённость находятся одним поиском.</t>
+          <t>Начните с бесплатной консультации</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr"/>
@@ -6761,1530 +6761,10 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>pain.chats.m1</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>How much is it?</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>ფასი რა ღირს?</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>Сколько стоит?</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr"/>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>pain.chats.m2</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Do you deliver?</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>მიწოდება გაქვთ?</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>Доставка есть?</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr"/>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>pain.chats.m3</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>Hi, are you there?</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>გამარჯობა, ხართ?</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>Здравствуйте, вы тут?</t>
-        </is>
-      </c>
-      <c r="G168" s="3" t="inlineStr"/>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>pain.chats.m4</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>I'd like to order</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>შეკვეთა მინდა</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="inlineStr">
-        <is>
-          <t>Хочу заказать</t>
-        </is>
-      </c>
-      <c r="G169" s="3" t="inlineStr"/>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>pain.chats.title</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>A client messaged you. Who replied?</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>კლიენტმა მოგწერა. ვინ უპასუხა?</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>Клиент написал. Кто ответил?</t>
-        </is>
-      </c>
-      <c r="G170" s="3" t="inlineStr"/>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>pain.chats.body</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>While you look for the answer, the client buys elsewhere.</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>სანამ პასუხს ეძებ, კლიენტი სხვასთან ყიდულობს.</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>Пока вы ищете ответ, клиент покупает у другого.</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr"/>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>pain.chats.fix</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>All channels in one window: you see who replied and what.</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>ყველა არხი ერთ ფანჯარაში: ჩანს, ვინ უპასუხა და რა უპასუხა.</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>Все каналы в одном окне: видно, кто и что ответил.</t>
-        </is>
-      </c>
-      <c r="G172" s="3" t="inlineStr"/>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.manager.a</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>Your manager left.</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>მენეჯერი წავიდა.</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>Менеджер ушёл.</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr"/>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.manager.b</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>With your clients?</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>კლიენტებიც თან წაიყვანა?</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>Вместе с клиентами?</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr"/>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.28.a</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>Only 28% of sales time</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>გაყიდვების დროის მხოლოდ</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>Только 28% времени</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr"/>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.28.b</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>goes to selling</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>28% მიდის გაყიდვაზე</t>
-        </is>
-      </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>уходит на продажи</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr"/>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.owner.a</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>Business owner</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>ბიზნესის მფლობელი ხარ</t>
-        </is>
-      </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>Владелец бизнеса</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr"/>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.owner.b</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>or manager of everything?</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>თუ ყველაფრის მენეჯერი?</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>или менеджер всего?</t>
-        </is>
-      </c>
-      <c r="G178" s="3" t="inlineStr"/>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.excel.a</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>Still searching Excel</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>ისევ Excel-ში ეძებ,</t>
-        </is>
-      </c>
-      <c r="F179" s="3" t="inlineStr">
-        <is>
-          <t>Всё ещё ищете в Excel,</t>
-        </is>
-      </c>
-      <c r="G179" s="3" t="inlineStr"/>
-      <c r="H179" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.excel.b</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>for who bought what?</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>ვის რა მიჰყიდე?</t>
-        </is>
-      </c>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>кому что продали?</t>
-        </is>
-      </c>
-      <c r="G180" s="3" t="inlineStr"/>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.chats.a</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>A client messaged you.</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>კლიენტმა მოგწერა.</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>Клиент написал.</t>
-        </is>
-      </c>
-      <c r="G181" s="3" t="inlineStr"/>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>hero.v.chats.b</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Who replied?</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>ვინ უპასუხა?</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>Кто ответил?</t>
-        </is>
-      </c>
-      <c r="G182" s="3" t="inlineStr"/>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>process.eyebrow</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>How we work</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>როგორ ვმუშაობთ</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>Как мы работаем</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="inlineStr"/>
-      <c r="H183" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="inlineStr">
-        <is>
-          <t>process.title</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>Three steps to results</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>სამი ნაბიჯი შედეგამდე</t>
-        </is>
-      </c>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>Три шага к результату</t>
-        </is>
-      </c>
-      <c r="G184" s="3" t="inlineStr"/>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
-        <is>
-          <t>process.sub</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>We start small, prove the result, and only then scale.</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>ვიწყებთ პატარა ნაბიჯით, ვამოწმებთ შედეგს და მხოლოდ ამის შემდეგ ვაფართოებთ.</t>
-        </is>
-      </c>
-      <c r="F185" s="3" t="inlineStr">
-        <is>
-          <t>Начинаем с малого, проверяем результат и только потом масштабируем.</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="inlineStr"/>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C186" s="3" t="inlineStr">
-        <is>
-          <t>process.1.name</t>
-        </is>
-      </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>Consultation</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="inlineStr">
-        <is>
-          <t>კონსულტაცია</t>
-        </is>
-      </c>
-      <c r="F186" s="3" t="inlineStr">
-        <is>
-          <t>Консультация</t>
-        </is>
-      </c>
-      <c r="G186" s="3" t="inlineStr"/>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>process.1.desc</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>We find the real problem and pick the right tool.</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>ვიგებთ რეალურ პრობლემას და ვარჩევთ სწორ ინსტრუმენტს.</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="inlineStr">
-        <is>
-          <t>Находим реальную проблему и подбираем правильный инструмент.</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr"/>
-      <c r="H187" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="inlineStr">
-        <is>
-          <t>process.1.item.1</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>Review of your processes and current systems</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>პროცესებისა და არსებული სისტემების ანალიზი</t>
-        </is>
-      </c>
-      <c r="F188" s="3" t="inlineStr">
-        <is>
-          <t>Анализ процессов и текущих систем</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr"/>
-      <c r="H188" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>process.1.item.2</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>1-3 tools that fit (and what you don't need)</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>1-3 ინსტრუმენტის შერჩევა (და რა არ გჭირდება)</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="inlineStr">
-        <is>
-          <t>1-3 подходящих инструмента (и что вам не нужно)</t>
-        </is>
-      </c>
-      <c r="G189" s="3" t="inlineStr"/>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
-        <is>
-          <t>process.1.item.3</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>Implementation plan, budget and timeline</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>დანერგვის გეგმა, ბიუჯეტი და ვადები</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="inlineStr">
-        <is>
-          <t>План внедрения, бюджет и сроки</t>
-        </is>
-      </c>
-      <c r="G190" s="3" t="inlineStr"/>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>process.1.time</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>First call · 20 min · free</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>პირველი ზარი · 20 წთ · უფასო</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>Первый звонок · 20 мин · бесплатно</t>
-        </is>
-      </c>
-      <c r="G191" s="3" t="inlineStr"/>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="inlineStr">
-        <is>
-          <t>process.2.name</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>Implementation</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>დანერგვა</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>Внедрение</t>
-        </is>
-      </c>
-      <c r="G192" s="3" t="inlineStr"/>
-      <c r="H192" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>process.2.desc</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>We build the system in short sprints. You see the first result in 1-2 weeks.</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>ვაწყობთ სისტემას მოკლე სპრინტებით. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
-        </is>
-      </c>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>Строим систему короткими спринтами. Первый результат - через 1-2 недели.</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr"/>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="inlineStr">
-        <is>
-          <t>process.2.item.1</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>System setup and data migration</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>სისტემის აწყობა და მონაცემების გადატანა</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>Настройка системы и перенос данных</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="inlineStr"/>
-      <c r="H194" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>process.2.item.2</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>Automations and integrations</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>ავტომატიზაციები და ინტეგრაციები</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>Автоматизации и интеграции</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr"/>
-      <c r="H195" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="inlineStr">
-        <is>
-          <t>process.2.item.3</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>Team training</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>გუნდის ტრენინგი</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>Обучение команды</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="inlineStr"/>
-      <c r="H196" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
-        <is>
-          <t>process.2.time</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>Sprint · 1-2 weeks</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>სპრინტი · 1-2 კვირა</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>Спринт · 1-2 недели</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="inlineStr"/>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C198" s="3" t="inlineStr">
-        <is>
-          <t>process.3.name</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>მხარდაჭერა</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>Поддержка</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr"/>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
-        <is>
-          <t>process.3.desc</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>The system keeps working after launch and grows with your business.</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>სისტემა გაშვების შემდეგაც მუშაობს და იზრდება ბიზნესთან ერთად.</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>Система продолжает работать после запуска и растёт вместе с бизнесом.</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr"/>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t>process.3.item.1</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>Technical support when you need it</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>ტექნიკური მხარდაჭერა, როცა გჭირდება</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>Техническая поддержка, когда она нужна</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr"/>
-      <c r="H200" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>process.3.item.2</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>Ongoing optimization and improvements</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>მუდმივი ოპტიმიზაცია და განვითარება</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>Постоянная оптимизация и развитие</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="inlineStr"/>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr">
-        <is>
-          <t>process.3.item.3</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>New tools added as you need them</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>ახალი ინსტრუმენტების დამატება საჭიროებისამებრ</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>Новые инструменты - по мере необходимости</t>
-        </is>
-      </c>
-      <c r="G202" s="3" t="inlineStr"/>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>process.3.time</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>Ongoing · as needed</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>მუდმივად · საჭიროებისამებრ</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>Постоянно · по необходимости</t>
-        </is>
-      </c>
-      <c r="G203" s="3" t="inlineStr"/>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>process.note</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>Pricing is set individually and starts from 2,990 GEL (excl. VAT).</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება და იწყება 2990 ლარიდან (ფასები არ მოიცავს დღგ-ს).</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>Стоимость определяется индивидуально и начинается от 2990 лари (без НДС).</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr"/>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>process.cta</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>Start with a free consultation</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>დაიწყე უფასო კონსულტაციით</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>Начните с бесплатной консультации</t>
-        </is>
-      </c>
-      <c r="G205" s="3" t="inlineStr"/>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H205"/>
+  <autoFilter ref="A1:H165"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H364" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15347,23 +13827,23 @@
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>We start small, prove the result, and only then scale.</t>
+          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ პატარა ნაბიჯით, ვამოწმებთ შედეგს და მხოლოდ ამის შემდეგ ვაფართოებთ.</t>
+          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с малого, проверяем результат и только потом масштабируем.</t>
+          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr"/>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -16069,23 +14549,23 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Pricing is set individually and starts from 2,990 GEL (excl. VAT).</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება და იწყება 2990 ლარიდან (ფასები არ მოიცავს დღგ-ს).</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Стоимость определяется индивидуально и начинается от 2990 лари (без НДС).</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr"/>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -23197,23 +21677,23 @@
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>We start small, prove the result, and only then scale.</t>
+          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ პატარა ნაბიჯით, ვამოწმებთ შედეგს და მხოლოდ ამის შემდეგ ვაფართოებთ.</t>
+          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с малого, проверяем результат и только потом масштабируем.</t>
+          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr"/>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -23919,23 +22399,23 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Pricing is set individually and starts from 2,990 GEL (excl. VAT).</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება და იწყება 2990 ლარიდან (ფასები არ მოიცავს დღგ-ს).</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Стоимость определяется индивидуально и начинается от 2990 лари (без НДС).</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr"/>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -29523,23 +28003,23 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>We start small, prove the result, and only then scale.</t>
+          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ პატარა ნაბიჯით, ვამოწმებთ შედეგს და მხოლოდ ამის შემდეგ ვაფართოებთ.</t>
+          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с малого, проверяем результат и только потом масштабируем.</t>
+          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -30245,23 +28725,23 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Pricing is set individually and starts from 2,990 GEL (excl. VAT).</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება და იწყება 2990 ლარიდან (ფასები არ მოიცავს დღგ-ს).</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Стоимость определяется индивидуально и начинается от 2990 лари (без НДС).</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -35837,23 +34317,23 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>We start small, prove the result, and only then scale.</t>
+          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ პატარა ნაბიჯით, ვამოწმებთ შედეგს და მხოლოდ ამის შემდეგ ვაფართოებთ.</t>
+          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с малого, проверяем результат и только потом масштабируем.</t>
+          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -36559,23 +35039,23 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Pricing is set individually and starts from 2,990 GEL (excl. VAT).</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება და იწყება 2990 ლარიდან (ფასები არ მოიცავს დღგ-ს).</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Стоимость определяется индивидуально и начинается от 2990 лари (без НДС).</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated</t>
         </is>
       </c>
     </row>
@@ -39166,1638 +37646,1638 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>pricing.eyebrow</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>Collaboration</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>თანამშრომლობა</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>Сотрудничество</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>pricing.title</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>Three models of collaboration</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>თანამშრომლობის სამი მოდელი</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>Три модели сотрудничества</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" s="0" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>pricing.sub</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>We offer three collaboration models, based on how much of our resource you need. Pick the one that suits you best.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>ჩვენგან გამოსაყოფი რესურსის შესაბამისად, თანამშრომლობის სამ მოდელს გთავაზობთ. აირჩიე შენთვის ყველაზე მოსახერხებელი.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>В зависимости от того, сколько нашего ресурса вам нужно, мы предлагаем три модели сотрудничества. Выберите самую удобную.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" s="0" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>pricing.1.tag</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>We share our tools and experience</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>გიზიარებთ ინსტრუმენტებს და გამოცდილებას</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>Делимся инструментами и опытом</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" s="0" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>pricing.1.name</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>CONSULTING</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>კონსულტაცია</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>КОНСУЛЬТАЦИЯ</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" s="0" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>pricing.1.pitch</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Add 1-2 specific solutions from our catalog into your existing setup. Fast, focused, no rebuild required.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>1-2 კონკრეტული გადაწყვეტა ჩვენი კატალოგიდან, არსებულ სისტემაში დანერგილი. სწრაფად, ფოკუსირებულად, ხელახალი აწყობის გარეშე.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>1-2 конкретных решения из нашего каталога, внедрённых в вашу систему. Быстро, точно, без переделки.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" s="0" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>pricing.1.price</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>€990+</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>€990+</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>€990+</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" s="0" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>pricing.1.priceUnit</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>+ VAT · one-time</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>+ დღგ · ერთჯერადად</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr">
         <is>
           <t>+ НДС · разово</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" s="0" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>pricing.1.timeline</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>3+ working days</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>3+ სამუშაო დღე</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="0" t="inlineStr">
         <is>
           <t>3+ рабочих дня</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" s="0" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>pricing.1.feature.1</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>1-2 specific solutions</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>1-2 კონკრეტული გადაწყვეტა</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="0" t="inlineStr">
         <is>
           <t>1-2 конкретных решения</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" s="0" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>pricing.1.feature.2</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>Integrated into your existing system</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>ინტეგრირდება არსებულ სისტემაში</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr">
         <is>
           <t>Интеграция в существующую систему</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" s="0" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>pricing.1.feature.3</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>30-minute team training</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>30-წუთიანი გუნდის ტრენინგი</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="0" t="inlineStr">
         <is>
           <t>30-минутное обучение команды</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>pricing.1.feature.4</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>Consulting sessions</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>საკონსულტაციო შეხვედრები</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="0" t="inlineStr">
         <is>
           <t>Консультационные встречи</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" s="0" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>pricing.1.cta</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>Request consulting</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>მოითხოვე კონსულტაცია</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t>Запросить консультацию</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" s="0" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>pricing.2.badge</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>⭐ Most Popular</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>⭐ ყველაზე პოპულარული</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="0" t="inlineStr">
         <is>
           <t>⭐ Самый популярный</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" s="0" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>pricing.2.tag</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>We help you implement step by step</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>გეხმარებით ეტაპობრივად დანერგვაში</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr">
         <is>
           <t>Помогаем внедрять поэтапно</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" s="0" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>pricing.2.name</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>IMPLEMENTATION</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>დანერგვა</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr">
         <is>
           <t>ВНЕДРЕНИЕ</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" s="0" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>pricing.2.pitch</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>Full system build or your sharpest pain solved. Done in 2 weeks, team trained, you own it.</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>სრული სისტემის აწყობა ან უდიდესი ტკივილის მოგვარება. 2 კვირაში, გუნდი დატრენინგებული, შენი კუთვნილება.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
         <is>
           <t>Построение полной системы или решение главной боли. За 2 недели, команда обучена, всё ваше.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" s="0" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>pricing.2.price</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>€2,990</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>€2,990</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr">
         <is>
           <t>€2,990</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" s="0" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>pricing.2.priceUnit</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>+ VAT · one-time</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>+ დღგ · ერთჯერადად</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr">
         <is>
           <t>+ НДС · разово</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" s="0" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>pricing.2.timeline</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>10-15 working days</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>10-15 სამუშაო დღე</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr">
         <is>
           <t>10-15 рабочих дней</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" s="0" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>pricing.2.feature.1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>Full Data Foundation or Sharpest Pain sprint</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>სრული Data Foundation ან Sharpest Pain Sprint</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="0" t="inlineStr">
         <is>
           <t>Полный спринт Data Foundation или Sharpest Pain</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" s="0" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>pricing.2.feature.2</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>Up to 6 solutions</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>6-მდე გადაწყვეტა</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="0" t="inlineStr">
         <is>
           <t>До 6 решений</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" s="0" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>pricing.2.feature.3</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>Automations + 1 integration</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>ავტომატიზაცია + 1 ინტეგრაცია</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr">
         <is>
           <t>Автоматизация + 1 интеграция</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" s="0" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>pricing.2.feature.4</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>Data migration (1 source)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>მონაცემთა მიგრაცია (1 წყარო)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
         <is>
           <t>Миграция данных (1 источник)</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" s="0" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>pricing.2.feature.5</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>1-hour team training</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>1-საათიანი გუნდის ტრენინგი</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr">
         <is>
           <t>1-часовое обучение команды</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" s="0" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>pricing.2.cta</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>Request implementation</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>მოითხოვე დანერგვა</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr">
         <is>
           <t>Запросить внедрение</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" s="0" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>pricing.3.tag</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>We keep your growth moving, continuously</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>მუდმივად ვზრუნავთ განვითარებაზე</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
         <is>
           <t>Постоянно заботимся о развитии</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" s="0" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>pricing.3.name</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>PARTNERSHIP</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>პარტნიორობა</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="0" t="inlineStr">
         <is>
           <t>ПАРТНЁРСТВО</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" s="0" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>pricing.3.pitch</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>Multi-sprint build + ongoing managed services. Priority queue, direct line to our CEO + Tech Lead.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>მრავალ-სპრინტიანი აწყობა + მუდმივი managed services. პრიორიტეტული რიგი, პირდაპირი კავშირი CEO-სთან და Tech Lead-სთან.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="0" t="inlineStr">
         <is>
           <t>Многоспринтовое построение + постоянные managed services. Приоритетная очередь, прямая связь с CEO и Tech Lead.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" s="0" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>pricing.3.price</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>€7,990 + €790/mo</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>€7,990 + €790/თვე</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="0" t="inlineStr">
         <is>
           <t>€7,990 + €790/мес</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" s="0" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>pricing.3.priceUnit</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>+ VAT · 6-month minimum</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>+ დღგ · 6 თვე მინ.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="0" t="inlineStr">
         <is>
           <t>+ НДС · минимум 6 месяцев</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" s="0" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>pricing.3.timeline</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>90-day engagement</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>90-დღიანი ჩართულობა</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="0" t="inlineStr">
         <is>
           <t>90-дневное взаимодействие</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" s="0" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>pricing.3.feature.1</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>Everything included in Implementation</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="0" t="inlineStr">
         <is>
           <t>ყველაფერი, რასაც დანერგვა მოიცავს</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr">
         <is>
           <t>Всё, что входит во Внедрение</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" s="0" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>pricing.3.feature.2</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
         <is>
           <t>Priority dev queue</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="0" t="inlineStr">
         <is>
           <t>პრიორიტეტული dev-ის რიგი</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="0" t="inlineStr">
         <is>
           <t>Приоритетная очередь разработки</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" s="0" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>pricing.3.feature.3</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>A dedicated specialist from our team</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="0" t="inlineStr">
         <is>
           <t>გამოყოფილი სპეციალისტი გუნდიდან</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="0" t="inlineStr">
         <is>
           <t>Выделенный специалист из команды</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" s="0" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>pricing.3.feature.4</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>Ongoing optimization</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="0" t="inlineStr">
         <is>
           <t>მუდმივი ოპტიმიზაცია</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="0" t="inlineStr">
         <is>
           <t>Постоянная оптимизация</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" s="0" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>pricing.3.feature.5</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>Monthly strategy review (CEO level)</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="0" t="inlineStr">
         <is>
           <t>თვიური სტრატეგიული შეხვედრა (CEO)</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="0" t="inlineStr">
         <is>
           <t>Ежемесячная стратегическая встреча (CEO)</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" s="0" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>pricing.3.cta</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t>Request partnership</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="0" t="inlineStr">
         <is>
           <t>მოითხოვე პარტნიორობა</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="0" t="inlineStr">
         <is>
           <t>Запросить партнёрство</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" s="0" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>pricing.blueprint.title</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t>Need more flexibility? Use our resource - by the hour</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="0" t="inlineStr">
         <is>
           <t>მეტი მოქნილობა გჭირდება? გამოიყენე ჩვენი რესურსი - საათობრივად</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="0" t="inlineStr">
         <is>
           <t>Нужно больше гибкости? Используйте наш ресурс - почасово</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" s="0" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>pricing.blueprint.body</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
         <is>
           <t>Order technical and expert support by the hour. Our team helps with implementation, know-how, and years of experience - exactly when you need it. €69/h + VAT, no minimum commitment.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="0" t="inlineStr">
         <is>
           <t>შეუკვეთე ტექნიკური და საექსპერტო მხარდაჭერა საათობრივად. ჩვენი გუნდი დაგეხმარება ტექნიკური დანერგვით, ცოდნითა და წლების გამოცდილებით - ზუსტად მაშინ, როცა გჭირდება. €69/სთ + დღგ, არანაირი მინიმალური ვალდებულება.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="0" t="inlineStr">
         <is>
           <t>Закажите техническую и экспертную поддержку почасово. Наша команда поможет с технической реализацией, знаниями и многолетним опытом - именно тогда, когда это нужно. €69/ч + НДС, без минимальных обязательств.</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" s="0" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>pricing.blueprint.cta</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="0" t="inlineStr">
         <is>
           <t>Request support →</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="0" t="inlineStr">
         <is>
           <t>მოითხოვე მხარდაჭერა →</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="0" t="inlineStr">
         <is>
           <t>Запросить поддержку →</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" s="0" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>Landing (all)</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>Pricing (removed 2026-10-26, replaced by 3-step process)</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>pricing.note</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>These packages describe our ways of working together. The cost is set individually and starts from 2,990 GEL (prices exclude VAT).</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="0" t="inlineStr">
         <is>
           <t>ეს პაკეტები ასახავს თანამშრომლობის მიდგომებს. ღირებულება ინდივიდუალურად განისაზღვრება და იწყება 2990 ლარიდან (ფასები არ მოიცავს დღგ-ს).</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="0" t="inlineStr">
         <is>
           <t>Эти пакеты описывают подходы к сотрудничеству. Стоимость определяется индивидуально и начинается от 2990 лари (цены без НДС).</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="0" t="inlineStr">
         <is>
           <t>Pricing section removed</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -14,11 +14,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$205</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$208</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$176</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -386,7 +386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" style="6" min="1" max="1"/>
@@ -465,6 +465,24 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -927,17 +945,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე უფასო ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4347,17 +4365,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a Call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -5997,7 +6015,7 @@
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6737,7 @@
       <c r="G164" s="3" t="inlineStr"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -6741,17 +6759,17 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Start with a free consultation</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>დაიწყე უფასო კონსულტაციით</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Начните с бесплатной консультации</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr"/>
@@ -6778,7 +6796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -6929,17 +6947,17 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Choosing the right CRM is hard</t>
+          <t>Choose the right CRM</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>სწორი CRM-ის შერჩევა რთულია</t>
+          <t>შეარჩიე სწორი CRM</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Выбрать правильную CRM сложно</t>
+          <t>Выберите правильную CRM</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -6969,22 +6987,26 @@
           <t>hero.headline.line2.accent</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>20 minutes with me</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>20 წუთი ჩემთან</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>20 минут со мной</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>and save</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>და დაზოგე</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>и сэкономьте</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7007,22 +7029,14 @@
           <t>hero.headline.line2.plain</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>saves you</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>დაგიზოგავს</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>сэкономят вам</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7045,22 +7059,26 @@
           <t>hero.headline.line3.underline</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>100+ hours</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>100+ საათიან</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>100+ საათი</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>100+ часов</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -7083,21 +7101,9 @@
           <t>hero.headline.line3.plain</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>of research and trials</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>კვლევას და ტესტირებას</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>исследований и тестов</t>
-        </is>
-      </c>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
@@ -7127,17 +7133,17 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>With 500+ successful implementations behind us, in 20 minutes I'll tell you which CRM fits your sales, what implementation costs and how fast it can go live. Free if you book now.</t>
+          <t>With 500+ implementations behind us, in 20 minutes we tell you which CRM fits your sales and what implementation costs. Free if you book now.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>500+ წარმატებული დანერგვის გამოცდილებით, 20 წუთში მოგიყვები, რომელი CRM მოერგება შენს გაყიდვებს, რა ეღირება დანერგვა და რამდენ ხანში ამუშავდება. უფასოდ - თუ ახლავე დაჯავშნი.</t>
+          <t>500+ დანერგვის გამოცდილებით 20 წუთში გეტყვით, რომელი CRM მოერგება შენს გაყიდვებს და რა ეღირება დანერგვა. უფასოდ - თუ ახლავე დაჯავშნი.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Опираясь на 500+ успешных внедрений, за 20 минут расскажу, какая CRM подойдёт вашим продажам, сколько стоит внедрение и как быстро она заработает. Бесплатно - если бронируете сейчас.</t>
+          <t>Опираясь на 500+ внедрений, за 20 минут скажем, какая CRM подойдёт вашим продажам и сколько стоит внедрение. Бесплатно - если бронируете сейчас.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -7245,17 +7251,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე უფასო ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -10673,17 +10679,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a Call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -10823,22 +10829,26 @@
           <t>faq.q1</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>How is this different from hiring a Zoho / Monday / ClickUp partner directly?</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>რით განსხვავდება ეს უშუალოდ Zoho-ს, Monday-ს ან ClickUp-ის პარტნიორის დაქირავებისგან?</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>Чем это отличается от работы напрямую с партнёром Zoho / Monday / ClickUp?</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr"/>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>How are you different from a single-CRM partner?</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>რით განსხვავდებით კონკრეტული CRM-ის პარტნიორისგან?</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Чем вы отличаетесь от партнёра одной CRM?</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -10861,22 +10871,26 @@
           <t>faq.a1</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>We're vendor-neutral. Zoho partners sell Zoho, Monday partners sell Monday. We tell you honestly which platform fits your case, and if it isn't a platform we work with, we say so. The 20-minute call is where we find out which one you need.</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>ჩვენ სრულიად დამოუკიდებლები (vendor-neutral) ვართ. Zoho-ს პარტნიორი გთავაზობს მხოლოდ Zoho-ს, Monday-ს პარტნიორი - Monday-ს. ჩვენ გულწრფელად გირჩევთ იმ სისტემას, რომელიც რეალურად მოერგება შენს ბიზნესს; და თუ ისეთ ხელსაწყოზეა საუბარი, რომელთანაც არ ვმუშაობთ, პირდაპირ გეტყვით. 20-წუთიანი ზარი სწორედ იმისთვისაა, რომ გავარკვიოთ, რა გჭირდება რეალურად.</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>Мы вендор-нейтральны. Партнёр Zoho продаёт Zoho, партнёр Monday - Monday. Мы честно говорим, какая платформа подходит именно вам, и если это не та, с которой мы работаем - так и скажем. 20-минутный звонок как раз о том, чтобы это выяснить.</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr"/>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>We're vendor-neutral. A Zoho partner offers only Zoho, a Bitrix24 partner only Bitrix24. We recommend the system that actually fits your sales, and if the best option is one we don't implement, we tell you so.</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>ვართ დამოუკიდებელი (vendor-neutral). Zoho-ს პარტნიორი გთავაზობს მხოლოდ Zoho-ს, Bitrix24-ის პარტნიორი მხოლოდ Bitrix24-ს. ჩვენ გირჩევთ იმ სისტემას, რომელიც რეალურად მოერგება შენს გაყიდვებს, და თუ საუკეთესო ვარიანტი ისეთი სისტემაა, რომელსაც ჩვენ არ ვნერგავთ, ამასაც პირდაპირ გეტყვით.</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Мы независимы (vendor-neutral). Партнёр Zoho предлагает только Zoho, партнёр Bitrix24 - только Bitrix24. Мы советуем систему, которая действительно подходит вашим продажам, а если лучший вариант - система, которую мы не внедряем, прямо скажем об этом.</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -10899,22 +10913,26 @@
           <t>faq.q2</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Why only one sprint instead of a full roadmap?</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>რატომ ვიწყებთ ერთი კონკრეტული სპრინტით და არა გრძელვადიანი გეგმით?</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>Почему только один спринт, а не полная дорожная карта?</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr"/>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>Which CRMs do you implement?</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>რომელ CRM-ებს ნერგავთ?</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Какие CRM вы внедряете?</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -10937,22 +10955,26 @@
           <t>faq.a2</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Because 31% of IT projects actually succeed, and the ones that fail usually failed because they were too big. We ship one real thing in 10-15 days, your team adopts it, then Sprint 2 is informed by what you learned. No lock-in, no 6-month contract.</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>იმიტომ, რომ IT პროექტების მხოლოდ 31% სრულდება წარმატებით, ჩავარდნის მთავარი მიზეზი კი ხშირად მათი ზედმეტი სირთულე და მოცულობაა. ჩვენ ვნერგავთ ერთ კონკრეტულ, გამართულ ფუნქციონალს 10-15 დღეში, შენი გუნდი უპრობლემოდ ითვისებს მას, მეორე სპრინტი კი უკვე მიღებულ პრაქტიკულ გამოცდილებას ეფუძნება. არანაირი ხელოვნური მიბმა და 6-თვიანი სავალდებულო კონტრაქტები.</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>Потому что успешны лишь 31% IT-проектов, а провалы обычно случаются из-за того, что проект слишком большой. Мы запускаем одну реальную вещь за 10-15 дней, команда её осваивает, а Спринт 2 строится уже на этом опыте. Никакой привязки, никаких шестимесячных контрактов.</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr"/>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>We're a certified partner of Zoho, Pipedrive, Kommo, monday.com, Bitrix24 and Odoo (and also ClickUp and Manychat). On the call we tell you which one fits your team, processes and budget.</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>ვართ Zoho-ს, Pipedrive-ის, Kommo-ს, monday.com-ის, Bitrix24-ისა და Odoo-ს სერტიფიცირებული პარტნიორი (ასევე ClickUp-ის და Manychat-ის). ზარზე გეტყვით, რომელი ერგება შენს გუნდს, პროცესებს და ბიუჯეტს.</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Мы сертифицированный партнёр Zoho, Pipedrive, Kommo, monday.com, Bitrix24 и Odoo (а также ClickUp и Manychat). На звонке скажем, какая подходит вашей команде, процессам и бюджету.</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -10975,22 +10997,26 @@
           <t>faq.q3</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>What does it actually cost?</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>რეალურად რა ჯდება მომსახურება?</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>Сколько это стоит на деле?</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr"/>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>What does a CRM implementation cost?</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>რა ჯდება CRM-ის დანერგვა?</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Сколько стоит внедрение CRM?</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11013,22 +11039,26 @@
           <t>faq.a3</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Minimum engagement is €1,990 + VAT. Most first sprints land €2,000-5,000 depending on which solutions you pick. Licensing (Zoho, Monday, etc.) is billed separately by the vendor at their public prices. We tell you both numbers on the call.</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>მინიმალური ჩართულობა შეადგენს €1,990-ს (+ დღგ). პირველი სპრინტების უმრავლესობის ღირებულება შერჩეული გადაწყვეტების მიხედვით €2,000-დან €5,000-მდე მერყეობს. პლატფორმის ლიცენზიებს (Zoho, Monday და ა.შ.) პირდაპირ მწარმოებელს უხდით მათი ოფიციალური საჯარო ტარიფებით. ორივე ციფრს ზარზე დეტალურად დაგითვლით.</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>Минимальный заказ - €1,990 + НДС. Большинство первых спринтов - €2,000-5,000 в зависимости от выбранных решений. Лицензии (Zoho, Monday и т.д.) оплачиваются отдельно напрямую вендору по его публичным ценам. Обе цифры называем на звонке.</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr"/>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>The price is set individually: it depends on the number of users, your processes, data migration and integrations. You pay the CRM licence directly to the vendor at its official price; we charge for the implementation. We give you both numbers on the 20-minute call.</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება: დამოკიდებულია მომხმარებლების რაოდენობაზე, პროცესებზე, მონაცემების გადმოტანასა და ინტეგრაციებზე. CRM-ის ლიცენზიას პირდაპირ მწარმოებელს უხდი მისი ოფიციალური ფასით, ჩვენ კი ვიღებთ დანერგვის საფასურს. ორივე ციფრს 20-წუთიან ზარზე გეტყვით.</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Стоимость определяется индивидуально: зависит от числа пользователей, процессов, переноса данных и интеграций. Лицензию CRM вы оплачиваете напрямую производителю по официальной цене, а мы берём плату за внедрение. Обе цифры назовём на 20-минутном звонке.</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11051,22 +11081,26 @@
           <t>faq.q4</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Do you work with my industry?</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>მუშაობთ თუ არა ჩემს კონკრეტულ ინდუსტრიაში?</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>Вы работаете в моей отрасли?</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr"/>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>How long does implementation take?</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>რამდენ ხანს გრძელდება დანერგვა?</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Сколько длится внедрение?</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11089,22 +11123,26 @@
           <t>faq.a4</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>We've deployed in real estate, education, logistics, hospitality, medical, retail, finance, construction, and services. If your work is on an Excel sheet, a shared inbox, or a WhatsApp group right now, we can help. If you need something only a very narrow vertical tool does (legal case management, specific medical records), we'll tell you.</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>ჩვენ განვახორციელეთ დანერგვები უძრავ ქონებაში, განათლებაში, ლოგისტიკაში, HoReCa სექტორში, მედიცინაში, რითეილში, ფინანსებში, მშენებლობასა და მომსახურების სფეროში. თუ დღეს შენი საქმე იმართება Excel-ის ცხრილებით, საერთო მეილით ან WhatsApp-ის ჩატებით - ჩვენ შეგვიძლია შენი დახმარება. ხოლო თუ სპეციფიკური ვიწრო-პროფილური სისტემა გჭირდება (მაგ. იურიდიული საქმისწარმოება ან სპეციფიკური სამედიცინო ბარათები), ამასაც პირდაპირ გეტყვით.</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>Мы внедряли в недвижимости, образовании, логистике, гостеприимстве, медицине, рознице, финансах, строительстве и сервисах. Если вы сейчас работаете в Excel, общем inbox или WhatsApp-группе - мы поможем. Если нужен узкоспециализированный вертикальный инструмент (управление юридическими кейсами, медицинские записи) - честно скажем.</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr"/>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>A core CRM (sales stages, fields, data migration, team training) usually goes live in 1-2 weeks. We start with what matters most, your team adopts it, then we add automations and integrations. That keeps risk low and you see results fast.</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>საბაზისო CRM (გაყიდვების ეტაპები, ველები, მონაცემების გადმოტანა, გუნდის ტრენინგი) როგორც წესი 1-2 კვირაში ეშვება. ვიწყებთ ყველაზე მნიშვნელოვანით, გუნდი ითვისებს და მერე ვამატებთ ავტომატიზაციებსა და ინტეგრაციებს. ასე რისკი მინიმალურია და შედეგს სწრაფად ხედავ.</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Базовая CRM (этапы продаж, поля, перенос данных, обучение команды) обычно запускается за 1-2 недели. Начинаем с самого важного, команда осваивает систему, затем добавляем автоматизации и интеграции. Так риск минимален, а результат виден быстро.</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11127,22 +11165,26 @@
           <t>faq.q5</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>What if I don't know what my problem is?</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>რა ვქნა, თუ ზუსტად არ ვიცი, რა არის ჩემი მთავარი პრობლემა?</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>А если я не знаю, в чём моя проблема?</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr"/>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>Can you move our data from Excel or another CRM?</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>შეგიძლიათ მონაცემები Excel-იდან ან სხვა CRM-იდან გადმოიტანოთ?</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Можете перенести данные из Excel или другой CRM?</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11165,22 +11207,26 @@
           <t>faq.a5</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>That's what the 20 minutes are for. Most founders arrive with a vague "I need a CRM" and leave with a specific one-page plan. If after the call it's still unclear, we offer a paid Discovery (€99/h) to go deeper - only when it genuinely helps.</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>20-წუთიანი ზარი სწორედ ამისთვისაა. დამფუძნებლების უმეტესობა მოდის ზოგადი ფრაზით „CRM მჭირდება“ და ზარიდან გადის კონკრეტული 1-გვერდიანი სამოქმედო გეგმით. თუ ზარის შემდეგ მაინც საჭირო გახდა სიღრმისეული ანალიზი, გთავაზობთ ფასიან Discovery სესიას (€99/სთ) - მხოლოდ იმ შემთხვევაში, თუ ეს რეალურ სარგებელს მოგიტანს.</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>Для этого и нужны 20 минут. Большинство основателей приходят с размытым "мне нужна CRM", а уходят с конкретным планом на одну страницу. Если после звонка всё ещё непонятно - предлагаем платный Discovery (€99/ч), чтобы копнуть глубже. Только если это реально поможет.</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr"/>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Yes. We move clients, contacts, deals and history from Excel, Google Sheets or another CRM. Before the move we clean duplicates and normalise phone numbers, so the new system starts with a clean database.</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>კი. კლიენტებს, კონტაქტებს, გარიგებებს და ისტორიას გადმოვიტანთ Excel-იდან, Google Sheets-იდან ან სხვა CRM-იდან. გადმოტანამდე ვასუფთავებთ დუბლიკატებს და ვაწესრიგებთ ტელეფონის ნომრებს, რომ ახალი სისტემა სუფთა ბაზით დაიწყოს.</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Да. Переносим клиентов, контакты, сделки и историю из Excel, Google Sheets или другой CRM. Перед переносом чистим дубликаты и приводим номера телефонов к единому формату, чтобы новая система стартовала с чистой базой.</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11203,22 +11249,26 @@
           <t>faq.q6</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>Who owns the system you build?</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>ვის საკუთრებაში რჩება აწყობილი სისტემა?</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>Кому принадлежит система, которую вы строите?</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr"/>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>Can the CRM connect chats, website forms and telephony?</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>შეიძლება CRM-ს ჩატები, საიტის ფორმები და ტელეფონია მივაბა?</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Можно подключить к CRM чаты, формы сайта и телефонию?</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11241,22 +11291,26 @@
           <t>faq.a6</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>You own all your data and all platform accounts - they're registered under your company. The implementation IP (configurations, custom code) belongs to us, but you can take your data anywhere, anytime. Anything we host on our side is a transparent paid subscription you can cancel.</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>ყველა შენი მონაცემი და პლატფორმის ანგარიში რეგისტრირდება შენი კომპანიის სახელზე და რჩება შენს სრულ მფლობელობაში. დანერგვის ინტელექტუალური საკუთრება (კონფიგურაცია, custom კოდი) ეკუთვნის ჩვენს გუნდს, თუმცა შენი მონაცემების ექსპორტი და წაღება ნებისმიერ დროს შეგიძლია. ნებისმიერი სერვისი, რომელსაც ჩვენს მხარეს ვჰოსტავთ, წარმოადგენს გამჭვირვალე ყოველთვიურ გამოწერას, რომლის გაუქმებაც ნებისმიერ მომენტშია შესაძლებელი.</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>Все ваши данные и аккаунты платформ принадлежат вам - они зарегистрированы на вашу компанию. Интеллектуальная собственность на внедрение (конфигурации, кастомный код) принадлежит нам, но данные вы можете забрать куда угодно и когда угодно. Всё, что мы хостим у себя - прозрачная платная подписка, её можно отменить.</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr"/>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>Yes. WhatsApp, Instagram, Facebook Messenger, website forms, Meta ad leads and telephony (including GEONET) can all land in one CRM, so every request is in one place. On the call we confirm what connects to the CRM you choose and how.</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>კი. WhatsApp, Instagram, Facebook Messenger, საიტის ფორმები, Meta-ს რეკლამის ლიდები და ტელეფონია (მათ შორის GEONET) შეგვიძლია ერთ CRM-ში შევკრიბოთ, რომ ყველა მომართვა ერთ ადგილას ჩანდეს. რა და როგორ უკავშირდება შენს არჩეულ CRM-ს, ზარზე დაგიზუსტებთ.</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>Да. WhatsApp, Instagram, Facebook Messenger, формы сайта, лиды из рекламы Meta и телефонию (включая GEONET) можно собрать в одной CRM, чтобы все обращения были в одном месте. Что и как подключается к выбранной CRM, уточним на звонке.</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11279,22 +11333,26 @@
           <t>faq.q7</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>What happens after the sprint delivers?</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>რა ხდება სპრინტის დასრულებისა და ჩაბარების შემდეგ?</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>Что происходит после сдачи спринта?</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr"/>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>Do you work with my industry?</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>მუშაობთ თუ არა ჩემს ინდუსტრიაში?</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>Работаете ли вы в моей отрасли?</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11317,22 +11375,26 @@
           <t>faq.a7</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Three business days to review and accept. Then your team runs it. Technical support is available at €69/h - only if you need it. Many clients then book Sprint 2 (automations, integrations) or move to Managed Services for ongoing optimization.</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>გაქვს 3 სამუშაო დღე სისტემის შესამოწმებლად და ჩასაბარებლად, რის შემდეგაც შენი გუნდი სრულფასოვნად იწყებს მუშაობას. ტექნიკური მხარდაჭერა ხელმისაწვდომია ტარიფით €69/სთ - მხოლოდ საჭიროების შემთხვევაში. ბევრი კლიენტი შემდგომ ჯავშნის მეორე სპრინტს (ავტომატიზაციები, ინტეგრაციები) ან გადადის მუდმივი ოპტიმიზაციის მხარდაჭერის პაკეტზე (Managed Services).</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>Три рабочих дня на проверку и приёмку. Дальше система работает у вашей команды. Техподдержка доступна за €69/ч - только по необходимости. Многие клиенты затем бронируют Спринт 2 (автоматизация, интеграции) или переходят на Managed Services для постоянной оптимизации.</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr"/>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>We've implemented CRM in real estate, education, logistics, hospitality, healthcare, retail, finance, construction and services. If your sales run on Excel, a shared inbox or WhatsApp chats today, we can help.</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>CRM დაგვინერგავს უძრავ ქონებაში, განათლებაში, ლოგისტიკაში, HoReCa სექტორში, მედიცინაში, რითეილში, ფინანსებში, მშენებლობასა და მომსახურების სფეროში. თუ დღეს გაყიდვები Excel-ში, საერთო მეილში ან WhatsApp-ის ჩატებში იმართება, შეგვიძლია დაგეხმაროთ.</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Мы внедряли CRM в недвижимости, образовании, логистике, HoReCa, медицине, ритейле, финансах, строительстве и сфере услуг. Если сегодня продажи ведутся в Excel, общей почте или чатах WhatsApp, мы поможем.</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11355,22 +11417,26 @@
           <t>faq.q8</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Can I pick 5 solutions and combine them?</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>შემიძლია ავირჩიო 5 სხვადასხვა გადაწყვეტა და ერთად გავაერთიანო?</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>Можно выбрать 5 решений и объединить их?</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr"/>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>What if I don't know which CRM I need?</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>რა ვქნა, თუ არ ვიცი, რომელი CRM მჭირდება?</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Что делать, если я не знаю, какая CRM мне нужна?</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11393,22 +11459,26 @@
           <t>faq.a8</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Yes, that's what the "Add to request" list is for. On the call we help you order them by sequence (what has to come first) and sprint capacity. You usually won't ship all 5 at once, but you can.</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>რა თქმა უნდა! ღილაკი „სიაში დამატება“ სწორედ ამისთვისაა. ზარზე ერთად განვსაზღვრავთ პრიორიტეტებს - რა უნდა გაკეთდეს პირველ ეტაპზე და რა გადანაწილდეს შემდგომ სპრინტებზე. როგორც წესი, ხუთივე ერთდროულად არ ეშვება, თუმცა ტექნიკურად ეს სრულიად შესაძლებელია.</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>Да, именно для этого и существует список "Добавить в запрос". На звонке мы помогаем расставить их по порядку (что должно идти первым) и по ёмкости спринта. Обычно 5 сразу не внедряют, но технически это возможно.</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr"/>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>That is exactly what the 20-minute call is for. Most people arrive with "I need a CRM" and leave with a specific recommendation: which system, what the licence and implementation cost, and how long it takes.</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>20-წუთიანი ზარი სწორედ ამისთვისაა. უმეტესობა მოდის ფრაზით „CRM მჭირდება“ და ზარიდან გადის კონკრეტული რეკომენდაციით: რომელი სისტემა, რა ეღირება ლიცენზია და დანერგვა, რა ვადაში ეშვება.</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Для этого и нужен 20-минутный звонок. Большинство приходит с фразой «мне нужна CRM» и уходит с конкретной рекомендацией: какая система, сколько стоят лицензия и внедрение, за какой срок запускается.</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11431,22 +11501,26 @@
           <t>faq.q9</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Do you work with international clients, or Georgia only?</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>მუშაობთ საერთაშორისო კლიენტებთან, თუ მხოლოდ საქართველოში?</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>Вы работаете с международными клиентами или только в Грузии?</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr"/>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>What happens after launch?</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>რა ხდება დანერგვის შემდეგ?</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>Что происходит после запуска?</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11469,22 +11543,26 @@
           <t>faq.a9</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>We focus on Georgia because of language, local banking, and GEONET telephony integrations. We also serve select international clients - the call is in English or Russian or Georgian, whichever works for you.</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>ჩვენი მთავარი ფოკუსი საქართველოა ქართული ენის, ადგილობრივი ბანკინგისა და GEONET-ის ტელეფონიის ინტეგრაციების გამო. თუმცა ვთანამშრომლობთ შერჩეულ საერთაშორისო კლიენტებთანაც - საკონსულტაციო ზარი შეგვიძლია ჩავატაროთ ქართულად, ინგლისურად ან რუსულად, შენი სურვილისამებრ.</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>Мы сфокусированы на Грузии из-за языка, местного банкинга и интеграций с GEONET-телефонией. Работаем и с избранными международными клиентами - звонок на английском, русском или грузинском, как вам удобно.</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr"/>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>You have 3 business days to review and accept the system, then your team works in the CRM. Technical support is available when you need it, and for those who want the system to keep improving we offer monthly support.</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>გაქვს 3 სამუშაო დღე სისტემის შესამოწმებლად და ჩასაბარებლად, მერე გუნდი უკვე CRM-ში მუშაობს. ტექნიკური მხარდაჭერა ხელმისაწვდომია საჭიროებისამებრ, ხოლო ვისაც უნდა, რომ სისტემა მუდმივად ვითარდებოდეს, ვთავაზობთ ყოველთვიურ მხარდაჭერას.</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>У вас есть 3 рабочих дня, чтобы проверить и принять систему, после чего команда работает в CRM. Техподдержка доступна по необходимости, а тем, кто хочет постоянно развивать систему, предлагаем ежемесячное сопровождение.</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11507,22 +11585,26 @@
           <t>faq.q10</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>What if 20 minutes isn't enough?</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>რა მოხდება, თუ 20 წუთი საკმარისი არ აღმოჩნდება?</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>А если 20 минут не хватит?</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr"/>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>Who owns the CRM and the data?</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>ვის საკუთრებაში რჩება CRM და მონაცემები?</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>Кому принадлежат CRM и данные?</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11545,22 +11627,26 @@
           <t>faq.a10</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>Then we schedule a second call, or you book paid Discovery. We've never had a founder arrive and leave more confused - the agenda is tight on purpose. If you have a complex multi-system case, mention it on the booking form and we'll block 45 minutes instead.</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>ასეთ შემთხვევაში დავნიშნავთ მეორე ზარს, ან შევთანხმდებით სიღრმისეულ Discovery-ზე. არ ყოფილა შემთხვევა, რომ დამფუძნებელი ჩვენი ზარიდან უფრო დაბნეული გასულიყო - დღის წესრიგი მიზანმიმართულად მკაფიო და ლაკონიურია. თუ გაქვს კომპლექსური, მრავალსისტემიანი ქეისი, უბრალოდ მიუთითე ჯავშნის ფორმაში და შენთვის წინასწარ 45 წუთს დავჯავშნით.</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>Тогда назначим второй звонок или вы бронируете платный Discovery. У нас не было случая, когда основатель уходил бы ещё более запутанным - повестка намеренно плотная. Если у вас сложный мульти-системный кейс, отметьте это в форме бронирования, и мы выделим 45 минут.</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr"/>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>The CRM account and all data are registered to your company and stay fully yours. You can export your data at any time. Anything we host on our side is a transparent monthly subscription you can cancel at any time.</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>CRM-ის ანგარიში და ყველა მონაცემი რეგისტრირდება შენი კომპანიის სახელზე და რჩება შენს სრულ მფლობელობაში. მონაცემების ექსპორტი ნებისმიერ დროს შეგიძლია. თუ რამეს ჩვენს მხარეს ვჰოსტავთ, ეს არის გამჭვირვალე ყოველთვიური გამოწერა, რომელსაც ნებისმიერ დროს გააუქმებ.</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Аккаунт CRM и все данные зарегистрированы на вашу компанию и полностью принадлежат вам. Экспортировать данные можно в любой момент. Всё, что мы размещаем на своей стороне, - прозрачная ежемесячная подписка, которую можно отменить в любое время.</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -11851,17 +11937,17 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Sound familiar?</t>
+          <t>Do these situations sound familiar?</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>ნაცნობია?</t>
+          <t>გეცნობა ეს სიტუაციები?</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Знакомо?</t>
+          <t>Знакомы такие ситуации?</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr"/>
@@ -11927,17 +12013,17 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Request a free call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე უფასო ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
@@ -13843,7 +13929,7 @@
       <c r="G185" s="3" t="inlineStr"/>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -14565,7 +14651,7 @@
       <c r="G204" s="3" t="inlineStr"/>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -14587,17 +14673,17 @@
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Start with a free consultation</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>დაიწყე უფასო კონსულტაციით</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Начните с бесплатной консультации</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr"/>
@@ -14607,10 +14693,1342 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>pain.manager.left</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Ana left the chat</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>ანამ დატოვა ჩატი</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>Анна покинула чат</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr"/>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>pain.owner.note</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Today!!</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>დღეს!!</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>Сегодня!!</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr"/>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>pain.chats.more</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>+11 unanswered</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>+11 უპასუხო</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>+11 без ответа</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr"/>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>fit.title</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>Which CRM fits you?</t>
+        </is>
+      </c>
+      <c r="E209" s="9" t="inlineStr">
+        <is>
+          <t>რომელი CRM გერგება?</t>
+        </is>
+      </c>
+      <c r="F209" s="9" t="inlineStr">
+        <is>
+          <t>Какая CRM вам подходит?</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>fit.sub</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
+        <is>
+          <t>We're an independent partner: we recommend what fits your sales, not what we'd like to sell.</t>
+        </is>
+      </c>
+      <c r="E210" s="9" t="inlineStr">
+        <is>
+          <t>ვართ დამოუკიდებელი პარტნიორი: გირჩევთ იმას, რაც შენს გაყიდვებს ერგება, და არა იმას, რისი გაყიდვაც გვინდა.</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>Мы независимый партнёр: советуем то, что подходит вашим продажам, а не то, что нам выгодно продать.</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>fit.zoho.when</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>When your processes are complex and you want deep customisation, automations and analytics in one ecosystem.</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="inlineStr">
+        <is>
+          <t>როცა პროცესები რთულია და გინდა ღრმა მორგება, ავტომატიზაციები და ანალიტიკა ერთ ეკოსისტემაში.</t>
+        </is>
+      </c>
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>Когда процессы сложные и нужна глубокая настройка, автоматизации и аналитика в одной экосистеме.</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>fit.zoho.t1</t>
+        </is>
+      </c>
+      <c r="D212" s="9" t="inlineStr">
+        <is>
+          <t>Customisation</t>
+        </is>
+      </c>
+      <c r="E212" s="9" t="inlineStr">
+        <is>
+          <t>მორგება</t>
+        </is>
+      </c>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>Настройка</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>fit.zoho.t2</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="E213" s="9" t="inlineStr">
+        <is>
+          <t>ავტომატიზაცია</t>
+        </is>
+      </c>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>Автоматизация</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>fit.zoho.t3</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="E214" s="9" t="inlineStr">
+        <is>
+          <t>ანალიტიკა</t>
+        </is>
+      </c>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>fit.pipedrive.when</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>When your sales team needs a simple, visual pipeline and a fast start.</t>
+        </is>
+      </c>
+      <c r="E215" s="9" t="inlineStr">
+        <is>
+          <t>როცა გაყიდვების გუნდს მარტივი, ვიზუალური გაყიდვების ძაბრი და სწრაფი სტარტი სჭირდება.</t>
+        </is>
+      </c>
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>Когда отделу продаж нужна простая наглядная воронка и быстрый старт.</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>fit.pipedrive.t1</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="E216" s="9" t="inlineStr">
+        <is>
+          <t>მარტივი</t>
+        </is>
+      </c>
+      <c r="F216" s="9" t="inlineStr">
+        <is>
+          <t>Просто</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>fit.pipedrive.t2</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>Visual pipeline</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
+          <t>ვიზუალური ძაბრი</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>Наглядная воронка</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>fit.pipedrive.t3</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="inlineStr">
+        <is>
+          <t>Fast start</t>
+        </is>
+      </c>
+      <c r="E218" s="9" t="inlineStr">
+        <is>
+          <t>სწრაფი სტარტი</t>
+        </is>
+      </c>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>Быстрый старт</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>fit.kommo.when</t>
+        </is>
+      </c>
+      <c r="D219" s="9" t="inlineStr">
+        <is>
+          <t>When most of your sales happen in chats: WhatsApp, Instagram, Facebook.</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="inlineStr">
+        <is>
+          <t>როცა გაყიდვები ძირითადად ჩატებში მიდის: WhatsApp, Instagram, Facebook.</t>
+        </is>
+      </c>
+      <c r="F219" s="9" t="inlineStr">
+        <is>
+          <t>Когда продажи идут в основном в чатах: WhatsApp, Instagram, Facebook.</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>fit.kommo.t1</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="inlineStr">
+        <is>
+          <t>Chats</t>
+        </is>
+      </c>
+      <c r="E220" s="9" t="inlineStr">
+        <is>
+          <t>ჩატები</t>
+        </is>
+      </c>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>Чаты</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>fit.kommo.t2</t>
+        </is>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>Messengers</t>
+        </is>
+      </c>
+      <c r="E221" s="9" t="inlineStr">
+        <is>
+          <t>მესენჯერები</t>
+        </is>
+      </c>
+      <c r="F221" s="9" t="inlineStr">
+        <is>
+          <t>Мессенджеры</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>fit.kommo.t3</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="inlineStr">
+        <is>
+          <t>Chatbots</t>
+        </is>
+      </c>
+      <c r="E222" s="9" t="inlineStr">
+        <is>
+          <t>ჩატბოტები</t>
+        </is>
+      </c>
+      <c r="F222" s="9" t="inlineStr">
+        <is>
+          <t>Чат-боты</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>fit.monday.when</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
+        <is>
+          <t>When you want to run sales and projects on the same flexible boards.</t>
+        </is>
+      </c>
+      <c r="E223" s="9" t="inlineStr">
+        <is>
+          <t>როცა გაყიდვები და პროექტები ერთ, მოქნილ დაფებზე გინდა მართო.</t>
+        </is>
+      </c>
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>Когда хотите вести продажи и проекты на одних гибких досках.</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>fit.monday.t1</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="inlineStr">
+        <is>
+          <t>Flexible boards</t>
+        </is>
+      </c>
+      <c r="E224" s="9" t="inlineStr">
+        <is>
+          <t>მოქნილი დაფები</t>
+        </is>
+      </c>
+      <c r="F224" s="9" t="inlineStr">
+        <is>
+          <t>Гибкие доски</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>fit.monday.t2</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="E225" s="9" t="inlineStr">
+        <is>
+          <t>პროექტები</t>
+        </is>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>Проекты</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>fit.monday.t3</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="inlineStr">
+        <is>
+          <t>Teamwork</t>
+        </is>
+      </c>
+      <c r="E226" s="9" t="inlineStr">
+        <is>
+          <t>გუნდური მუშაობა</t>
+        </is>
+      </c>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>Командная работа</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>fit.bitrix.when</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>When you need internal chat, tasks and telephony in the same place as your CRM.</t>
+        </is>
+      </c>
+      <c r="E227" s="9" t="inlineStr">
+        <is>
+          <t>როცა CRM-თან ერთად შიდა ჩატი, დავალებები და ტელეფონია ერთ სივრცეში გჭირდება.</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>Когда рядом с CRM нужны внутренний чат, задачи и телефония в одном месте.</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>fit.bitrix.t1</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E228" s="9" t="inlineStr">
+        <is>
+          <t>დავალებები</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>Задачи</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>fit.bitrix.t2</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr">
+        <is>
+          <t>Internal chat</t>
+        </is>
+      </c>
+      <c r="E229" s="9" t="inlineStr">
+        <is>
+          <t>შიდა ჩატი</t>
+        </is>
+      </c>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>Внутренний чат</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>fit.bitrix.t3</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr">
+        <is>
+          <t>Telephony</t>
+        </is>
+      </c>
+      <c r="E230" s="9" t="inlineStr">
+        <is>
+          <t>ტელეფონია</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>Телефония</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H230" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>fit.odoo.when</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>When you want inventory, invoicing and accounting in the same system as sales.</t>
+        </is>
+      </c>
+      <c r="E231" s="9" t="inlineStr">
+        <is>
+          <t>როცა გაყიდვებთან ერთად საწყობი, ინვოისები და ბუღალტერია ერთ სისტემაში გინდა.</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>Когда вместе с продажами нужны склад, счета и бухгалтерия в одной системе.</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>fit.odoo.t1</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="inlineStr">
+        <is>
+          <t>CRM + ERP</t>
+        </is>
+      </c>
+      <c r="E232" s="9" t="inlineStr">
+        <is>
+          <t>CRM + ERP</t>
+        </is>
+      </c>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>CRM + ERP</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>fit.odoo.t2</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E233" s="9" t="inlineStr">
+        <is>
+          <t>საწყობი</t>
+        </is>
+      </c>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>Склад</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>fit.odoo.t3</t>
+        </is>
+      </c>
+      <c r="D234" s="9" t="inlineStr">
+        <is>
+          <t>Invoicing</t>
+        </is>
+      </c>
+      <c r="E234" s="9" t="inlineStr">
+        <is>
+          <t>ინვოისები</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>Счета</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>fit.foot.title</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>Not sure which one?</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="inlineStr">
+        <is>
+          <t>არ იცი, რომელი?</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>Не знаете, какую выбрать?</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>fit.foot.note</t>
+        </is>
+      </c>
+      <c r="D236" s="9" t="inlineStr">
+        <is>
+          <t>We'll choose together in 20 minutes. We're a certified partner of these platforms; you pay the licence directly to the vendor.</t>
+        </is>
+      </c>
+      <c r="E236" s="9" t="inlineStr">
+        <is>
+          <t>20 წუთში ერთად შევარჩევთ. ვართ ამ პლატფორმების სერტიფიცირებული პარტნიორები; ლიცენზიას პირდაპირ მწარმოებელს უხდი.</t>
+        </is>
+      </c>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>Выберем вместе за 20 минут. Мы сертифицированный партнёр этих платформ; лицензию вы оплачиваете напрямую производителю.</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>fit.cta</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
+        <is>
+          <t>Request a free 20-minute call</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="inlineStr">
+        <is>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+        </is>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>Запросить бесплатный 20-минутный звонок</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H205"/>
+  <autoFilter ref="A1:H237"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H436" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14624,7 +16042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -15091,17 +16509,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე უფასო ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -18519,17 +19937,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a Call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -19697,17 +21115,17 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Sound familiar?</t>
+          <t>Do these situations sound familiar?</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>ნაცნობია?</t>
+          <t>გეცნობა ეს სიტუაციები?</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Знакомо?</t>
+          <t>Знакомы такие ситуации?</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr"/>
@@ -19773,17 +21191,17 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Request a free call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე უფასო ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
@@ -21693,7 +23111,7 @@
       <c r="G185" s="3" t="inlineStr"/>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -22415,7 +23833,7 @@
       <c r="G204" s="3" t="inlineStr"/>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -22437,17 +23855,17 @@
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Start with a free consultation</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>დაიწყე უფასო კონსულტაციით</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Начните с бесплатной консультации</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr"/>
@@ -22457,10 +23875,124 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>pain.manager.left</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Ana left the chat</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>ანამ დატოვა ჩატი</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>Анна покинула чат</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr"/>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>pain.owner.note</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Today!!</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>დღეს!!</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>Сегодня!!</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr"/>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>pain.chats.more</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>+11 unanswered</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>+11 უპასუხო</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>+11 без ответа</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr"/>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H205"/>
+  <autoFilter ref="A1:H208"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H407" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22941,17 +24473,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე უფასო ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -26369,17 +27901,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a Call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -28019,7 +29551,7 @@
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -28741,7 +30273,7 @@
       <c r="G164" s="3" t="inlineStr"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -28763,17 +30295,17 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Start with a free consultation</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>დაიწყე უფასო კონსულტაციით</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Начните с бесплатной консультации</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr"/>
@@ -29263,17 +30795,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე უფასო ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -32683,17 +34215,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a Call</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -34333,7 +35865,7 @@
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -35055,7 +36587,7 @@
       <c r="G164" s="3" t="inlineStr"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>Updated</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -35077,17 +36609,17 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Start with a free consultation</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>დაიწყე უფასო კონსულტაციით</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Начните с бесплатной консультации</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr"/>
@@ -35576,7 +37108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -36487,7 +38019,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Choose a slot that works for you</t>
+          <t>Choose a time that works for you</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -36705,10 +38237,48 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Thank-you (all landings)</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>ty.bonus.text</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Your bonus: &lt;b&gt;Productivity Stack 2026&lt;/b&gt; - 10 tools for research, call transcripts, scheduling, analytics, CRM and automation. For each: what it is for, why this one, and the setting most people miss.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>შენი ბონუსი: &lt;b&gt;Productivity Stack 2026&lt;/b&gt; - 10 ინსტრუმენტი კვლევისთვის, ზარების ტრანსკრიპტისთვის, დაგეგმვისთვის, ანალიტიკისთვის, CRM-ისთვის და ავტომატიზაციისთვის. თითოეულზე: რისთვის, რატომ და რომელი პარამეტრი გამოგრჩება.</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Ваш бонус: &lt;b&gt;Productivity Stack 2026&lt;/b&gt; - 10 инструментов для исследований, транскрипции звонков, планирования, аналитики, CRM и автоматизации. Для каждого: для чего, почему именно он и какую настройку обычно упускают.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H27"/>
+  <autoFilter ref="A1:H28"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H226" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H227" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -4446,7 +4446,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>შეცდომა დაფიქსირდა. გთხოვთ, სცადო ხელახლა ან მოგვწერო: digital@unitty.io</t>
+          <t>შეცდომა დაფიქსირდა. სცადე ხელახლა ან მოგვწერე: digital@unitty.io</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>შეცდომა დაფიქსირდა. გთხოვთ, სცადო ხელახლა ან მოგვწერო: digital@unitty.io</t>
+          <t>შეცდომა დაფიქსირდა. სცადე ხელახლა ან მოგვწერე: digital@unitty.io</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>შეგიძლიათ მონაცემები Excel-იდან ან სხვა CRM-იდან გადმოიტანოთ?</t>
+          <t>შესაძლებელია მონაცემების Excel-იდან ან სხვა CRM-იდან გადმოტანა?</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
@@ -20018,7 +20018,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>შეცდომა დაფიქსირდა. გთხოვთ, სცადო ხელახლა ან მოგვწერო: digital@unitty.io</t>
+          <t>შეცდომა დაფიქსირდა. სცადე ხელახლა ან მოგვწერე: digital@unitty.io</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -27982,7 +27982,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>შეცდომა დაფიქსირდა. გთხოვთ, სცადო ხელახლა ან მოგვწერო: digital@unitty.io</t>
+          <t>შეცდომა დაფიქსირდა. სცადე ხელახლა ან მოგვწერე: digital@unitty.io</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>შეცდომა დაფიქსირდა. გთხოვთ, სცადო ხელახლა ან მოგვწერო: digital@unitty.io</t>
+          <t>შეცდომა დაფიქსირდა. სცადე ხელახლა ან მოგვწერე: digital@unitty.io</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -37184,7 +37184,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>მადლობა {name}, თქვენი მოთხოვნა მიღებულია.</t>
+          <t>მადლობა {name}, შენი მოთხოვნა მიღებულია.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>რა გზები სცადეთ უკვე და კონკრეტულად რატომ არ გაამართლა?</t>
+          <t>რა გზები სცადე უკვე და კონკრეტულად რატომ არ გაამართლა?</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -38138,7 +38138,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>მადლობა, თქვენი მოთხოვნა მიღებულია.</t>
+          <t>მადლობა, შენი მოთხოვნა მიღებულია.</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -38255,17 +38255,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Your bonus: &lt;b&gt;Productivity Stack 2026&lt;/b&gt; - 10 tools for research, call transcripts, scheduling, analytics, CRM and automation. For each: what it is for, why this one, and the setting most people miss.</t>
+          <t>&lt;b&gt;Your promised bonus:&lt;/b&gt;&lt;br&gt;10 tools I use every day - they will help you and your team be more productive every day and save you a lot of time.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>შენი ბონუსი: &lt;b&gt;Productivity Stack 2026&lt;/b&gt; - 10 ინსტრუმენტი კვლევისთვის, ზარების ტრანსკრიპტისთვის, დაგეგმვისთვის, ანალიტიკისთვის, CRM-ისთვის და ავტომატიზაციისთვის. თითოეულზე: რისთვის, რატომ და რომელი პარამეტრი გამოგრჩება.</t>
+          <t>&lt;b&gt;დაპირებული ბონუსი:&lt;/b&gt;&lt;br&gt;10 ინსტრუმენტი, რომელსაც ყოველდღიურად ვიყენებ - შენ და შენს გუნდს დაგეხმარებათ ყოველდღიური პროდუქტიულობის გაზრდაში და უამრავ დროს დაგაზოგინებთ.</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Ваш бонус: &lt;b&gt;Productivity Stack 2026&lt;/b&gt; - 10 инструментов для исследований, транскрипции звонков, планирования, аналитики, CRM и автоматизации. Для каждого: для чего, почему именно он и какую настройку обычно упускают.</t>
+          <t>&lt;b&gt;Обещанный бонус:&lt;/b&gt;&lt;br&gt;10 инструментов, которыми я пользуюсь каждый день, - они помогут вам и вашей команде повысить ежедневную продуктивность и сэкономят массу времени.</t>
         </is>
       </c>
       <c r="G28" s="3" t="n"/>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$355</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$208</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$176</definedName>
@@ -6796,7 +6796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -11041,17 +11041,17 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>The price is set individually: it depends on the number of users, your processes, data migration and integrations. You pay the CRM licence directly to the vendor at its official price; we charge for the implementation. We give you both numbers on the 20-minute call.</t>
+          <t>Implementation packages have fixed prices: Starter €990 (5 working days), Essentials €2,990 (15 days), Growth €5,990 (25 days), add-ons from €190. VAT (18%) is added. You pay the CRM licence directly to the vendor at its official price. On the 20-minute call we tell you which package you need and what the licence costs.</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება: დამოკიდებულია მომხმარებლების რაოდენობაზე, პროცესებზე, მონაცემების გადმოტანასა და ინტეგრაციებზე. CRM-ის ლიცენზიას პირდაპირ მწარმოებელს უხდი მისი ოფიციალური ფასით, ჩვენ კი ვიღებთ დანერგვის საფასურს. ორივე ციფრს 20-წუთიან ზარზე გეტყვით.</t>
+          <t>დანერგვის პაკეტები ფიქსირებული ფასისაა: სტარტი €990 (5 სამუშაო დღე), ოპტიმალური €2,990 (15 დღე), ზრდა €5,990 (25 დღე), დამატებები €190-დან. ფასებს ემატება დღგ (18%). CRM-ის ლიცენზიას პირდაპირ მწარმოებელს უხდი მისი ოფიციალური ფასით. 20-წუთიან ზარზე გეტყვით, რომელი პაკეტი გჭირდება და რამდენი დაჯდება ლიცენზია.</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>Стоимость определяется индивидуально: зависит от числа пользователей, процессов, переноса данных и интеграций. Лицензию CRM вы оплачиваете напрямую производителю по официальной цене, а мы берём плату за внедрение. Обе цифры назовём на 20-минутном звонке.</t>
+          <t>Пакеты внедрения с фиксированной ценой: «Старт» €990 (5 рабочих дней), «Оптимальный» €2,990 (15 дней), «Рост» €5,990 (25 дней), дополнения от €190. Добавляется НДС (18%). Лицензию CRM вы оплачиваете напрямую производителю по официальной цене. На 20-минутном звонке скажем, какой пакет нужен и сколько стоит лицензия.</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -14633,22 +14633,26 @@
           <t>process.note</t>
         </is>
       </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>Pricing is set individually, based on your needs.</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr"/>
+      <c r="D204" s="9" t="inlineStr">
+        <is>
+          <t>Implementation packages with fixed prices are below. We confirm the right one together on the call.</t>
+        </is>
+      </c>
+      <c r="E204" s="9" t="inlineStr">
+        <is>
+          <t>დანერგვის პაკეტები ფიქსირებული ფასით ქვემოთაა. რომელი გჭირდება, ზარზე ერთად დავაზუსტებთ.</t>
+        </is>
+      </c>
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>Пакеты внедрения с фиксированной ценой ниже. Какой подходит, уточним вместе на звонке.</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16025,10 +16029,4966 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>pk.title</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
+        <is>
+          <t>Choose where to start</t>
+        </is>
+      </c>
+      <c r="E238" s="9" t="inlineStr">
+        <is>
+          <t>აირჩიე, საიდან დაიწყო</t>
+        </is>
+      </c>
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>Выберите, с чего начать</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>pk.sub</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>Fixed price, fixed timeline. Start with a small package and add only what you actually need.</t>
+        </is>
+      </c>
+      <c r="E239" s="9" t="inlineStr">
+        <is>
+          <t>ფიქსირებული ფასი და ვადა. იწყებ პატარა პაკეტით და ამატებ მხოლოდ იმას, რაც ნამდვილად გჭირდება.</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>Фиксированная цена и срок. Начинаете с небольшого пакета и добавляете только то, что действительно нужно.</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>pk.popular</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="inlineStr">
+        <is>
+          <t>Most popular</t>
+        </is>
+      </c>
+      <c r="E240" s="9" t="inlineStr">
+        <is>
+          <t>ყველაზე ხშირად ირჩევენ</t>
+        </is>
+      </c>
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>Выбирают чаще всего</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>pk.once</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>One-time · fixed price</t>
+        </is>
+      </c>
+      <c r="E241" s="9" t="inlineStr">
+        <is>
+          <t>ერთჯერადად · ფიქსირებული ფასი</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>Разово · фиксированная цена</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>pk.days</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="inlineStr">
+        <is>
+          <t>working days</t>
+        </is>
+      </c>
+      <c r="E242" s="9" t="inlineStr">
+        <is>
+          <t>სამუშაო დღე</t>
+        </is>
+      </c>
+      <c r="F242" s="9" t="inlineStr">
+        <is>
+          <t>рабочих дней</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>pk.more</t>
+        </is>
+      </c>
+      <c r="D243" s="9" t="inlineStr">
+        <is>
+          <t>Show everything included</t>
+        </is>
+      </c>
+      <c r="E243" s="9" t="inlineStr">
+        <is>
+          <t>ყველა პუნქტის ნახვა</t>
+        </is>
+      </c>
+      <c r="F243" s="9" t="inlineStr">
+        <is>
+          <t>Показать всё, что входит</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>pk.less</t>
+        </is>
+      </c>
+      <c r="D244" s="9" t="inlineStr">
+        <is>
+          <t>Show less</t>
+        </is>
+      </c>
+      <c r="E244" s="9" t="inlineStr">
+        <is>
+          <t>დაკეცვა</t>
+        </is>
+      </c>
+      <c r="F244" s="9" t="inlineStr">
+        <is>
+          <t>Свернуть</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>pk.choose</t>
+        </is>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>Choose this package</t>
+        </is>
+      </c>
+      <c r="E245" s="9" t="inlineStr">
+        <is>
+          <t>ამ პაკეტის არჩევა</t>
+        </is>
+      </c>
+      <c r="F245" s="9" t="inlineStr">
+        <is>
+          <t>Выбрать этот пакет</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H245" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>pk.chosen</t>
+        </is>
+      </c>
+      <c r="D246" s="9" t="inlineStr">
+        <is>
+          <t>Selected</t>
+        </is>
+      </c>
+      <c r="E246" s="9" t="inlineStr">
+        <is>
+          <t>არჩეულია</t>
+        </is>
+      </c>
+      <c r="F246" s="9" t="inlineStr">
+        <is>
+          <t>Выбран</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>pk.trust.1</t>
+        </is>
+      </c>
+      <c r="D247" s="9" t="inlineStr">
+        <is>
+          <t>Fixed price, no change orders inside the scope</t>
+        </is>
+      </c>
+      <c r="E247" s="9" t="inlineStr">
+        <is>
+          <t>ფასი ფიქსირებულია, დამატებითი ხარჯების გარეშე</t>
+        </is>
+      </c>
+      <c r="F247" s="9" t="inlineStr">
+        <is>
+          <t>Цена фиксирована, без доплат внутри объёма</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>pk.trust.2</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>3 days to review, defects fixed at no cost</t>
+        </is>
+      </c>
+      <c r="E248" s="9" t="inlineStr">
+        <is>
+          <t>3 დღე ჩასაბარებლად, ხარვეზებს უფასოდ ვასწორებთ</t>
+        </is>
+      </c>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>3 дня на приёмку, недочёты исправляем бесплатно</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>pk.trust.3</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="inlineStr">
+        <is>
+          <t>The CRM, the account and the data are yours</t>
+        </is>
+      </c>
+      <c r="E249" s="9" t="inlineStr">
+        <is>
+          <t>CRM, ანგარიში და მონაცემები შენია</t>
+        </is>
+      </c>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>CRM, аккаунт и данные принадлежат вам</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>pk.trust.4</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
+        <is>
+          <t>Training and documentation in every package</t>
+        </is>
+      </c>
+      <c r="E250" s="9" t="inlineStr">
+        <is>
+          <t>ტრენინგი და დოკუმენტაცია ყველა პაკეტში</t>
+        </is>
+      </c>
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>Обучение и документация в каждом пакете</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>pk.note</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>Prices are in EUR, excluding 18% VAT and the CRM licence. You pay the licence directly to the vendor.</t>
+        </is>
+      </c>
+      <c r="E251" s="9" t="inlineStr">
+        <is>
+          <t>ფასები ევროშია, დღგ-ს (18%) და CRM-ის ლიცენზიის გარეშე. ლიცენზიას პირდაპირ მწარმოებელს უხდი.</t>
+        </is>
+      </c>
+      <c r="F251" s="9" t="inlineStr">
+        <is>
+          <t>Цены в евро, без НДС (18%) и лицензии CRM. Лицензию вы оплачиваете напрямую производителю.</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>ao.title</t>
+        </is>
+      </c>
+      <c r="D252" s="9" t="inlineStr">
+        <is>
+          <t>Add-ons</t>
+        </is>
+      </c>
+      <c r="E252" s="9" t="inlineStr">
+        <is>
+          <t>დამატებები</t>
+        </is>
+      </c>
+      <c r="F252" s="9" t="inlineStr">
+        <is>
+          <t>Дополнения</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>ao.sub</t>
+        </is>
+      </c>
+      <c r="D253" s="9" t="inlineStr">
+        <is>
+          <t>Add to any package or order as a standalone sprint. Each has a fixed price and timeline.</t>
+        </is>
+      </c>
+      <c r="E253" s="9" t="inlineStr">
+        <is>
+          <t>დაამატე ნებისმიერ პაკეტს ან შეუკვეთე ცალკე სპრინტად. თითოეულს ფიქსირებული ფასი და ვადა აქვს.</t>
+        </is>
+      </c>
+      <c r="F253" s="9" t="inlineStr">
+        <is>
+          <t>Добавьте к любому пакету или закажите отдельным спринтом. У каждого фиксированная цена и срок.</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>ao.rec</t>
+        </is>
+      </c>
+      <c r="D254" s="9" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="E254" s="9" t="inlineStr">
+        <is>
+          <t>რეკომენდებული</t>
+        </is>
+      </c>
+      <c r="F254" s="9" t="inlineStr">
+        <is>
+          <t>Рекомендуем</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>ao.all</t>
+        </is>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E255" s="9" t="inlineStr">
+        <is>
+          <t>ყველა</t>
+        </is>
+      </c>
+      <c r="F255" s="9" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>ao.days</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="E256" s="9" t="inlineStr">
+        <is>
+          <t>დღე</t>
+        </is>
+      </c>
+      <c r="F256" s="9" t="inlineStr">
+        <is>
+          <t>дн.</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>ao.add</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="E257" s="9" t="inlineStr">
+        <is>
+          <t>დამატება</t>
+        </is>
+      </c>
+      <c r="F257" s="9" t="inlineStr">
+        <is>
+          <t>Добавить</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>ao.remove</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="E258" s="9" t="inlineStr">
+        <is>
+          <t>მოშორება</t>
+        </is>
+      </c>
+      <c r="F258" s="9" t="inlineStr">
+        <is>
+          <t>Убрать</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>ao.catalog</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
+        </is>
+      </c>
+      <c r="E259" s="9" t="inlineStr">
+        <is>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
+        </is>
+      </c>
+      <c r="F259" s="9" t="inlineStr">
+        <is>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>sum.empty</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="inlineStr">
+        <is>
+          <t>Pick a package or an add-on</t>
+        </is>
+      </c>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
+          <t>აირჩიე პაკეტი ან დამატება</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>Выберите пакет или дополнение</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>sum.addons</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>add-ons</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
+          <t>დამატება</t>
+        </is>
+      </c>
+      <c r="F261" s="9" t="inlineStr">
+        <is>
+          <t>доп.</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>sum.vat</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="inlineStr">
+        <is>
+          <t>+ VAT</t>
+        </is>
+      </c>
+      <c r="E262" s="9" t="inlineStr">
+        <is>
+          <t>+ დღგ</t>
+        </is>
+      </c>
+      <c r="F262" s="9" t="inlineStr">
+        <is>
+          <t>+ НДС</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>sum.days</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>working days</t>
+        </is>
+      </c>
+      <c r="E263" s="9" t="inlineStr">
+        <is>
+          <t>სამუშაო დღე</t>
+        </is>
+      </c>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>раб. дней</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>sum.from</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
+        <is>
+          <t>Packages from €990</t>
+        </is>
+      </c>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
+          <t>პაკეტები €990-დან</t>
+        </is>
+      </c>
+      <c r="F264" s="9" t="inlineStr">
+        <is>
+          <t>Пакеты от €990</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>sum.cta</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>Request a call</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr">
+        <is>
+          <t>მოითხოვე ზარი</t>
+        </is>
+      </c>
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>Запросить звонок</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>sum.clear</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="E266" s="9" t="inlineStr">
+        <is>
+          <t>გასუფთავება</t>
+        </is>
+      </c>
+      <c r="F266" s="9" t="inlineStr">
+        <is>
+          <t>Сбросить</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>sum.picked</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>Your selection:</t>
+        </is>
+      </c>
+      <c r="E267" s="9" t="inlineStr">
+        <is>
+          <t>შენი არჩევანი:</t>
+        </is>
+      </c>
+      <c r="F267" s="9" t="inlineStr">
+        <is>
+          <t>Ваш выбор:</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.name</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="E268" s="9" t="inlineStr">
+        <is>
+          <t>სტარტი</t>
+        </is>
+      </c>
+      <c r="F268" s="9" t="inlineStr">
+        <is>
+          <t>Старт</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.title</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
+        <is>
+          <t>CRM in 5 days</t>
+        </is>
+      </c>
+      <c r="E269" s="9" t="inlineStr">
+        <is>
+          <t>CRM 5 დღეში</t>
+        </is>
+      </c>
+      <c r="F269" s="9" t="inlineStr">
+        <is>
+          <t>CRM за 5 дней</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.for</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="inlineStr">
+        <is>
+          <t>For teams moving off spreadsheets into one system.</t>
+        </is>
+      </c>
+      <c r="E270" s="9" t="inlineStr">
+        <is>
+          <t>გუნდებისთვის, რომლებიც Excel-იდან ერთ სისტემაზე გადადიან.</t>
+        </is>
+      </c>
+      <c r="F270" s="9" t="inlineStr">
+        <is>
+          <t>Для команд, которые переходят с таблиц на одну систему.</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.i1</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
+        </is>
+      </c>
+      <c r="E271" s="9" t="inlineStr">
+        <is>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
+        </is>
+      </c>
+      <c r="F271" s="9" t="inlineStr">
+        <is>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.i2</t>
+        </is>
+      </c>
+      <c r="D272" s="9" t="inlineStr">
+        <is>
+          <t>2-way email sync (Google or Microsoft 365)</t>
+        </is>
+      </c>
+      <c r="E272" s="9" t="inlineStr">
+        <is>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
+        </is>
+      </c>
+      <c r="F272" s="9" t="inlineStr">
+        <is>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.i3</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>Facebook messages right inside the CRM</t>
+        </is>
+      </c>
+      <c r="E273" s="9" t="inlineStr">
+        <is>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
+        </is>
+      </c>
+      <c r="F273" s="9" t="inlineStr">
+        <is>
+          <t>Сообщения Facebook прямо в CRM</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.i4</t>
+        </is>
+      </c>
+      <c r="D274" s="9" t="inlineStr">
+        <is>
+          <t>1 web form to capture leads</t>
+        </is>
+      </c>
+      <c r="E274" s="9" t="inlineStr">
+        <is>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
+        </is>
+      </c>
+      <c r="F274" s="9" t="inlineStr">
+        <is>
+          <t>1 веб-форма для приёма лидов</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.i5</t>
+        </is>
+      </c>
+      <c r="D275" s="9" t="inlineStr">
+        <is>
+          <t>1 sales-pipeline KPI dashboard</t>
+        </is>
+      </c>
+      <c r="E275" s="9" t="inlineStr">
+        <is>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
+        </is>
+      </c>
+      <c r="F275" s="9" t="inlineStr">
+        <is>
+          <t>Дашборд KPI воронки продаж</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>pk.starter.i6</t>
+        </is>
+      </c>
+      <c r="D276" s="9" t="inlineStr">
+        <is>
+          <t>Recorded video instructions for the team</t>
+        </is>
+      </c>
+      <c r="E276" s="9" t="inlineStr">
+        <is>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+        </is>
+      </c>
+      <c r="F276" s="9" t="inlineStr">
+        <is>
+          <t>Видеоинструкции для команды</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.name</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
+        <is>
+          <t>Essentials</t>
+        </is>
+      </c>
+      <c r="E277" s="9" t="inlineStr">
+        <is>
+          <t>ოპტიმალური</t>
+        </is>
+      </c>
+      <c r="F277" s="9" t="inlineStr">
+        <is>
+          <t>Оптимальный</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.title</t>
+        </is>
+      </c>
+      <c r="D278" s="9" t="inlineStr">
+        <is>
+          <t>Custom CRM in 15 days</t>
+        </is>
+      </c>
+      <c r="E278" s="9" t="inlineStr">
+        <is>
+          <t>შენზე მორგებული CRM 15 დღეში</t>
+        </is>
+      </c>
+      <c r="F278" s="9" t="inlineStr">
+        <is>
+          <t>CRM под вас за 15 дней</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.for</t>
+        </is>
+      </c>
+      <c r="D279" s="9" t="inlineStr">
+        <is>
+          <t>For 5-10 person sales teams tightening their pipeline.</t>
+        </is>
+      </c>
+      <c r="E279" s="9" t="inlineStr">
+        <is>
+          <t>5-10 კაციანი გაყიდვების გუნდებისთვის, რომლებსაც ძაბრის მოწესრიგება უნდათ.</t>
+        </is>
+      </c>
+      <c r="F279" s="9" t="inlineStr">
+        <is>
+          <t>Для отделов продаж из 5-10 человек, которым нужен порядок в воронке.</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.base</t>
+        </is>
+      </c>
+      <c r="D280" s="9" t="inlineStr">
+        <is>
+          <t>Everything in Starter, plus:</t>
+        </is>
+      </c>
+      <c r="E280" s="9" t="inlineStr">
+        <is>
+          <t>სტარტის ყველაფერი, პლუს:</t>
+        </is>
+      </c>
+      <c r="F280" s="9" t="inlineStr">
+        <is>
+          <t>Всё из «Старта», плюс:</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i1</t>
+        </is>
+      </c>
+      <c r="D281" s="9" t="inlineStr">
+        <is>
+          <t>Up to 15 custom fields</t>
+        </is>
+      </c>
+      <c r="E281" s="9" t="inlineStr">
+        <is>
+          <t>15-მდე დამატებითი ველი</t>
+        </is>
+      </c>
+      <c r="F281" s="9" t="inlineStr">
+        <is>
+          <t>До 15 дополнительных полей</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i2</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>Products and invoices, with your invoice template</t>
+        </is>
+      </c>
+      <c r="E282" s="9" t="inlineStr">
+        <is>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+        </is>
+      </c>
+      <c r="F282" s="9" t="inlineStr">
+        <is>
+          <t>Товары и счета с вашим шаблоном счёта</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i3</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
+        <is>
+          <t>Sales stages with rules: no skipped steps</t>
+        </is>
+      </c>
+      <c r="E283" s="9" t="inlineStr">
+        <is>
+          <t>გაყიდვის ეტაპები წესებით: ეტაპს ვერ გამოტოვებ</t>
+        </is>
+      </c>
+      <c r="F283" s="9" t="inlineStr">
+        <is>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i4</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>Phone validation (+995) and deduplication</t>
+        </is>
+      </c>
+      <c r="E284" s="9" t="inlineStr">
+        <is>
+          <t>ნომრების ვალიდაცია (+995) და დუბლიკატების მოშორება</t>
+        </is>
+      </c>
+      <c r="F284" s="9" t="inlineStr">
+        <is>
+          <t>Проверка номеров (+995) и удаление дублей</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i5</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>Meta and Google Ads leads synced automatically</t>
+        </is>
+      </c>
+      <c r="E285" s="9" t="inlineStr">
+        <is>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+        </is>
+      </c>
+      <c r="F285" s="9" t="inlineStr">
+        <is>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i6</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>Automatic lead assignment across managers</t>
+        </is>
+      </c>
+      <c r="E286" s="9" t="inlineStr">
+        <is>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+        </is>
+      </c>
+      <c r="F286" s="9" t="inlineStr">
+        <is>
+          <t>Автоматическое распределение лидов по менеджерам</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i7</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>Follow-up reminders</t>
+        </is>
+      </c>
+      <c r="E287" s="9" t="inlineStr">
+        <is>
+          <t>follow-up შეხსენებები</t>
+        </is>
+      </c>
+      <c r="F287" s="9" t="inlineStr">
+        <is>
+          <t>Напоминания о follow-up</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i8</t>
+        </is>
+      </c>
+      <c r="D288" s="9" t="inlineStr">
+        <is>
+          <t>Contacts and products migration</t>
+        </is>
+      </c>
+      <c r="E288" s="9" t="inlineStr">
+        <is>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+        </is>
+      </c>
+      <c r="F288" s="9" t="inlineStr">
+        <is>
+          <t>Перенос контактов и товаров</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>pk.essentials.i9</t>
+        </is>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>30-minute training, recorded</t>
+        </is>
+      </c>
+      <c r="E289" s="9" t="inlineStr">
+        <is>
+          <t>30-წუთიანი ტრენინგი, ჩაწერილი</t>
+        </is>
+      </c>
+      <c r="F289" s="9" t="inlineStr">
+        <is>
+          <t>30-минутное обучение с записью</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.name</t>
+        </is>
+      </c>
+      <c r="D290" s="9" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="E290" s="9" t="inlineStr">
+        <is>
+          <t>ზრდა</t>
+        </is>
+      </c>
+      <c r="F290" s="9" t="inlineStr">
+        <is>
+          <t>Рост</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.title</t>
+        </is>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
+        <is>
+          <t>Full sales system in 25 days</t>
+        </is>
+      </c>
+      <c r="E291" s="9" t="inlineStr">
+        <is>
+          <t>გაყიდვების სრული სისტემა 25 დღეში</t>
+        </is>
+      </c>
+      <c r="F291" s="9" t="inlineStr">
+        <is>
+          <t>Полная система продаж за 25 дней</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.for</t>
+        </is>
+      </c>
+      <c r="D292" s="9" t="inlineStr">
+        <is>
+          <t>For 15-25 person teams scaling without losing deals.</t>
+        </is>
+      </c>
+      <c r="E292" s="9" t="inlineStr">
+        <is>
+          <t>15-25 კაციანი გუნდებისთვის, რომლებიც იზრდებიან და გარიგებებს არ კარგავენ.</t>
+        </is>
+      </c>
+      <c r="F292" s="9" t="inlineStr">
+        <is>
+          <t>Для команд из 15-25 человек, которые растут и не теряют сделки.</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.base</t>
+        </is>
+      </c>
+      <c r="D293" s="9" t="inlineStr">
+        <is>
+          <t>Everything in Essentials, plus:</t>
+        </is>
+      </c>
+      <c r="E293" s="9" t="inlineStr">
+        <is>
+          <t>ოპტიმალურის ყველაფერი, პლუს:</t>
+        </is>
+      </c>
+      <c r="F293" s="9" t="inlineStr">
+        <is>
+          <t>Всё из «Оптимального», плюс:</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i1</t>
+        </is>
+      </c>
+      <c r="D294" s="9" t="inlineStr">
+        <is>
+          <t>Up to 3 additional modules</t>
+        </is>
+      </c>
+      <c r="E294" s="9" t="inlineStr">
+        <is>
+          <t>3-მდე დამატებითი მოდული</t>
+        </is>
+      </c>
+      <c r="F294" s="9" t="inlineStr">
+        <is>
+          <t>До 3 дополнительных модулей</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i2</t>
+        </is>
+      </c>
+      <c r="D295" s="9" t="inlineStr">
+        <is>
+          <t>Up to 5 no-code automations</t>
+        </is>
+      </c>
+      <c r="E295" s="9" t="inlineStr">
+        <is>
+          <t>5-მდე ავტომატიზაცია</t>
+        </is>
+      </c>
+      <c r="F295" s="9" t="inlineStr">
+        <is>
+          <t>До 5 автоматизаций</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i3</t>
+        </is>
+      </c>
+      <c r="D296" s="9" t="inlineStr">
+        <is>
+          <t>Up to 3 automations with custom functions</t>
+        </is>
+      </c>
+      <c r="E296" s="9" t="inlineStr">
+        <is>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+        </is>
+      </c>
+      <c r="F296" s="9" t="inlineStr">
+        <is>
+          <t>До 3 автоматизаций с custom-функциями</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i4</t>
+        </is>
+      </c>
+      <c r="D297" s="9" t="inlineStr">
+        <is>
+          <t>Telephony: GEONET or another cloud PBX</t>
+        </is>
+      </c>
+      <c r="E297" s="9" t="inlineStr">
+        <is>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+        </is>
+      </c>
+      <c r="F297" s="9" t="inlineStr">
+        <is>
+          <t>Телефония: GEONET или другая облачная АТС</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i5</t>
+        </is>
+      </c>
+      <c r="D298" s="9" t="inlineStr">
+        <is>
+          <t>Call processing workflow in the CRM</t>
+        </is>
+      </c>
+      <c r="E298" s="9" t="inlineStr">
+        <is>
+          <t>ზარების დამუშავება CRM-ში</t>
+        </is>
+      </c>
+      <c r="F298" s="9" t="inlineStr">
+        <is>
+          <t>Обработка звонков в CRM</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i6</t>
+        </is>
+      </c>
+      <c r="D299" s="9" t="inlineStr">
+        <is>
+          <t>Website form + secure webhook</t>
+        </is>
+      </c>
+      <c r="E299" s="9" t="inlineStr">
+        <is>
+          <t>საიტის ფორმა + დაცული webhook</t>
+        </is>
+      </c>
+      <c r="F299" s="9" t="inlineStr">
+        <is>
+          <t>Форма сайта + защищённый webhook</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i7</t>
+        </is>
+      </c>
+      <c r="D300" s="9" t="inlineStr">
+        <is>
+          <t>Up to 10 reports</t>
+        </is>
+      </c>
+      <c r="E300" s="9" t="inlineStr">
+        <is>
+          <t>10-მდე რეპორტი</t>
+        </is>
+      </c>
+      <c r="F300" s="9" t="inlineStr">
+        <is>
+          <t>До 10 отчётов</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i8</t>
+        </is>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>AI: Claude connected to your CRM</t>
+        </is>
+      </c>
+      <c r="E301" s="9" t="inlineStr">
+        <is>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+        </is>
+      </c>
+      <c r="F301" s="9" t="inlineStr">
+        <is>
+          <t>AI: Claude, подключённый к вашей CRM</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>Pk</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>pk.growth.i9</t>
+        </is>
+      </c>
+      <c r="D302" s="9" t="inlineStr">
+        <is>
+          <t>60-minute training, recorded</t>
+        </is>
+      </c>
+      <c r="E302" s="9" t="inlineStr">
+        <is>
+          <t>60-წუთიანი ტრენინგი, ჩაწერილი</t>
+        </is>
+      </c>
+      <c r="F302" s="9" t="inlineStr">
+        <is>
+          <t>60-минутное обучение с записью</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.data</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
+        <is>
+          <t>Data foundation</t>
+        </is>
+      </c>
+      <c r="E303" s="9" t="inlineStr">
+        <is>
+          <t>მონაცემები</t>
+        </is>
+      </c>
+      <c r="F303" s="9" t="inlineStr">
+        <is>
+          <t>Данные</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.sales</t>
+        </is>
+      </c>
+      <c r="D304" s="9" t="inlineStr">
+        <is>
+          <t>Sales automation</t>
+        </is>
+      </c>
+      <c r="E304" s="9" t="inlineStr">
+        <is>
+          <t>გაყიდვების ავტომატიზაცია</t>
+        </is>
+      </c>
+      <c r="F304" s="9" t="inlineStr">
+        <is>
+          <t>Автоматизация продаж</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.comms</t>
+        </is>
+      </c>
+      <c r="D305" s="9" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="E305" s="9" t="inlineStr">
+        <is>
+          <t>კომუნიკაცია</t>
+        </is>
+      </c>
+      <c r="F305" s="9" t="inlineStr">
+        <is>
+          <t>Коммуникации</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.mkt</t>
+        </is>
+      </c>
+      <c r="D306" s="9" t="inlineStr">
+        <is>
+          <t>Marketing &amp; growth</t>
+        </is>
+      </c>
+      <c r="E306" s="9" t="inlineStr">
+        <is>
+          <t>მარკეტინგი</t>
+        </is>
+      </c>
+      <c r="F306" s="9" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.fin</t>
+        </is>
+      </c>
+      <c r="D307" s="9" t="inlineStr">
+        <is>
+          <t>Fintech &amp; accounting</t>
+        </is>
+      </c>
+      <c r="E307" s="9" t="inlineStr">
+        <is>
+          <t>ფინანსები და ბანკები</t>
+        </is>
+      </c>
+      <c r="F307" s="9" t="inlineStr">
+        <is>
+          <t>Финансы и банки</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.cx</t>
+        </is>
+      </c>
+      <c r="D308" s="9" t="inlineStr">
+        <is>
+          <t>Customer experience</t>
+        </is>
+      </c>
+      <c r="E308" s="9" t="inlineStr">
+        <is>
+          <t>მომხმარებლის მომსახურება</t>
+        </is>
+      </c>
+      <c r="F308" s="9" t="inlineStr">
+        <is>
+          <t>Клиентский сервис</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ai</t>
+        </is>
+      </c>
+      <c r="D309" s="9" t="inlineStr">
+        <is>
+          <t>AI &amp; automation</t>
+        </is>
+      </c>
+      <c r="E309" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F309" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ind</t>
+        </is>
+      </c>
+      <c r="D310" s="9" t="inlineStr">
+        <is>
+          <t>Industry solutions</t>
+        </is>
+      </c>
+      <c r="E310" s="9" t="inlineStr">
+        <is>
+          <t>დარგობრივი</t>
+        </is>
+      </c>
+      <c r="F310" s="9" t="inlineStr">
+        <is>
+          <t>Отраслевые</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ops</t>
+        </is>
+      </c>
+      <c r="D311" s="9" t="inlineStr">
+        <is>
+          <t>Operations &amp; ERP</t>
+        </is>
+      </c>
+      <c r="E311" s="9" t="inlineStr">
+        <is>
+          <t>ოპერაციები და ERP</t>
+        </is>
+      </c>
+      <c r="F311" s="9" t="inlineStr">
+        <is>
+          <t>Операции и ERP</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>ao.1</t>
+        </is>
+      </c>
+      <c r="D312" s="9" t="inlineStr">
+        <is>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
+        </is>
+      </c>
+      <c r="E312" s="9" t="inlineStr">
+        <is>
+          <t>ნომრების ვალიდაცია (+995) და დუბლიკატები</t>
+        </is>
+      </c>
+      <c r="F312" s="9" t="inlineStr">
+        <is>
+          <t>Проверка номеров (+995) и дубли</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>ao.2</t>
+        </is>
+      </c>
+      <c r="D313" s="9" t="inlineStr">
+        <is>
+          <t>Legacy spreadsheet → CRM migration</t>
+        </is>
+      </c>
+      <c r="E313" s="9" t="inlineStr">
+        <is>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+        </is>
+      </c>
+      <c r="F313" s="9" t="inlineStr">
+        <is>
+          <t>Перенос таблиц Excel в CRM</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H313" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>ao.3</t>
+        </is>
+      </c>
+      <c r="D314" s="9" t="inlineStr">
+        <is>
+          <t>Property stock database migration</t>
+        </is>
+      </c>
+      <c r="E314" s="9" t="inlineStr">
+        <is>
+          <t>ქონების/ობიექტების ბაზის გადმოტანა</t>
+        </is>
+      </c>
+      <c r="F314" s="9" t="inlineStr">
+        <is>
+          <t>Перенос базы объектов недвижимости</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>ao.4</t>
+        </is>
+      </c>
+      <c r="D315" s="9" t="inlineStr">
+        <is>
+          <t>Automated lead routing (round-robin)</t>
+        </is>
+      </c>
+      <c r="E315" s="9" t="inlineStr">
+        <is>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+        </is>
+      </c>
+      <c r="F315" s="9" t="inlineStr">
+        <is>
+          <t>Автораспределение лидов (round-robin)</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>ao.5</t>
+        </is>
+      </c>
+      <c r="D316" s="9" t="inlineStr">
+        <is>
+          <t>Enforced sales stage blueprint</t>
+        </is>
+      </c>
+      <c r="E316" s="9" t="inlineStr">
+        <is>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+        </is>
+      </c>
+      <c r="F316" s="9" t="inlineStr">
+        <is>
+          <t>Этапы продаж с правилами (Blueprint)</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>ao.6</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
+        <is>
+          <t>Follow-up reminders &amp; alerts</t>
+        </is>
+      </c>
+      <c r="E317" s="9" t="inlineStr">
+        <is>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
+        </is>
+      </c>
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>Напоминания и уведомления о follow-up</t>
+        </is>
+      </c>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>ao.7</t>
+        </is>
+      </c>
+      <c r="D318" s="9" t="inlineStr">
+        <is>
+          <t>One-click agreement PDF generator</t>
+        </is>
+      </c>
+      <c r="E318" s="9" t="inlineStr">
+        <is>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+        </is>
+      </c>
+      <c r="F318" s="9" t="inlineStr">
+        <is>
+          <t>PDF договора в один клик</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H318" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>ao.8</t>
+        </is>
+      </c>
+      <c r="D319" s="9" t="inlineStr">
+        <is>
+          <t>First-response SLA tracker</t>
+        </is>
+      </c>
+      <c r="E319" s="9" t="inlineStr">
+        <is>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+        </is>
+      </c>
+      <c r="F319" s="9" t="inlineStr">
+        <is>
+          <t>Контроль времени первого ответа (SLA)</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H319" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>ao.9</t>
+        </is>
+      </c>
+      <c r="D320" s="9" t="inlineStr">
+        <is>
+          <t>Broker commission tracking</t>
+        </is>
+      </c>
+      <c r="E320" s="9" t="inlineStr">
+        <is>
+          <t>ბროკერების საკომისიოს აღრიცხვა</t>
+        </is>
+      </c>
+      <c r="F320" s="9" t="inlineStr">
+        <is>
+          <t>Учёт комиссий брокеров</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H320" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>ao.10</t>
+        </is>
+      </c>
+      <c r="D321" s="9" t="inlineStr">
+        <is>
+          <t>Cloud telephony integration (GEONET)</t>
+        </is>
+      </c>
+      <c r="E321" s="9" t="inlineStr">
+        <is>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+        </is>
+      </c>
+      <c r="F321" s="9" t="inlineStr">
+        <is>
+          <t>Интеграция телефонии (GEONET)</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H321" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>ao.11</t>
+        </is>
+      </c>
+      <c r="D322" s="9" t="inlineStr">
+        <is>
+          <t>WhatsApp Business integration</t>
+        </is>
+      </c>
+      <c r="E322" s="9" t="inlineStr">
+        <is>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
+        </is>
+      </c>
+      <c r="F322" s="9" t="inlineStr">
+        <is>
+          <t>Интеграция WhatsApp Business</t>
+        </is>
+      </c>
+      <c r="G322" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H322" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>ao.12</t>
+        </is>
+      </c>
+      <c r="D323" s="9" t="inlineStr">
+        <is>
+          <t>Email + calendar 2-way sync</t>
+        </is>
+      </c>
+      <c r="E323" s="9" t="inlineStr">
+        <is>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+        </is>
+      </c>
+      <c r="F323" s="9" t="inlineStr">
+        <is>
+          <t>Двусторонняя синхронизация почты и календаря</t>
+        </is>
+      </c>
+      <c r="G323" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>ao.13</t>
+        </is>
+      </c>
+      <c r="D324" s="9" t="inlineStr">
+        <is>
+          <t>Missed-call recovery &amp; SMS callback</t>
+        </is>
+      </c>
+      <c r="E324" s="9" t="inlineStr">
+        <is>
+          <t>გამოტოვებული ზარის აღდგენა და SMS</t>
+        </is>
+      </c>
+      <c r="F324" s="9" t="inlineStr">
+        <is>
+          <t>Возврат пропущенных звонков и SMS</t>
+        </is>
+      </c>
+      <c r="G324" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H324" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>ao.14</t>
+        </is>
+      </c>
+      <c r="D325" s="9" t="inlineStr">
+        <is>
+          <t>Messaging bot lead capture webhook</t>
+        </is>
+      </c>
+      <c r="E325" s="9" t="inlineStr">
+        <is>
+          <t>ჩატბოტის ლიდები პირდაპირ CRM-ში</t>
+        </is>
+      </c>
+      <c r="F325" s="9" t="inlineStr">
+        <is>
+          <t>Лиды из чат-бота сразу в CRM</t>
+        </is>
+      </c>
+      <c r="G325" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H325" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>ao.15</t>
+        </is>
+      </c>
+      <c r="D326" s="9" t="inlineStr">
+        <is>
+          <t>Website lead form + webhook</t>
+        </is>
+      </c>
+      <c r="E326" s="9" t="inlineStr">
+        <is>
+          <t>საიტის ფორმა + webhook</t>
+        </is>
+      </c>
+      <c r="F326" s="9" t="inlineStr">
+        <is>
+          <t>Форма сайта + webhook</t>
+        </is>
+      </c>
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H326" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>ao.16</t>
+        </is>
+      </c>
+      <c r="D327" s="9" t="inlineStr">
+        <is>
+          <t>Lead source ROI &amp; campaign attribution</t>
+        </is>
+      </c>
+      <c r="E327" s="9" t="inlineStr">
+        <is>
+          <t>ლიდის წყაროს ROI და კამპანიების ატრიბუცია</t>
+        </is>
+      </c>
+      <c r="F327" s="9" t="inlineStr">
+        <is>
+          <t>ROI источников и атрибуция кампаний</t>
+        </is>
+      </c>
+      <c r="G327" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H327" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>ao.17</t>
+        </is>
+      </c>
+      <c r="D328" s="9" t="inlineStr">
+        <is>
+          <t>Email campaigns: account setup &amp; contact sync</t>
+        </is>
+      </c>
+      <c r="E328" s="9" t="inlineStr">
+        <is>
+          <t>იმეილ კამპანიები: ანგარიში და კონტაქტების სინქრონი</t>
+        </is>
+      </c>
+      <c r="F328" s="9" t="inlineStr">
+        <is>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
+        </is>
+      </c>
+      <c r="G328" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H328" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>ao.18</t>
+        </is>
+      </c>
+      <c r="D329" s="9" t="inlineStr">
+        <is>
+          <t>TBC/BOG bank wire deposit matching</t>
+        </is>
+      </c>
+      <c r="E329" s="9" t="inlineStr">
+        <is>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+        </is>
+      </c>
+      <c r="F329" s="9" t="inlineStr">
+        <is>
+          <t>Автосверка переводов TBC/BOG</t>
+        </is>
+      </c>
+      <c r="G329" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="inlineStr">
+        <is>
+          <t>ao.19</t>
+        </is>
+      </c>
+      <c r="D330" s="9" t="inlineStr">
+        <is>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="E330" s="9" t="inlineStr">
+        <is>
+          <t>მრავალვალუტიანი შეჯერება (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="F330" s="9" t="inlineStr">
+        <is>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="G330" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H330" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>ao.20</t>
+        </is>
+      </c>
+      <c r="D331" s="9" t="inlineStr">
+        <is>
+          <t>NBG daily exchange rate sync</t>
+        </is>
+      </c>
+      <c r="E331" s="9" t="inlineStr">
+        <is>
+          <t>ეროვნული ბანკის კურსის ყოველდღიური სინქრონი</t>
+        </is>
+      </c>
+      <c r="F331" s="9" t="inlineStr">
+        <is>
+          <t>Ежедневный курс НБГ</t>
+        </is>
+      </c>
+      <c r="G331" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>ao.21</t>
+        </is>
+      </c>
+      <c r="D332" s="9" t="inlineStr">
+        <is>
+          <t>Ambiguous payment reference fallback queue</t>
+        </is>
+      </c>
+      <c r="E332" s="9" t="inlineStr">
+        <is>
+          <t>გაურკვეველი გადარიცხვების რიგი</t>
+        </is>
+      </c>
+      <c r="F332" s="9" t="inlineStr">
+        <is>
+          <t>Очередь неопознанных платежей</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H332" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>ao.22</t>
+        </is>
+      </c>
+      <c r="D333" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic installment payment schedule</t>
+        </is>
+      </c>
+      <c r="E333" s="9" t="inlineStr">
+        <is>
+          <t>განვადების გრაფიკი</t>
+        </is>
+      </c>
+      <c r="F333" s="9" t="inlineStr">
+        <is>
+          <t>График рассрочки</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H333" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>ao.23</t>
+        </is>
+      </c>
+      <c r="D334" s="9" t="inlineStr">
+        <is>
+          <t>Overdue debt alert &amp; SMS warning</t>
+        </is>
+      </c>
+      <c r="E334" s="9" t="inlineStr">
+        <is>
+          <t>ვადაგადაცილებული დავალიანების SMS გაფრთხილება</t>
+        </is>
+      </c>
+      <c r="F334" s="9" t="inlineStr">
+        <is>
+          <t>SMS о просроченной задолженности</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>ao.24</t>
+        </is>
+      </c>
+      <c r="D335" s="9" t="inlineStr">
+        <is>
+          <t>SMS gateway &amp; OTP verification</t>
+        </is>
+      </c>
+      <c r="E335" s="9" t="inlineStr">
+        <is>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+        </is>
+      </c>
+      <c r="F335" s="9" t="inlineStr">
+        <is>
+          <t>SMS-шлюз и OTP-верификация</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>ao.25</t>
+        </is>
+      </c>
+      <c r="D336" s="9" t="inlineStr">
+        <is>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="E336" s="9" t="inlineStr">
+        <is>
+          <t>ომნიჩენელ ტიკეტები (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="F336" s="9" t="inlineStr">
+        <is>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>ao.26</t>
+        </is>
+      </c>
+      <c r="D337" s="9" t="inlineStr">
+        <is>
+          <t>Multi-tier SLA escalation matrix</t>
+        </is>
+      </c>
+      <c r="E337" s="9" t="inlineStr">
+        <is>
+          <t>SLA-ს ესკალაციის მატრიცა</t>
+        </is>
+      </c>
+      <c r="F337" s="9" t="inlineStr">
+        <is>
+          <t>Матрица эскалации SLA</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>ao.27</t>
+        </is>
+      </c>
+      <c r="D338" s="9" t="inlineStr">
+        <is>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
+        </is>
+      </c>
+      <c r="E338" s="9" t="inlineStr">
+        <is>
+          <t>NPS/CSAT შეფასება ტიკეტის შემდეგ</t>
+        </is>
+      </c>
+      <c r="F338" s="9" t="inlineStr">
+        <is>
+          <t>Оценка NPS/CSAT после тикета</t>
+        </is>
+      </c>
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>ao.28</t>
+        </is>
+      </c>
+      <c r="D339" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic KYC intake smart form</t>
+        </is>
+      </c>
+      <c r="E339" s="9" t="inlineStr">
+        <is>
+          <t>KYC-ის ჭკვიანი ფორმა</t>
+        </is>
+      </c>
+      <c r="F339" s="9" t="inlineStr">
+        <is>
+          <t>Умная KYC-форма</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H339" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>ao.29</t>
+        </is>
+      </c>
+      <c r="D340" s="9" t="inlineStr">
+        <is>
+          <t>Warranty expiration alerts</t>
+        </is>
+      </c>
+      <c r="E340" s="9" t="inlineStr">
+        <is>
+          <t>გარანტიის ვადის შეხსენებები</t>
+        </is>
+      </c>
+      <c r="F340" s="9" t="inlineStr">
+        <is>
+          <t>Напоминания об окончании гарантии</t>
+        </is>
+      </c>
+      <c r="G340" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H340" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>ao.30</t>
+        </is>
+      </c>
+      <c r="D341" s="9" t="inlineStr">
+        <is>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
+        </is>
+      </c>
+      <c r="E341" s="9" t="inlineStr">
+        <is>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+        </is>
+      </c>
+      <c r="F341" s="9" t="inlineStr">
+        <is>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+        </is>
+      </c>
+      <c r="G341" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>ao.31</t>
+        </is>
+      </c>
+      <c r="D342" s="9" t="inlineStr">
+        <is>
+          <t>Georgian voice meeting transcription</t>
+        </is>
+      </c>
+      <c r="E342" s="9" t="inlineStr">
+        <is>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+        </is>
+      </c>
+      <c r="F342" s="9" t="inlineStr">
+        <is>
+          <t>Транскрипция встреч на грузинском</t>
+        </is>
+      </c>
+      <c r="G342" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>ao.32</t>
+        </is>
+      </c>
+      <c r="D343" s="9" t="inlineStr">
+        <is>
+          <t>Audio call sentiment extractor</t>
+        </is>
+      </c>
+      <c r="E343" s="9" t="inlineStr">
+        <is>
+          <t>ზარის განწყობის ანალიზი</t>
+        </is>
+      </c>
+      <c r="F343" s="9" t="inlineStr">
+        <is>
+          <t>Анализ тональности звонков</t>
+        </is>
+      </c>
+      <c r="G343" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H343" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>ao.33</t>
+        </is>
+      </c>
+      <c r="D344" s="9" t="inlineStr">
+        <is>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
+        </is>
+      </c>
+      <c r="E344" s="9" t="inlineStr">
+        <is>
+          <t>უძრავი ქონება: ბინების ინვენტარი, ორმაგი ჯავშნის გარეშე</t>
+        </is>
+      </c>
+      <c r="F344" s="9" t="inlineStr">
+        <is>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
+        </is>
+      </c>
+      <c r="G344" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H344" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>ao.34</t>
+        </is>
+      </c>
+      <c r="D345" s="9" t="inlineStr">
+        <is>
+          <t>Client preference proactive matcher</t>
+        </is>
+      </c>
+      <c r="E345" s="9" t="inlineStr">
+        <is>
+          <t>კლიენტის სურვილების ავტომატური მატჩი</t>
+        </is>
+      </c>
+      <c r="F345" s="9" t="inlineStr">
+        <is>
+          <t>Автоподбор по пожеланиям клиента</t>
+        </is>
+      </c>
+      <c r="G345" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H345" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>ao.35</t>
+        </is>
+      </c>
+      <c r="D346" s="9" t="inlineStr">
+        <is>
+          <t>Reservation expiration timer</t>
+        </is>
+      </c>
+      <c r="E346" s="9" t="inlineStr">
+        <is>
+          <t>ჯავშნის ვადის ტაიმერი</t>
+        </is>
+      </c>
+      <c r="F346" s="9" t="inlineStr">
+        <is>
+          <t>Таймер истечения брони</t>
+        </is>
+      </c>
+      <c r="G346" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H346" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>ao.36</t>
+        </is>
+      </c>
+      <c r="D347" s="9" t="inlineStr">
+        <is>
+          <t>Floor plan &amp; proposal PDF generator</t>
+        </is>
+      </c>
+      <c r="E347" s="9" t="inlineStr">
+        <is>
+          <t>გეგმარებისა და შეთავაზების PDF</t>
+        </is>
+      </c>
+      <c r="F347" s="9" t="inlineStr">
+        <is>
+          <t>PDF планировки и предложения</t>
+        </is>
+      </c>
+      <c r="G347" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H347" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>ao.37</t>
+        </is>
+      </c>
+      <c r="D348" s="9" t="inlineStr">
+        <is>
+          <t>Field service visit tracking + approval</t>
+        </is>
+      </c>
+      <c r="E348" s="9" t="inlineStr">
+        <is>
+          <t>საველე ვიზიტების აღრიცხვა და დადასტურება</t>
+        </is>
+      </c>
+      <c r="F348" s="9" t="inlineStr">
+        <is>
+          <t>Учёт выездов и подтверждение</t>
+        </is>
+      </c>
+      <c r="G348" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H348" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>ao.38</t>
+        </is>
+      </c>
+      <c r="D349" s="9" t="inlineStr">
+        <is>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+        </is>
+      </c>
+      <c r="E349" s="9" t="inlineStr">
+        <is>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+        </is>
+      </c>
+      <c r="F349" s="9" t="inlineStr">
+        <is>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+        </is>
+      </c>
+      <c r="G349" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H349" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>ao.39</t>
+        </is>
+      </c>
+      <c r="D350" s="9" t="inlineStr">
+        <is>
+          <t>Cold storage WMS &amp; automated billing</t>
+        </is>
+      </c>
+      <c r="E350" s="9" t="inlineStr">
+        <is>
+          <t>სამაცივრე საწყობის WMS და ბილინგი</t>
+        </is>
+      </c>
+      <c r="F350" s="9" t="inlineStr">
+        <is>
+          <t>WMS холодного склада и биллинг</t>
+        </is>
+      </c>
+      <c r="G350" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H350" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>ao.40</t>
+        </is>
+      </c>
+      <c r="D351" s="9" t="inlineStr">
+        <is>
+          <t>Construction operations &amp; budget tracker</t>
+        </is>
+      </c>
+      <c r="E351" s="9" t="inlineStr">
+        <is>
+          <t>მშენებლობის ოპერაციები და ბიუჯეტი</t>
+        </is>
+      </c>
+      <c r="F351" s="9" t="inlineStr">
+        <is>
+          <t>Стройка: операции и бюджет</t>
+        </is>
+      </c>
+      <c r="G351" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H351" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C352" s="3" t="inlineStr">
+        <is>
+          <t>ao.41</t>
+        </is>
+      </c>
+      <c r="D352" s="9" t="inlineStr">
+        <is>
+          <t>Predictive debtor call queue</t>
+        </is>
+      </c>
+      <c r="E352" s="9" t="inlineStr">
+        <is>
+          <t>მოვალეების ზარების ჭკვიანი რიგი</t>
+        </is>
+      </c>
+      <c r="F352" s="9" t="inlineStr">
+        <is>
+          <t>Умная очередь звонков должникам</t>
+        </is>
+      </c>
+      <c r="G352" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H352" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t>ao.42</t>
+        </is>
+      </c>
+      <c r="D353" s="9" t="inlineStr">
+        <is>
+          <t>Agent attendance tracker</t>
+        </is>
+      </c>
+      <c r="E353" s="9" t="inlineStr">
+        <is>
+          <t>აგენტების დასწრების აღრიცხვა</t>
+        </is>
+      </c>
+      <c r="F353" s="9" t="inlineStr">
+        <is>
+          <t>Учёт посещаемости агентов</t>
+        </is>
+      </c>
+      <c r="G353" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H353" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C354" s="3" t="inlineStr">
+        <is>
+          <t>ao.43</t>
+        </is>
+      </c>
+      <c r="D354" s="9" t="inlineStr">
+        <is>
+          <t>Round-robin appointment balancing</t>
+        </is>
+      </c>
+      <c r="E354" s="9" t="inlineStr">
+        <is>
+          <t>შეხვედრების თანაბარი განაწილება</t>
+        </is>
+      </c>
+      <c r="F354" s="9" t="inlineStr">
+        <is>
+          <t>Равномерное распределение встреч</t>
+        </is>
+      </c>
+      <c r="G354" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H354" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>ao.44</t>
+        </is>
+      </c>
+      <c r="D355" s="9" t="inlineStr">
+        <is>
+          <t>Discovery call auto-scheduling</t>
+        </is>
+      </c>
+      <c r="E355" s="9" t="inlineStr">
+        <is>
+          <t>Discovery ზარის ავტომატური დაჯავშნა</t>
+        </is>
+      </c>
+      <c r="F355" s="9" t="inlineStr">
+        <is>
+          <t>Автозапись на discovery-звонок</t>
+        </is>
+      </c>
+      <c r="G355" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H355" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H237"/>
+  <autoFilter ref="A1:H355"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H436" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H554" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$355</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$322</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$208</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$176</definedName>
@@ -6796,7 +6796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -14819,27 +14819,27 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>fit.title</t>
+          <t>pk.title</t>
         </is>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>Which CRM fits you?</t>
+          <t>Choose where to start</t>
         </is>
       </c>
       <c r="E209" s="9" t="inlineStr">
         <is>
-          <t>რომელი CRM გერგება?</t>
+          <t>აირჩიე, საიდან დაიწყო</t>
         </is>
       </c>
       <c r="F209" s="9" t="inlineStr">
         <is>
-          <t>Какая CRM вам подходит?</t>
+          <t>Выберите, с чего начать</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14861,27 +14861,27 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>fit.sub</t>
+          <t>pk.sub</t>
         </is>
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>We're an independent partner: we recommend what fits your sales, not what we'd like to sell.</t>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
         </is>
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>ვართ დამოუკიდებელი პარტნიორი: გირჩევთ იმას, რაც შენს გაყიდვებს ერგება, და არა იმას, რისი გაყიდვაც გვინდა.</t>
+          <t>ფიქსირებული ფასი და ვადა. დაიწყე პატარა პაკეტით, დანარჩენს მერე დაამატებ.</t>
         </is>
       </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
-          <t>Мы независимый партнёр: советуем то, что подходит вашим продажам, а не то, что нам выгодно продать.</t>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14903,27 +14903,27 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>fit.zoho.when</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>When your processes are complex and you want deep customisation, automations and analytics in one ecosystem.</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>როცა პროცესები რთულია და გინდა ღრმა მორგება, ავტომატიზაციები და ანალიტიკა ერთ ეკოსისტემაში.</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>Когда процессы сложные и нужна глубокая настройка, автоматизации и аналитика в одной экосистеме.</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -14945,27 +14945,27 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>fit.zoho.t1</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>Customisation</t>
+          <t>one-time, + VAT</t>
         </is>
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>მორგება</t>
+          <t>ერთჯერადად, + დღგ</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>Настройка</t>
+          <t>разово, + НДС</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -14987,27 +14987,27 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>fit.zoho.t2</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაცია</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -15029,27 +15029,27 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>fit.zoho.t3</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>ანალიტიკა</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F214" s="9" t="inlineStr">
         <is>
-          <t>Аналитика</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -15071,27 +15071,27 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>fit.pipedrive.when</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>When your sales team needs a simple, visual pipeline and a fast start.</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>როცა გაყიდვების გუნდს მარტივი, ვიზუალური გაყიდვების ძაბრი და სწრაფი სტარტი სჭირდება.</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F215" s="9" t="inlineStr">
         <is>
-          <t>Когда отделу продаж нужна простая наглядная воронка и быстрый старт.</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -15113,27 +15113,27 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>fit.pipedrive.t1</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>მარტივი</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F216" s="9" t="inlineStr">
         <is>
-          <t>Просто</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -15155,27 +15155,27 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>fit.pipedrive.t2</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>Visual pipeline</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>ვიზუალური ძაბრი</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F217" s="9" t="inlineStr">
         <is>
-          <t>Наглядная воронка</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -15197,27 +15197,27 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>fit.pipedrive.t3</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>Fast start</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
-          <t>სწრაფი სტარტი</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F218" s="9" t="inlineStr">
         <is>
-          <t>Быстрый старт</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -15239,27 +15239,27 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>fit.kommo.when</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>When most of your sales happen in chats: WhatsApp, Instagram, Facebook.</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>როცა გაყიდვები ძირითადად ჩატებში მიდის: WhatsApp, Instagram, Facebook.</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>Когда продажи идут в основном в чатах: WhatsApp, Instagram, Facebook.</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -15281,27 +15281,27 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>fit.kommo.t1</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>Chats</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>ჩატები</t>
+          <t>არასავალდებულო. დაამატე, თუ გჭირდება</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
         <is>
-          <t>Чаты</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15323,27 +15323,27 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>fit.kommo.t2</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>Messengers</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>მესენჯერები</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>Мессенджеры</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15365,27 +15365,27 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>fit.kommo.t3</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>Chatbots</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტები</t>
+          <t>ყველა დამატება კატეგორიებით</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
         <is>
-          <t>Чат-боты</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -15407,27 +15407,27 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>fit.monday.when</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>When you want to run sales and projects on the same flexible boards.</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>როცა გაყიდვები და პროექტები ერთ, მოქნილ დაფებზე გინდა მართო.</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>Когда хотите вести продажи и проекты на одних гибких досках.</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -15449,27 +15449,27 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>fit.monday.t1</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>Flexible boards</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>მოქნილი დაფები</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>Гибкие доски</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15491,27 +15491,27 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>fit.monday.t2</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>პროექტები</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>Проекты</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -15533,27 +15533,27 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>fit.monday.t3</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>გუნდური მუშაობა</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>Командная работа</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15575,27 +15575,27 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>fit.bitrix.when</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>When you need internal chat, tasks and telephony in the same place as your CRM.</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>როცა CRM-თან ერთად შიდა ჩატი, დავალებები და ტელეფონია ერთ სივრცეში გჭირდება.</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>Когда рядом с CRM нужны внутренний чат, задачи и телефония в одном месте.</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15617,27 +15617,27 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>fit.bitrix.t1</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>დავალებები</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>Задачи</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -15659,27 +15659,27 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>fit.bitrix.t2</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>Internal chat</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>შიდა ჩატი</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>Внутренний чат</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15701,27 +15701,27 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>fit.bitrix.t3</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>Telephony</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>Телефония</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15743,27 +15743,27 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>fit.odoo.when</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>When you want inventory, invoicing and accounting in the same system as sales.</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>როცა გაყიდვებთან ერთად საწყობი, ინვოისები და ბუღალტერია ერთ სისტემაში გინდა.</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>Когда вместе с продажами нужны склад, счета и бухгалтерия в одной системе.</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -15785,27 +15785,27 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>fit.odoo.t1</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>CRM + ERP</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>CRM + ERP</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>CRM + ERP</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -15827,27 +15827,27 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>fit.odoo.t2</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>საწყობი</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -15869,27 +15869,27 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>fit.odoo.t3</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>Invoicing</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>ინვოისები</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>Счета</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -15911,27 +15911,27 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>fit.foot.title</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>Not sure which one?</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>არ იცი, რომელი?</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>Не знаете, какую выбрать?</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -15953,27 +15953,27 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>fit.foot.note</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>We'll choose together in 20 minutes. We're a certified partner of these platforms; you pay the licence directly to the vendor.</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>20 წუთში ერთად შევარჩევთ. ვართ ამ პლატფორმების სერტიფიცირებული პარტნიორები; ლიცენზიას პირდაპირ მწარმოებელს უხდი.</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
         <is>
-          <t>Выберем вместе за 20 минут. Мы сертифицированный партнёр этих платформ; лицензию вы оплачиваете напрямую производителю.</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -15995,27 +15995,27 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>fit.cta</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16042,22 +16042,22 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>Choose where to start</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr">
         <is>
-          <t>Выберите, с чего начать</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16084,22 +16084,22 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Fixed price, fixed timeline. Start with a small package and add only what you actually need.</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>ფიქსირებული ფასი და ვადა. იწყებ პატარა პაკეტით და ამატებ მხოლოდ იმას, რაც ნამდვილად გჭირდება.</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>Фиксированная цена и срок. Начинаете с небольшого пакета и добавляете только то, что действительно нужно.</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16126,22 +16126,22 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>Most popular</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>Выбирают чаще всего</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16168,22 +16168,22 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>One-time · fixed price</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>ერთჯერადად · ფიქსირებული ფასი</t>
+          <t>5-10 კაციანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Разово · фиксированная цена</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16210,22 +16210,22 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>working days</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>სამუშაო დღე</t>
+          <t>სტარტის ყველაფერი, პლუს:</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>рабочих дней</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16252,22 +16252,22 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>pk.more</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Show everything included</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>ყველა პუნქტის ნახვა</t>
+          <t>სტარტის ყველაფერი</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Показать всё, что входит</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -16294,22 +16294,22 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>pk.less</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>Show less</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>დაკეცვა</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>Свернуть</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -16336,22 +16336,22 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Choose this package</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>ამ პაკეტის არჩევა</t>
+          <t>ეტაპები წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>Выбрать этот пакет</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16378,22 +16378,22 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>არჩეულია</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>Выбран</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -16420,22 +16420,22 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>pk.trust.1</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Fixed price, no change orders inside the scope</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>ფასი ფიქსირებულია, დამატებითი ხარჯების გარეშე</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Цена фиксирована, без доплат внутри объёма</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16462,22 +16462,22 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>pk.trust.2</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>3 days to review, defects fixed at no cost</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>3 დღე ჩასაბარებლად, ხარვეზებს უფასოდ ვასწორებთ</t>
+          <t>გაყიდვის ეტაპები წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>3 дня на приёмку, недочёты исправляем бесплатно</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -16504,22 +16504,22 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>pk.trust.3</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>The CRM, the account and the data are yours</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>CRM, ანგარიში და მონაცემები შენია</t>
+          <t>ნომრების ვალიდაცია (+995) და დუბლიკატების მოშორება</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>CRM, аккаунт и данные принадлежат вам</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -16546,22 +16546,22 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>pk.trust.4</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>Training and documentation in every package</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>ტრენინგი და დოკუმენტაცია ყველა პაკეტში</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>Обучение и документация в каждом пакете</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16588,22 +16588,22 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Prices are in EUR, excluding 18% VAT and the CRM licence. You pay the licence directly to the vendor.</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>ფასები ევროშია, დღგ-ს (18%) და CRM-ის ლიცენზიის გარეშე. ლიცენზიას პირდაპირ მწარმოებელს უხდი.</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>Цены в евро, без НДС (18%) и лицензии CRM. Лицензию вы оплачиваете напрямую производителю.</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -16625,27 +16625,27 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>Add-ons</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>დამატებები</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>Дополнения</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -16667,27 +16667,27 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Add to any package or order as a standalone sprint. Each has a fixed price and timeline.</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>დაამატე ნებისმიერ პაკეტს ან შეუკვეთე ცალკე სპრინტად. თითოეულს ფიქსირებული ფასი და ვადა აქვს.</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Добавьте к любому пакету или закажите отдельным спринтом. У каждого фиксированная цена и срок.</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -16709,27 +16709,27 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>ao.rec</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>რეკომენდებული</t>
+          <t>30-წუთიანი ტრენინგი, ჩაწერილი</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Рекомендуем</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -16751,27 +16751,27 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>ao.all</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>ყველა</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>Все</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -16793,27 +16793,27 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>ao.days</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>დღე</t>
+          <t>15-25 კაციანი, მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>дн.</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -16835,27 +16835,27 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>ao.add</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>დამატება</t>
+          <t>ოპტიმალურის ყველაფერი, პლუს:</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>Добавить</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -16877,27 +16877,27 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>ao.remove</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>მოშორება</t>
+          <t>ოპტიმალურის ყველაფერი</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Убрать</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -16919,27 +16919,27 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -16961,27 +16961,27 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Pick a package or an add-on</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე პაკეტი ან დამატება</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Выберите пакет или дополнение</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17003,27 +17003,27 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>add-ons</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>დამატება</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>доп.</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -17045,27 +17045,27 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>+ VAT</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>+ დღგ</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>+ НДС</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -17087,27 +17087,27 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>sum.days</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>working days</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>სამუშაო დღე</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>раб. дней</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -17129,27 +17129,27 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>sum.from</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Packages from €990</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>პაკეტები €990-დან</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>Пакеты от €990</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -17171,27 +17171,27 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>Request a call</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -17213,27 +17213,27 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>sum.clear</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>გასუფთავება</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Сбросить</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17255,27 +17255,27 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Your selection:</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>შენი არჩევანი:</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Ваш выбор:</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -17302,22 +17302,22 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>სტარტი</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>Старт</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -17344,22 +17344,22 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.title</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>CRM in 5 days</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>CRM 5 დღეში</t>
+          <t>60-წუთიანი ტრენინგი, ჩაწერილი</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>CRM за 5 дней</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -17381,27 +17381,27 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.for</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>For teams moving off spreadsheets into one system.</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>გუნდებისთვის, რომლებიც Excel-იდან ერთ სისტემაზე გადადიან.</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>Для команд, которые переходят с таблиц на одну систему.</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -17423,27 +17423,27 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -17465,27 +17465,27 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -17507,27 +17507,27 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Facebook messages right inside the CRM</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Сообщения Facebook прямо в CRM</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -17549,27 +17549,27 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>1 web form to capture leads</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>1 веб-форма для приёма лидов</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -17591,27 +17591,27 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>1 sales-pipeline KPI dashboard</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Дашборд KPI воронки продаж</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -17633,27 +17633,27 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Recorded video instructions for the team</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>Видеоинструкции для команды</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -17675,27 +17675,27 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Essentials</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალური</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>Оптимальный</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -17717,27 +17717,27 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.title</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Custom CRM in 15 days</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>შენზე მორგებული CRM 15 დღეში</t>
+          <t>ნომრების ვალიდაცია (+995) და დუბლიკატები</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>CRM под вас за 15 дней</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -17759,27 +17759,27 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.for</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>For 5-10 person sales teams tightening their pipeline.</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>5-10 კაციანი გაყიდვების გუნდებისთვის, რომლებსაც ძაბრის მოწესრიგება უნდათ.</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Для отделов продаж из 5-10 человек, которым нужен порядок в воронке.</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -17801,27 +17801,27 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter, plus:</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>სტარტის ყველაფერი, პლუს:</t>
+          <t>ქონების/ობიექტების ბაზის გადმოტანა</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта», плюс:</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -17843,27 +17843,27 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -17885,27 +17885,27 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -17927,27 +17927,27 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -17969,27 +17969,27 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>ნომრების ვალიდაცია (+995) და დუბლიკატების მოშორება</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -18011,27 +18011,27 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>ბროკერების საკომისიოს აღრიცხვა</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -18053,27 +18053,27 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -18095,27 +18095,27 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>ao.12</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>Email + calendar 2-way sync</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>Двусторонняя синхронизация почты и календаря</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -18137,27 +18137,27 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>ao.13</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Missed-call recovery &amp; SMS callback</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>გამოტოვებული ზარის აღდგენა და SMS</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Возврат пропущенных звонков и SMS</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -18179,27 +18179,27 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>ao.14</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>Messaging bot lead capture webhook</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი, ჩაწერილი</t>
+          <t>ჩატბოტის ლიდები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>Лиды из чат-бота сразу в CRM</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -18221,27 +18221,27 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>ao.cat.mkt</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Marketing &amp; growth</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>მარკეტინგი</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -18263,27 +18263,27 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.title</t>
+          <t>ao.15</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Full sales system in 25 days</t>
+          <t>Website lead form + webhook</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების სრული სისტემა 25 დღეში</t>
+          <t>საიტის ფორმა + webhook</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Полная система продаж за 25 дней</t>
+          <t>Форма сайта + webhook</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -18305,27 +18305,27 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.for</t>
+          <t>ao.16</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>For 15-25 person teams scaling without losing deals.</t>
+          <t>Lead source ROI &amp; campaign attribution</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>15-25 კაციანი გუნდებისთვის, რომლებიც იზრდებიან და გარიგებებს არ კარგავენ.</t>
+          <t>ლიდის წყაროს ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>Для команд из 15-25 человек, которые растут и не теряют сделки.</t>
+          <t>ROI источников и атрибуция кампаний</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -18347,27 +18347,27 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>ao.17</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>Email campaigns: account setup &amp; contact sync</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის ყველაფერი, პლუს:</t>
+          <t>იმეილ კამპანიები: ანგარიში და კონტაქტების სინქრონი</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -18389,27 +18389,27 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>ao.cat.fin</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>Fintech &amp; accounting</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>ფინანსები და ბანკები</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>Финансы и банки</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -18431,27 +18431,27 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>ao.19</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>მრავალვალუტიანი შეჯერება (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -18473,27 +18473,27 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>ao.20</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>NBG daily exchange rate sync</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>ეროვნული ბანკის კურსის ყოველდღიური სინქრონი</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>Ежедневный курс НБГ</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -18515,27 +18515,27 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>ao.21</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>Ambiguous payment reference fallback queue</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>გაურკვეველი გადარიცხვების რიგი</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>Очередь неопознанных платежей</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -18557,27 +18557,27 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>ao.22</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>Dynamic installment payment schedule</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>განვადების გრაფიკი</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>График рассрочки</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -18599,27 +18599,27 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>ao.23</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>Overdue debt alert &amp; SMS warning</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>ვადაგადაცილებული დავალიანების SMS გაფრთხილება</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>SMS о просроченной задолженности</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -18641,27 +18641,27 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>ao.24</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>SMS gateway &amp; OTP verification</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>SMS-шлюз и OTP-верификация</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -18683,27 +18683,27 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>ao.cat.cx</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Customer experience</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>მომხმარებლის მომსახურება</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>Клиентский сервис</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -18725,27 +18725,27 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>ao.25</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი, ჩაწერილი</t>
+          <t>ომნიჩენელ ტიკეტები (Zoho Desk)</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -18772,22 +18772,22 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>ao.26</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Multi-tier SLA escalation matrix</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>SLA-ს ესკალაციის მატრიცა</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>Матрица эскалации SLA</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -18814,22 +18814,22 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>ao.27</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>NPS/CSAT შეფასება ტიკეტის შემდეგ</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>Оценка NPS/CSAT после тикета</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -18856,22 +18856,22 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>ao.28</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Dynamic KYC intake smart form</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>KYC-ის ჭკვიანი ფორმა</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Умная KYC-форма</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -18898,22 +18898,22 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>ao.29</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Warranty expiration alerts</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>გარანტიის ვადის შეხსენებები</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Напоминания об окончании гарантии</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -18940,22 +18940,22 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>ao.cat.ai</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>AI &amp; automation</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -18982,22 +18982,22 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>ao.31</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>Georgian voice meeting transcription</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>Транскрипция встреч на грузинском</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -19024,22 +19024,22 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.32</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Audio call sentiment extractor</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ზარის განწყობის ანალიზი</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Анализ тональности звонков</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -19108,22 +19108,22 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.33</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>უძრავი ქონება: ბინების ინვენტარი, ორმაგი ჯავშნის გარეშე</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -19150,22 +19150,22 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>ao.34</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>Client preference proactive matcher</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>ნომრების ვალიდაცია (+995) და დუბლიკატები</t>
+          <t>კლიენტის სურვილების ავტომატური მატჩი</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Автоподбор по пожеланиям клиента</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -19192,22 +19192,22 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>ao.35</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>Reservation expiration timer</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>ჯავშნის ვადის ტაიმერი</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Таймер истечения брони</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -19234,22 +19234,22 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>ao.36</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Floor plan &amp; proposal PDF generator</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>ქონების/ობიექტების ბაზის გადმოტანა</t>
+          <t>გეგმარებისა და შეთავაზების PDF</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>PDF планировки и предложения</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -19276,22 +19276,22 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>ao.37</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>Field service visit tracking + approval</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>საველე ვიზიტების აღრიცხვა და დადასტურება</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>Учёт выездов и подтверждение</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -19318,22 +19318,22 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>ao.cat.ops</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>Operations &amp; ERP</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>ოპერაციები და ERP</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>Операции и ERP</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -19360,22 +19360,22 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>ao.39</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>Cold storage WMS &amp; automated billing</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>სამაცივრე საწყობის WMS და ბილინგი</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>WMS холодного склада и биллинг</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -19402,22 +19402,22 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>ao.40</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>Construction operations &amp; budget tracker</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>მშენებლობის ოპერაციები და ბიუჯეტი</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>Стройка: операции и бюджет</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -19444,22 +19444,22 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>ao.41</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>Predictive debtor call queue</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>მოვალეების ზარების ჭკვიანი რიგი</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>Умная очередь звонков должникам</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -19486,22 +19486,22 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>ao.42</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>Agent attendance tracker</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოს აღრიცხვა</t>
+          <t>აგენტების დასწრების აღრიცხვა</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>Учёт посещаемости агентов</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -19528,22 +19528,22 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>ao.43</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>Round-robin appointment balancing</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>შეხვედრების თანაბარი განაწილება</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>Равномерное распределение встреч</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -19570,22 +19570,22 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>ao.44</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>Discovery call auto-scheduling</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -19599,1396 +19599,10 @@
         </is>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B323" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C323" s="3" t="inlineStr">
-        <is>
-          <t>ao.12</t>
-        </is>
-      </c>
-      <c r="D323" s="9" t="inlineStr">
-        <is>
-          <t>Email + calendar 2-way sync</t>
-        </is>
-      </c>
-      <c r="E323" s="9" t="inlineStr">
-        <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
-        </is>
-      </c>
-      <c r="F323" s="9" t="inlineStr">
-        <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
-        </is>
-      </c>
-      <c r="G323" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H323" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B324" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C324" s="3" t="inlineStr">
-        <is>
-          <t>ao.13</t>
-        </is>
-      </c>
-      <c r="D324" s="9" t="inlineStr">
-        <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
-        </is>
-      </c>
-      <c r="E324" s="9" t="inlineStr">
-        <is>
-          <t>გამოტოვებული ზარის აღდგენა და SMS</t>
-        </is>
-      </c>
-      <c r="F324" s="9" t="inlineStr">
-        <is>
-          <t>Возврат пропущенных звонков и SMS</t>
-        </is>
-      </c>
-      <c r="G324" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H324" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B325" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C325" s="3" t="inlineStr">
-        <is>
-          <t>ao.14</t>
-        </is>
-      </c>
-      <c r="D325" s="9" t="inlineStr">
-        <is>
-          <t>Messaging bot lead capture webhook</t>
-        </is>
-      </c>
-      <c r="E325" s="9" t="inlineStr">
-        <is>
-          <t>ჩატბოტის ლიდები პირდაპირ CRM-ში</t>
-        </is>
-      </c>
-      <c r="F325" s="9" t="inlineStr">
-        <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
-        </is>
-      </c>
-      <c r="G325" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H325" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B326" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C326" s="3" t="inlineStr">
-        <is>
-          <t>ao.15</t>
-        </is>
-      </c>
-      <c r="D326" s="9" t="inlineStr">
-        <is>
-          <t>Website lead form + webhook</t>
-        </is>
-      </c>
-      <c r="E326" s="9" t="inlineStr">
-        <is>
-          <t>საიტის ფორმა + webhook</t>
-        </is>
-      </c>
-      <c r="F326" s="9" t="inlineStr">
-        <is>
-          <t>Форма сайта + webhook</t>
-        </is>
-      </c>
-      <c r="G326" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H326" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B327" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C327" s="3" t="inlineStr">
-        <is>
-          <t>ao.16</t>
-        </is>
-      </c>
-      <c r="D327" s="9" t="inlineStr">
-        <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
-        </is>
-      </c>
-      <c r="E327" s="9" t="inlineStr">
-        <is>
-          <t>ლიდის წყაროს ROI და კამპანიების ატრიბუცია</t>
-        </is>
-      </c>
-      <c r="F327" s="9" t="inlineStr">
-        <is>
-          <t>ROI источников и атрибуция кампаний</t>
-        </is>
-      </c>
-      <c r="G327" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H327" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B328" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C328" s="3" t="inlineStr">
-        <is>
-          <t>ao.17</t>
-        </is>
-      </c>
-      <c r="D328" s="9" t="inlineStr">
-        <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
-        </is>
-      </c>
-      <c r="E328" s="9" t="inlineStr">
-        <is>
-          <t>იმეილ კამპანიები: ანგარიში და კონტაქტების სინქრონი</t>
-        </is>
-      </c>
-      <c r="F328" s="9" t="inlineStr">
-        <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
-        </is>
-      </c>
-      <c r="G328" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H328" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B329" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C329" s="3" t="inlineStr">
-        <is>
-          <t>ao.18</t>
-        </is>
-      </c>
-      <c r="D329" s="9" t="inlineStr">
-        <is>
-          <t>TBC/BOG bank wire deposit matching</t>
-        </is>
-      </c>
-      <c r="E329" s="9" t="inlineStr">
-        <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
-        </is>
-      </c>
-      <c r="F329" s="9" t="inlineStr">
-        <is>
-          <t>Автосверка переводов TBC/BOG</t>
-        </is>
-      </c>
-      <c r="G329" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H329" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B330" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C330" s="3" t="inlineStr">
-        <is>
-          <t>ao.19</t>
-        </is>
-      </c>
-      <c r="D330" s="9" t="inlineStr">
-        <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
-        </is>
-      </c>
-      <c r="E330" s="9" t="inlineStr">
-        <is>
-          <t>მრავალვალუტიანი შეჯერება (GEL/USD/EUR)</t>
-        </is>
-      </c>
-      <c r="F330" s="9" t="inlineStr">
-        <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
-        </is>
-      </c>
-      <c r="G330" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H330" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B331" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C331" s="3" t="inlineStr">
-        <is>
-          <t>ao.20</t>
-        </is>
-      </c>
-      <c r="D331" s="9" t="inlineStr">
-        <is>
-          <t>NBG daily exchange rate sync</t>
-        </is>
-      </c>
-      <c r="E331" s="9" t="inlineStr">
-        <is>
-          <t>ეროვნული ბანკის კურსის ყოველდღიური სინქრონი</t>
-        </is>
-      </c>
-      <c r="F331" s="9" t="inlineStr">
-        <is>
-          <t>Ежедневный курс НБГ</t>
-        </is>
-      </c>
-      <c r="G331" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H331" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C332" s="3" t="inlineStr">
-        <is>
-          <t>ao.21</t>
-        </is>
-      </c>
-      <c r="D332" s="9" t="inlineStr">
-        <is>
-          <t>Ambiguous payment reference fallback queue</t>
-        </is>
-      </c>
-      <c r="E332" s="9" t="inlineStr">
-        <is>
-          <t>გაურკვეველი გადარიცხვების რიგი</t>
-        </is>
-      </c>
-      <c r="F332" s="9" t="inlineStr">
-        <is>
-          <t>Очередь неопознанных платежей</t>
-        </is>
-      </c>
-      <c r="G332" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H332" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B333" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C333" s="3" t="inlineStr">
-        <is>
-          <t>ao.22</t>
-        </is>
-      </c>
-      <c r="D333" s="9" t="inlineStr">
-        <is>
-          <t>Dynamic installment payment schedule</t>
-        </is>
-      </c>
-      <c r="E333" s="9" t="inlineStr">
-        <is>
-          <t>განვადების გრაფიკი</t>
-        </is>
-      </c>
-      <c r="F333" s="9" t="inlineStr">
-        <is>
-          <t>График рассрочки</t>
-        </is>
-      </c>
-      <c r="G333" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H333" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B334" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C334" s="3" t="inlineStr">
-        <is>
-          <t>ao.23</t>
-        </is>
-      </c>
-      <c r="D334" s="9" t="inlineStr">
-        <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
-        </is>
-      </c>
-      <c r="E334" s="9" t="inlineStr">
-        <is>
-          <t>ვადაგადაცილებული დავალიანების SMS გაფრთხილება</t>
-        </is>
-      </c>
-      <c r="F334" s="9" t="inlineStr">
-        <is>
-          <t>SMS о просроченной задолженности</t>
-        </is>
-      </c>
-      <c r="G334" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H334" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B335" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C335" s="3" t="inlineStr">
-        <is>
-          <t>ao.24</t>
-        </is>
-      </c>
-      <c r="D335" s="9" t="inlineStr">
-        <is>
-          <t>SMS gateway &amp; OTP verification</t>
-        </is>
-      </c>
-      <c r="E335" s="9" t="inlineStr">
-        <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
-        </is>
-      </c>
-      <c r="F335" s="9" t="inlineStr">
-        <is>
-          <t>SMS-шлюз и OTP-верификация</t>
-        </is>
-      </c>
-      <c r="G335" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H335" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C336" s="3" t="inlineStr">
-        <is>
-          <t>ao.25</t>
-        </is>
-      </c>
-      <c r="D336" s="9" t="inlineStr">
-        <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
-        </is>
-      </c>
-      <c r="E336" s="9" t="inlineStr">
-        <is>
-          <t>ომნიჩენელ ტიკეტები (Zoho Desk)</t>
-        </is>
-      </c>
-      <c r="F336" s="9" t="inlineStr">
-        <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
-        </is>
-      </c>
-      <c r="G336" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H336" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B337" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C337" s="3" t="inlineStr">
-        <is>
-          <t>ao.26</t>
-        </is>
-      </c>
-      <c r="D337" s="9" t="inlineStr">
-        <is>
-          <t>Multi-tier SLA escalation matrix</t>
-        </is>
-      </c>
-      <c r="E337" s="9" t="inlineStr">
-        <is>
-          <t>SLA-ს ესკალაციის მატრიცა</t>
-        </is>
-      </c>
-      <c r="F337" s="9" t="inlineStr">
-        <is>
-          <t>Матрица эскалации SLA</t>
-        </is>
-      </c>
-      <c r="G337" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H337" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B338" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C338" s="3" t="inlineStr">
-        <is>
-          <t>ao.27</t>
-        </is>
-      </c>
-      <c r="D338" s="9" t="inlineStr">
-        <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
-        </is>
-      </c>
-      <c r="E338" s="9" t="inlineStr">
-        <is>
-          <t>NPS/CSAT შეფასება ტიკეტის შემდეგ</t>
-        </is>
-      </c>
-      <c r="F338" s="9" t="inlineStr">
-        <is>
-          <t>Оценка NPS/CSAT после тикета</t>
-        </is>
-      </c>
-      <c r="G338" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H338" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B339" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C339" s="3" t="inlineStr">
-        <is>
-          <t>ao.28</t>
-        </is>
-      </c>
-      <c r="D339" s="9" t="inlineStr">
-        <is>
-          <t>Dynamic KYC intake smart form</t>
-        </is>
-      </c>
-      <c r="E339" s="9" t="inlineStr">
-        <is>
-          <t>KYC-ის ჭკვიანი ფორმა</t>
-        </is>
-      </c>
-      <c r="F339" s="9" t="inlineStr">
-        <is>
-          <t>Умная KYC-форма</t>
-        </is>
-      </c>
-      <c r="G339" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H339" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B340" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C340" s="3" t="inlineStr">
-        <is>
-          <t>ao.29</t>
-        </is>
-      </c>
-      <c r="D340" s="9" t="inlineStr">
-        <is>
-          <t>Warranty expiration alerts</t>
-        </is>
-      </c>
-      <c r="E340" s="9" t="inlineStr">
-        <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
-        </is>
-      </c>
-      <c r="F340" s="9" t="inlineStr">
-        <is>
-          <t>Напоминания об окончании гарантии</t>
-        </is>
-      </c>
-      <c r="G340" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H340" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B341" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C341" s="3" t="inlineStr">
-        <is>
-          <t>ao.30</t>
-        </is>
-      </c>
-      <c r="D341" s="9" t="inlineStr">
-        <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
-        </is>
-      </c>
-      <c r="E341" s="9" t="inlineStr">
-        <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
-        </is>
-      </c>
-      <c r="F341" s="9" t="inlineStr">
-        <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
-        </is>
-      </c>
-      <c r="G341" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H341" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B342" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C342" s="3" t="inlineStr">
-        <is>
-          <t>ao.31</t>
-        </is>
-      </c>
-      <c r="D342" s="9" t="inlineStr">
-        <is>
-          <t>Georgian voice meeting transcription</t>
-        </is>
-      </c>
-      <c r="E342" s="9" t="inlineStr">
-        <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
-        </is>
-      </c>
-      <c r="F342" s="9" t="inlineStr">
-        <is>
-          <t>Транскрипция встреч на грузинском</t>
-        </is>
-      </c>
-      <c r="G342" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H342" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B343" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C343" s="3" t="inlineStr">
-        <is>
-          <t>ao.32</t>
-        </is>
-      </c>
-      <c r="D343" s="9" t="inlineStr">
-        <is>
-          <t>Audio call sentiment extractor</t>
-        </is>
-      </c>
-      <c r="E343" s="9" t="inlineStr">
-        <is>
-          <t>ზარის განწყობის ანალიზი</t>
-        </is>
-      </c>
-      <c r="F343" s="9" t="inlineStr">
-        <is>
-          <t>Анализ тональности звонков</t>
-        </is>
-      </c>
-      <c r="G343" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H343" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B344" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C344" s="3" t="inlineStr">
-        <is>
-          <t>ao.33</t>
-        </is>
-      </c>
-      <c r="D344" s="9" t="inlineStr">
-        <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
-        </is>
-      </c>
-      <c r="E344" s="9" t="inlineStr">
-        <is>
-          <t>უძრავი ქონება: ბინების ინვენტარი, ორმაგი ჯავშნის გარეშე</t>
-        </is>
-      </c>
-      <c r="F344" s="9" t="inlineStr">
-        <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
-        </is>
-      </c>
-      <c r="G344" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H344" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B345" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C345" s="3" t="inlineStr">
-        <is>
-          <t>ao.34</t>
-        </is>
-      </c>
-      <c r="D345" s="9" t="inlineStr">
-        <is>
-          <t>Client preference proactive matcher</t>
-        </is>
-      </c>
-      <c r="E345" s="9" t="inlineStr">
-        <is>
-          <t>კლიენტის სურვილების ავტომატური მატჩი</t>
-        </is>
-      </c>
-      <c r="F345" s="9" t="inlineStr">
-        <is>
-          <t>Автоподбор по пожеланиям клиента</t>
-        </is>
-      </c>
-      <c r="G345" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H345" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B346" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C346" s="3" t="inlineStr">
-        <is>
-          <t>ao.35</t>
-        </is>
-      </c>
-      <c r="D346" s="9" t="inlineStr">
-        <is>
-          <t>Reservation expiration timer</t>
-        </is>
-      </c>
-      <c r="E346" s="9" t="inlineStr">
-        <is>
-          <t>ჯავშნის ვადის ტაიმერი</t>
-        </is>
-      </c>
-      <c r="F346" s="9" t="inlineStr">
-        <is>
-          <t>Таймер истечения брони</t>
-        </is>
-      </c>
-      <c r="G346" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H346" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B347" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C347" s="3" t="inlineStr">
-        <is>
-          <t>ao.36</t>
-        </is>
-      </c>
-      <c r="D347" s="9" t="inlineStr">
-        <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
-        </is>
-      </c>
-      <c r="E347" s="9" t="inlineStr">
-        <is>
-          <t>გეგმარებისა და შეთავაზების PDF</t>
-        </is>
-      </c>
-      <c r="F347" s="9" t="inlineStr">
-        <is>
-          <t>PDF планировки и предложения</t>
-        </is>
-      </c>
-      <c r="G347" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H347" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B348" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C348" s="3" t="inlineStr">
-        <is>
-          <t>ao.37</t>
-        </is>
-      </c>
-      <c r="D348" s="9" t="inlineStr">
-        <is>
-          <t>Field service visit tracking + approval</t>
-        </is>
-      </c>
-      <c r="E348" s="9" t="inlineStr">
-        <is>
-          <t>საველე ვიზიტების აღრიცხვა და დადასტურება</t>
-        </is>
-      </c>
-      <c r="F348" s="9" t="inlineStr">
-        <is>
-          <t>Учёт выездов и подтверждение</t>
-        </is>
-      </c>
-      <c r="G348" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H348" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B349" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C349" s="3" t="inlineStr">
-        <is>
-          <t>ao.38</t>
-        </is>
-      </c>
-      <c r="D349" s="9" t="inlineStr">
-        <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
-        </is>
-      </c>
-      <c r="E349" s="9" t="inlineStr">
-        <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
-        </is>
-      </c>
-      <c r="F349" s="9" t="inlineStr">
-        <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
-        </is>
-      </c>
-      <c r="G349" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H349" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B350" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C350" s="3" t="inlineStr">
-        <is>
-          <t>ao.39</t>
-        </is>
-      </c>
-      <c r="D350" s="9" t="inlineStr">
-        <is>
-          <t>Cold storage WMS &amp; automated billing</t>
-        </is>
-      </c>
-      <c r="E350" s="9" t="inlineStr">
-        <is>
-          <t>სამაცივრე საწყობის WMS და ბილინგი</t>
-        </is>
-      </c>
-      <c r="F350" s="9" t="inlineStr">
-        <is>
-          <t>WMS холодного склада и биллинг</t>
-        </is>
-      </c>
-      <c r="G350" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H350" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B351" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C351" s="3" t="inlineStr">
-        <is>
-          <t>ao.40</t>
-        </is>
-      </c>
-      <c r="D351" s="9" t="inlineStr">
-        <is>
-          <t>Construction operations &amp; budget tracker</t>
-        </is>
-      </c>
-      <c r="E351" s="9" t="inlineStr">
-        <is>
-          <t>მშენებლობის ოპერაციები და ბიუჯეტი</t>
-        </is>
-      </c>
-      <c r="F351" s="9" t="inlineStr">
-        <is>
-          <t>Стройка: операции и бюджет</t>
-        </is>
-      </c>
-      <c r="G351" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H351" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B352" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C352" s="3" t="inlineStr">
-        <is>
-          <t>ao.41</t>
-        </is>
-      </c>
-      <c r="D352" s="9" t="inlineStr">
-        <is>
-          <t>Predictive debtor call queue</t>
-        </is>
-      </c>
-      <c r="E352" s="9" t="inlineStr">
-        <is>
-          <t>მოვალეების ზარების ჭკვიანი რიგი</t>
-        </is>
-      </c>
-      <c r="F352" s="9" t="inlineStr">
-        <is>
-          <t>Умная очередь звонков должникам</t>
-        </is>
-      </c>
-      <c r="G352" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H352" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B353" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C353" s="3" t="inlineStr">
-        <is>
-          <t>ao.42</t>
-        </is>
-      </c>
-      <c r="D353" s="9" t="inlineStr">
-        <is>
-          <t>Agent attendance tracker</t>
-        </is>
-      </c>
-      <c r="E353" s="9" t="inlineStr">
-        <is>
-          <t>აგენტების დასწრების აღრიცხვა</t>
-        </is>
-      </c>
-      <c r="F353" s="9" t="inlineStr">
-        <is>
-          <t>Учёт посещаемости агентов</t>
-        </is>
-      </c>
-      <c r="G353" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H353" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B354" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C354" s="3" t="inlineStr">
-        <is>
-          <t>ao.43</t>
-        </is>
-      </c>
-      <c r="D354" s="9" t="inlineStr">
-        <is>
-          <t>Round-robin appointment balancing</t>
-        </is>
-      </c>
-      <c r="E354" s="9" t="inlineStr">
-        <is>
-          <t>შეხვედრების თანაბარი განაწილება</t>
-        </is>
-      </c>
-      <c r="F354" s="9" t="inlineStr">
-        <is>
-          <t>Равномерное распределение встреч</t>
-        </is>
-      </c>
-      <c r="G354" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H354" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B355" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C355" s="3" t="inlineStr">
-        <is>
-          <t>ao.44</t>
-        </is>
-      </c>
-      <c r="D355" s="9" t="inlineStr">
-        <is>
-          <t>Discovery call auto-scheduling</t>
-        </is>
-      </c>
-      <c r="E355" s="9" t="inlineStr">
-        <is>
-          <t>Discovery ზარის ავტომატური დაჯავშნა</t>
-        </is>
-      </c>
-      <c r="F355" s="9" t="inlineStr">
-        <is>
-          <t>Автозапись на discovery-звонок</t>
-        </is>
-      </c>
-      <c r="G355" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H355" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H355"/>
+  <autoFilter ref="A1:H322"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H554" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H521" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -14635,17 +14635,17 @@
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>Implementation packages with fixed prices are below. We confirm the right one together on the call.</t>
+          <t>Package prices are fixed. We confirm the right one together on the call.</t>
         </is>
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>დანერგვის პაკეტები ფიქსირებული ფასით ქვემოთაა. რომელი გჭირდება, ზარზე ერთად დავაზუსტებთ.</t>
+          <t>პაკეტების ფასი ფიქსირებულია. რომელი გჭირდება, ზარზე ერთად დავაზუსტებთ.</t>
         </is>
       </c>
       <c r="F204" s="9" t="inlineStr">
         <is>
-          <t>Пакеты внедрения с фиксированной ценой ниже. Какой подходит, уточним вместе на звонке.</t>
+          <t>Цены пакетов фиксированы. Какой подходит, уточним вместе на звонке.</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -13,11 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed keys" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$322</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$208</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -4707,17 +4707,17 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Minimum engagement is €1,990 + VAT. Most first sprints land €2,000-5,000 depending on which solutions you pick. Licensing (Zoho, Monday, etc.) is billed separately by the vendor at their public prices. We tell you both numbers on the call.</t>
+          <t>The price is set individually and depends on the task: how many systems we touch, how many users there are and which integrations you need. You pay the platform licence (Zoho, monday, etc.) directly to the vendor. We give you exact numbers on the 20-minute call.</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>მინიმალური ჩართულობა შეადგენს €1,990-ს (+ დღგ). პირველი სპრინტების უმრავლესობის ღირებულება შერჩეული გადაწყვეტების მიხედვით €2,000-დან €5,000-მდე მერყეობს. პლატფორმის ლიცენზიებს (Zoho, Monday და ა.შ.) პირდაპირ მწარმოებელს უხდით მათი ოფიციალური საჯარო ტარიფებით. ორივე ციფრს ზარზე დეტალურად დაგითვლით.</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება და დამოკიდებულია ამოცანაზე: რამდენ სისტემას ვეხებით, რამდენი მომხმარებელია და რა ინტეგრაციებია საჭირო. პლატფორმის ლიცენზიას (Zoho, monday და სხვ.) პირდაპირ მწარმოებელს უხდი. ზუსტ ციფრებს 20-წუთიან ზარზე გეტყვით.</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Минимальный заказ - €1,990 + НДС. Большинство первых спринтов - €2,000-5,000 в зависимости от выбранных решений. Лицензии (Zoho, Monday и т.д.) оплачиваются отдельно напрямую вендору по его публичным ценам. Обе цифры называем на звонке.</t>
+          <t>Стоимость определяется индивидуально и зависит от задачи: сколько систем затрагиваем, сколько пользователей и какие нужны интеграции. Лицензию платформы (Zoho, monday и др.) вы оплачиваете напрямую производителю. Точные цифры назовём на 20-минутном звонке.</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr"/>
@@ -5049,17 +5049,17 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Can I pick 5 solutions and combine them?</t>
+          <t>Can you automate without replacing the systems we already use?</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>შემიძლია ავირჩიო 5 სხვადასხვა გადაწყვეტა და ერთად გავაერთიანო?</t>
+          <t>შეიძლება ავტომატიზაცია ჩემი არსებული სისტემების შეცვლის გარეშე?</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Можно выбрать 5 решений и объединить их?</t>
+          <t>Можно автоматизировать, не меняя систем, которыми мы уже пользуемся?</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr"/>
@@ -5087,17 +5087,17 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Yes, that's what the "Add to request" list is for. On the call we help you order them by sequence (what has to come first) and sprint capacity. You usually won't ship all 5 at once, but you can.</t>
+          <t>Yes, in most cases. We connect the systems you already use through APIs and integrations, so your team does not have to relearn everything. If a current tool really holds the work back, we tell you plainly.</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>რა თქმა უნდა! ღილაკი „სიაში დამატება“ სწორედ ამისთვისაა. ზარზე ერთად განვსაზღვრავთ პრიორიტეტებს - რა უნდა გაკეთდეს პირველ ეტაპზე და რა გადანაწილდეს შემდგომ სპრინტებზე. როგორც წესი, ხუთივე ერთდროულად არ ეშვება, თუმცა ტექნიკურად ეს სრულიად შესაძლებელია.</t>
+          <t>კი, უმეტეს შემთხვევაში. API-ებით და ინტეგრაციებით ვაკავშირებთ იმ სისტემებს, რომლებსაც უკვე იყენებ, ასე რომ გუნდს ყველაფრის თავიდან სწავლა არ უწევს. თუ არსებული ინსტრუმენტი ნამდვილად აფერხებს საქმეს, ამას პირდაპირ გეტყვით.</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Да, именно для этого и существует список "Добавить в запрос". На звонке мы помогаем расставить их по порядку (что должно идти первым) и по ёмкости спринта. Обычно 5 сразу не внедряют, но технически это возможно.</t>
+          <t>Да, в большинстве случаев. Мы связываем системы, которыми вы уже пользуетесь, через API и интеграции, поэтому команде не нужно всё переучивать. Если текущий инструмент действительно мешает работе, скажем об этом прямо.</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr"/>
@@ -6779,10 +6779,52 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Seo</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Unitty - CRM, AI and automation for your business</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Unitty - CRM, AI და ავტომატიზაცია ბიზნესისთვის</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>Unitty - CRM, AI и автоматизация для бизнеса</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H165"/>
+  <autoFilter ref="A1:H166"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H364" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H365" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6796,7 +6838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H322"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -10831,17 +10873,17 @@
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>How are you different from a single-CRM partner?</t>
+          <t>What is a CRM and why does my business need one?</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>რით განსხვავდებით კონკრეტული CRM-ის პარტნიორისგან?</t>
+          <t>რა არის CRM და რატომ სჭირდება ჩემს ბიზნესს?</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>Чем вы отличаетесь от партнёра одной CRM?</t>
+          <t>Что такое CRM и зачем она моему бизнесу?</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -10873,17 +10915,17 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>We're vendor-neutral. A Zoho partner offers only Zoho, a Bitrix24 partner only Bitrix24. We recommend the system that actually fits your sales, and if the best option is one we don't implement, we tell you so.</t>
+          <t>A CRM is a system that keeps clients, deals, calls, messages and tasks in one place. You see who talked to whom, what stage each deal is at and who has to do what. The result: fewer lost clients, less manual work and sales you can see in real time.</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>ვართ დამოუკიდებელი (vendor-neutral). Zoho-ს პარტნიორი გთავაზობს მხოლოდ Zoho-ს, Bitrix24-ის პარტნიორი მხოლოდ Bitrix24-ს. ჩვენ გირჩევთ იმ სისტემას, რომელიც რეალურად მოერგება შენს გაყიდვებს, და თუ საუკეთესო ვარიანტი ისეთი სისტემაა, რომელსაც ჩვენ არ ვნერგავთ, ამასაც პირდაპირ გეტყვით.</t>
+          <t>CRM არის სისტემა, სადაც ერთ ადგილას ინახება კლიენტები, გარიგებები, ზარები, მიმოწერა და დავალებები. ჩანს, ვინ ვის ესაუბრა, რა ეტაპზეა თითოეული გარიგება და ვის რა უნდა გააკეთოს. შედეგი: ნაკლები დაკარგული კლიენტი, ნაკლები ხელით მუშაობა და გაყიდვები, რომლებსაც რეალურ დროში ხედავ.</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>Мы независимы (vendor-neutral). Партнёр Zoho предлагает только Zoho, партнёр Bitrix24 - только Bitrix24. Мы советуем систему, которая действительно подходит вашим продажам, а если лучший вариант - система, которую мы не внедряем, прямо скажем об этом.</t>
+          <t>CRM - это система, где в одном месте хранятся клиенты, сделки, звонки, переписка и задачи. Видно, кто с кем общался, на каком этапе каждая сделка и кому что нужно сделать. Результат: меньше потерянных клиентов, меньше ручной работы и продажи, которые видны в реальном времени.</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -10915,17 +10957,17 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Which CRMs do you implement?</t>
+          <t>How is a CRM different from Excel or a plain client database?</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>რომელ CRM-ებს ნერგავთ?</t>
+          <t>რით განსხვავდება CRM Excel-ისგან ან ჩვეულებრივი კლიენტების ბაზისგან?</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Какие CRM вы внедряете?</t>
+          <t>Чем CRM отличается от Excel или обычной базы клиентов?</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -10957,17 +10999,17 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>We're a certified partner of Zoho, Pipedrive, Kommo, monday.com, Bitrix24 and Odoo (and also ClickUp and Manychat). On the call we tell you which one fits your team, processes and budget.</t>
+          <t>Excel and a database only store information. A CRM works: it reminds you about follow-ups, assigns leads, shows the sales pipeline and keeps the history of every call and message. When a manager leaves, the clients stay with the company.</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>ვართ Zoho-ს, Pipedrive-ის, Kommo-ს, monday.com-ის, Bitrix24-ისა და Odoo-ს სერტიფიცირებული პარტნიორი (ასევე ClickUp-ის და Manychat-ის). ზარზე გეტყვით, რომელი ერგება შენს გუნდს, პროცესებს და ბიუჯეტს.</t>
+          <t>Excel და ბაზა მხოლოდ ინახავს ინფორმაციას. CRM მუშაობს: გახსენებს follow-up-ს, ანაწილებს ლიდებს, აჩვენებს გაყიდვების ძაბრს და ინახავს ყველა ზარისა და წერილის ისტორიას. მენეჯერის წასვლისას კლიენტები კომპანიაში რჩება.</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>Мы сертифицированный партнёр Zoho, Pipedrive, Kommo, monday.com, Bitrix24 и Odoo (а также ClickUp и Manychat). На звонке скажем, какая подходит вашей команде, процессам и бюджету.</t>
+          <t>Excel и база только хранят информацию. CRM работает: напоминает о follow-up, распределяет лиды, показывает воронку продаж и хранит историю всех звонков и писем. Когда менеджер уходит, клиенты остаются в компании.</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -10999,17 +11041,17 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>What does a CRM implementation cost?</t>
+          <t>How do I choose the right CRM for my business?</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>რა ჯდება CRM-ის დანერგვა?</t>
+          <t>როგორ ავირჩიო ჩემი ბიზნესისთვის შესაფერისი CRM?</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>Сколько стоит внедрение CRM?</t>
+          <t>Как выбрать подходящую CRM для моего бизнеса?</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -11041,17 +11083,17 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Implementation packages have fixed prices: Starter €990 (5 working days), Essentials €2,990 (15 days), Growth €5,990 (25 days), add-ons from €190. VAT (18%) is added. You pay the CRM licence directly to the vendor at its official price. On the 20-minute call we tell you which package you need and what the licence costs.</t>
+          <t>The right CRM depends on your sales process, team size, channels (calls, chats, website) and budget. We are an independent partner: we look at how you work first, then recommend the system that fits it, not the one we would like to sell. That is exactly what the 20-minute call is for.</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>დანერგვის პაკეტები ფიქსირებული ფასისაა: სტარტი €990 (5 სამუშაო დღე), ოპტიმალური €2,990 (15 დღე), ზრდა €5,990 (25 დღე), დამატებები €190-დან. ფასებს ემატება დღგ (18%). CRM-ის ლიცენზიას პირდაპირ მწარმოებელს უხდი მისი ოფიციალური ფასით. 20-წუთიან ზარზე გეტყვით, რომელი პაკეტი გჭირდება და რამდენი დაჯდება ლიცენზია.</t>
+          <t>სწორი CRM დამოკიდებულია შენს გაყიდვების პროცესზე, გუნდის ზომაზე, არხებზე (ზარები, ჩატები, საიტი) და ბიუჯეტზე. ჩვენ დამოუკიდებელი პარტნიორი ვართ: ჯერ ვხედავთ, როგორ მუშაობ, მერე გირჩევთ სისტემას, რომელიც ამას ერგება, და არა იმას, რისი გაყიდვაც გვინდა. ზუსტად ამას ვაკეთებთ 20-წუთიან ზარზე.</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>Пакеты внедрения с фиксированной ценой: «Старт» €990 (5 рабочих дней), «Оптимальный» €2,990 (15 дней), «Рост» €5,990 (25 дней), дополнения от €190. Добавляется НДС (18%). Лицензию CRM вы оплачиваете напрямую производителю по официальной цене. На 20-минутном звонке скажем, какой пакет нужен и сколько стоит лицензия.</t>
+          <t>Правильная CRM зависит от вашего процесса продаж, размера команды, каналов (звонки, чаты, сайт) и бюджета. Мы независимый партнёр: сначала смотрим, как вы работаете, затем советуем систему, которая этому подходит, а не ту, которую нам выгодно продать. Именно для этого 20-минутный звонок.</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -11083,17 +11125,17 @@
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>How long does implementation take?</t>
+          <t>Which CRMs do you implement?</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>რამდენ ხანს გრძელდება დანერგვა?</t>
+          <t>რომელ CRM-ებს ნერგავთ?</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>Сколько длится внедрение?</t>
+          <t>Какие CRM вы внедряете?</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -11125,17 +11167,17 @@
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>A core CRM (sales stages, fields, data migration, team training) usually goes live in 1-2 weeks. We start with what matters most, your team adopts it, then we add automations and integrations. That keeps risk low and you see results fast.</t>
+          <t>We're a certified partner of Zoho, Pipedrive, Kommo, monday.com, Bitrix24 and Odoo (and also ClickUp and Manychat). On the call we tell you which one fits your team, processes and budget.</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>საბაზისო CRM (გაყიდვების ეტაპები, ველები, მონაცემების გადმოტანა, გუნდის ტრენინგი) როგორც წესი 1-2 კვირაში ეშვება. ვიწყებთ ყველაზე მნიშვნელოვანით, გუნდი ითვისებს და მერე ვამატებთ ავტომატიზაციებსა და ინტეგრაციებს. ასე რისკი მინიმალურია და შედეგს სწრაფად ხედავ.</t>
+          <t>ვართ Zoho-ს, Pipedrive-ის, Kommo-ს, monday.com-ის, Bitrix24-ისა და Odoo-ს სერტიფიცირებული პარტნიორი (ასევე ClickUp-ის და Manychat-ის). ზარზე გეტყვით, რომელი ერგება შენს გუნდს, პროცესებს და ბიუჯეტს.</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>Базовая CRM (этапы продаж, поля, перенос данных, обучение команды) обычно запускается за 1-2 недели. Начинаем с самого важного, команда осваивает систему, затем добавляем автоматизации и интеграции. Так риск минимален, а результат виден быстро.</t>
+          <t>Мы сертифицированный партнёр Zoho, Pipedrive, Kommo, monday.com, Bitrix24 и Odoo (а также ClickUp и Manychat). На звонке скажем, какая подходит вашей команде, процессам и бюджету.</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -11167,17 +11209,17 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Can you move our data from Excel or another CRM?</t>
+          <t>How much does a CRM implementation cost?</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>შესაძლებელია მონაცემების Excel-იდან ან სხვა CRM-იდან გადმოტანა?</t>
+          <t>რა ღირს CRM-ის დანერგვა?</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>Можете перенести данные из Excel или другой CRM?</t>
+          <t>Сколько стоит внедрение CRM?</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -11209,17 +11251,17 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Yes. We move clients, contacts, deals and history from Excel, Google Sheets or another CRM. Before the move we clean duplicates and normalise phone numbers, so the new system starts with a clean database.</t>
+          <t>Implementation packages have fixed prices: Starter €990 (5 working days), Essentials €2,990 (15 days), Growth €5,990 (25 days), add-ons from €190. VAT (18%) is added. You pay the CRM licence directly to the vendor at its official price. On the 20-minute call we tell you which package you need and what the licence costs.</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>კი. კლიენტებს, კონტაქტებს, გარიგებებს და ისტორიას გადმოვიტანთ Excel-იდან, Google Sheets-იდან ან სხვა CRM-იდან. გადმოტანამდე ვასუფთავებთ დუბლიკატებს და ვაწესრიგებთ ტელეფონის ნომრებს, რომ ახალი სისტემა სუფთა ბაზით დაიწყოს.</t>
+          <t>დანერგვის პაკეტები ფიქსირებული ფასისაა: სტარტი €990 (5 სამუშაო დღე), ოპტიმალური €2,990 (15 დღე), ზრდა €5,990 (25 დღე), დამატებები €190-დან. ფასებს ემატება დღგ (18%). CRM-ის ლიცენზიას პირდაპირ მწარმოებელს უხდი მისი ოფიციალური ფასით. 20-წუთიან ზარზე გეტყვით, რომელი პაკეტი გჭირდება და რამდენი დაჯდება ლიცენზია.</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>Да. Переносим клиентов, контакты, сделки и историю из Excel, Google Sheets или другой CRM. Перед переносом чистим дубликаты и приводим номера телефонов к единому формату, чтобы новая система стартовала с чистой базой.</t>
+          <t>Пакеты внедрения с фиксированной ценой: «Старт» €990 (5 рабочих дней), «Оптимальный» €2,990 (15 дней), «Рост» €5,990 (25 дней), дополнения от €190. Добавляется НДС (18%). Лицензию CRM вы оплачиваете напрямую производителю по официальной цене. На 20-минутном звонке скажем, какой пакет нужен и сколько стоит лицензия.</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -11251,17 +11293,17 @@
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Can the CRM connect chats, website forms and telephony?</t>
+          <t>How long does a CRM implementation take?</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>შეიძლება CRM-ს ჩატები, საიტის ფორმები და ტელეფონია მივაბა?</t>
+          <t>რამდენი ხანი სჭირდება CRM-ის დანერგვას?</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>Можно подключить к CRM чаты, формы сайта и телефонию?</t>
+          <t>Сколько времени занимает внедрение CRM?</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -11293,17 +11335,17 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Yes. WhatsApp, Instagram, Facebook Messenger, website forms, Meta ad leads and telephony (including GEONET) can all land in one CRM, so every request is in one place. On the call we confirm what connects to the CRM you choose and how.</t>
+          <t>On fixed timelines: Starter in 5 working days, Essentials in 15, Growth in 25. We start with what matters most, your team adopts it, then we add automations and integrations. That keeps the risk low and you see results fast.</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>კი. WhatsApp, Instagram, Facebook Messenger, საიტის ფორმები, Meta-ს რეკლამის ლიდები და ტელეფონია (მათ შორის GEONET) შეგვიძლია ერთ CRM-ში შევკრიბოთ, რომ ყველა მომართვა ერთ ადგილას ჩანდეს. რა და როგორ უკავშირდება შენს არჩეულ CRM-ს, ზარზე დაგიზუსტებთ.</t>
+          <t>ფიქსირებული ვადებით: სტარტი 5 სამუშაო დღეში, ოპტიმალური 15 დღეში, ზრდა 25 დღეში. ვიწყებთ ყველაზე მნიშვნელოვანით, გუნდი ითვისებს და მერე ვამატებთ ავტომატიზაციებსა და ინტეგრაციებს. ასე რისკი მინიმალურია და შედეგს სწრაფად ხედავ.</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>Да. WhatsApp, Instagram, Facebook Messenger, формы сайта, лиды из рекламы Meta и телефонию (включая GEONET) можно собрать в одной CRM, чтобы все обращения были в одном месте. Что и как подключается к выбранной CRM, уточним на звонке.</t>
+          <t>В фиксированные сроки: «Старт» за 5 рабочих дней, «Оптимальный» за 15, «Рост» за 25. Начинаем с самого важного, команда осваивает систему, затем добавляем автоматизации и интеграции. Так риск минимален, а результат виден быстро.</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -11335,17 +11377,17 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Do you work with my industry?</t>
+          <t>Can the CRM connect to our other systems?</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>მუშაობთ თუ არა ჩემს ინდუსტრიაში?</t>
+          <t>შეიძლება CRM-ის დაკავშირება სხვა სისტემებთან?</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>Работаете ли вы в моей отрасли?</t>
+          <t>Можно связать CRM с другими системами?</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -11377,17 +11419,17 @@
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>We've implemented CRM in real estate, education, logistics, hospitality, healthcare, retail, finance, construction and services. If your sales run on Excel, a shared inbox or WhatsApp chats today, we can help.</t>
+          <t>Yes. We connect the CRM to email, WhatsApp, Instagram and Facebook, website forms, Meta and Google ad leads, telephony (including GEONET), banks and accounting or ERP systems (1C, FINA). So nobody enters data twice and every request is in one place.</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>CRM დაგვინერგავს უძრავ ქონებაში, განათლებაში, ლოგისტიკაში, HoReCa სექტორში, მედიცინაში, რითეილში, ფინანსებში, მშენებლობასა და მომსახურების სფეროში. თუ დღეს გაყიდვები Excel-ში, საერთო მეილში ან WhatsApp-ის ჩატებში იმართება, შეგვიძლია დაგეხმაროთ.</t>
+          <t>კი. CRM-ს ვაკავშირებთ ელფოსტასთან, WhatsApp-თან, Instagram-თან და Facebook-თან, საიტის ფორმებთან, Meta-სა და Google-ის რეკლამის ლიდებთან, ტელეფონიასთან (მათ შორის GEONET), ბანკებთან და ბუღალტრულ ან ERP სისტემებთან (1C, FINA). ასე მონაცემები ორჯერ აღარ შეგყავს და ყველა მომართვა ერთ ადგილას ჩანს.</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>Мы внедряли CRM в недвижимости, образовании, логистике, HoReCa, медицине, ритейле, финансах, строительстве и сфере услуг. Если сегодня продажи ведутся в Excel, общей почте или чатах WhatsApp, мы поможем.</t>
+          <t>Да. Мы подключаем CRM к почте, WhatsApp, Instagram и Facebook, формам сайта, лидам из рекламы Meta и Google, телефонии (включая GEONET), банкам и бухгалтерским или ERP-системам (1C, FINA). Так данные не вводятся дважды, а все обращения видны в одном месте.</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -11419,17 +11461,17 @@
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>What if I don't know which CRM I need?</t>
+          <t>Can you move our data from Excel or another CRM?</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>რა ვქნა, თუ არ ვიცი, რომელი CRM მჭირდება?</t>
+          <t>შესაძლებელია მონაცემების Excel-იდან ან სხვა CRM-იდან გადმოტანა?</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>Что делать, если я не знаю, какая CRM мне нужна?</t>
+          <t>Можно перенести данные из Excel или другой CRM?</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -11461,17 +11503,17 @@
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>That is exactly what the 20-minute call is for. Most people arrive with "I need a CRM" and leave with a specific recommendation: which system, what the licence and implementation cost, and how long it takes.</t>
+          <t>Yes. We move clients, contacts, deals and history from Excel, Google Sheets or another CRM. Before the move we clean duplicates and normalise phone numbers, so the new system starts with a clean database.</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>20-წუთიანი ზარი სწორედ ამისთვისაა. უმეტესობა მოდის ფრაზით „CRM მჭირდება“ და ზარიდან გადის კონკრეტული რეკომენდაციით: რომელი სისტემა, რა ეღირება ლიცენზია და დანერგვა, რა ვადაში ეშვება.</t>
+          <t>კი. კლიენტებს, კონტაქტებს, გარიგებებს და ისტორიას გადმოვიტანთ Excel-იდან, Google Sheets-იდან ან სხვა CRM-იდან. გადმოტანამდე ვასუფთავებთ დუბლიკატებს და ვაწესრიგებთ ტელეფონის ნომრებს, რომ ახალი სისტემა სუფთა ბაზით დაიწყოს.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>Для этого и нужен 20-минутный звонок. Большинство приходит с фразой «мне нужна CRM» и уходит с конкретной рекомендацией: какая система, сколько стоят лицензия и внедрение, за какой срок запускается.</t>
+          <t>Да. Переносим клиентов, контакты, сделки и историю из Excel, Google Sheets или другой CRM. Перед переносом чистим дубликаты и приводим номера телефонов к единому формату, чтобы новая система стартовала с чистой базой.</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -14819,27 +14861,27 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
+          <t>seo.title</t>
         </is>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>Choose where to start</t>
+          <t>CRM selection and implementation in Georgia | Unitty</t>
         </is>
       </c>
       <c r="E209" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
+          <t>CRM-ის შერჩევა და დანერგვა საქართველოში | Unitty</t>
         </is>
       </c>
       <c r="F209" s="9" t="inlineStr">
         <is>
-          <t>Выберите, с чего начать</t>
+          <t>Подбор и внедрение CRM в Грузии | Unitty</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14866,22 +14908,22 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
+          <t>pk.title</t>
         </is>
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
+          <t>Choose where to start</t>
         </is>
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>ფიქსირებული ფასი და ვადა. დაიწყე პატარა პაკეტით, დანარჩენს მერე დაამატებ.</t>
+          <t>აირჩიე, საიდან დაიწყო</t>
         </is>
       </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
-          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
+          <t>Выберите, с чего начать</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14908,22 +14950,22 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
+          <t>pk.sub</t>
         </is>
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>Most popular</t>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
         </is>
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
+          <t>ფიქსირებული ფასი და ვადა. დაიწყე პატარა პაკეტით, დანარჩენს მერე დაამატებ.</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>Выбирают чаще всего</t>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -14950,22 +14992,22 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>one-time, + VAT</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>ერთჯერადად, + დღგ</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>разово, + НДС</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -14992,22 +15034,22 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>working days</t>
+          <t>one-time, + VAT</t>
         </is>
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>სამუშაო დღე</t>
+          <t>ერთჯერადად, + დღგ</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>рабочих дней</t>
+          <t>разово, + НДС</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -15034,22 +15076,22 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>pk.full</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>Everything included</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>სრული ჩამონათვალი</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F214" s="9" t="inlineStr">
         <is>
-          <t>Всё, что входит</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -15076,22 +15118,22 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>Choose this package</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>ამ პაკეტის არჩევა</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F215" s="9" t="inlineStr">
         <is>
-          <t>Выбрать этот пакет</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -15118,22 +15160,22 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>არჩეულია</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F216" s="9" t="inlineStr">
         <is>
-          <t>Выбран</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -15160,22 +15202,22 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F217" s="9" t="inlineStr">
         <is>
-          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -15202,22 +15244,22 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>pk.cur</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
-          <t>ვალუტა</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F218" s="9" t="inlineStr">
         <is>
-          <t>Валюта</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -15239,27 +15281,27 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>Extra features</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>დამატებითი ფუნქციები</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>Дополнительные функции</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -15286,22 +15328,22 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>Optional. Add only if you need them</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>არასავალდებულო. დაამატე, თუ გჭირდება</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
         <is>
-          <t>Необязательно. Добавьте, если нужно</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15328,22 +15370,22 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>ao.popular</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>Often added</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>ხშირად ამატებენ</t>
+          <t>არასავალდებულო. დაამატე, თუ გჭირდება</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>Часто добавляют</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15370,22 +15412,22 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>ao.more</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>All add-ons by category</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>ყველა დამატება კატეგორიებით</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
         <is>
-          <t>Все дополнения по категориям</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -15412,22 +15454,22 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
+          <t>ყველა დამატება კატეგორიებით</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -15449,27 +15491,27 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>Choose a package</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე პაკეტი</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>Выберите пакет</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15496,22 +15538,22 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>ფუნქცია</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>функц.</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -15538,22 +15580,22 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>+ VAT</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>+ დღგ</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>+ НДС</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15580,22 +15622,22 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>Request a call</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15622,22 +15664,22 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>Your selection:</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>შენი არჩევანი:</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>Ваш выбор:</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -15659,27 +15701,27 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>სტარტი</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>Старт</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15706,22 +15748,22 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.short</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>To move from Excel into a CRM</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>Чтобы перейти с Excel на CRM</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15748,22 +15790,22 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h1</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>4 core modules</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -15790,22 +15832,22 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h2</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>Email and Facebook inside the CRM</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტა და Facebook CRM-ში</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>Почта и Facebook внутри CRM</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -15832,22 +15874,22 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h3</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Lead form and KPI dashboard</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ფორმა და KPI დაფა</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>Форма лидов и дашборд KPI</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -15874,22 +15916,22 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -15916,22 +15958,22 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -15958,22 +16000,22 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>Facebook messages right inside the CRM</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
         <is>
-          <t>Сообщения Facebook прямо в CRM</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -16000,22 +16042,22 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>1 web form to capture leads</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>1 веб-форма для приёма лидов</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16042,22 +16084,22 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>1 sales-pipeline KPI dashboard</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr">
         <is>
-          <t>Дашборд KPI воронки продаж</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16084,22 +16126,22 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Recorded video instructions for the team</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>Видеоинструкции для команды</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16126,22 +16168,22 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>Essentials</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალური</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>Оптимальный</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16168,22 +16210,22 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.short</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>For a 5-10 person sales team</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>5-10 კაციანი გაყიდვების გუნდისთვის</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Для отдела продаж из 5-10 человек</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16210,22 +16252,22 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter, plus:</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>სტარტის ყველაფერი, პლუს:</t>
+          <t>5-10 კაციანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта», плюс:</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16252,22 +16294,22 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h1</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>სტარტის ყველაფერი</t>
+          <t>სტარტის ყველაფერი, პლუს:</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта»</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -16294,22 +16336,22 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h2</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads, automatically</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
+          <t>სტარტის ყველაფერი</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -16336,22 +16378,22 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h3</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Stage rules and lead assignment</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>ეტაპები წესებით და ლიდების განაწილება</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>Правила этапов и распределение лидов</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16378,22 +16420,22 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>ეტაპები წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -16420,22 +16462,22 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16462,22 +16504,22 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -16504,22 +16546,22 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>ნომრების ვალიდაცია (+995) და დუბლიკატების მოშორება</t>
+          <t>გაყიდვის ეტაპები წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -16546,22 +16588,22 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>ნომრების ვალიდაცია (+995) და დუბლიკატების მოშორება</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16588,22 +16630,22 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -16630,22 +16672,22 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -16672,22 +16714,22 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -16714,22 +16756,22 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი, ჩაწერილი</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -16756,22 +16798,22 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>30-წუთიანი ტრენინგი, ჩაწერილი</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -16798,22 +16840,22 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.short</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>For a growing 15-25 person team</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>15-25 კაციანი, მზარდი გუნდისთვის</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>Для растущей команды из 15-25 человек</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -16840,22 +16882,22 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის ყველაფერი, პლუს:</t>
+          <t>15-25 კაციანი, მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -16882,22 +16924,22 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h1</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის ყველაფერი</t>
+          <t>ოპტიმალურის ყველაფერი, პლუს:</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального»</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -16924,22 +16966,22 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h2</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Telephony and call processing</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია და ზარების დამუშავება</t>
+          <t>ოპტიმალურის ყველაფერი</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Телефония и обработка звонков</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -16966,22 +17008,22 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h3</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Automations and AI (Claude)</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და AI (Claude)</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Автоматизации и AI (Claude)</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17008,22 +17050,22 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -17050,22 +17092,22 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -17092,22 +17134,22 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -17134,22 +17176,22 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -17176,22 +17218,22 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -17218,22 +17260,22 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17260,22 +17302,22 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -17302,22 +17344,22 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -17344,22 +17386,22 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი, ჩაწერილი</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -17381,27 +17423,27 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>60-წუთიანი ტრენინგი, ჩაწერილი</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -17428,22 +17470,22 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -17470,22 +17512,22 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -17512,22 +17554,22 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -17554,22 +17596,22 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>ao.18</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG bank wire deposit matching</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Автосверка переводов TBC/BOG</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -17596,22 +17638,22 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>ao.30</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -17638,22 +17680,22 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>ao.38</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -17680,22 +17722,22 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -17722,22 +17764,22 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>ნომრების ვალიდაცია (+995) და დუბლიკატები</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -17764,22 +17806,22 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>ნომრების ვალიდაცია (+995) და დუბლიკატები</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -17806,22 +17848,22 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>ქონების/ობიექტების ბაზის გადმოტანა</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -17848,22 +17890,22 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>ქონების/ობიექტების ბაზის გადმოტანა</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -17890,22 +17932,22 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -17932,22 +17974,22 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -17974,22 +18016,22 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -18016,22 +18058,22 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოს აღრიცხვა</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -18058,22 +18100,22 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>ბროკერების საკომისიოს აღრიცხვა</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -18100,22 +18142,22 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>ao.12</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Email + calendar 2-way sync</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -18142,22 +18184,22 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>ao.13</t>
+          <t>ao.12</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
+          <t>Email + calendar 2-way sync</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარის აღდგენა და SMS</t>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Возврат пропущенных звонков и SMS</t>
+          <t>Двусторонняя синхронизация почты и календаря</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -18184,22 +18226,22 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>ao.14</t>
+          <t>ao.13</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Messaging bot lead capture webhook</t>
+          <t>Missed-call recovery &amp; SMS callback</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდები პირდაპირ CRM-ში</t>
+          <t>გამოტოვებული ზარის აღდგენა და SMS</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
+          <t>Возврат пропущенных звонков и SMS</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -18226,22 +18268,22 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>ao.14</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Messaging bot lead capture webhook</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>ჩატბოტის ლიდები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Лиды из чат-бота сразу в CRM</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -18268,22 +18310,22 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>ao.15</t>
+          <t>ao.cat.mkt</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Website lead form + webhook</t>
+          <t>Marketing &amp; growth</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + webhook</t>
+          <t>მარკეტინგი</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + webhook</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -18310,22 +18352,22 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>ao.16</t>
+          <t>ao.15</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
+          <t>Website lead form + webhook</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>ლიდის წყაროს ROI და კამპანიების ატრიბუცია</t>
+          <t>საიტის ფორმა + webhook</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>ROI источников и атрибуция кампаний</t>
+          <t>Форма сайта + webhook</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -18352,22 +18394,22 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>ao.17</t>
+          <t>ao.16</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
+          <t>Lead source ROI &amp; campaign attribution</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიში და კონტაქტების სინქრონი</t>
+          <t>ლიდის წყაროს ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
+          <t>ROI источников и атрибуция кампаний</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -18394,22 +18436,22 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>ao.17</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>Email campaigns: account setup &amp; contact sync</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>იმეილ კამპანიები: ანგარიში და კონტაქტების სინქრონი</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -18436,22 +18478,22 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>ao.19</t>
+          <t>ao.cat.fin</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+          <t>Fintech &amp; accounting</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი შეჯერება (GEL/USD/EUR)</t>
+          <t>ფინანსები და ბანკები</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+          <t>Финансы и банки</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -18478,22 +18520,22 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>ao.20</t>
+          <t>ao.19</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>NBG daily exchange rate sync</t>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის კურსის ყოველდღიური სინქრონი</t>
+          <t>მრავალვალუტიანი შეჯერება (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>Ежедневный курс НБГ</t>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -18520,22 +18562,22 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>ao.21</t>
+          <t>ao.20</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Ambiguous payment reference fallback queue</t>
+          <t>NBG daily exchange rate sync</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>გაურკვეველი გადარიცხვების რიგი</t>
+          <t>ეროვნული ბანკის კურსის ყოველდღიური სინქრონი</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Очередь неопознанных платежей</t>
+          <t>Ежедневный курс НБГ</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -18562,22 +18604,22 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>ao.22</t>
+          <t>ao.21</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>Dynamic installment payment schedule</t>
+          <t>Ambiguous payment reference fallback queue</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>განვადების გრაფიკი</t>
+          <t>გაურკვეველი გადარიცხვების რიგი</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>График рассрочки</t>
+          <t>Очередь неопознанных платежей</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -18604,22 +18646,22 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>ao.23</t>
+          <t>ao.22</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
+          <t>Dynamic installment payment schedule</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS გაფრთხილება</t>
+          <t>განვადების გრაფიკი</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>SMS о просроченной задолженности</t>
+          <t>График рассрочки</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -18646,22 +18688,22 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>ao.24</t>
+          <t>ao.23</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>SMS gateway &amp; OTP verification</t>
+          <t>Overdue debt alert &amp; SMS warning</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+          <t>ვადაგადაცილებული დავალიანების SMS გაფრთხილება</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>SMS-шлюз и OTP-верификация</t>
+          <t>SMS о просроченной задолженности</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -18688,22 +18730,22 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>ao.24</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>SMS gateway &amp; OTP verification</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>SMS-шлюз и OTP-верификация</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -18730,22 +18772,22 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>ao.25</t>
+          <t>ao.cat.cx</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
+          <t>Customer experience</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>ომნიჩენელ ტიკეტები (Zoho Desk)</t>
+          <t>მომხმარებლის მომსახურება</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
+          <t>Клиентский сервис</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -18772,22 +18814,22 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>ao.26</t>
+          <t>ao.25</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Multi-tier SLA escalation matrix</t>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>SLA-ს ესკალაციის მატრიცა</t>
+          <t>ომნიჩენელ ტიკეტები (Zoho Desk)</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Матрица эскалации SLA</t>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -18814,22 +18856,22 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>ao.27</t>
+          <t>ao.26</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
+          <t>Multi-tier SLA escalation matrix</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT შეფასება ტიკეტის შემდეგ</t>
+          <t>SLA-ს ესკალაციის მატრიცა</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Оценка NPS/CSAT после тикета</t>
+          <t>Матрица эскалации SLA</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -18856,22 +18898,22 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>ao.28</t>
+          <t>ao.27</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Dynamic KYC intake smart form</t>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის ჭკვიანი ფორმა</t>
+          <t>NPS/CSAT შეფასება ტიკეტის შემდეგ</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Умная KYC-форма</t>
+          <t>Оценка NPS/CSAT после тикета</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -18898,22 +18940,22 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>ao.29</t>
+          <t>ao.28</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Warranty expiration alerts</t>
+          <t>Dynamic KYC intake smart form</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
+          <t>KYC-ის ჭკვიანი ფორმა</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>Напоминания об окончании гарантии</t>
+          <t>Умная KYC-форма</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -18940,22 +18982,22 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.29</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Warranty expiration alerts</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>გარანტიის ვადის შეხსენებები</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Напоминания об окончании гарантии</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -18982,22 +19024,22 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>ao.31</t>
+          <t>ao.cat.ai</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Georgian voice meeting transcription</t>
+          <t>AI &amp; automation</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>Транскрипция встреч на грузинском</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -19024,22 +19066,22 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>ao.32</t>
+          <t>ao.31</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Audio call sentiment extractor</t>
+          <t>Georgian voice meeting transcription</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>ზარის განწყობის ანალიზი</t>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>Анализ тональности звонков</t>
+          <t>Транскрипция встреч на грузинском</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -19066,22 +19108,22 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ind</t>
+          <t>ao.32</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Industry solutions</t>
+          <t>Audio call sentiment extractor</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>დარგობრივი</t>
+          <t>ზარის განწყობის ანალიზი</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Отраслевые</t>
+          <t>Анализ тональности звонков</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -19108,22 +19150,22 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>ao.33</t>
+          <t>ao.cat.ind</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
+          <t>Industry solutions</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარი, ორმაგი ჯავშნის გარეშე</t>
+          <t>დარგობრივი</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
+          <t>Отраслевые</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -19150,22 +19192,22 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>ao.34</t>
+          <t>ao.33</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Client preference proactive matcher</t>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის სურვილების ავტომატური მატჩი</t>
+          <t>უძრავი ქონება: ბინების ინვენტარი, ორმაგი ჯავშნის გარეშე</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>Автоподбор по пожеланиям клиента</t>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -19192,22 +19234,22 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>ao.35</t>
+          <t>ao.34</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Reservation expiration timer</t>
+          <t>Client preference proactive matcher</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ტაიმერი</t>
+          <t>კლიენტის სურვილების ავტომატური მატჩი</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Таймер истечения брони</t>
+          <t>Автоподбор по пожеланиям клиента</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -19234,22 +19276,22 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ao.36</t>
+          <t>ao.35</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
+          <t>Reservation expiration timer</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF</t>
+          <t>ჯავშნის ვადის ტაიმერი</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>PDF планировки и предложения</t>
+          <t>Таймер истечения брони</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -19276,22 +19318,22 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>ao.37</t>
+          <t>ao.36</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Field service visit tracking + approval</t>
+          <t>Floor plan &amp; proposal PDF generator</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების აღრიცხვა და დადასტურება</t>
+          <t>გეგმარებისა და შეთავაზების PDF</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Учёт выездов и подтверждение</t>
+          <t>PDF планировки и предложения</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -19318,22 +19360,22 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.37</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Field service visit tracking + approval</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>საველე ვიზიტების აღრიცხვა და დადასტურება</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>Учёт выездов и подтверждение</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -19360,22 +19402,22 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>ao.39</t>
+          <t>ao.cat.ops</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Cold storage WMS &amp; automated billing</t>
+          <t>Operations &amp; ERP</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS და ბილინგი</t>
+          <t>ოპერაციები და ERP</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>WMS холодного склада и биллинг</t>
+          <t>Операции и ERP</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -19402,22 +19444,22 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ao.40</t>
+          <t>ao.39</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>Construction operations &amp; budget tracker</t>
+          <t>Cold storage WMS &amp; automated billing</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>მშენებლობის ოპერაციები და ბიუჯეტი</t>
+          <t>სამაცივრე საწყობის WMS და ბილინგი</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>Стройка: операции и бюджет</t>
+          <t>WMS холодного склада и биллинг</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -19444,22 +19486,22 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>ao.41</t>
+          <t>ao.40</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Predictive debtor call queue</t>
+          <t>Construction operations &amp; budget tracker</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>მოვალეების ზარების ჭკვიანი რიგი</t>
+          <t>მშენებლობის ოპერაციები და ბიუჯეტი</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Умная очередь звонков должникам</t>
+          <t>Стройка: операции и бюджет</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -19486,22 +19528,22 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ao.42</t>
+          <t>ao.41</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Agent attendance tracker</t>
+          <t>Predictive debtor call queue</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>აგენტების დასწრების აღრიცხვა</t>
+          <t>მოვალეების ზარების ჭკვიანი რიგი</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Учёт посещаемости агентов</t>
+          <t>Умная очередь звонков должникам</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -19528,22 +19570,22 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>ao.43</t>
+          <t>ao.42</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Round-robin appointment balancing</t>
+          <t>Agent attendance tracker</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>შეხვედრების თანაბარი განაწილება</t>
+          <t>აგენტების დასწრების აღრიცხვა</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Равномерное распределение встреч</t>
+          <t>Учёт посещаемости агентов</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -19570,39 +19612,81 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
+          <t>ao.43</t>
+        </is>
+      </c>
+      <c r="D322" s="9" t="inlineStr">
+        <is>
+          <t>Round-robin appointment balancing</t>
+        </is>
+      </c>
+      <c r="E322" s="9" t="inlineStr">
+        <is>
+          <t>შეხვედრების თანაბარი განაწილება</t>
+        </is>
+      </c>
+      <c r="F322" s="9" t="inlineStr">
+        <is>
+          <t>Равномерное распределение встреч</t>
+        </is>
+      </c>
+      <c r="G322" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H322" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
           <t>ao.44</t>
         </is>
       </c>
-      <c r="D322" s="9" t="inlineStr">
+      <c r="D323" s="9" t="inlineStr">
         <is>
           <t>Discovery call auto-scheduling</t>
         </is>
       </c>
-      <c r="E322" s="9" t="inlineStr">
+      <c r="E323" s="9" t="inlineStr">
         <is>
           <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
-      <c r="F322" s="9" t="inlineStr">
+      <c r="F323" s="9" t="inlineStr">
         <is>
           <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
-      <c r="G322" s="3" t="inlineStr">
+      <c r="G323" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H322" s="3" t="inlineStr">
+      <c r="H323" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H322"/>
+  <autoFilter ref="A1:H323"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H521" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H522" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19616,7 +19700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H208"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -23661,22 +23745,26 @@
           <t>faq.q1</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>How is this different from hiring a Zoho / Monday / ClickUp partner directly?</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>რით განსხვავდება ეს უშუალოდ Zoho-ს, Monday-ს ან ClickUp-ის პარტნიორის დაქირავებისგან?</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>Чем это отличается от работы напрямую с партнёром Zoho / Monday / ClickUp?</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr"/>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>What is process automation and how does it help me?</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>რა არის პროცესების ავტომატიზაცია და როგორ დამეხმარება?</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Что такое автоматизация процессов и чем она поможет?</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -23699,22 +23787,26 @@
           <t>faq.a1</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>We're vendor-neutral. Zoho partners sell Zoho, Monday partners sell Monday. We tell you honestly which platform fits your case, and if it isn't a platform we work with, we say so. The 20-minute call is where we find out which one you need.</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>ჩვენ სრულიად დამოუკიდებლები (vendor-neutral) ვართ. Zoho-ს პარტნიორი გთავაზობს მხოლოდ Zoho-ს, Monday-ს პარტნიორი - Monday-ს. ჩვენ გულწრფელად გირჩევთ იმ სისტემას, რომელიც რეალურად მოერგება შენს ბიზნესს; და თუ ისეთ ხელსაწყოზეა საუბარი, რომელთანაც არ ვმუშაობთ, პირდაპირ გეტყვით. 20-წუთიანი ზარი სწორედ იმისთვისაა, რომ გავარკვიოთ, რა გჭირდება რეალურად.</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>Мы вендор-нейтральны. Партнёр Zoho продаёт Zoho, партнёр Monday - Monday. Мы честно говорим, какая платформа подходит именно вам, и если это не та, с которой мы работаем - так и скажем. 20-минутный звонок как раз о том, чтобы это выяснить.</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr"/>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>It means handing repetitive manual work to a system: lead assignment, reminders, documents, reports, notifications. The result: fewer mistakes, faster replies to clients and a team focused on selling instead of routine.</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>ეს არის განმეორებადი, ხელით შესასრულებელი სამუშაოს გადაბარება სისტემისთვის: ლიდების განაწილება, შეხსენებები, დოკუმენტები, ანგარიშები, შეტყობინებები. შედეგი: ნაკლები შეცდომა, უფრო სწრაფი პასუხი კლიენტს და გუნდი, რომელიც გაყიდვებზეა ფოკუსირებული და არა რუტინაზე.</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Это передача повторяющейся ручной работы системе: распределение лидов, напоминания, документы, отчёты, уведомления. Результат: меньше ошибок, более быстрые ответы клиентам и команда, которая занята продажами, а не рутиной.</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -23737,22 +23829,26 @@
           <t>faq.q2</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Why only one sprint instead of a full roadmap?</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>რატომ ვიწყებთ ერთი კონკრეტული სპრინტით და არა გრძელვადიანი გეგმით?</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>Почему только один спринт, а не полная дорожная карта?</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr"/>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>Which processes should we automate first?</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>რომელი პროცესები ავტომატიზირდეს პირველ რიგში?</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Какие процессы автоматизировать в первую очередь?</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -23775,22 +23871,26 @@
           <t>faq.a2</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Because 31% of IT projects actually succeed, and the ones that fail usually failed because they were too big. We ship one real thing in 10-15 days, your team adopts it, then Sprint 2 is informed by what you learned. No lock-in, no 6-month contract.</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>იმიტომ, რომ IT პროექტების მხოლოდ 31% სრულდება წარმატებით, ჩავარდნის მთავარი მიზეზი კი ხშირად მათი ზედმეტი სირთულე და მოცულობაა. ჩვენ ვნერგავთ ერთ კონკრეტულ, გამართულ ფუნქციონალს 10-15 დღეში, შენი გუნდი უპრობლემოდ ითვისებს მას, მეორე სპრინტი კი უკვე მიღებულ პრაქტიკულ გამოცდილებას ეფუძნება. არანაირი ხელოვნური მიბმა და 6-თვიანი სავალდებულო კონტრაქტები.</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>Потому что успешны лишь 31% IT-проектов, а провалы обычно случаются из-за того, что проект слишком большой. Мы запускаем одну реальную вещь за 10-15 дней, команда её осваивает, а Спринт 2 строится уже на этом опыте. Никакой привязки, никаких шестимесячных контрактов.</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr"/>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>The work that repeats every day, takes a lot of time and follows the same rules: for example the first reply in chats, lead assignment, follow-up reminders or preparing reports. On the call we find 1-2 such processes that give you the fastest result.</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>ის, რაც ყოველდღე მეორდება, ბევრ დროს იღებს და ერთი და იგივე წესით კეთდება: მაგალითად, პირველი პასუხი ჩატებში, ლიდების განაწილება, follow-up შეხსენებები ან ანგარიშების მომზადება. ზარზე ერთად ვიპოვით 1-2 ასეთ პროცესს, რომელიც ყველაზე სწრაფ შედეგს მოგცემს.</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>То, что повторяется каждый день, отнимает много времени и делается по одним и тем же правилам: например, первый ответ в чатах, распределение лидов, напоминания о follow-up или подготовка отчётов. На звонке вместе найдём 1-2 таких процесса, которые дадут самый быстрый результат.</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -23813,22 +23913,26 @@
           <t>faq.q3</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>What does it actually cost?</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>რეალურად რა ჯდება მომსახურება?</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>Сколько это стоит на деле?</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr"/>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>How is AI different from regular automation?</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>რით განსხვავდება AI ჩვეულებრივი ავტომატიზაციისგან?</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Чем AI отличается от обычной автоматизации?</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -23851,22 +23955,26 @@
           <t>faq.a3</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Minimum engagement is €1,990 + VAT. Most first sprints land €2,000-5,000 depending on which solutions you pick. Licensing (Zoho, Monday, etc.) is billed separately by the vendor at their public prices. We tell you both numbers on the call.</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>მინიმალური ჩართულობა შეადგენს €1,990-ს (+ დღგ). პირველი სპრინტების უმრავლესობის ღირებულება შერჩეული გადაწყვეტების მიხედვით €2,000-დან €5,000-მდე მერყეობს. პლატფორმის ლიცენზიებს (Zoho, Monday და ა.შ.) პირდაპირ მწარმოებელს უხდით მათი ოფიციალური საჯარო ტარიფებით. ორივე ციფრს ზარზე დეტალურად დაგითვლით.</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>Минимальный заказ - €1,990 + НДС. Большинство первых спринтов - €2,000-5,000 в зависимости от выбранных решений. Лицензии (Zoho, Monday и т.д.) оплачиваются отдельно напрямую вендору по его публичным ценам. Обе цифры называем на звонке.</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr"/>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Regular automation follows a fixed rule: if this, then that. AI can understand text and make decisions: answer a client question, summarise a call, recognise an order in a message. The best results come from using both together.</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>ჩვეულებრივი ავტომატიზაცია მკაცრ წესს მისდევს: თუ ეს, მაშინ ის. AI-ს ტექსტის გაგება და გადაწყვეტილების მიღება შეუძლია: უპასუხოს კლიენტის კითხვას, შეაჯამოს ზარი, ამოიცნოს შეკვეთა წერილიდან. საუკეთესო შედეგს ორივე ერთად იძლევა.</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Обычная автоматизация следует жёсткому правилу: если это, то то. AI понимает текст и принимает решения: отвечает на вопрос клиента, резюмирует звонок, распознаёт заказ в сообщении. Лучший результат дают оба подхода вместе.</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -23889,22 +23997,26 @@
           <t>faq.q4</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Do you work with my industry?</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>მუშაობთ თუ არა ჩემს კონკრეტულ ინდუსტრიაში?</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>Вы работаете в моей отрасли?</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr"/>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>Which AI solutions do you implement?</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>რა AI გადაწყვეტებს ნერგავთ?</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Какие AI-решения вы внедряете?</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -23927,22 +24039,26 @@
           <t>faq.a4</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>We've deployed in real estate, education, logistics, hospitality, medical, retail, finance, construction, and services. If your work is on an Excel sheet, a shared inbox, or a WhatsApp group right now, we can help. If you need something only a very narrow vertical tool does (legal case management, specific medical records), we'll tell you.</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>ჩვენ განვახორციელეთ დანერგვები უძრავ ქონებაში, განათლებაში, ლოგისტიკაში, HoReCa სექტორში, მედიცინაში, რითეილში, ფინანსებში, მშენებლობასა და მომსახურების სფეროში. თუ დღეს შენი საქმე იმართება Excel-ის ცხრილებით, საერთო მეილით ან WhatsApp-ის ჩატებით - ჩვენ შეგვიძლია შენი დახმარება. ხოლო თუ სპეციფიკური ვიწრო-პროფილური სისტემა გჭირდება (მაგ. იურიდიული საქმისწარმოება ან სპეციფიკური სამედიცინო ბარათები), ამასაც პირდაპირ გეტყვით.</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>Мы внедряли в недвижимости, образовании, логистике, гостеприимстве, медицине, рознице, финансах, строительстве и сервисах. Если вы сейчас работаете в Excel, общем inbox или WhatsApp-группе - мы поможем. Если нужен узкоспециализированный вертикальный инструмент (управление юридическими кейсами, медицинские записи) - честно скажем.</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr"/>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>An AI chat assistant on your website and messengers, Georgian-language meeting transcription, call analysis and Claude connected to your CRM so you can ask your data questions in plain language. On the call we tell you which one gives you the biggest result.</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>AI ჩატ-ასისტენტი საიტზე და მესენჯერებში, ქართულ ენაზე შეხვედრების ტრანსკრიფცია, ზარების ანალიზი და Claude-ის დაკავშირება შენს CRM-თან, რომ მონაცემებს კითხვები ჩვეულებრივ ენაზე დაუსვა. ზარზე გეტყვით, რომელი მოგცემს ყველაზე დიდ შედეგს.</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>AI чат-ассистент на сайте и в мессенджерах, транскрипция встреч на грузинском, анализ звонков и Claude, подключённый к вашей CRM, чтобы задавать вопросы данным обычным языком. На звонке скажем, что даст наибольший результат.</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -23965,22 +24081,26 @@
           <t>faq.q5</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>What if I don't know what my problem is?</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>რა ვქნა, თუ ზუსტად არ ვიცი, რა არის ჩემი მთავარი პრობლემა?</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>А если я не знаю, в чём моя проблема?</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr"/>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>Can you automate without replacing the systems we already use?</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>შეიძლება ავტომატიზაცია ჩემი არსებული სისტემების შეცვლის გარეშე?</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Можно автоматизировать, не меняя систем, которыми мы уже пользуемся?</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24003,22 +24123,26 @@
           <t>faq.a5</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>That's what the 20 minutes are for. Most founders arrive with a vague "I need a CRM" and leave with a specific one-page plan. If after the call it's still unclear, we offer a paid Discovery (€99/h) to go deeper - only when it genuinely helps.</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>20-წუთიანი ზარი სწორედ ამისთვისაა. დამფუძნებლების უმეტესობა მოდის ზოგადი ფრაზით „CRM მჭირდება“ და ზარიდან გადის კონკრეტული 1-გვერდიანი სამოქმედო გეგმით. თუ ზარის შემდეგ მაინც საჭირო გახდა სიღრმისეული ანალიზი, გთავაზობთ ფასიან Discovery სესიას (€99/სთ) - მხოლოდ იმ შემთხვევაში, თუ ეს რეალურ სარგებელს მოგიტანს.</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>Для этого и нужны 20 минут. Большинство основателей приходят с размытым "мне нужна CRM", а уходят с конкретным планом на одну страницу. Если после звонка всё ещё непонятно - предлагаем платный Discovery (€99/ч), чтобы копнуть глубже. Только если это реально поможет.</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr"/>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Yes, in most cases. We connect the systems you already use through APIs and integrations, so your team does not have to relearn everything. If a current tool really holds the work back, we tell you plainly.</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>კი, უმეტეს შემთხვევაში. API-ებით და ინტეგრაციებით ვაკავშირებთ იმ სისტემებს, რომლებსაც უკვე იყენებ, ასე რომ გუნდს ყველაფრის თავიდან სწავლა არ უწევს. თუ არსებული ინსტრუმენტი ნამდვილად აფერხებს საქმეს, ამას პირდაპირ გეტყვით.</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Да, в большинстве случаев. Мы связываем системы, которыми вы уже пользуетесь, через API и интеграции, поэтому команде не нужно всё переучивать. Если текущий инструмент действительно мешает работе, скажем об этом прямо.</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24041,22 +24165,26 @@
           <t>faq.q6</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>Who owns the system you build?</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>ვის საკუთრებაში რჩება აწყობილი სისტემა?</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>Кому принадлежит система, которую вы строите?</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr"/>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>Is my data safe?</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>უსაფრთხოა ჩემი მონაცემები?</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Безопасны ли мои данные?</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24079,22 +24207,26 @@
           <t>faq.a6</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>You own all your data and all platform accounts - they're registered under your company. The implementation IP (configurations, custom code) belongs to us, but you can take your data anywhere, anytime. Anything we host on our side is a transparent paid subscription you can cancel.</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>ყველა შენი მონაცემი და პლატფორმის ანგარიში რეგისტრირდება შენი კომპანიის სახელზე და რჩება შენს სრულ მფლობელობაში. დანერგვის ინტელექტუალური საკუთრება (კონფიგურაცია, custom კოდი) ეკუთვნის ჩვენს გუნდს, თუმცა შენი მონაცემების ექსპორტი და წაღება ნებისმიერ დროს შეგიძლია. ნებისმიერი სერვისი, რომელსაც ჩვენს მხარეს ვჰოსტავთ, წარმოადგენს გამჭვირვალე ყოველთვიურ გამოწერას, რომლის გაუქმებაც ნებისმიერ მომენტშია შესაძლებელი.</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>Все ваши данные и аккаунты платформ принадлежат вам - они зарегистрированы на вашу компанию. Интеллектуальная собственность на внедрение (конфигурации, кастомный код) принадлежит нам, но данные вы можете забрать куда угодно и когда угодно. Всё, что мы хостим у себя - прозрачная платная подписка, её можно отменить.</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr"/>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>The AI only sees the data a specific task needs. Accounts are created in your company's name and you control access. Before we start, we give you a written risks and recommendations review.</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>AI ხედავს მხოლოდ იმ მონაცემებს, რაც კონკრეტული ამოცანისთვისაა საჭირო. ანგარიშები შენი კომპანიის სახელზე იქმნება და წვდომას შენ აკონტროლებ. დაწყებამდე წერილობით გაჩვენებთ რისკებსა და რეკომენდაციებს.</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>AI видит только те данные, которые нужны для конкретной задачи. Аккаунты создаются на вашу компанию, доступом управляете вы. До начала работы даём письменный обзор рисков и рекомендаций.</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24117,22 +24249,26 @@
           <t>faq.q7</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>What happens after the sprint delivers?</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>რა ხდება სპრინტის დასრულებისა და ჩაბარების შემდეგ?</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>Что происходит после сдачи спринта?</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr"/>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>What does it actually cost?</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>რეალურად რა ჯდება მომსახურება?</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>Сколько это стоит на деле?</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24155,22 +24291,26 @@
           <t>faq.a7</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Three business days to review and accept. Then your team runs it. Technical support is available at €69/h - only if you need it. Many clients then book Sprint 2 (automations, integrations) or move to Managed Services for ongoing optimization.</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>გაქვს 3 სამუშაო დღე სისტემის შესამოწმებლად და ჩასაბარებლად, რის შემდეგაც შენი გუნდი სრულფასოვნად იწყებს მუშაობას. ტექნიკური მხარდაჭერა ხელმისაწვდომია ტარიფით €69/სთ - მხოლოდ საჭიროების შემთხვევაში. ბევრი კლიენტი შემდგომ ჯავშნის მეორე სპრინტს (ავტომატიზაციები, ინტეგრაციები) ან გადადის მუდმივი ოპტიმიზაციის მხარდაჭერის პაკეტზე (Managed Services).</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>Три рабочих дня на проверку и приёмку. Дальше система работает у вашей команды. Техподдержка доступна за €69/ч - только по необходимости. Многие клиенты затем бронируют Спринт 2 (автоматизация, интеграции) или переходят на Managed Services для постоянной оптимизации.</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr"/>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>The price is set individually and depends on the task: how many systems we touch, how many users there are and which integrations you need. You pay the platform licence (Zoho, monday, etc.) directly to the vendor. We give you exact numbers on the 20-minute call.</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება და დამოკიდებულია ამოცანაზე: რამდენ სისტემას ვეხებით, რამდენი მომხმარებელია და რა ინტეგრაციებია საჭირო. პლატფორმის ლიცენზიას (Zoho, monday და სხვ.) პირდაპირ მწარმოებელს უხდი. ზუსტ ციფრებს 20-წუთიან ზარზე გეტყვით.</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Стоимость определяется индивидуально и зависит от задачи: сколько систем затрагиваем, сколько пользователей и какие нужны интеграции. Лицензию платформы (Zoho, monday и др.) вы оплачиваете напрямую производителю. Точные цифры назовём на 20-минутном звонке.</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24193,22 +24333,26 @@
           <t>faq.q8</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Can I pick 5 solutions and combine them?</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>შემიძლია ავირჩიო 5 სხვადასხვა გადაწყვეტა და ერთად გავაერთიანო?</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>Можно выбрать 5 решений и объединить их?</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr"/>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>How soon will I see results?</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>რამდენ ხანში ვნახავ შედეგს?</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Как скоро будет результат?</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24231,22 +24375,26 @@
           <t>faq.a8</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Yes, that's what the "Add to request" list is for. On the call we help you order them by sequence (what has to come first) and sprint capacity. You usually won't ship all 5 at once, but you can.</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>რა თქმა უნდა! ღილაკი „სიაში დამატება“ სწორედ ამისთვისაა. ზარზე ერთად განვსაზღვრავთ პრიორიტეტებს - რა უნდა გაკეთდეს პირველ ეტაპზე და რა გადანაწილდეს შემდგომ სპრინტებზე. როგორც წესი, ხუთივე ერთდროულად არ ეშვება, თუმცა ტექნიკურად ეს სრულიად შესაძლებელია.</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>Да, именно для этого и существует список "Добавить в запрос". На звонке мы помогаем расставить их по порядку (что должно идти первым) и по ёмкости спринта. Обычно 5 сразу не внедряют, но технически это возможно.</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr"/>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>The first solution usually goes live in 5-10 working days. We start with one process, check the result and then expand.</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>პირველი გადაწყვეტა, როგორც წესი, 5-10 სამუშაო დღეში ეშვება. ვიწყებთ ერთი პროცესით, ვამოწმებთ შედეგს და მერე ვაფართოებთ.</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Первое решение обычно запускается за 5-10 рабочих дней. Начинаем с одного процесса, проверяем результат и затем расширяем.</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24269,22 +24417,26 @@
           <t>faq.q9</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Do you work with international clients, or Georgia only?</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>მუშაობთ საერთაშორისო კლიენტებთან, თუ მხოლოდ საქართველოში?</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>Вы работаете с международными клиентами или только в Грузии?</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr"/>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>Who owns the system you build?</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>ვის საკუთრებაში რჩება აწყობილი სისტემა?</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>Кому принадлежит система, которую вы строите?</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24307,22 +24459,26 @@
           <t>faq.a9</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>We focus on Georgia because of language, local banking, and GEONET telephony integrations. We also serve select international clients - the call is in English or Russian or Georgian, whichever works for you.</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>ჩვენი მთავარი ფოკუსი საქართველოა ქართული ენის, ადგილობრივი ბანკინგისა და GEONET-ის ტელეფონიის ინტეგრაციების გამო. თუმცა ვთანამშრომლობთ შერჩეულ საერთაშორისო კლიენტებთანაც - საკონსულტაციო ზარი შეგვიძლია ჩავატაროთ ქართულად, ინგლისურად ან რუსულად, შენი სურვილისამებრ.</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>Мы сфокусированы на Грузии из-за языка, местного банкинга и интеграций с GEONET-телефонией. Работаем и с избранными международными клиентами - звонок на английском, русском или грузинском, как вам удобно.</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr"/>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>You own all your data and all platform accounts - they're registered under your company. The implementation IP (configurations, custom code) belongs to us, but you can take your data anywhere, anytime. Anything we host on our side is a transparent paid subscription you can cancel.</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>ყველა შენი მონაცემი და პლატფორმის ანგარიში რეგისტრირდება შენი კომპანიის სახელზე და რჩება შენს სრულ მფლობელობაში. დანერგვის ინტელექტუალური საკუთრება (კონფიგურაცია, custom კოდი) ეკუთვნის ჩვენს გუნდს, თუმცა შენი მონაცემების ექსპორტი და წაღება ნებისმიერ დროს შეგიძლია. ნებისმიერი სერვისი, რომელსაც ჩვენს მხარეს ვჰოსტავთ, წარმოადგენს გამჭვირვალე ყოველთვიურ გამოწერას, რომლის გაუქმებაც ნებისმიერ მომენტშია შესაძლებელი.</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>Все ваши данные и аккаунты платформ принадлежат вам - они зарегистрированы на вашу компанию. Интеллектуальная собственность на внедрение (конфигурации, кастомный код) принадлежит нам, но данные вы можете забрать куда угодно и когда угодно. Всё, что мы хостим у себя - прозрачная платная подписка, её можно отменить.</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24345,22 +24501,26 @@
           <t>faq.q10</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>What if 20 minutes isn't enough?</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>რა მოხდება, თუ 20 წუთი საკმარისი არ აღმოჩნდება?</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>А если 20 минут не хватит?</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr"/>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>What if I don't know where to use AI?</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>რა ვქნა, თუ არ ვიცი, სად გამოვიყენო AI?</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>Что делать, если я не знаю, где применить AI?</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -24383,22 +24543,26 @@
           <t>faq.a10</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>Then we schedule a second call, or you book paid Discovery. We've never had a founder arrive and leave more confused - the agenda is tight on purpose. If you have a complex multi-system case, mention it on the booking form and we'll block 45 minutes instead.</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>ასეთ შემთხვევაში დავნიშნავთ მეორე ზარს, ან შევთანხმდებით სიღრმისეულ Discovery-ზე. არ ყოფილა შემთხვევა, რომ დამფუძნებელი ჩვენი ზარიდან უფრო დაბნეული გასულიყო - დღის წესრიგი მიზანმიმართულად მკაფიო და ლაკონიურია. თუ გაქვს კომპლექსური, მრავალსისტემიანი ქეისი, უბრალოდ მიუთითე ჯავშნის ფორმაში და შენთვის წინასწარ 45 წუთს დავჯავშნით.</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>Тогда назначим второй звонок или вы бронируете платный Discovery. У нас не было случая, когда основатель уходил бы ещё более запутанным - повестка намеренно плотная. Если у вас сложный мульти-системный кейс, отметьте это в форме бронирования, и мы выделим 45 минут.</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr"/>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>That is exactly what the 20-minute call is for. Tell us how your team works and we tell you where AI really saves time and where it is not worth it.</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>20-წუთიანი ზარი სწორედ ამისთვისაა. მოგვიყევი, როგორ მუშაობს შენი გუნდი, და გეტყვით, სად დაზოგავს AI რეალურად დროს და სად არ ღირს მისი დანერგვა.</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Для этого и нужен 20-минутный звонок. Расскажите, как работает ваша команда, и мы скажем, где AI действительно экономит время, а где его внедрять не стоит.</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -27563,10 +27727,52 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Seo</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>AI and process automation for business | Unitty</t>
+        </is>
+      </c>
+      <c r="E209" s="9" t="inlineStr">
+        <is>
+          <t>AI და პროცესების ავტომატიზაცია ბიზნესისთვის | Unitty</t>
+        </is>
+      </c>
+      <c r="F209" s="9" t="inlineStr">
+        <is>
+          <t>AI и автоматизация процессов для бизнеса | Unitty</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H208"/>
+  <autoFilter ref="A1:H209"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H407" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H408" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -27580,7 +27786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -31701,22 +31907,26 @@
           <t>faq.q2</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Why only one sprint instead of a full roadmap?</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>რატომ ვიწყებთ ერთი კონკრეტული სპრინტით და არა გრძელვადიანი გეგმით?</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>Почему только один спринт, а не полная дорожная карта?</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr"/>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>Which banks do you work with?</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>რომელ ბანკებთან მუშაობთ?</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>С какими банками вы работаете?</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -31739,22 +31949,26 @@
           <t>faq.a2</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Because 31% of IT projects actually succeed, and the ones that fail usually failed because they were too big. We ship one real thing in 10-15 days, your team adopts it, then Sprint 2 is informed by what you learned. No lock-in, no 6-month contract.</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>იმიტომ, რომ IT პროექტების მხოლოდ 31% სრულდება წარმატებით, ჩავარდნის მთავარი მიზეზი კი ხშირად მათი ზედმეტი სირთულე და მოცულობაა. ჩვენ ვნერგავთ ერთ კონკრეტულ, გამართულ ფუნქციონალს 10-15 დღეში, შენი გუნდი უპრობლემოდ ითვისებს მას, მეორე სპრინტი კი უკვე მიღებულ პრაქტიკულ გამოცდილებას ეფუძნება. არანაირი ხელოვნური მიბმა და 6-თვიანი სავალდებულო კონტრაქტები.</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>Потому что успешны лишь 31% IT-проектов, а провалы обычно случаются из-за того, что проект слишком большой. Мы запускаем одну реальную вещь за 10-15 дней, команда её осваивает, а Спринт 2 строится уже на этом опыте. Никакой привязки, никаких шестимесячных контрактов.</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr"/>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>We connect TBC Bank and Bank of Georgia. For another bank, we confirm on the call which kind of integration is possible.</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>ვაკავშირებთ TBC ბანკს და საქართველოს ბანკს. სხვა ბანკის შემთხვევაში ზარზე დავაზუსტებთ, რა ტიპის ინტეგრაციაა შესაძლებელი.</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Подключаем TBC Bank и Bank of Georgia. Для другого банка уточним на звонке, какая интеграция возможна.</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -31817,17 +32031,17 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Minimum engagement is €1,990 + VAT. Most first sprints land €2,000-5,000 depending on which solutions you pick. Licensing (Zoho, Monday, etc.) is billed separately by the vendor at their public prices. We tell you both numbers on the call.</t>
+          <t>The price is set individually and depends on the task: how many systems we touch, how many users there are and which integrations you need. You pay the platform licence (Zoho, monday, etc.) directly to the vendor. We give you exact numbers on the 20-minute call.</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>მინიმალური ჩართულობა შეადგენს €1,990-ს (+ დღგ). პირველი სპრინტების უმრავლესობის ღირებულება შერჩეული გადაწყვეტების მიხედვით €2,000-დან €5,000-მდე მერყეობს. პლატფორმის ლიცენზიებს (Zoho, Monday და ა.შ.) პირდაპირ მწარმოებელს უხდით მათი ოფიციალური საჯარო ტარიფებით. ორივე ციფრს ზარზე დეტალურად დაგითვლით.</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება და დამოკიდებულია ამოცანაზე: რამდენ სისტემას ვეხებით, რამდენი მომხმარებელია და რა ინტეგრაციებია საჭირო. პლატფორმის ლიცენზიას (Zoho, monday და სხვ.) პირდაპირ მწარმოებელს უხდი. ზუსტ ციფრებს 20-წუთიან ზარზე გეტყვით.</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Минимальный заказ - €1,990 + НДС. Большинство первых спринтов - €2,000-5,000 в зависимости от выбранных решений. Лицензии (Zoho, Monday и т.д.) оплачиваются отдельно напрямую вендору по его публичным ценам. Обе цифры называем на звонке.</t>
+          <t>Стоимость определяется индивидуально и зависит от задачи: сколько систем затрагиваем, сколько пользователей и какие нужны интеграции. Лицензию платформы (Zoho, monday и др.) вы оплачиваете напрямую производителю. Точные цифры назовём на 20-минутном звонке.</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr"/>
@@ -31929,22 +32143,26 @@
           <t>faq.q5</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>What if I don't know what my problem is?</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>რა ვქნა, თუ ზუსტად არ ვიცი, რა არის ჩემი მთავარი პრობლემა?</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>А если я не знаю, в чём моя проблема?</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr"/>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>How does automatic payment matching work?</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>როგორ მუშაობს გადარიცხვების ავტომატური შეჯერება?</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Как работает автоматическая сверка платежей?</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -31967,22 +32185,26 @@
           <t>faq.a5</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>That's what the 20 minutes are for. Most founders arrive with a vague "I need a CRM" and leave with a specific one-page plan. If after the call it's still unclear, we offer a paid Discovery (€99/h) to go deeper - only when it genuinely helps.</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>20-წუთიანი ზარი სწორედ ამისთვისაა. დამფუძნებლების უმეტესობა მოდის ზოგადი ფრაზით „CRM მჭირდება“ და ზარიდან გადის კონკრეტული 1-გვერდიანი სამოქმედო გეგმით. თუ ზარის შემდეგ მაინც საჭირო გახდა სიღრმისეული ანალიზი, გთავაზობთ ფასიან Discovery სესიას (€99/სთ) - მხოლოდ იმ შემთხვევაში, თუ ეს რეალურ სარგებელს მოგიტანს.</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>Для этого и нужны 20 минут. Большинство основателей приходят с размытым "мне нужна CRM", а уходят с конкретным планом на одну страницу. Если после звонка всё ещё непонятно - предлагаем платный Discovery (€99/ч), чтобы копнуть глубже. Только если это реально поможет.</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr"/>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Bank transactions land in the CRM automatically and are matched to the right client or payment by their reference. Anything the system cannot recognise appears in a separate list for you to confirm. Multi-currency matching (GEL/USD/EUR) and a daily National Bank exchange rate are also available.</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>ბანკის ტრანზაქციები ავტომატურად ჩადის CRM-ში და დანიშნულების მიხედვით ებმება სწორ კლიენტს ან გადახდას. რასაც სისტემა ვერ ამოიცნობს, ცალკე სიაში ჩანს, რომ ხელით დაადასტურო. ასევე შესაძლებელია ვალუტების (GEL/USD/EUR) შეჯერება და ეროვნული ბანკის კურსის ყოველდღიური განახლება.</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Банковские транзакции автоматически попадают в CRM и по назначению платежа привязываются к нужному клиенту или оплате. То, что система не распознала, видно в отдельном списке для ручного подтверждения. Также доступны мультивалютная сверка (GEL/USD/EUR) и ежедневный курс Национального банка.</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -32157,22 +32379,26 @@
           <t>faq.q8</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Can I pick 5 solutions and combine them?</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>შემიძლია ავირჩიო 5 სხვადასხვა გადაწყვეტა და ერთად გავაერთიანო?</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>Можно выбрать 5 решений и объединить их?</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr"/>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Is it safe to connect the bank to the CRM?</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>უსაფრთხოა ბანკის CRM-თან დაკავშირება?</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Безопасно ли подключать банк к CRM?</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -32195,22 +32421,26 @@
           <t>faq.a8</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Yes, that's what the "Add to request" list is for. On the call we help you order them by sequence (what has to come first) and sprint capacity. You usually won't ship all 5 at once, but you can.</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>რა თქმა უნდა! ღილაკი „სიაში დამატება“ სწორედ ამისთვისაა. ზარზე ერთად განვსაზღვრავთ პრიორიტეტებს - რა უნდა გაკეთდეს პირველ ეტაპზე და რა გადანაწილდეს შემდგომ სპრინტებზე. როგორც წესი, ხუთივე ერთდროულად არ ეშვება, თუმცა ტექნიკურად ეს სრულიად შესაძლებელია.</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>Да, именно для этого и существует список "Добавить в запрос". На звонке мы помогаем расставить их по порядку (что должно идти первым) и по ёмкости спринта. Обычно 5 сразу не внедряют, но технически это возможно.</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr"/>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>The connection uses the bank's official integration with secured access. It reads account movements for the CRM and does not send money. Before we start, we give you a written risks and recommendations review.</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>კავშირი ბანკის ოფიციალური ინტეგრაციით ხდება, დაცული წვდომით. ინტეგრაცია ანგარიშის მოძრაობას კითხულობს CRM-ისთვის და თანხებს არ გზავნის. დაწყებამდე წერილობით გაჩვენებთ რისკებსა და რეკომენდაციებს.</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Подключение идёт через официальную интеграцию банка с защищённым доступом. Интеграция читает движение по счёту для CRM и не отправляет деньги. До начала работы даём письменный обзор рисков и рекомендаций.</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -33889,10 +34119,52 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Seo</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>Bank transactions in your CRM: TBC and Bank of Georgia | Unitty</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="inlineStr">
+        <is>
+          <t>ბანკის ტრანზაქციები CRM-ში: TBC და საქართველოს ბანკი | Unitty</t>
+        </is>
+      </c>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>Банковские транзакции в CRM: TBC и Bank of Georgia | Unitty</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H165"/>
+  <autoFilter ref="A1:H166"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H364" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H365" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -33906,7 +34178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -38131,17 +38403,17 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Minimum engagement is €1,990 + VAT. Most first sprints land €2,000-5,000 depending on which solutions you pick. Licensing (Zoho, Monday, etc.) is billed separately by the vendor at their public prices. We tell you both numbers on the call.</t>
+          <t>The price is set individually and depends on the task: how many systems we touch, how many users there are and which integrations you need. You pay the platform licence (Zoho, monday, etc.) directly to the vendor. We give you exact numbers on the 20-minute call.</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>მინიმალური ჩართულობა შეადგენს €1,990-ს (+ დღგ). პირველი სპრინტების უმრავლესობის ღირებულება შერჩეული გადაწყვეტების მიხედვით €2,000-დან €5,000-მდე მერყეობს. პლატფორმის ლიცენზიებს (Zoho, Monday და ა.შ.) პირდაპირ მწარმოებელს უხდით მათი ოფიციალური საჯარო ტარიფებით. ორივე ციფრს ზარზე დეტალურად დაგითვლით.</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება და დამოკიდებულია ამოცანაზე: რამდენ სისტემას ვეხებით, რამდენი მომხმარებელია და რა ინტეგრაციებია საჭირო. პლატფორმის ლიცენზიას (Zoho, monday და სხვ.) პირდაპირ მწარმოებელს უხდი. ზუსტ ციფრებს 20-წუთიან ზარზე გეტყვით.</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Минимальный заказ - €1,990 + НДС. Большинство первых спринтов - €2,000-5,000 в зависимости от выбранных решений. Лицензии (Zoho, Monday и т.д.) оплачиваются отдельно напрямую вендору по его публичным ценам. Обе цифры называем на звонке.</t>
+          <t>Стоимость определяется индивидуально и зависит от задачи: сколько систем затрагиваем, сколько пользователей и какие нужны интеграции. Лицензию платформы (Zoho, monday и др.) вы оплачиваете напрямую производителю. Точные цифры назовём на 20-минутном звонке.</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr"/>
@@ -38471,22 +38743,26 @@
           <t>faq.q8</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>Can I pick 5 solutions and combine them?</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E120" s="9" t="inlineStr">
         <is>
           <t>შემიძლია ავირჩიო 5 სხვადასხვა გადაწყვეტა და ერთად გავაერთიანო?</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F120" s="9" t="inlineStr">
         <is>
           <t>Можно выбрать 5 решений и объединить их?</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr"/>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -38509,22 +38785,26 @@
           <t>faq.a8</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D121" s="9" t="inlineStr">
         <is>
           <t>Yes, that's what the "Add to request" list is for. On the call we help you order them by sequence (what has to come first) and sprint capacity. You usually won't ship all 5 at once, but you can.</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E121" s="9" t="inlineStr">
         <is>
           <t>რა თქმა უნდა! ღილაკი „სიაში დამატება“ სწორედ ამისთვისაა. ზარზე ერთად განვსაზღვრავთ პრიორიტეტებს - რა უნდა გაკეთდეს პირველ ეტაპზე და რა გადანაწილდეს შემდგომ სპრინტებზე. როგორც წესი, ხუთივე ერთდროულად არ ეშვება, თუმცა ტექნიკურად ეს სრულიად შესაძლებელია.</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F121" s="9" t="inlineStr">
         <is>
           <t>Да, именно для этого и существует список "Добавить в запрос". На звонке мы помогаем расставить их по порядку (что должно идти первым) и по ёмкости спринта. Обычно 5 сразу не внедряют, но технически это возможно.</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr"/>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -40211,27 +40491,27 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>prod.title</t>
+          <t>seo.title</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>Our own products</t>
+          <t>75+ ready-made CRM, AI and analytics solutions | Unitty</t>
         </is>
       </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
-          <t>ჩვენი პროდუქტები</t>
+          <t>75+ მზა გადაწყვეტა CRM-ის, AI-ს და ანალიტიკისთვის | Unitty</t>
         </is>
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>Наши продукты</t>
+          <t>75+ готовых решений для CRM, AI и аналитики | Unitty</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -40258,22 +40538,22 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>prod.sub</t>
+          <t>prod.title</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
+          <t>Our own products</t>
         </is>
       </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
-          <t>ჩვენ მიერ შექმნილი მზა სერვისები, რომლებიც სწრაფად ერთვება შენს სისტემაში.</t>
+          <t>ჩვენი პროდუქტები</t>
         </is>
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
+          <t>Наши продукты</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -40300,22 +40580,22 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>prod.cta</t>
+          <t>prod.sub</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Request →</t>
+          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე →</t>
+          <t>ჩვენ მიერ შექმნილი მზა სერვისები, რომლებიც სწრაფად ერთვება შენს სისტემაში.</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>Запросить →</t>
+          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -40342,22 +40622,22 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>prod.1.desc</t>
+          <t>prod.cta</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
+          <t>Request →</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>ბანკის ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად შედის CRM-ში - გადახდების მიბმით და შიდა განვადების გრაფიკით.</t>
+          <t>მოითხოვე →</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
+          <t>Запросить →</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -40384,22 +40664,22 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>prod.2.desc</t>
+          <t>prod.1.desc</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
+          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს კითხვებს და ლიდებს პირდაპირ CRM-ში წერს.</t>
+          <t>ბანკის ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად შედის CRM-ში - გადახდების მიბმით და შიდა განვადების გრაფიკით.</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
+          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -40426,22 +40706,22 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>prod.3.desc</t>
+          <t>prod.2.desc</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
+          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
         </is>
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და შემდეგი ნაბიჯები - ავტომატურად.</t>
+          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს კითხვებს და ლიდებს პირდაპირ CRM-ში წერს.</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
+          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -40468,22 +40748,22 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>prod.4.desc</t>
+          <t>prod.3.desc</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
+          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
         </is>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>Claude, მიერთებული შენს მონაცემებთან: დასვი კითხვა ჩვეულებრივი ენით და მიიღე პასუხი რიცხვებით.</t>
+          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და შემდეგი ნაბიჯები - ავტომატურად.</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
+          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -40510,22 +40790,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>prod.5.desc</t>
+          <t>prod.4.desc</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
+          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>ზარები, ჩანაწერები და click-to-call პირდაპირ CRM-ში - ზარის სწორ მენეჯერზე გადამისამართებით.</t>
+          <t>Claude, მიერთებული შენს მონაცემებთან: დასვი კითხვა ჩვეულებრივი ენით და მიიღე პასუხი რიცხვებით.</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
+          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -40552,22 +40832,22 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>prod.6.desc</t>
+          <t>prod.5.desc</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
+          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>ყოველი ახალი ლიდი ავტომატურად მუშავდება: კონტაქტის შექმნა, დუბლიკატების პოვნა, მენეჯერზე მიბმა.</t>
+          <t>ზარები, ჩანაწერები და click-to-call პირდაპირ CRM-ში - ზარის სწორ მენეჯერზე გადამისამართებით.</t>
         </is>
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
+          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -40594,22 +40874,22 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>prod.7.desc</t>
+          <t>prod.6.desc</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
+          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>პარტნიორები ლიდებს ერთ სივრცეში აგზავნიან და სტატუსს ხედავენ, შენ კი ყოველი რეკომენდაციის სრულ ისტორიას.</t>
+          <t>ყოველი ახალი ლიდი ავტომატურად მუშავდება: კონტაქტის შექმნა, დუბლიკატების პოვნა, მენეჯერზე მიბმა.</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
+          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -40636,39 +40916,81 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
+          <t>prod.7.desc</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>პარტნიორები ლიდებს ერთ სივრცეში აგზავნიან და სტატუსს ხედავენ, შენ კი ყოველი რეკომენდაციის სრულ ისტორიას.</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
           <t>prod.8.desc</t>
         </is>
       </c>
-      <c r="D176" s="9" t="inlineStr">
+      <c r="D177" s="9" t="inlineStr">
         <is>
           <t>Personalised SMS reminders and notifications straight from your CRM - for payments, meetings and bookings.</t>
         </is>
       </c>
-      <c r="E176" s="9" t="inlineStr">
+      <c r="E177" s="9" t="inlineStr">
         <is>
           <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან - გადახდებზე, შეხვედრებზე, ჯავშნებზე.</t>
         </is>
       </c>
-      <c r="F176" s="9" t="inlineStr">
+      <c r="F177" s="9" t="inlineStr">
         <is>
           <t>Персональные SMS-напоминания и уведомления прямо из CRM - о платежах, встречах и бронях.</t>
         </is>
       </c>
-      <c r="G176" s="3" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H176" s="3" t="inlineStr">
+      <c r="H177" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H176"/>
+  <autoFilter ref="A1:H177"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H375" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H376" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -7180,7 +7180,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>500+ დანერგვის გამოცდილებით 20 წუთში გეტყვით, რომელი CRM მოერგება შენს გაყიდვებს და რა ეღირება დანერგვა. უფასოდ - თუ ახლავე დაჯავშნი.</t>
+          <t>500+ დანერგვის გამოცდილებით, 20 წუთში გეტყვი, რომელი CRM მოერგება შენს გაყიდვებს და რა დაჯდება დანერგვა. უფასოდ - თუ ახლავე დაჯავშნი.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>CRM-ის ანგარიში და ყველა მონაცემი რეგისტრირდება შენი კომპანიის სახელზე და რჩება შენს სრულ მფლობელობაში. მონაცემების ექსპორტი ნებისმიერ დროს შეგიძლია. თუ რამეს ჩვენს მხარეს ვჰოსტავთ, ეს არის გამჭვირვალე ყოველთვიური გამოწერა, რომელსაც ნებისმიერ დროს გააუქმებ.</t>
+          <t>CRM-ის ანგარიში და ყველა მონაცემი რეგისტრირდება შენი კომპანიის სახელზე და რჩება შენს სრულ მფლობელობაში. მონაცემების ექსპორტი ნებისმიერ დროს შეგიძლია. თუ რამეს ჩვენს მხარეს ვჰოსტავთ, ეს არის გამჭვირვალე ყოველთვიური გამოწერა, რომლის გაუქმებაც ნებისმიერ დროს შეგიძლია.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>გეცნობა ეს სიტუაციები?</t>
+          <t>ნაცნობი მდგომარეობაა?</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>სწორ CRM-ში კლიენტის ისტორია კომპანიას რჩება და არა თანამშრომლის ტელეფონს.</t>
+          <t>სწორ CRM-ში კლიენტის ისტორია კომპანიაში რჩება და არა თანამშრომლის ტელეფონში.</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>ავტომატიზაცია რუტინას აშორებს და მენეჯერს გაყიდვას უბრუნებს.</t>
+          <t>ავტომატიზაცია აქრობს რუტინას და მენეჯერს გაყიდვებს უბრუნებს.</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>ვინ წაშალა მე-3 სვეტი?!</t>
+          <t>ვინ წაშალა C სვეტი?!</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>ერთ სისტემაში ყველა კლიენტი, გაყიდვა და შეთანხმება ერთი ძებნით ჩანს.</t>
+          <t>ერთ სისტემაში ყველა კლიენტი, გარიგება და შეთანხმება ერთი ძებნით მოიძებნება.</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>ყველა არხი ერთ ფანჯარაში: ჩანს, ვინ უპასუხა და რა უპასუხა.</t>
+          <t>ყველა საკომუნიკაციო არხი ერთ ფანჯარაში: ზუსტად ხედავ, ვინ რა უპასუხა კლიენტს.</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>ფიქსირებული ფასი და ვადა. დაიწყე პატარა პაკეტით, დანარჩენს მერე დაამატებ.</t>
+          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>არასავალდებულო. დაამატე, თუ გჭირდება</t>
+          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>ყველა დამატება კატეგორიებით</t>
+          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>5-10 კაციანი გაყიდვების გუნდისთვის</t>
+          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>სტარტის ყველაფერი, პლუს:</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>სტარტის ყველაფერი</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>ეტაპები წესებით და ლიდების განაწილება</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>ნომრების ვალიდაცია (+995) და დუბლიკატების მოშორება</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი, ჩაწერილი</t>
+          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>15-25 კაციანი, მზარდი გუნდისთვის</t>
+          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის ყველაფერი, პლუს:</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის ყველაფერი</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი, ჩაწერილი</t>
+          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>ნომრების ვალიდაცია (+995) და დუბლიკატები</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>ქონების/ობიექტების ბაზის გადმოტანა</t>
+          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოს აღრიცხვა</t>
+          <t>ბროკერების საკომისიოების აღრიცხვა</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
@@ -18236,7 +18236,7 @@
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარის აღდგენა და SMS</t>
+          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდები პირდაპირ CRM-ში</t>
+          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>ლიდის წყაროს ROI და კამპანიების ატრიბუცია</t>
+          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიში და კონტაქტების სინქრონი</t>
+          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი შეჯერება (GEL/USD/EUR)</t>
+          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის კურსის ყოველდღიური სინქრონი</t>
+          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>გაურკვეველი გადარიცხვების რიგი</t>
+          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>განვადების გრაფიკი</t>
+          <t>შიდა განვადების დინამიკური გრაფიკი</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS გაფრთხილება</t>
+          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>ომნიჩენელ ტიკეტები (Zoho Desk)</t>
+          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>SLA-ს ესკალაციის მატრიცა</t>
+          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT შეფასება ტიკეტის შემდეგ</t>
+          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის ჭკვიანი ფორმა</t>
+          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>ზარის განწყობის ანალიზი</t>
+          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარი, ორმაგი ჯავშნის გარეშე</t>
+          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის სურვილების ავტომატური მატჩი</t>
+          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ტაიმერი</t>
+          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF</t>
+          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების აღრიცხვა და დადასტურება</t>
+          <t>საველე ვიზიტების მართვა და დადასტურება</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS და ბილინგი</t>
+          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>მშენებლობის ოპერაციები და ბიუჯეტი</t>
+          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
@@ -19538,7 +19538,7 @@
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>მოვალეების ზარების ჭკვიანი რიგი</t>
+          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>აგენტების დასწრების აღრიცხვა</t>
+          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>შეხვედრების თანაბარი განაწილება</t>
+          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>AI ყველგანაა, შედეგი - არა</t>
+          <t>AI ყველგანაა, რეალური შედეგი — არსად</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>ცდას და შეცდომას</t>
+          <t>ცდასა და შეცდომებს</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>500+ წარმატებული დანერგვის გამოცდილებით, 20 წუთში მოგიყვები, სად დაგიზოგავს AI რეალურად დროს - ჩატ-ასისტენტიდან შეხვედრების ტრანსკრიფციამდე და პროცესების ავტომატიზაციამდე. უფასოდ - თუ ახლავე დაჯავშნი.</t>
+          <t>500+ წარმატებული დანერგვის გამოცდილებით, 20 წუთში გაჩვენებ, სად დაგიზოგავს AI რეალურად დროს — ჩატ-ასისტენტიდან დაწყებული, შეხვედრების ტრანსკრიფციითა და პროცესების ავტომატიზაციით დასრულებული. უფასოდ — თუ ახლავე დაჯავშნი.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -20127,22 +20127,26 @@
           <t>hero.sub.free</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Free if you book now.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>უფასოდ - თუ ახლავე დაჯავშნი.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>უფასოდ — თუ ახლავე დაჯავშნი.</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Бесплатно - если бронируете сейчас.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -20894,7 +20898,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>AI-ს ხელსაწყოები ყოველ კვირა ჩნდება, მაგრამ უმეტესობა ექსპერიმენტად რჩება. ერთი ზარი გაჩვენებს, რომელი მათგანი მოიტანს შედეგს შენს ბიზნესში.</t>
+          <t>ახალი AI ხელსაწყოები ყოველ კვირას ჩნდება, თუმცა უმეტესობა მხოლოდ ექსპერიმენტად რჩება. ერთი ზარი გაჩვენებს, რომელი მათგანი მოუტანს რეალურ შედეგს შენს ბიზნესს.</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -23064,7 +23068,7 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>მოგვიყევი, სად გეხარჯება ყველაზე მეტი დრო - ერთად ვიპოვით, სად დაგეხმარება AI.</t>
+          <t>გაგვიზიარე, სად კარგავს შენი გუნდი ყველაზე მეტ დროს — ერთად ვიპოვით, სად შეძლებს AI რეალურ დახმარებას.</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
@@ -24858,7 +24862,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>გეცნობა ეს სიტუაციები?</t>
+          <t>ნაცნობი მდგომარეობაა?</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -25238,7 +25242,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>სწორ CRM-ში კლიენტის ისტორია კომპანიას რჩება და არა თანამშრომლის ტელეფონს.</t>
+          <t>სწორ CRM-ში კლიენტის ისტორია კომპანიაში რჩება და არა თანამშრომლის ტელეფონში.</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -25428,7 +25432,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>ავტომატიზაცია რუტინას აშორებს და მენეჯერს გაყიდვას უბრუნებს.</t>
+          <t>ავტომატიზაცია აქრობს რუტინას და მენეჯერს გაყიდვებს უბრუნებს.</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -25960,7 +25964,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>ვინ წაშალა მე-3 სვეტი?!</t>
+          <t>ვინ წაშალა C სვეტი?!</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -26074,7 +26078,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>ერთ სისტემაში ყველა კლიენტი, გაყიდვა და შეთანხმება ერთი ძებნით ჩანს.</t>
+          <t>ერთ სისტემაში ყველა კლიენტი, გარიგება და შეთანხმება ერთი ძებნით მოიძებნება.</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -26340,7 +26344,7 @@
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>AI ასისტენტი 24/7 პასუხობს ყველა არხზე, რთულ კითხვებს კი მენეჯერს გადასცემს.</t>
+          <t>AI ასისტენტი 24/7 პასუხობს ყველა არხზე, ხოლო რთულ და არასტანდარტულ კითხვებს მენეჯერს გადასცემს.</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
@@ -27942,7 +27946,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>ტრანზაქციების ხელით გადატანა ძვირი ჯდება</t>
+          <t>საბანკო ტრანზაქციების ხელით გადატანა ძვირი ჯდება</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -28098,7 +28102,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>ხელით მუშაობას</t>
+          <t>რუტინულ ხელით შრომას</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -28140,7 +28144,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>500+ წარმატებული დანერგვის გამოცდილებით, 20 წუთში მოგიყვები, როგორ ჩავიდეს TBC-ის, საქართველოს ბანკის და სხვა ბანკების ტრანზაქციები პირდაპირ შენს CRM-ში - გადახდების ავტომატური მიბმით და შიდა განვადების გრაფიკით. უფასოდ - თუ ახლავე დაჯავშნი.</t>
+          <t>500+ წარმატებული დანერგვის გამოცდილებით, 20 წუთში გაჩვენებ, როგორ აისახოს TBC-ის, საქართველოს ბანკისა და სხვა ბანკების ტრანზაქციები პირდაპირ შენს CRM-ში — გადახდების ავტომატური შეჯერებითა და შიდა განვადების გრაფიკით. უფასოდ — თუ ახლავე დაჯავშნი.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -28213,22 +28217,26 @@
           <t>hero.sub.free</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Free if you book now.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>უფასოდ - თუ ახლავე დაჯავშნი.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>უფასოდ — თუ ახლავე დაჯავშნი.</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Бесплатно - если бронируете сейчас.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -28980,7 +28988,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>ყოველდღე ვიღაც ამოწმებს ამონაწერს, ეძებს ვინ გადაიხადა და ხელით ავსებს ცხრილს. ერთი ზარი გაჩვენებს, როგორ გააკეთოს ეს სისტემამ შენს მაგივრად.</t>
+          <t>ყოველდღე ვიღაც ამოწმებს საბანკო ამონაწერებს, ეძებს გადამხდელს და ხელით ავსებს ცხრილებს. ერთი ზარი გაჩვენებს, როგორ გააკეთოს ეს ყველაფერი სისტემამ ავტომატურად.</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -31150,7 +31158,7 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>მოგვიყევი, რომელ ბანკებთან და რომელ სისტემაში მუშაობ - დანარჩენზე ჩვენ ვიზრუნებთ.</t>
+          <t>გვითხარი, რომელ ბანკებთან და რა სისტემებში მუშაობ — დანარჩენ პროცესებზე ჩვენ ვიზრუნებთ.</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
@@ -34528,7 +34536,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>500+ წარმატებული დანერგვის გამოცდილებით: შეარჩიე შენთვის საინტერესო გადაწყვეტები, დაამატე მოთხოვნაში და 20 წუთში ერთად განვიხილავთ, რომელი გამოგადგება. უფასოდ - თუ ახლავე დაჯავშნი.</t>
+          <t>500+ წარმატებული დანერგვის გამოცდილებით: შეარჩიე შენთვის საინტერესო გადაწყვეტები, დაამატე მოთხოვნაში და 20 წუთში ერთად განვიხილავთ, რომელი მოერგება შენს ამოცანებს. უფასოდ — თუ ახლავე დაჯავშნი.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -34601,22 +34609,26 @@
           <t>hero.sub.free</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Free if you book now.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>უფასოდ - თუ ახლავე დაჯავშნი.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>უფასოდ — თუ ახლავე დაჯავშნი.</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Бесплатно - если бронируете сейчас.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -40590,7 +40602,7 @@
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>ჩვენ მიერ შექმნილი მზა სერვისები, რომლებიც სწრაფად ერთვება შენს სისტემაში.</t>
+          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr">
@@ -40674,7 +40686,7 @@
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>ბანკის ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად შედის CRM-ში - გადახდების მიბმით და შიდა განვადების გრაფიკით.</t>
+          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
@@ -40716,7 +40728,7 @@
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს კითხვებს და ლიდებს პირდაპირ CRM-ში წერს.</t>
+          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr">
@@ -40758,7 +40770,7 @@
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და შემდეგი ნაბიჯები - ავტომატურად.</t>
+          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
@@ -40800,7 +40812,7 @@
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>Claude, მიერთებული შენს მონაცემებთან: დასვი კითხვა ჩვეულებრივი ენით და მიიღე პასუხი რიცხვებით.</t>
+          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr">
@@ -40842,7 +40854,7 @@
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>ზარები, ჩანაწერები და click-to-call პირდაპირ CRM-ში - ზარის სწორ მენეჯერზე გადამისამართებით.</t>
+          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
         </is>
       </c>
       <c r="F174" s="9" t="inlineStr">
@@ -40884,7 +40896,7 @@
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>ყოველი ახალი ლიდი ავტომატურად მუშავდება: კონტაქტის შექმნა, დუბლიკატების პოვნა, მენეჯერზე მიბმა.</t>
+          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
@@ -40926,7 +40938,7 @@
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>პარტნიორები ლიდებს ერთ სივრცეში აგზავნიან და სტატუსს ხედავენ, შენ კი ყოველი რეკომენდაციის სრულ ისტორიას.</t>
+          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
         </is>
       </c>
       <c r="F176" s="9" t="inlineStr">
@@ -40968,7 +40980,7 @@
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
-          <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან - გადახდებზე, შეხვედრებზე, ჯავშნებზე.</t>
+          <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან — გადახდებზე, შეხვედრებსა და ჯავშნებზე.</t>
         </is>
       </c>
       <c r="F177" s="9" t="inlineStr">
@@ -41164,7 +41176,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>ნუ დაელოდები ზარს - დაჯავშნე 20-წუთიანი სლოტი პირდაპირ ჩემს კალენდარში</t>
+          <t>ნუ დაელოდები ზარს — დაჯავშნე 20-წუთიანი შეხვედრა პირდაპირ ჩემს კალენდარში</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -41416,7 +41428,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>სურვილისამებრ - თუ გსურს უფრო სიღრმისეულად მომზადება</t>
+          <t>სურვილისამებრ — თუ გსურს უფრო საფუძვლიანად მომზადება</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -41500,7 +41512,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>არ არის სავალდებულო. მაგრამ თუ გსურს, ჩვენი 20 წუთი პირდაპირ გადაწყვეტაზე ორიენტირებული იყოს, ეს ის კითხვებია, რითაც ყოველთვის ვიწყებ.</t>
+          <t>არ არის სავალდებულო. თუმცა თუ გსურს, რომ ჩვენი 20 წუთი მაქსიმალურად შედეგიანი იყოს, ეს ის კითხვებია, რითაც ყოველთვის ვიწყებ.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -41710,7 +41722,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>რა არის შენი სავარაუდო საორიენტაციო ბიუჯეტი? (ეს არ არის ვალდებულება, უბრალოდ იმისთვის, რომ არ შემოგთავაზოთ ისეთი რამ, რაც შენს შესაძლებლობებს არ შეესაბამება).</t>
+          <t>რა არის შენი საორიენტაციო ბიუჯეტი? (ეს არ წარმოადგენს ვალდებულებას — უბრალოდ გვეხმარება, შემოგთავაზოთ მხოლოდ შენს შესაძლებლობებზე მორგებული გადაწყვეტა).</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -41958,7 +41970,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>დადასტურება და Google Meet-ის ბმული მაშინვე მოგივა ელფოსტაზე.</t>
+          <t>დადასტურება და Google Meet-ის ბმული მომენტალურად გამოიგზავნება შენს ელფოსტაზე.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -42118,7 +42130,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>ჩამოტვირთე PDF ბონუსად</t>
+          <t>ჩამოტვირთე ბონუს PDF</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -42156,7 +42168,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;დაპირებული ბონუსი:&lt;/b&gt;&lt;br&gt;10 ინსტრუმენტი, რომელსაც ყოველდღიურად ვიყენებ - შენ და შენს გუნდს დაგეხმარებათ ყოველდღიური პროდუქტიულობის გაზრდაში და უამრავ დროს დაგაზოგინებთ.</t>
+          <t>&lt;b&gt;დაპირებული ბონუსი:&lt;/b&gt;&lt;br&gt;10 ინსტრუმენტი, რომელსაც ყოველდღიურად ვიყენებ — დაეხმარება შენს გუნდს პროდუქტიულობის გაზრდაში და დაგიზოგავთ უამრავ დროს.</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$323</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$352</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$238</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
@@ -6838,7 +6838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -14903,34 +14903,30 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
-        </is>
-      </c>
-      <c r="D210" s="9" t="inlineStr">
-        <is>
-          <t>Choose where to start</t>
-        </is>
-      </c>
-      <c r="E210" s="9" t="inlineStr">
-        <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
-        </is>
-      </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>Выберите, с чего начать</t>
-        </is>
-      </c>
-      <c r="G210" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.ba.before</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Without CRM</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>CRM-ის გარეშე</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>Без CRM</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr"/>
       <c r="H210" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14945,34 +14941,30 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
-        </is>
-      </c>
-      <c r="D211" s="9" t="inlineStr">
-        <is>
-          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
-        </is>
-      </c>
-      <c r="E211" s="9" t="inlineStr">
-        <is>
-          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
-        </is>
-      </c>
-      <c r="F211" s="9" t="inlineStr">
-        <is>
-          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
-        </is>
-      </c>
-      <c r="G211" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.ba.after</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>With Zoho CRM</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>Zoho CRM-ით</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>С Zoho CRM</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr"/>
       <c r="H211" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14987,34 +14979,30 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
-        </is>
-      </c>
-      <c r="D212" s="9" t="inlineStr">
-        <is>
-          <t>Most popular</t>
-        </is>
-      </c>
-      <c r="E212" s="9" t="inlineStr">
-        <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
-        </is>
-      </c>
-      <c r="F212" s="9" t="inlineStr">
-        <is>
-          <t>Выбирают чаще всего</t>
-        </is>
-      </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.ba.hint</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Switch to see the same situation with a CRM</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>Переключите и посмотрите то же самое с CRM</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr"/>
       <c r="H212" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15029,34 +15017,30 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
-        </is>
-      </c>
-      <c r="D213" s="9" t="inlineStr">
-        <is>
-          <t>one-time, + VAT</t>
-        </is>
-      </c>
-      <c r="E213" s="9" t="inlineStr">
-        <is>
-          <t>ერთჯერადად, + დღგ</t>
-        </is>
-      </c>
-      <c r="F213" s="9" t="inlineStr">
-        <is>
-          <t>разово, + НДС</t>
-        </is>
-      </c>
-      <c r="G213" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.ba.peek</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>See the result with CRM</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>ნახე შედეგი CRM-ით</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>Посмотреть результат с CRM</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr"/>
       <c r="H213" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15071,34 +15055,30 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
-        </is>
-      </c>
-      <c r="D214" s="9" t="inlineStr">
-        <is>
-          <t>working days</t>
-        </is>
-      </c>
-      <c r="E214" s="9" t="inlineStr">
-        <is>
-          <t>სამუშაო დღე</t>
-        </is>
-      </c>
-      <c r="F214" s="9" t="inlineStr">
-        <is>
-          <t>рабочих дней</t>
-        </is>
-      </c>
-      <c r="G214" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.excel.atitle</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>The client's full history in one search</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>Вся история клиента — в одном поиске</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr"/>
       <c r="H214" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15113,34 +15093,30 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>pk.full</t>
-        </is>
-      </c>
-      <c r="D215" s="9" t="inlineStr">
-        <is>
-          <t>Everything included</t>
-        </is>
-      </c>
-      <c r="E215" s="9" t="inlineStr">
-        <is>
-          <t>სრული ჩამონათვალი</t>
-        </is>
-      </c>
-      <c r="F215" s="9" t="inlineStr">
-        <is>
-          <t>Всё, что входит</t>
-        </is>
-      </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.owner.atitle</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>The team knows who does what</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>Команда знает, кто что делает</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr"/>
       <c r="H215" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15155,34 +15131,30 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
-        </is>
-      </c>
-      <c r="D216" s="9" t="inlineStr">
-        <is>
-          <t>Choose this package</t>
-        </is>
-      </c>
-      <c r="E216" s="9" t="inlineStr">
-        <is>
-          <t>ამ პაკეტის არჩევა</t>
-        </is>
-      </c>
-      <c r="F216" s="9" t="inlineStr">
-        <is>
-          <t>Выбрать этот пакет</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.chats.atitle</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Every message in one window</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>Все сообщения — в одном окне</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr"/>
       <c r="H216" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15197,34 +15169,30 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
-        </is>
-      </c>
-      <c r="D217" s="9" t="inlineStr">
-        <is>
-          <t>Selected</t>
-        </is>
-      </c>
-      <c r="E217" s="9" t="inlineStr">
-        <is>
-          <t>არჩეულია</t>
-        </is>
-      </c>
-      <c r="F217" s="9" t="inlineStr">
-        <is>
-          <t>Выбран</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.contacts</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Contacts</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>კონტაქტები</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr"/>
       <c r="H217" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15239,34 +15207,30 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
-        </is>
-      </c>
-      <c r="D218" s="9" t="inlineStr">
-        <is>
-          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
-        </is>
-      </c>
-      <c r="E218" s="9" t="inlineStr">
-        <is>
-          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
-        </is>
-      </c>
-      <c r="F218" s="9" t="inlineStr">
-        <is>
-          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.found</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>1 result</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>1 შედეგი</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>1 результат</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr"/>
       <c r="H218" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15281,34 +15245,30 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>pk.cur</t>
-        </is>
-      </c>
-      <c r="D219" s="9" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E219" s="9" t="inlineStr">
-        <is>
-          <t>ვალუტა</t>
-        </is>
-      </c>
-      <c r="F219" s="9" t="inlineStr">
-        <is>
-          <t>Валюта</t>
-        </is>
-      </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.stage</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>შეთავაზება</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>Предложение</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr"/>
       <c r="H219" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15323,34 +15283,30 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
-        </is>
-      </c>
-      <c r="D220" s="9" t="inlineStr">
-        <is>
-          <t>Extra features</t>
-        </is>
-      </c>
-      <c r="E220" s="9" t="inlineStr">
-        <is>
-          <t>დამატებითი ფუნქციები</t>
-        </is>
-      </c>
-      <c r="F220" s="9" t="inlineStr">
-        <is>
-          <t>Дополнительные функции</t>
-        </is>
-      </c>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.last</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Last purchase</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>ბოლო შეძენა</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>Последняя покупка</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr"/>
       <c r="H220" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15365,34 +15321,30 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
-        </is>
-      </c>
-      <c r="D221" s="9" t="inlineStr">
-        <is>
-          <t>Optional. Add only if you need them</t>
-        </is>
-      </c>
-      <c r="E221" s="9" t="inlineStr">
-        <is>
-          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
-        </is>
-      </c>
-      <c r="F221" s="9" t="inlineStr">
-        <is>
-          <t>Необязательно. Добавьте, если нужно</t>
-        </is>
-      </c>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.deals</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Deals</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>გარიგებები</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>Сделки</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr"/>
       <c r="H221" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15407,34 +15359,30 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>ao.popular</t>
-        </is>
-      </c>
-      <c r="D222" s="9" t="inlineStr">
-        <is>
-          <t>Often added</t>
-        </is>
-      </c>
-      <c r="E222" s="9" t="inlineStr">
-        <is>
-          <t>ხშირად ამატებენ</t>
-        </is>
-      </c>
-      <c r="F222" s="9" t="inlineStr">
-        <is>
-          <t>Часто добавляют</t>
-        </is>
-      </c>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.merged</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate merged</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>დუბლიკატი გაერთიანდა</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>Дубликат объединён</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr"/>
       <c r="H222" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15449,34 +15397,30 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>ao.more</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
-        <is>
-          <t>All add-ons by category</t>
-        </is>
-      </c>
-      <c r="E223" s="9" t="inlineStr">
-        <is>
-          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
-        </is>
-      </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>Все дополнения по категориям</t>
-        </is>
-      </c>
-      <c r="G223" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.tasks</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>დავალებები</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Задачи</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr"/>
       <c r="H223" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15491,34 +15435,30 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
-        </is>
-      </c>
-      <c r="D224" s="9" t="inlineStr">
-        <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
-        </is>
-      </c>
-      <c r="E224" s="9" t="inlineStr">
-        <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
-        </is>
-      </c>
-      <c r="F224" s="9" t="inlineStr">
-        <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
-        </is>
-      </c>
-      <c r="G224" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.ontrack</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>On track</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>გეგმაშია</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>По плану</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr"/>
       <c r="H224" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15533,34 +15473,30 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
-        </is>
-      </c>
-      <c r="D225" s="9" t="inlineStr">
-        <is>
-          <t>Choose a package</t>
-        </is>
-      </c>
-      <c r="E225" s="9" t="inlineStr">
-        <is>
-          <t>აირჩიე პაკეტი</t>
-        </is>
-      </c>
-      <c r="F225" s="9" t="inlineStr">
-        <is>
-          <t>Выберите пакет</t>
-        </is>
-      </c>
-      <c r="G225" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.t1</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Call the client</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>კლიენტთან ზარი</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>Звонок клиенту</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr"/>
       <c r="H225" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15575,34 +15511,30 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
-        </is>
-      </c>
-      <c r="D226" s="9" t="inlineStr">
-        <is>
-          <t>features</t>
-        </is>
-      </c>
-      <c r="E226" s="9" t="inlineStr">
-        <is>
-          <t>ფუნქცია</t>
-        </is>
-      </c>
-      <c r="F226" s="9" t="inlineStr">
-        <is>
-          <t>функц.</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.t2</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Invoice on rs.ge</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>ინვოისი rs.ge-ზე</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>Счёт на rs.ge</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr"/>
       <c r="H226" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15617,34 +15549,30 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
-        </is>
-      </c>
-      <c r="D227" s="9" t="inlineStr">
-        <is>
-          <t>+ VAT</t>
-        </is>
-      </c>
-      <c r="E227" s="9" t="inlineStr">
-        <is>
-          <t>+ დღგ</t>
-        </is>
-      </c>
-      <c r="F227" s="9" t="inlineStr">
-        <is>
-          <t>+ НДС</t>
-        </is>
-      </c>
-      <c r="G227" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.t3</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Send the price</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>ფასის გაგზავნა</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>Отправить цену</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr"/>
       <c r="H227" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15659,34 +15587,30 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
-        </is>
-      </c>
-      <c r="D228" s="9" t="inlineStr">
-        <is>
-          <t>Request a call</t>
-        </is>
-      </c>
-      <c r="E228" s="9" t="inlineStr">
-        <is>
-          <t>მოითხოვე ზარი</t>
-        </is>
-      </c>
-      <c r="F228" s="9" t="inlineStr">
-        <is>
-          <t>Запросить звонок</t>
-        </is>
-      </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.t4</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Weekly report</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>კვირის რეპორტი</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>Недельный отчёт</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr"/>
       <c r="H228" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15701,34 +15625,30 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
-        </is>
-      </c>
-      <c r="D229" s="9" t="inlineStr">
-        <is>
-          <t>Your selection:</t>
-        </is>
-      </c>
-      <c r="E229" s="9" t="inlineStr">
-        <is>
-          <t>შენი არჩევანი:</t>
-        </is>
-      </c>
-      <c r="F229" s="9" t="inlineStr">
-        <is>
-          <t>Ваш выбор:</t>
-        </is>
-      </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.n1</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Nika</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>ნიკა</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>Ника</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr"/>
       <c r="H229" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15743,34 +15663,30 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
-        </is>
-      </c>
-      <c r="D230" s="9" t="inlineStr">
-        <is>
-          <t>Starter</t>
-        </is>
-      </c>
-      <c r="E230" s="9" t="inlineStr">
-        <is>
-          <t>სტარტი</t>
-        </is>
-      </c>
-      <c r="F230" s="9" t="inlineStr">
-        <is>
-          <t>Старт</t>
-        </is>
-      </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.n2</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ანა</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>Анна</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr"/>
       <c r="H230" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15785,34 +15701,30 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.short</t>
-        </is>
-      </c>
-      <c r="D231" s="9" t="inlineStr">
-        <is>
-          <t>To move from Excel into a CRM</t>
-        </is>
-      </c>
-      <c r="E231" s="9" t="inlineStr">
-        <is>
-          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
-        </is>
-      </c>
-      <c r="F231" s="9" t="inlineStr">
-        <is>
-          <t>Чтобы перейти с Excel на CRM</t>
-        </is>
-      </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.n3</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Luka</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>ლუკა</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>Лука</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr"/>
       <c r="H231" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15827,34 +15739,30 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h1</t>
-        </is>
-      </c>
-      <c r="D232" s="9" t="inlineStr">
-        <is>
-          <t>4 core modules</t>
-        </is>
-      </c>
-      <c r="E232" s="9" t="inlineStr">
-        <is>
-          <t>4 ძირითადი მოდული</t>
-        </is>
-      </c>
-      <c r="F232" s="9" t="inlineStr">
-        <is>
-          <t>4 базовых модуля</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.done</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>შესრულდა</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr"/>
       <c r="H232" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15869,34 +15777,30 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h2</t>
-        </is>
-      </c>
-      <c r="D233" s="9" t="inlineStr">
-        <is>
-          <t>Email and Facebook inside the CRM</t>
-        </is>
-      </c>
-      <c r="E233" s="9" t="inlineStr">
-        <is>
-          <t>ელფოსტა და Facebook CRM-ში</t>
-        </is>
-      </c>
-      <c r="F233" s="9" t="inlineStr">
-        <is>
-          <t>Почта и Facebook внутри CRM</t>
-        </is>
-      </c>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.auto</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>ავტომატური</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>Авто</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr"/>
       <c r="H233" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15911,34 +15815,30 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h3</t>
-        </is>
-      </c>
-      <c r="D234" s="9" t="inlineStr">
-        <is>
-          <t>Lead form and KPI dashboard</t>
-        </is>
-      </c>
-      <c r="E234" s="9" t="inlineStr">
-        <is>
-          <t>ლიდების ფორმა და KPI დაფა</t>
-        </is>
-      </c>
-      <c r="F234" s="9" t="inlineStr">
-        <is>
-          <t>Форма лидов и дашборд KPI</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.everymon</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Every Monday</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>ყოველ ორშაბათს</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>Каждый понедельник</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr"/>
       <c r="H234" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15953,34 +15853,30 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
-        </is>
-      </c>
-      <c r="D235" s="9" t="inlineStr">
-        <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
-        </is>
-      </c>
-      <c r="E235" s="9" t="inlineStr">
-        <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
-        </is>
-      </c>
-      <c r="F235" s="9" t="inlineStr">
-        <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.reminder</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Reminder sent to Luka</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>ლუკას შეხსენება გაეგზავნა</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>Луке отправлено напоминание</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr"/>
       <c r="H235" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15995,34 +15891,30 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
-        </is>
-      </c>
-      <c r="D236" s="9" t="inlineStr">
-        <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
-        </is>
-      </c>
-      <c r="E236" s="9" t="inlineStr">
-        <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
-        </is>
-      </c>
-      <c r="F236" s="9" t="inlineStr">
-        <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.inbox</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Inbox</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>შეტყობინებები</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>Сообщения</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr"/>
       <c r="H236" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16037,34 +15929,30 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
-        </is>
-      </c>
-      <c r="D237" s="9" t="inlineStr">
-        <is>
-          <t>Facebook messages right inside the CRM</t>
-        </is>
-      </c>
-      <c r="E237" s="9" t="inlineStr">
-        <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
-        </is>
-      </c>
-      <c r="F237" s="9" t="inlineStr">
-        <is>
-          <t>Сообщения Facebook прямо в CRM</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.zero</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>0 unanswered</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>0 უპასუხო</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>0 без ответа</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr"/>
       <c r="H237" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16079,34 +15967,30 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
-        </is>
-      </c>
-      <c r="D238" s="9" t="inlineStr">
-        <is>
-          <t>1 web form to capture leads</t>
-        </is>
-      </c>
-      <c r="E238" s="9" t="inlineStr">
-        <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
-        </is>
-      </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>1 веб-форма для приёма лидов</t>
-        </is>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.min</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>წთ</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>мин</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr"/>
       <c r="H238" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16126,22 +16010,22 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
+          <t>pk.title</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>1 sales-pipeline KPI dashboard</t>
+          <t>Choose where to start</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
+          <t>აირჩიე, საიდან დაიწყო</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>Дашборд KPI воронки продаж</t>
+          <t>Выберите, с чего начать</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16168,22 +16052,22 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
+          <t>pk.sub</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>Recorded video instructions for the team</t>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>Видеоинструкции для команды</t>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16210,22 +16094,22 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>Essentials</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალური</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Оптимальный</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16252,22 +16136,22 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.short</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>For a 5-10 person sales team</t>
+          <t>one-time, + VAT</t>
         </is>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
+          <t>ერთჯერადად, + დღგ</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>Для отдела продаж из 5-10 человек</t>
+          <t>разово, + НДС</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16294,22 +16178,22 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter, plus:</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта», плюс:</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -16336,22 +16220,22 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h1</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта»</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -16378,22 +16262,22 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h2</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads, automatically</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16420,22 +16304,22 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h3</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>Stage rules and lead assignment</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>Правила этапов и распределение лидов</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -16462,22 +16346,22 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16504,22 +16388,22 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -16541,27 +16425,27 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -16583,27 +16467,27 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16625,27 +16509,27 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -16667,27 +16551,27 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -16709,27 +16593,27 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -16751,27 +16635,27 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -16793,27 +16677,27 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -16835,27 +16719,27 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -16877,27 +16761,27 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.short</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>For a growing 15-25 person team</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>Для растущей команды из 15-25 человек</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -16919,27 +16803,27 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -16966,22 +16850,22 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h1</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального»</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -17008,22 +16892,22 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h2</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Telephony and call processing</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია და ზარების დამუშავება</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Телефония и обработка звонков</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17050,22 +16934,22 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h3</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Automations and AI (Claude)</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და AI (Claude)</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>Автоматизации и AI (Claude)</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -17092,22 +16976,22 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -17134,22 +17018,22 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -17176,22 +17060,22 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -17218,22 +17102,22 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -17260,22 +17144,22 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17302,22 +17186,22 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -17344,22 +17228,22 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -17386,22 +17270,22 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -17428,22 +17312,22 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -17465,27 +17349,27 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -17507,27 +17391,27 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -17549,27 +17433,27 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -17591,27 +17475,27 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -17633,27 +17517,27 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>ao.18</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG bank wire deposit matching</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Автосверка переводов TBC/BOG</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -17675,27 +17559,27 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>ao.30</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -17717,27 +17601,27 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>ao.38</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -17759,27 +17643,27 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -17801,17 +17685,17 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
@@ -17821,7 +17705,7 @@
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -17843,27 +17727,27 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -17885,27 +17769,27 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -17927,27 +17811,27 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -17969,27 +17853,27 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -18011,27 +17895,27 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -18053,27 +17937,27 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -18095,27 +17979,27 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოების აღრიცხვა</t>
+          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -18137,27 +18021,27 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -18179,27 +18063,27 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>ao.12</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Email + calendar 2-way sync</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -18221,27 +18105,27 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>ao.13</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Возврат пропущенных звонков и SMS</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -18263,27 +18147,27 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>ao.14</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Messaging bot lead capture webhook</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -18305,27 +18189,27 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -18347,27 +18231,27 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>ao.15</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Website lead form + webhook</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + webhook</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + webhook</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -18389,27 +18273,27 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>ao.16</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>ROI источников и атрибуция кампаний</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -18431,27 +18315,27 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>ao.17</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -18473,27 +18357,27 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -18515,27 +18399,27 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>ao.19</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -18557,27 +18441,27 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>ao.20</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>NBG daily exchange rate sync</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Ежедневный курс НБГ</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -18599,27 +18483,27 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>ao.21</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>Ambiguous payment reference fallback queue</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>Очередь неопознанных платежей</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -18641,27 +18525,27 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>ao.22</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Dynamic installment payment schedule</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>График рассрочки</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -18688,22 +18572,22 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>ao.23</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>SMS о просроченной задолженности</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -18730,22 +18614,22 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>ao.24</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>SMS gateway &amp; OTP verification</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>SMS-шлюз и OTP-верификация</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -18772,22 +18656,22 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -18814,22 +18698,22 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>ao.25</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -18856,22 +18740,22 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>ao.26</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Multi-tier SLA escalation matrix</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Матрица эскалации SLA</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -18898,22 +18782,22 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>ao.27</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Оценка NPS/CSAT после тикета</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -18940,22 +18824,22 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>ao.28</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Dynamic KYC intake smart form</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>Умная KYC-форма</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -18982,22 +18866,22 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>ao.29</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Warranty expiration alerts</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>Напоминания об окончании гарантии</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -19024,22 +18908,22 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -19066,22 +18950,22 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>ao.31</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Georgian voice meeting transcription</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>Транскрипция встреч на грузинском</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -19108,22 +18992,22 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>ao.32</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Audio call sentiment extractor</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Анализ тональности звонков</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -19150,22 +19034,22 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ind</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Industry solutions</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>დარგობრივი</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>Отраслевые</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -19192,22 +19076,22 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>ao.33</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -19234,22 +19118,22 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>ao.34</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Client preference proactive matcher</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Автоподбор по пожеланиям клиента</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -19276,22 +19160,22 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ao.35</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Reservation expiration timer</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Таймер истечения брони</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -19318,22 +19202,22 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>ao.36</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+          <t>ბროკერების საკომისიოების აღრიცხვა</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>PDF планировки и предложения</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -19360,22 +19244,22 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>ao.37</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Field service visit tracking + approval</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>Учёт выездов и подтверждение</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -19402,22 +19286,22 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.12</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Email + calendar 2-way sync</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>Двусторонняя синхронизация почты и календаря</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -19444,22 +19328,22 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ao.39</t>
+          <t>ao.13</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>Cold storage WMS &amp; automated billing</t>
+          <t>Missed-call recovery &amp; SMS callback</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>WMS холодного склада и биллинг</t>
+          <t>Возврат пропущенных звонков и SMS</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -19486,22 +19370,22 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>ao.40</t>
+          <t>ao.14</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Construction operations &amp; budget tracker</t>
+          <t>Messaging bot lead capture webhook</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Стройка: операции и бюджет</t>
+          <t>Лиды из чат-бота сразу в CRM</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -19528,22 +19412,22 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ao.41</t>
+          <t>ao.cat.mkt</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Predictive debtor call queue</t>
+          <t>Marketing &amp; growth</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+          <t>მარკეტინგი</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Умная очередь звонков должникам</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -19570,22 +19454,22 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>ao.42</t>
+          <t>ao.15</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Agent attendance tracker</t>
+          <t>Website lead form + webhook</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+          <t>საიტის ფორმა + webhook</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Учёт посещаемости агентов</t>
+          <t>Форма сайта + webhook</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -19612,22 +19496,22 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>ao.43</t>
+          <t>ao.16</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>Round-robin appointment balancing</t>
+          <t>Lead source ROI &amp; campaign attribution</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Равномерное распределение встреч</t>
+          <t>ROI источников и атрибуция кампаний</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -19654,39 +19538,1257 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
+          <t>ao.17</t>
+        </is>
+      </c>
+      <c r="D323" s="9" t="inlineStr">
+        <is>
+          <t>Email campaigns: account setup &amp; contact sync</t>
+        </is>
+      </c>
+      <c r="E323" s="9" t="inlineStr">
+        <is>
+          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+        </is>
+      </c>
+      <c r="F323" s="9" t="inlineStr">
+        <is>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
+        </is>
+      </c>
+      <c r="G323" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.fin</t>
+        </is>
+      </c>
+      <c r="D324" s="9" t="inlineStr">
+        <is>
+          <t>Fintech &amp; accounting</t>
+        </is>
+      </c>
+      <c r="E324" s="9" t="inlineStr">
+        <is>
+          <t>ფინანსები და ბანკები</t>
+        </is>
+      </c>
+      <c r="F324" s="9" t="inlineStr">
+        <is>
+          <t>Финансы и банки</t>
+        </is>
+      </c>
+      <c r="G324" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H324" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>ao.19</t>
+        </is>
+      </c>
+      <c r="D325" s="9" t="inlineStr">
+        <is>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="E325" s="9" t="inlineStr">
+        <is>
+          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="F325" s="9" t="inlineStr">
+        <is>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="G325" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H325" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>ao.20</t>
+        </is>
+      </c>
+      <c r="D326" s="9" t="inlineStr">
+        <is>
+          <t>NBG daily exchange rate sync</t>
+        </is>
+      </c>
+      <c r="E326" s="9" t="inlineStr">
+        <is>
+          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+        </is>
+      </c>
+      <c r="F326" s="9" t="inlineStr">
+        <is>
+          <t>Ежедневный курс НБГ</t>
+        </is>
+      </c>
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H326" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>ao.21</t>
+        </is>
+      </c>
+      <c r="D327" s="9" t="inlineStr">
+        <is>
+          <t>Ambiguous payment reference fallback queue</t>
+        </is>
+      </c>
+      <c r="E327" s="9" t="inlineStr">
+        <is>
+          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+        </is>
+      </c>
+      <c r="F327" s="9" t="inlineStr">
+        <is>
+          <t>Очередь неопознанных платежей</t>
+        </is>
+      </c>
+      <c r="G327" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H327" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>ao.22</t>
+        </is>
+      </c>
+      <c r="D328" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic installment payment schedule</t>
+        </is>
+      </c>
+      <c r="E328" s="9" t="inlineStr">
+        <is>
+          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+        </is>
+      </c>
+      <c r="F328" s="9" t="inlineStr">
+        <is>
+          <t>График рассрочки</t>
+        </is>
+      </c>
+      <c r="G328" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H328" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>ao.23</t>
+        </is>
+      </c>
+      <c r="D329" s="9" t="inlineStr">
+        <is>
+          <t>Overdue debt alert &amp; SMS warning</t>
+        </is>
+      </c>
+      <c r="E329" s="9" t="inlineStr">
+        <is>
+          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+        </is>
+      </c>
+      <c r="F329" s="9" t="inlineStr">
+        <is>
+          <t>SMS о просроченной задолженности</t>
+        </is>
+      </c>
+      <c r="G329" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="inlineStr">
+        <is>
+          <t>ao.24</t>
+        </is>
+      </c>
+      <c r="D330" s="9" t="inlineStr">
+        <is>
+          <t>SMS gateway &amp; OTP verification</t>
+        </is>
+      </c>
+      <c r="E330" s="9" t="inlineStr">
+        <is>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+        </is>
+      </c>
+      <c r="F330" s="9" t="inlineStr">
+        <is>
+          <t>SMS-шлюз и OTP-верификация</t>
+        </is>
+      </c>
+      <c r="G330" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H330" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.cx</t>
+        </is>
+      </c>
+      <c r="D331" s="9" t="inlineStr">
+        <is>
+          <t>Customer experience</t>
+        </is>
+      </c>
+      <c r="E331" s="9" t="inlineStr">
+        <is>
+          <t>მომხმარებლის მომსახურება</t>
+        </is>
+      </c>
+      <c r="F331" s="9" t="inlineStr">
+        <is>
+          <t>Клиентский сервис</t>
+        </is>
+      </c>
+      <c r="G331" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>ao.25</t>
+        </is>
+      </c>
+      <c r="D332" s="9" t="inlineStr">
+        <is>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="E332" s="9" t="inlineStr">
+        <is>
+          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="F332" s="9" t="inlineStr">
+        <is>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H332" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>ao.26</t>
+        </is>
+      </c>
+      <c r="D333" s="9" t="inlineStr">
+        <is>
+          <t>Multi-tier SLA escalation matrix</t>
+        </is>
+      </c>
+      <c r="E333" s="9" t="inlineStr">
+        <is>
+          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+        </is>
+      </c>
+      <c r="F333" s="9" t="inlineStr">
+        <is>
+          <t>Матрица эскалации SLA</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H333" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>ao.27</t>
+        </is>
+      </c>
+      <c r="D334" s="9" t="inlineStr">
+        <is>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
+        </is>
+      </c>
+      <c r="E334" s="9" t="inlineStr">
+        <is>
+          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+        </is>
+      </c>
+      <c r="F334" s="9" t="inlineStr">
+        <is>
+          <t>Оценка NPS/CSAT после тикета</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>ao.28</t>
+        </is>
+      </c>
+      <c r="D335" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic KYC intake smart form</t>
+        </is>
+      </c>
+      <c r="E335" s="9" t="inlineStr">
+        <is>
+          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+        </is>
+      </c>
+      <c r="F335" s="9" t="inlineStr">
+        <is>
+          <t>Умная KYC-форма</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>ao.29</t>
+        </is>
+      </c>
+      <c r="D336" s="9" t="inlineStr">
+        <is>
+          <t>Warranty expiration alerts</t>
+        </is>
+      </c>
+      <c r="E336" s="9" t="inlineStr">
+        <is>
+          <t>გარანტიის ვადის შეხსენებები</t>
+        </is>
+      </c>
+      <c r="F336" s="9" t="inlineStr">
+        <is>
+          <t>Напоминания об окончании гарантии</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ai</t>
+        </is>
+      </c>
+      <c r="D337" s="9" t="inlineStr">
+        <is>
+          <t>AI &amp; automation</t>
+        </is>
+      </c>
+      <c r="E337" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F337" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>ao.31</t>
+        </is>
+      </c>
+      <c r="D338" s="9" t="inlineStr">
+        <is>
+          <t>Georgian voice meeting transcription</t>
+        </is>
+      </c>
+      <c r="E338" s="9" t="inlineStr">
+        <is>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+        </is>
+      </c>
+      <c r="F338" s="9" t="inlineStr">
+        <is>
+          <t>Транскрипция встреч на грузинском</t>
+        </is>
+      </c>
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>ao.32</t>
+        </is>
+      </c>
+      <c r="D339" s="9" t="inlineStr">
+        <is>
+          <t>Audio call sentiment extractor</t>
+        </is>
+      </c>
+      <c r="E339" s="9" t="inlineStr">
+        <is>
+          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+        </is>
+      </c>
+      <c r="F339" s="9" t="inlineStr">
+        <is>
+          <t>Анализ тональности звонков</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H339" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ind</t>
+        </is>
+      </c>
+      <c r="D340" s="9" t="inlineStr">
+        <is>
+          <t>Industry solutions</t>
+        </is>
+      </c>
+      <c r="E340" s="9" t="inlineStr">
+        <is>
+          <t>დარგობრივი</t>
+        </is>
+      </c>
+      <c r="F340" s="9" t="inlineStr">
+        <is>
+          <t>Отраслевые</t>
+        </is>
+      </c>
+      <c r="G340" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H340" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>ao.33</t>
+        </is>
+      </c>
+      <c r="D341" s="9" t="inlineStr">
+        <is>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
+        </is>
+      </c>
+      <c r="E341" s="9" t="inlineStr">
+        <is>
+          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+        </is>
+      </c>
+      <c r="F341" s="9" t="inlineStr">
+        <is>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
+        </is>
+      </c>
+      <c r="G341" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>ao.34</t>
+        </is>
+      </c>
+      <c r="D342" s="9" t="inlineStr">
+        <is>
+          <t>Client preference proactive matcher</t>
+        </is>
+      </c>
+      <c r="E342" s="9" t="inlineStr">
+        <is>
+          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+        </is>
+      </c>
+      <c r="F342" s="9" t="inlineStr">
+        <is>
+          <t>Автоподбор по пожеланиям клиента</t>
+        </is>
+      </c>
+      <c r="G342" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>ao.35</t>
+        </is>
+      </c>
+      <c r="D343" s="9" t="inlineStr">
+        <is>
+          <t>Reservation expiration timer</t>
+        </is>
+      </c>
+      <c r="E343" s="9" t="inlineStr">
+        <is>
+          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+        </is>
+      </c>
+      <c r="F343" s="9" t="inlineStr">
+        <is>
+          <t>Таймер истечения брони</t>
+        </is>
+      </c>
+      <c r="G343" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H343" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>ao.36</t>
+        </is>
+      </c>
+      <c r="D344" s="9" t="inlineStr">
+        <is>
+          <t>Floor plan &amp; proposal PDF generator</t>
+        </is>
+      </c>
+      <c r="E344" s="9" t="inlineStr">
+        <is>
+          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+        </is>
+      </c>
+      <c r="F344" s="9" t="inlineStr">
+        <is>
+          <t>PDF планировки и предложения</t>
+        </is>
+      </c>
+      <c r="G344" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H344" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>ao.37</t>
+        </is>
+      </c>
+      <c r="D345" s="9" t="inlineStr">
+        <is>
+          <t>Field service visit tracking + approval</t>
+        </is>
+      </c>
+      <c r="E345" s="9" t="inlineStr">
+        <is>
+          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+        </is>
+      </c>
+      <c r="F345" s="9" t="inlineStr">
+        <is>
+          <t>Учёт выездов и подтверждение</t>
+        </is>
+      </c>
+      <c r="G345" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H345" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ops</t>
+        </is>
+      </c>
+      <c r="D346" s="9" t="inlineStr">
+        <is>
+          <t>Operations &amp; ERP</t>
+        </is>
+      </c>
+      <c r="E346" s="9" t="inlineStr">
+        <is>
+          <t>ოპერაციები და ERP</t>
+        </is>
+      </c>
+      <c r="F346" s="9" t="inlineStr">
+        <is>
+          <t>Операции и ERP</t>
+        </is>
+      </c>
+      <c r="G346" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H346" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>ao.39</t>
+        </is>
+      </c>
+      <c r="D347" s="9" t="inlineStr">
+        <is>
+          <t>Cold storage WMS &amp; automated billing</t>
+        </is>
+      </c>
+      <c r="E347" s="9" t="inlineStr">
+        <is>
+          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+        </is>
+      </c>
+      <c r="F347" s="9" t="inlineStr">
+        <is>
+          <t>WMS холодного склада и биллинг</t>
+        </is>
+      </c>
+      <c r="G347" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H347" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>ao.40</t>
+        </is>
+      </c>
+      <c r="D348" s="9" t="inlineStr">
+        <is>
+          <t>Construction operations &amp; budget tracker</t>
+        </is>
+      </c>
+      <c r="E348" s="9" t="inlineStr">
+        <is>
+          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+        </is>
+      </c>
+      <c r="F348" s="9" t="inlineStr">
+        <is>
+          <t>Стройка: операции и бюджет</t>
+        </is>
+      </c>
+      <c r="G348" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H348" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>ao.41</t>
+        </is>
+      </c>
+      <c r="D349" s="9" t="inlineStr">
+        <is>
+          <t>Predictive debtor call queue</t>
+        </is>
+      </c>
+      <c r="E349" s="9" t="inlineStr">
+        <is>
+          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+        </is>
+      </c>
+      <c r="F349" s="9" t="inlineStr">
+        <is>
+          <t>Умная очередь звонков должникам</t>
+        </is>
+      </c>
+      <c r="G349" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H349" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>ao.42</t>
+        </is>
+      </c>
+      <c r="D350" s="9" t="inlineStr">
+        <is>
+          <t>Agent attendance tracker</t>
+        </is>
+      </c>
+      <c r="E350" s="9" t="inlineStr">
+        <is>
+          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+        </is>
+      </c>
+      <c r="F350" s="9" t="inlineStr">
+        <is>
+          <t>Учёт посещаемости агентов</t>
+        </is>
+      </c>
+      <c r="G350" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H350" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>ao.43</t>
+        </is>
+      </c>
+      <c r="D351" s="9" t="inlineStr">
+        <is>
+          <t>Round-robin appointment balancing</t>
+        </is>
+      </c>
+      <c r="E351" s="9" t="inlineStr">
+        <is>
+          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+        </is>
+      </c>
+      <c r="F351" s="9" t="inlineStr">
+        <is>
+          <t>Равномерное распределение встреч</t>
+        </is>
+      </c>
+      <c r="G351" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H351" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C352" s="3" t="inlineStr">
+        <is>
           <t>ao.44</t>
         </is>
       </c>
-      <c r="D323" s="9" t="inlineStr">
+      <c r="D352" s="9" t="inlineStr">
         <is>
           <t>Discovery call auto-scheduling</t>
         </is>
       </c>
-      <c r="E323" s="9" t="inlineStr">
+      <c r="E352" s="9" t="inlineStr">
         <is>
           <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
-      <c r="F323" s="9" t="inlineStr">
+      <c r="F352" s="9" t="inlineStr">
         <is>
           <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
-      <c r="G323" s="3" t="inlineStr">
+      <c r="G352" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H323" s="3" t="inlineStr">
+      <c r="H352" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H323"/>
+  <autoFilter ref="A1:H352"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H522" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H551" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19700,7 +20802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -27773,10 +28875,1112 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>pain.ba.before</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Without CRM</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>CRM-ის გარეშე</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>Без CRM</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr"/>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>pain.ba.after</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>With Zoho CRM</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>Zoho CRM-ით</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>С Zoho CRM</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr"/>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>pain.ba.hint</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Switch to see the same situation with a CRM</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>Переключите и посмотрите то же самое с CRM</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr"/>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>pain.ba.peek</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>See the result with CRM</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>ნახე შედეგი CRM-ით</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>Посмотреть результат с CRM</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr"/>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>pain.excel.atitle</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>The client's full history in one search</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>Вся история клиента — в одном поиске</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr"/>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>pain.owner.atitle</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>The team knows who does what</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>Команда знает, кто что делает</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr"/>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>pain.chats.atitle</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Every message in one window</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>Все сообщения — в одном окне</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr"/>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.contacts</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Contacts</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>კონტაქტები</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr"/>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.found</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>1 result</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>1 შედეგი</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>1 результат</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr"/>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.stage</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>შეთავაზება</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>Предложение</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr"/>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.last</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Last purchase</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>ბოლო შეძენა</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>Последняя покупка</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr"/>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.deals</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Deals</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>გარიგებები</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>Сделки</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr"/>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.merged</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate merged</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>დუბლიკატი გაერთიანდა</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>Дубликат объединён</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr"/>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.tasks</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>დავალებები</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Задачи</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr"/>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.ontrack</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>On track</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>გეგმაშია</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>По плану</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr"/>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.t1</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Call the client</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>კლიენტთან ზარი</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>Звонок клиенту</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr"/>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.t2</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Invoice on rs.ge</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>ინვოისი rs.ge-ზე</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>Счёт на rs.ge</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr"/>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.t3</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Send the price</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>ფასის გაგზავნა</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>Отправить цену</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr"/>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.t4</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Weekly report</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>კვირის რეპორტი</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>Недельный отчёт</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr"/>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.n1</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Nika</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>ნიკა</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>Ника</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr"/>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.n2</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ანა</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>Анна</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr"/>
+      <c r="H230" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.n3</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Luka</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>ლუკა</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>Лука</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr"/>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.done</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>შესრულდა</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr"/>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.auto</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>ავტომატური</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>Авто</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr"/>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.everymon</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Every Monday</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>ყოველ ორშაბათს</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>Каждый понедельник</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr"/>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.reminder</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Reminder sent to Luka</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>ლუკას შეხსენება გაეგზავნა</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>Луке отправлено напоминание</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr"/>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.inbox</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Inbox</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>შეტყობინებები</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>Сообщения</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr"/>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.zero</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>0 unanswered</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>0 უპასუხო</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>0 без ответа</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr"/>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.min</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>წთ</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>мин</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr"/>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H209"/>
+  <autoFilter ref="A1:H238"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H408" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H437" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -13,11 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed keys" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$352</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$238</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$357</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$173</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -5999,17 +5999,17 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
+          <t>From chaos to steady growth: see the path you'll take with us.</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
+          <t>ქაოსიდან სტაბილურ ზრდამდე: ნახე, რა გზას გაივლი ჩვენთან ერთად.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
+          <t>От хаоса к стабильному росту: посмотрите, какой путь вы пройдёте с нами.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
@@ -6075,17 +6075,17 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>We find the real problem and pick the right tool.</t>
+          <t>Instead of chaos, an exact plan: which tools, what timeline, what budget.</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>ვიგებთ რეალურ პრობლემას და ვარჩევთ სწორ ინსტრუმენტს.</t>
+          <t>ქაოსის ნაცვლად — ზუსტი გეგმა: რა ინსტრუმენტი, რა ვადაში და რა ბიუჯეტით.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Находим реальную проблему и подбираем правильный инструмент.</t>
+          <t>Вместо хаоса — точный план: какие инструменты, сроки и бюджет.</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr"/>
@@ -6108,22 +6108,22 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.1</t>
+          <t>process.1.time</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Review of your processes and current systems</t>
+          <t>First call · 20 min · free</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>პროცესებისა და არსებული სისტემების ანალიზი</t>
+          <t>პირველი ზარი · 20 წთ · უფასო</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Анализ процессов и текущих систем</t>
+          <t>Первый звонок · 20 мин · бесплатно</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr"/>
@@ -6146,22 +6146,22 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.2</t>
+          <t>process.2.name</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>1-3 tools that fit (and what you don't need)</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>1-3 ინსტრუმენტის შერჩევა (და რა არ გჭირდება)</t>
+          <t>დანერგვა</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>1-3 подходящих инструмента (и что вам не нужно)</t>
+          <t>Внедрение</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr"/>
@@ -6184,22 +6184,22 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.3</t>
+          <t>process.2.desc</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Implementation plan, budget and timeline</t>
+          <t>We build the system in short sprints and the business gets stronger. You see first results in 1-2 weeks.</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>დანერგვის გეგმა, ბიუჯეტი და ვადები</t>
+          <t>სისტემას მოკლე სპრინტებით ვაწყობთ და ბიზნესი ძლიერდება. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>План внедрения, бюджет и сроки</t>
+          <t>Мы строим систему короткими спринтами, и бизнес становится сильнее. Первый результат — через 1-2 недели.</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr"/>
@@ -6222,22 +6222,22 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>process.1.time</t>
+          <t>process.2.time</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>First call · 20 min · free</t>
+          <t>Sprint · 1-2 weeks</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>პირველი ზარი · 20 წთ · უფასო</t>
+          <t>სპრინტი · 1-2 კვირა</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Первый звонок · 20 мин · бесплатно</t>
+          <t>Спринт · 1-2 недели</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr"/>
@@ -6260,22 +6260,22 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>process.2.name</t>
+          <t>process.3.name</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>დანერგვა</t>
+          <t>მხარდაჭერა</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Внедрение</t>
+          <t>Поддержка</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr"/>
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>process.2.desc</t>
+          <t>process.3.desc</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>We build the system in short sprints. You see the first result in 1-2 weeks.</t>
+          <t>The system grows with your business, and growth has no ceiling.</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>ვაწყობთ სისტემას მოკლე სპრინტებით. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
+          <t>სისტემა ბიზნესთან ერთად იზრდება და ზრდას ზღვარი არ აქვს.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Строим систему короткими спринтами. Первый результат - через 1-2 недели.</t>
+          <t>Система растёт вместе с бизнесом, и у роста нет потолка.</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr"/>
@@ -6336,22 +6336,22 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.1</t>
+          <t>process.3.time</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>System setup and data migration</t>
+          <t>Ongoing · as needed</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>სისტემის აწყობა და მონაცემების გადატანა</t>
+          <t>მუდმივად · საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Настройка системы и перенос данных</t>
+          <t>Постоянно · по необходимости</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr"/>
@@ -6374,22 +6374,22 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.2</t>
+          <t>process.note</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Automations and integrations</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და ინტეგრაციები</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Автоматизации и интеграции</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr"/>
@@ -6412,22 +6412,22 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.3</t>
+          <t>process.cta</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Team training</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>გუნდის ტრენინგი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Обучение команды</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr"/>
@@ -6445,30 +6445,34 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>process.2.time</t>
+          <t>seo.title</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Sprint · 1-2 weeks</t>
+          <t>Unitty - CRM, AI and automation for your business</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>სპრინტი · 1-2 კვირა</t>
+          <t>Unitty - CRM, AI და ავტომატიზაცია ბიზნესისთვის</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Спринт · 1-2 недели</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr"/>
+          <t>Unitty - CRM, AI и автоматизация для бизнеса</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -6488,22 +6492,22 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>process.3.name</t>
+          <t>process.0.name</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Where you are today</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>მხარდაჭერა</t>
+          <t>დღევანდელი რეალობა</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Поддержка</t>
+          <t>Где вы сейчас</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr"/>
@@ -6526,22 +6530,22 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>process.3.desc</t>
+          <t>process.0.desc</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>The system keeps working after launch and grows with your business.</t>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>სისტემა გაშვების შემდეგაც მუშაობს და იზრდება ბიზნესთან ერთად.</t>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Система продолжает работать после запуска и растёт вместе с бизнесом.</t>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr"/>
@@ -6564,22 +6568,22 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.1</t>
+          <t>process.0.time</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Technical support when you need it</t>
+          <t>Starting point</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>ტექნიკური მხარდაჭერა, როცა გჭირდება</t>
+          <t>საწყისი წერტილი</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Техническая поддержка, когда она нужна</t>
+          <t>Отправная точка</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr"/>
@@ -6602,22 +6606,22 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.2</t>
+          <t>process.chart.chaos</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Ongoing optimization and improvements</t>
+          <t>Chaos</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>მუდმივი ოპტიმიზაცია და განვითარება</t>
+          <t>ქაოსი</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Постоянная оптимизация и развитие</t>
+          <t>Хаос</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr"/>
@@ -6640,22 +6644,22 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.3</t>
+          <t>process.chart.growth</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>New tools added as you need them</t>
+          <t>Growth ∞</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>ახალი ინსტრუმენტების დამატება საჭიროებისამებრ</t>
+          <t>ზრდა ∞</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Новые инструменты - по мере необходимости</t>
+          <t>Рост ∞</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr"/>
@@ -6665,166 +6669,10 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>process.3.time</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Ongoing · as needed</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>მუდმივად · საჭიროებისამებრ</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>Постоянно · по необходимости</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr"/>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>process.note</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Pricing is set individually, based on your needs.</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr"/>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>process.cta</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Request a free 20-minute call</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr"/>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>Seo</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>seo.title</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Unitty - CRM, AI and automation for your business</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>Unitty - CRM, AI და ავტომატიზაცია ბიზნესისთვის</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>Unitty - CRM, AI и автоматизация для бизнеса</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H166"/>
+  <autoFilter ref="A1:H162"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H365" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H361" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6838,7 +6686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H352"/>
+  <dimension ref="A1:H357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -13955,17 +13803,17 @@
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
+          <t>From chaos to steady growth: see the path you'll take with us.</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
+          <t>ქაოსიდან სტაბილურ ზრდამდე: ნახე, რა გზას გაივლი ჩვენთან ერთად.</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
+          <t>От хаоса к стабильному росту: посмотрите, какой путь вы пройдёте с нами.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr"/>
@@ -14031,17 +13879,17 @@
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>We find the real problem and pick the right tool.</t>
+          <t>Instead of chaos, an exact plan: which tools, what timeline, what budget.</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>ვიგებთ რეალურ პრობლემას და ვარჩევთ სწორ ინსტრუმენტს.</t>
+          <t>ქაოსის ნაცვლად — ზუსტი გეგმა: რა ინსტრუმენტი, რა ვადაში და რა ბიუჯეტით.</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Находим реальную проблему и подбираем правильный инструмент.</t>
+          <t>Вместо хаоса — точный план: какие инструменты, сроки и бюджет.</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr"/>
@@ -14064,22 +13912,22 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.1</t>
+          <t>process.1.time</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Review of your processes and current systems</t>
+          <t>First call · 20 min · free</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>პროცესებისა და არსებული სისტემების ანალიზი</t>
+          <t>პირველი ზარი · 20 წთ · უფასო</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Анализ процессов и текущих систем</t>
+          <t>Первый звонок · 20 мин · бесплатно</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr"/>
@@ -14102,22 +13950,22 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.2</t>
+          <t>process.2.name</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>1-3 tools that fit (and what you don't need)</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>1-3 ინსტრუმენტის შერჩევა (და რა არ გჭირდება)</t>
+          <t>დანერგვა</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>1-3 подходящих инструмента (и что вам не нужно)</t>
+          <t>Внедрение</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -14140,22 +13988,22 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.3</t>
+          <t>process.2.desc</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Implementation plan, budget and timeline</t>
+          <t>We build the system in short sprints and the business gets stronger. You see first results in 1-2 weeks.</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>დანერგვის გეგმა, ბიუჯეტი და ვადები</t>
+          <t>სისტემას მოკლე სპრინტებით ვაწყობთ და ბიზნესი ძლიერდება. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>План внедрения, бюджет и сроки</t>
+          <t>Мы строим систему короткими спринтами, и бизнес становится сильнее. Первый результат — через 1-2 недели.</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr"/>
@@ -14178,22 +14026,22 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>process.1.time</t>
+          <t>process.2.time</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>First call · 20 min · free</t>
+          <t>Sprint · 1-2 weeks</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>პირველი ზარი · 20 წთ · უფასო</t>
+          <t>სპრინტი · 1-2 კვირა</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Первый звонок · 20 мин · бесплатно</t>
+          <t>Спринт · 1-2 недели</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr"/>
@@ -14216,22 +14064,22 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>process.2.name</t>
+          <t>process.3.name</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>დანერგვა</t>
+          <t>მხარდაჭერა</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Внедрение</t>
+          <t>Поддержка</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr"/>
@@ -14254,22 +14102,22 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>process.2.desc</t>
+          <t>process.3.desc</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>We build the system in short sprints. You see the first result in 1-2 weeks.</t>
+          <t>The system grows with your business, and growth has no ceiling.</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>ვაწყობთ სისტემას მოკლე სპრინტებით. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
+          <t>სისტემა ბიზნესთან ერთად იზრდება და ზრდას ზღვარი არ აქვს.</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Строим систему короткими спринтами. Первый результат - через 1-2 недели.</t>
+          <t>Система растёт вместе с бизнесом, и у роста нет потолка.</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr"/>
@@ -14292,22 +14140,22 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.1</t>
+          <t>process.3.time</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>System setup and data migration</t>
+          <t>Ongoing · as needed</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>სისტემის აწყობა და მონაცემების გადატანა</t>
+          <t>მუდმივად · საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Настройка системы и перенос данных</t>
+          <t>Постоянно · по необходимости</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr"/>
@@ -14330,25 +14178,29 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.2</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>Automations and integrations</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>ავტომატიზაციები და ინტეგრაციები</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>Автоматизации и интеграции</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr"/>
+          <t>process.note</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>Package prices are fixed. We confirm the right one together on the call.</t>
+        </is>
+      </c>
+      <c r="E195" s="9" t="inlineStr">
+        <is>
+          <t>პაკეტების ფასი ფიქსირებულია. რომელი გჭირდება, ზარზე ერთად დავაზუსტებთ.</t>
+        </is>
+      </c>
+      <c r="F195" s="9" t="inlineStr">
+        <is>
+          <t>Цены пакетов фиксированы. Какой подходит, уточним вместе на звонке.</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14368,22 +14220,22 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.3</t>
+          <t>process.cta</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Team training</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>გუნდის ტრენინგი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Обучение команды</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr"/>
@@ -14401,27 +14253,27 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>process.2.time</t>
+          <t>pain.manager.left</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Sprint · 1-2 weeks</t>
+          <t>Ana left the chat</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>სპრინტი · 1-2 კვირა</t>
+          <t>ანამ დატოვა ჩატი</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Спринт · 1-2 недели</t>
+          <t>Анна покинула чат</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr"/>
@@ -14439,27 +14291,27 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>process.3.name</t>
+          <t>pain.owner.note</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Today!!</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>მხარდაჭერა</t>
+          <t>დღეს!!</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Поддержка</t>
+          <t>Сегодня!!</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr"/>
@@ -14477,27 +14329,27 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>process.3.desc</t>
+          <t>pain.chats.more</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>The system keeps working after launch and grows with your business.</t>
+          <t>+11 unanswered</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>სისტემა გაშვების შემდეგაც მუშაობს და იზრდება ბიზნესთან ერთად.</t>
+          <t>+11 უპასუხო</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Система продолжает работать после запуска и растёт вместе с бизнесом.</t>
+          <t>+11 без ответа</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr"/>
@@ -14515,30 +14367,34 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.1</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>Technical support when you need it</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>ტექნიკური მხარდაჭერა, როცა გჭირდება</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>Техническая поддержка, когда она нужна</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr"/>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="inlineStr">
+        <is>
+          <t>CRM selection and implementation in Georgia | Unitty</t>
+        </is>
+      </c>
+      <c r="E200" s="9" t="inlineStr">
+        <is>
+          <t>CRM-ის შერჩევა და დანერგვა საქართველოში | Unitty</t>
+        </is>
+      </c>
+      <c r="F200" s="9" t="inlineStr">
+        <is>
+          <t>Подбор и внедрение CRM в Грузии | Unitty</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14553,27 +14409,27 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.2</t>
+          <t>pain.ba.before</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Ongoing optimization and improvements</t>
+          <t>Before</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>მუდმივი ოპტიმიზაცია და განვითარება</t>
+          <t>დანერგვამდე</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Постоянная оптимизация и развитие</t>
+          <t>До внедрения</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr"/>
@@ -14591,27 +14447,27 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.3</t>
+          <t>pain.ba.after</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>New tools added as you need them</t>
+          <t>After</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>ახალი ინსტრუმენტების დამატება საჭიროებისამებრ</t>
+          <t>შედეგად</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Новые инструменты - по мере необходимости</t>
+          <t>Результат</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr"/>
@@ -14629,27 +14485,27 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>process.3.time</t>
+          <t>pain.ba.hint</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Ongoing · as needed</t>
+          <t>Switch to see the same situation with a CRM</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>მუდმივად · საჭიროებისამებრ</t>
+          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Постоянно · по необходимости</t>
+          <t>Переключите и посмотрите то же самое с CRM</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr"/>
@@ -14667,34 +14523,30 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>process.note</t>
-        </is>
-      </c>
-      <c r="D204" s="9" t="inlineStr">
-        <is>
-          <t>Package prices are fixed. We confirm the right one together on the call.</t>
-        </is>
-      </c>
-      <c r="E204" s="9" t="inlineStr">
-        <is>
-          <t>პაკეტების ფასი ფიქსირებულია. რომელი გჭირდება, ზარზე ერთად დავაზუსტებთ.</t>
-        </is>
-      </c>
-      <c r="F204" s="9" t="inlineStr">
-        <is>
-          <t>Цены пакетов фиксированы. Какой подходит, уточним вместе на звонке.</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.ba.peek</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>See the result with CRM</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>ნახე შედეგი CRM-ით</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>Посмотреть результат с CRM</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr"/>
       <c r="H204" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14709,27 +14561,27 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>process.cta</t>
+          <t>pain.excel.atitle</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>The client's full history in one search</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Вся история клиента — в одном поиске</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr"/>
@@ -14752,22 +14604,22 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.left</t>
+          <t>pain.owner.atitle</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Ana left the chat</t>
+          <t>The team knows who does what</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>ანამ დატოვა ჩატი</t>
+          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Анна покинула чат</t>
+          <t>Команда знает, кто что делает</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr"/>
@@ -14790,22 +14642,22 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.note</t>
+          <t>pain.chats.atitle</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Today!!</t>
+          <t>Every message in one window</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>დღეს!!</t>
+          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Сегодня!!</t>
+          <t>Все сообщения — в одном окне</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr"/>
@@ -14828,22 +14680,22 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.more</t>
+          <t>pain.z.contacts</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>+11 unanswered</t>
+          <t>Contacts</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>+11 უპასუხო</t>
+          <t>კონტაქტები</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>+11 без ответа</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr"/>
@@ -14861,34 +14713,30 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Seo</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>seo.title</t>
-        </is>
-      </c>
-      <c r="D209" s="9" t="inlineStr">
-        <is>
-          <t>CRM selection and implementation in Georgia | Unitty</t>
-        </is>
-      </c>
-      <c r="E209" s="9" t="inlineStr">
-        <is>
-          <t>CRM-ის შერჩევა და დანერგვა საქართველოში | Unitty</t>
-        </is>
-      </c>
-      <c r="F209" s="9" t="inlineStr">
-        <is>
-          <t>Подбор и внедрение CRM в Грузии | Unitty</t>
-        </is>
-      </c>
-      <c r="G209" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.found</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>1 result</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>1 შედეგი</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>1 результат</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr"/>
       <c r="H209" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14908,22 +14756,22 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.before</t>
+          <t>pain.z.stage</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Without CRM</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>CRM-ის გარეშე</t>
+          <t>შეთავაზება</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Без CRM</t>
+          <t>Предложение</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr"/>
@@ -14946,22 +14794,22 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.after</t>
+          <t>pain.z.last</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>With Zoho CRM</t>
+          <t>Last purchase</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Zoho CRM-ით</t>
+          <t>ბოლო შეძენა</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>С Zoho CRM</t>
+          <t>Последняя покупка</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr"/>
@@ -14984,22 +14832,22 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.hint</t>
+          <t>pain.z.deals</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Switch to see the same situation with a CRM</t>
+          <t>Deals</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
+          <t>გარიგებები</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Переключите и посмотрите то же самое с CRM</t>
+          <t>Сделки</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr"/>
@@ -15022,22 +14870,22 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.peek</t>
+          <t>pain.z.merged</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>See the result with CRM</t>
+          <t>Duplicate merged</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>ნახე შედეგი CRM-ით</t>
+          <t>დუბლიკატი გაერთიანდა</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Посмотреть результат с CRM</t>
+          <t>Дубликат объединён</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr"/>
@@ -15060,22 +14908,22 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.atitle</t>
+          <t>pain.z.tasks</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>The client's full history in one search</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
+          <t>დავალებები</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Вся история клиента — в одном поиске</t>
+          <t>Задачи</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr"/>
@@ -15098,22 +14946,22 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.atitle</t>
+          <t>pain.z.ontrack</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>The team knows who does what</t>
+          <t>On track</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
+          <t>გეგმაშია</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Команда знает, кто что делает</t>
+          <t>По плану</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr"/>
@@ -15136,22 +14984,22 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.atitle</t>
+          <t>pain.z.t1</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Every message in one window</t>
+          <t>Call the client</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
+          <t>კლიენტთან ზარი</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Все сообщения — в одном окне</t>
+          <t>Звонок клиенту</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr"/>
@@ -15174,22 +15022,22 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>pain.z.contacts</t>
+          <t>pain.z.t2</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Invoice on rs.ge</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>კონტაქტები</t>
+          <t>ინვოისი rs.ge-ზე</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Счёт на rs.ge</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr"/>
@@ -15212,22 +15060,22 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>pain.z.found</t>
+          <t>pain.z.t3</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>1 result</t>
+          <t>Send the price</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>1 შედეგი</t>
+          <t>ფასის გაგზავნა</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>1 результат</t>
+          <t>Отправить цену</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr"/>
@@ -15250,22 +15098,22 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>pain.z.stage</t>
+          <t>pain.z.t4</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Weekly report</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>შეთავაზება</t>
+          <t>კვირის რეპორტი</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Предложение</t>
+          <t>Недельный отчёт</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr"/>
@@ -15288,22 +15136,22 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>pain.z.last</t>
+          <t>pain.z.n1</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Last purchase</t>
+          <t>Nika</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>ბოლო შეძენა</t>
+          <t>ნიკა</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Последняя покупка</t>
+          <t>Ника</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr"/>
@@ -15326,22 +15174,22 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>pain.z.deals</t>
+          <t>pain.z.n2</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Deals</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>გარიგებები</t>
+          <t>ანა</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Сделки</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr"/>
@@ -15364,22 +15212,22 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>pain.z.merged</t>
+          <t>pain.z.n3</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Duplicate merged</t>
+          <t>Luka</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>დუბლიკატი გაერთიანდა</t>
+          <t>ლუკა</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Дубликат объединён</t>
+          <t>Лука</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr"/>
@@ -15402,22 +15250,22 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>pain.z.tasks</t>
+          <t>pain.z.done</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>დავალებები</t>
+          <t>შესრულდა</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Задачи</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr"/>
@@ -15440,22 +15288,22 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>pain.z.ontrack</t>
+          <t>pain.z.auto</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>On track</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>გეგმაშია</t>
+          <t>ავტომატური</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>По плану</t>
+          <t>Авто</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr"/>
@@ -15478,22 +15326,22 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t1</t>
+          <t>pain.z.everymon</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Call the client</t>
+          <t>Every Monday</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>კლიენტთან ზარი</t>
+          <t>ყოველ ორშაბათს</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Звонок клиенту</t>
+          <t>Каждый понедельник</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr"/>
@@ -15516,22 +15364,22 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t2</t>
+          <t>pain.z.reminder</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Invoice on rs.ge</t>
+          <t>Reminder sent to Luka</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>ინვოისი rs.ge-ზე</t>
+          <t>ლუკას შეხსენება გაეგზავნა</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Счёт на rs.ge</t>
+          <t>Луке отправлено напоминание</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr"/>
@@ -15554,22 +15402,22 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t3</t>
+          <t>pain.z.inbox</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Send the price</t>
+          <t>Inbox</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>ფასის გაგზავნა</t>
+          <t>შეტყობინებები</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Отправить цену</t>
+          <t>Сообщения</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr"/>
@@ -15592,22 +15440,22 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t4</t>
+          <t>pain.z.zero</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Weekly report</t>
+          <t>0 unanswered</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>კვირის რეპორტი</t>
+          <t>0 უპასუხო</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Недельный отчёт</t>
+          <t>0 без ответа</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr"/>
@@ -15630,22 +15478,22 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n1</t>
+          <t>pain.z.min</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Nika</t>
+          <t>min</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>ნიკა</t>
+          <t>წთ</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Ника</t>
+          <t>мин</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr"/>
@@ -15668,22 +15516,22 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n2</t>
+          <t>pain.excel.statn</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>1.8 h</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>ანა</t>
+          <t>1.8 სთ</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>1,8 ч</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr"/>
@@ -15706,22 +15554,22 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n3</t>
+          <t>pain.excel.stat</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Luka</t>
+          <t>a day: the average time an employee spends searching for information</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>ლუკა</t>
+          <t>დღეში ხარჯავს საშუალოდ თანამშრომელი საჭირო ინფორმაციის ძებნაში</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Лука</t>
+          <t>в день в среднем тратит сотрудник на поиск нужной информации</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr"/>
@@ -15744,22 +15592,22 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>pain.z.done</t>
+          <t>pain.excel.src</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Source: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>შესრულდა</t>
+          <t>წყარო: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>Источник: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr"/>
@@ -15782,22 +15630,22 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>pain.z.auto</t>
+          <t>pain.owner.statn</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>ავტომატური</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Авто</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr"/>
@@ -15820,22 +15668,22 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>pain.z.everymon</t>
+          <t>pain.owner.stat</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Every Monday</t>
+          <t>of business owners spend over 40% of their time on admin</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>ყოველ ორშაბათს</t>
+          <t>მეწარმეების სამუშაო დროის 40%-ზე მეტს ადმინისტრაციულ საქმეებს ახმარს</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Каждый понедельник</t>
+          <t>предпринимателей тратят на администрирование больше 40% времени</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr"/>
@@ -15858,22 +15706,22 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>pain.z.reminder</t>
+          <t>pain.owner.src</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>Reminder sent to Luka</t>
+          <t>Source: Visma &amp; Kantar, 2,000 business owners, 2024</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>ლუკას შეხსენება გაეგზავნა</t>
+          <t>წყარო: Visma &amp; Kantar, 2 000 მეწარმე, 2024</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Луке отправлено напоминание</t>
+          <t>Источник: Visma &amp; Kantar, 2 000 предпринимателей, 2024</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr"/>
@@ -15896,22 +15744,22 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>pain.z.inbox</t>
+          <t>pain.chats.statn</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Inbox</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>შეტყობინებები</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Сообщения</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr"/>
@@ -15934,22 +15782,22 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>pain.z.zero</t>
+          <t>pain.chats.stat</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>0 unanswered</t>
+          <t>higher chance to qualify a lead when you reply within an hour rather than later</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>0 უპასუხო</t>
+          <t>მეტია ლიდის დაკვალიფიცირების შანსი, თუ 1 საათში უპასუხებ და არა მოგვიანებით</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>0 без ответа</t>
+          <t>выше шанс квалифицировать лид, если ответить в течение часа, а не позже</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr"/>
@@ -15972,22 +15820,22 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>pain.z.min</t>
+          <t>pain.chats.src</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>Source: Harvard Business Review</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>წთ</t>
+          <t>წყარო: Harvard Business Review</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>мин</t>
+          <t>Источник: Harvard Business Review</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr"/>
@@ -16005,34 +15853,30 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
-        </is>
-      </c>
-      <c r="D239" s="9" t="inlineStr">
-        <is>
-          <t>Choose where to start</t>
-        </is>
-      </c>
-      <c r="E239" s="9" t="inlineStr">
-        <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
-        </is>
-      </c>
-      <c r="F239" s="9" t="inlineStr">
-        <is>
-          <t>Выберите, с чего начать</t>
-        </is>
-      </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.0.name</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Where you are today</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>დღევანდელი რეალობა</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>Где вы сейчас</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr"/>
       <c r="H239" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16047,34 +15891,30 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
-        </is>
-      </c>
-      <c r="D240" s="9" t="inlineStr">
-        <is>
-          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
-        </is>
-      </c>
-      <c r="E240" s="9" t="inlineStr">
-        <is>
-          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
-        </is>
-      </c>
-      <c r="F240" s="9" t="inlineStr">
-        <is>
-          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
-        </is>
-      </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.0.desc</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr"/>
       <c r="H240" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16089,34 +15929,30 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
-        </is>
-      </c>
-      <c r="D241" s="9" t="inlineStr">
-        <is>
-          <t>Most popular</t>
-        </is>
-      </c>
-      <c r="E241" s="9" t="inlineStr">
-        <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
-        </is>
-      </c>
-      <c r="F241" s="9" t="inlineStr">
-        <is>
-          <t>Выбирают чаще всего</t>
-        </is>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.0.time</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Starting point</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>საწყისი წერტილი</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>Отправная точка</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr"/>
       <c r="H241" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16131,34 +15967,30 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
-        </is>
-      </c>
-      <c r="D242" s="9" t="inlineStr">
-        <is>
-          <t>one-time, + VAT</t>
-        </is>
-      </c>
-      <c r="E242" s="9" t="inlineStr">
-        <is>
-          <t>ერთჯერადად, + დღგ</t>
-        </is>
-      </c>
-      <c r="F242" s="9" t="inlineStr">
-        <is>
-          <t>разово, + НДС</t>
-        </is>
-      </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.chart.chaos</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Chaos</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>ქაოსი</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>Хаос</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr"/>
       <c r="H242" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16173,34 +16005,30 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
-        </is>
-      </c>
-      <c r="D243" s="9" t="inlineStr">
-        <is>
-          <t>working days</t>
-        </is>
-      </c>
-      <c r="E243" s="9" t="inlineStr">
-        <is>
-          <t>სამუშაო დღე</t>
-        </is>
-      </c>
-      <c r="F243" s="9" t="inlineStr">
-        <is>
-          <t>рабочих дней</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.chart.growth</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Growth ∞</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>ზრდა ∞</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Рост ∞</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr"/>
       <c r="H243" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -16220,22 +16048,22 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>pk.full</t>
+          <t>pk.title</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>Everything included</t>
+          <t>Choose where to start</t>
         </is>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>სრული ჩამონათვალი</t>
+          <t>აირჩიე, საიდან დაიწყო</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>Всё, что входит</t>
+          <t>Выберите, с чего начать</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -16262,22 +16090,22 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
+          <t>pk.sub</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Choose this package</t>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>ამ პაკეტის არჩევა</t>
+          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>Выбрать этот пакет</t>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16304,22 +16132,22 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>არჩეულია</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>Выбран</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -16346,22 +16174,22 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
+          <t>one-time, + VAT</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
+          <t>ერთჯერადად, + დღგ</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
+          <t>разово, + НДС</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16388,22 +16216,22 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>pk.cur</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>ვალუტა</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>Валюта</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -16425,27 +16253,27 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Extra features</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>დამატებითი ფუნქციები</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>Дополнительные функции</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -16467,27 +16295,27 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>Optional. Add only if you need them</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>Необязательно. Добавьте, если нужно</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16509,27 +16337,27 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>ao.popular</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Often added</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>ხშირად ამატებენ</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>Часто добавляют</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -16551,27 +16379,27 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>ao.more</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>All add-ons by category</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>Все дополнения по категориям</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -16593,27 +16421,27 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -16635,27 +16463,27 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Choose a package</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე პაკეტი</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Выберите пакет</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -16677,27 +16505,27 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>ფუნქცია</t>
+          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>функц.</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -16719,27 +16547,27 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>+ VAT</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>+ დღგ</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>+ НДС</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -16761,27 +16589,27 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Request a call</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -16803,27 +16631,27 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Your selection:</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>შენი არჩევანი:</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Ваш выбор:</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -16845,27 +16673,27 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>სტარტი</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Старт</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -16887,27 +16715,27 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.short</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>To move from Excel into a CRM</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Чтобы перейти с Excel на CRM</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -16929,27 +16757,27 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h1</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>4 core modules</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -16971,27 +16799,27 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h2</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Email and Facebook inside the CRM</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტა და Facebook CRM-ში</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>Почта и Facebook внутри CRM</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -17013,27 +16841,27 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h3</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Lead form and KPI dashboard</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ფორმა და KPI დაფა</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>Форма лидов и дашборд KPI</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -17060,22 +16888,22 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -17102,22 +16930,22 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -17144,22 +16972,22 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Facebook messages right inside the CRM</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Сообщения Facebook прямо в CRM</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17186,22 +17014,22 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>1 web form to capture leads</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>1 веб-форма для приёма лидов</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -17228,22 +17056,22 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>1 sales-pipeline KPI dashboard</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>Дашборд KPI воронки продаж</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -17270,22 +17098,22 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Recorded video instructions for the team</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>Видеоинструкции для команды</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -17312,22 +17140,22 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Essentials</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალური</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>Оптимальный</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -17354,22 +17182,22 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.short</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>For a 5-10 person sales team</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>Для отдела продаж из 5-10 человек</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -17396,22 +17224,22 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter, plus:</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта», плюс:</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -17438,22 +17266,22 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h1</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта»</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -17480,22 +17308,22 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h2</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads, automatically</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -17522,22 +17350,22 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h3</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Stage rules and lead assignment</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Правила этапов и распределение лидов</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -17564,22 +17392,22 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -17606,22 +17434,22 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -17648,22 +17476,22 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -17690,22 +17518,22 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -17732,22 +17560,22 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -17774,22 +17602,22 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -17816,22 +17644,22 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -17858,22 +17686,22 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -17900,22 +17728,22 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -17942,22 +17770,22 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -17984,22 +17812,22 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.short</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>For a growing 15-25 person team</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Для растущей команды из 15-25 человек</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -18026,22 +17854,22 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -18068,22 +17896,22 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h1</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального»</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -18110,22 +17938,22 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h2</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Telephony and call processing</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია და ზარების დამუშავება</t>
+          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Телефония и обработка звонков</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -18152,22 +17980,22 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h3</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Automations and AI (Claude)</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და AI (Claude)</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>Автоматизации и AI (Claude)</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -18194,22 +18022,22 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -18236,22 +18064,22 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -18278,22 +18106,22 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -18320,22 +18148,22 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -18362,22 +18190,22 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -18404,22 +18232,22 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -18446,22 +18274,22 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -18488,22 +18316,22 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -18530,22 +18358,22 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -18567,27 +18395,27 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -18609,27 +18437,27 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -18651,27 +18479,27 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -18693,27 +18521,27 @@
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -18735,27 +18563,27 @@
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>ao.18</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG bank wire deposit matching</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Автосверка переводов TBC/BOG</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -18782,22 +18610,22 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>ao.30</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -18824,22 +18652,22 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>ao.38</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -18866,22 +18694,22 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -18908,22 +18736,22 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -18950,22 +18778,22 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -18992,22 +18820,22 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -19034,22 +18862,22 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -19076,22 +18904,22 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -19118,22 +18946,22 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -19160,22 +18988,22 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -19202,22 +19030,22 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოების აღრიცხვა</t>
+          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -19244,22 +19072,22 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -19286,22 +19114,22 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>ao.12</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Email + calendar 2-way sync</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -19328,22 +19156,22 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ao.13</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>Возврат пропущенных звонков и SMS</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -19370,22 +19198,22 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>ao.14</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Messaging bot lead capture webhook</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -19412,22 +19240,22 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>ბროკერების საკომისიოების აღრიცხვა</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -19454,22 +19282,22 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>ao.15</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Website lead form + webhook</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + webhook</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + webhook</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -19496,22 +19324,22 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>ao.16</t>
+          <t>ao.12</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
+          <t>Email + calendar 2-way sync</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>ROI источников и атрибуция кампаний</t>
+          <t>Двусторонняя синхронизация почты и календаря</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -19538,22 +19366,22 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>ao.17</t>
+          <t>ao.13</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
+          <t>Missed-call recovery &amp; SMS callback</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
+          <t>Возврат пропущенных звонков и SMS</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -19580,22 +19408,22 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>ao.14</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>Messaging bot lead capture webhook</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>Лиды из чат-бота сразу в CRM</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -19622,22 +19450,22 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>ao.19</t>
+          <t>ao.cat.mkt</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+          <t>Marketing &amp; growth</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+          <t>მარკეტინგი</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -19664,22 +19492,22 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>ao.20</t>
+          <t>ao.15</t>
         </is>
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>NBG daily exchange rate sync</t>
+          <t>Website lead form + webhook</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+          <t>საიტის ფორმა + webhook</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>Ежедневный курс НБГ</t>
+          <t>Форма сайта + webhook</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -19706,22 +19534,22 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>ao.21</t>
+          <t>ao.16</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>Ambiguous payment reference fallback queue</t>
+          <t>Lead source ROI &amp; campaign attribution</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>Очередь неопознанных платежей</t>
+          <t>ROI источников и атрибуция кампаний</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -19748,22 +19576,22 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>ao.22</t>
+          <t>ao.17</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Dynamic installment payment schedule</t>
+          <t>Email campaigns: account setup &amp; contact sync</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>График рассрочки</t>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -19790,22 +19618,22 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>ao.23</t>
+          <t>ao.cat.fin</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
+          <t>Fintech &amp; accounting</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+          <t>ფინანსები და ბანკები</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>SMS о просроченной задолженности</t>
+          <t>Финансы и банки</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -19832,22 +19660,22 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>ao.24</t>
+          <t>ao.19</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>SMS gateway &amp; OTP verification</t>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>SMS-шлюз и OTP-верификация</t>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -19874,22 +19702,22 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>ao.20</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>NBG daily exchange rate sync</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>Ежедневный курс НБГ</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -19916,22 +19744,22 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>ao.25</t>
+          <t>ao.21</t>
         </is>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
+          <t>Ambiguous payment reference fallback queue</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
+          <t>Очередь неопознанных платежей</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -19958,22 +19786,22 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>ao.26</t>
+          <t>ao.22</t>
         </is>
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>Multi-tier SLA escalation matrix</t>
+          <t>Dynamic installment payment schedule</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+          <t>შიდა განვადების დინამიკური გრაფიკი</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>Матрица эскалации SLA</t>
+          <t>График рассрочки</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -20000,22 +19828,22 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>ao.27</t>
+          <t>ao.23</t>
         </is>
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
+          <t>Overdue debt alert &amp; SMS warning</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>Оценка NPS/CSAT после тикета</t>
+          <t>SMS о просроченной задолженности</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -20042,22 +19870,22 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>ao.28</t>
+          <t>ao.24</t>
         </is>
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>Dynamic KYC intake smart form</t>
+          <t>SMS gateway &amp; OTP verification</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>Умная KYC-форма</t>
+          <t>SMS-шлюз и OTP-верификация</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -20084,22 +19912,22 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>ao.29</t>
+          <t>ao.cat.cx</t>
         </is>
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>Warranty expiration alerts</t>
+          <t>Customer experience</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
+          <t>მომხმარებლის მომსახურება</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>Напоминания об окончании гарантии</t>
+          <t>Клиентский сервис</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -20126,22 +19954,22 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.25</t>
         </is>
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -20168,22 +19996,22 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>ao.31</t>
+          <t>ao.26</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>Georgian voice meeting transcription</t>
+          <t>Multi-tier SLA escalation matrix</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>Транскрипция встреч на грузинском</t>
+          <t>Матрица эскалации SLA</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -20210,22 +20038,22 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>ao.32</t>
+          <t>ao.27</t>
         </is>
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>Audio call sentiment extractor</t>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>Анализ тональности звонков</t>
+          <t>Оценка NPS/CSAT после тикета</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -20252,22 +20080,22 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ind</t>
+          <t>ao.28</t>
         </is>
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>Industry solutions</t>
+          <t>Dynamic KYC intake smart form</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>დარგობრივი</t>
+          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>Отраслевые</t>
+          <t>Умная KYC-форма</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -20294,22 +20122,22 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>ao.33</t>
+          <t>ao.29</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
+          <t>Warranty expiration alerts</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+          <t>გარანტიის ვადის შეხსენებები</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
+          <t>Напоминания об окончании гарантии</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -20336,22 +20164,22 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>ao.34</t>
+          <t>ao.cat.ai</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>Client preference proactive matcher</t>
+          <t>AI &amp; automation</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>Автоподбор по пожеланиям клиента</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -20378,22 +20206,22 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>ao.35</t>
+          <t>ao.31</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>Reservation expiration timer</t>
+          <t>Georgian voice meeting transcription</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>Таймер истечения брони</t>
+          <t>Транскрипция встреч на грузинском</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -20420,22 +20248,22 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>ao.36</t>
+          <t>ao.32</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
+          <t>Audio call sentiment extractor</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>PDF планировки и предложения</t>
+          <t>Анализ тональности звонков</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -20462,22 +20290,22 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>ao.37</t>
+          <t>ao.cat.ind</t>
         </is>
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>Field service visit tracking + approval</t>
+          <t>Industry solutions</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+          <t>დარგობრივი</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>Учёт выездов и подтверждение</t>
+          <t>Отраслевые</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -20504,22 +20332,22 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.33</t>
         </is>
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -20546,22 +20374,22 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>ao.39</t>
+          <t>ao.34</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>Cold storage WMS &amp; automated billing</t>
+          <t>Client preference proactive matcher</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>WMS холодного склада и биллинг</t>
+          <t>Автоподбор по пожеланиям клиента</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -20588,22 +20416,22 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>ao.40</t>
+          <t>ao.35</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>Construction operations &amp; budget tracker</t>
+          <t>Reservation expiration timer</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>Стройка: операции и бюджет</t>
+          <t>Таймер истечения брони</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -20630,22 +20458,22 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>ao.41</t>
+          <t>ao.36</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>Predictive debtor call queue</t>
+          <t>Floor plan &amp; proposal PDF generator</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>Умная очередь звонков должникам</t>
+          <t>PDF планировки и предложения</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -20672,22 +20500,22 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>ao.42</t>
+          <t>ao.37</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>Agent attendance tracker</t>
+          <t>Field service visit tracking + approval</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+          <t>საველე ვიზიტების მართვა და დადასტურება</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>Учёт посещаемости агентов</t>
+          <t>Учёт выездов и подтверждение</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -20714,22 +20542,22 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>ao.43</t>
+          <t>ao.cat.ops</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>Round-robin appointment balancing</t>
+          <t>Operations &amp; ERP</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+          <t>ოპერაციები და ERP</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>Равномерное распределение встреч</t>
+          <t>Операции и ERP</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -20756,39 +20584,249 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
+          <t>ao.39</t>
+        </is>
+      </c>
+      <c r="D352" s="9" t="inlineStr">
+        <is>
+          <t>Cold storage WMS &amp; automated billing</t>
+        </is>
+      </c>
+      <c r="E352" s="9" t="inlineStr">
+        <is>
+          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+        </is>
+      </c>
+      <c r="F352" s="9" t="inlineStr">
+        <is>
+          <t>WMS холодного склада и биллинг</t>
+        </is>
+      </c>
+      <c r="G352" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H352" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t>ao.40</t>
+        </is>
+      </c>
+      <c r="D353" s="9" t="inlineStr">
+        <is>
+          <t>Construction operations &amp; budget tracker</t>
+        </is>
+      </c>
+      <c r="E353" s="9" t="inlineStr">
+        <is>
+          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+        </is>
+      </c>
+      <c r="F353" s="9" t="inlineStr">
+        <is>
+          <t>Стройка: операции и бюджет</t>
+        </is>
+      </c>
+      <c r="G353" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H353" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C354" s="3" t="inlineStr">
+        <is>
+          <t>ao.41</t>
+        </is>
+      </c>
+      <c r="D354" s="9" t="inlineStr">
+        <is>
+          <t>Predictive debtor call queue</t>
+        </is>
+      </c>
+      <c r="E354" s="9" t="inlineStr">
+        <is>
+          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+        </is>
+      </c>
+      <c r="F354" s="9" t="inlineStr">
+        <is>
+          <t>Умная очередь звонков должникам</t>
+        </is>
+      </c>
+      <c r="G354" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H354" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>ao.42</t>
+        </is>
+      </c>
+      <c r="D355" s="9" t="inlineStr">
+        <is>
+          <t>Agent attendance tracker</t>
+        </is>
+      </c>
+      <c r="E355" s="9" t="inlineStr">
+        <is>
+          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+        </is>
+      </c>
+      <c r="F355" s="9" t="inlineStr">
+        <is>
+          <t>Учёт посещаемости агентов</t>
+        </is>
+      </c>
+      <c r="G355" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H355" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C356" s="3" t="inlineStr">
+        <is>
+          <t>ao.43</t>
+        </is>
+      </c>
+      <c r="D356" s="9" t="inlineStr">
+        <is>
+          <t>Round-robin appointment balancing</t>
+        </is>
+      </c>
+      <c r="E356" s="9" t="inlineStr">
+        <is>
+          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+        </is>
+      </c>
+      <c r="F356" s="9" t="inlineStr">
+        <is>
+          <t>Равномерное распределение встреч</t>
+        </is>
+      </c>
+      <c r="G356" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H356" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
           <t>ao.44</t>
         </is>
       </c>
-      <c r="D352" s="9" t="inlineStr">
+      <c r="D357" s="9" t="inlineStr">
         <is>
           <t>Discovery call auto-scheduling</t>
         </is>
       </c>
-      <c r="E352" s="9" t="inlineStr">
+      <c r="E357" s="9" t="inlineStr">
         <is>
           <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
-      <c r="F352" s="9" t="inlineStr">
+      <c r="F357" s="9" t="inlineStr">
         <is>
           <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
-      <c r="G352" s="3" t="inlineStr">
+      <c r="G357" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H352" s="3" t="inlineStr">
+      <c r="H357" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H352"/>
+  <autoFilter ref="A1:H357"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H551" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H556" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20802,7 +20840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -27939,17 +27977,17 @@
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
+          <t>From chaos to steady growth: see the path you'll take with us.</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
+          <t>ქაოსიდან სტაბილურ ზრდამდე: ნახე, რა გზას გაივლი ჩვენთან ერთად.</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
+          <t>От хаоса к стабильному росту: посмотрите, какой путь вы пройдёте с нами.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr"/>
@@ -28015,17 +28053,17 @@
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>We find the real problem and pick the right tool.</t>
+          <t>Instead of chaos, an exact plan: which tools, what timeline, what budget.</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>ვიგებთ რეალურ პრობლემას და ვარჩევთ სწორ ინსტრუმენტს.</t>
+          <t>ქაოსის ნაცვლად — ზუსტი გეგმა: რა ინსტრუმენტი, რა ვადაში და რა ბიუჯეტით.</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Находим реальную проблему и подбираем правильный инструмент.</t>
+          <t>Вместо хаоса — точный план: какие инструменты, сроки и бюджет.</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr"/>
@@ -28048,22 +28086,22 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.1</t>
+          <t>process.1.time</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Review of your processes and current systems</t>
+          <t>First call · 20 min · free</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>პროცესებისა და არსებული სისტემების ანალიზი</t>
+          <t>პირველი ზარი · 20 წთ · უფასო</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Анализ процессов и текущих систем</t>
+          <t>Первый звонок · 20 мин · бесплатно</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr"/>
@@ -28086,22 +28124,22 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.2</t>
+          <t>process.2.name</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>1-3 tools that fit (and what you don't need)</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>1-3 ინსტრუმენტის შერჩევა (და რა არ გჭირდება)</t>
+          <t>დანერგვა</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>1-3 подходящих инструмента (и что вам не нужно)</t>
+          <t>Внедрение</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -28124,22 +28162,22 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.3</t>
+          <t>process.2.desc</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Implementation plan, budget and timeline</t>
+          <t>We build the system in short sprints and the business gets stronger. You see first results in 1-2 weeks.</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>დანერგვის გეგმა, ბიუჯეტი და ვადები</t>
+          <t>სისტემას მოკლე სპრინტებით ვაწყობთ და ბიზნესი ძლიერდება. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>План внедрения, бюджет и сроки</t>
+          <t>Мы строим систему короткими спринтами, и бизнес становится сильнее. Первый результат — через 1-2 недели.</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr"/>
@@ -28162,22 +28200,22 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>process.1.time</t>
+          <t>process.2.time</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>First call · 20 min · free</t>
+          <t>Sprint · 1-2 weeks</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>პირველი ზარი · 20 წთ · უფასო</t>
+          <t>სპრინტი · 1-2 კვირა</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Первый звонок · 20 мин · бесплатно</t>
+          <t>Спринт · 1-2 недели</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr"/>
@@ -28200,22 +28238,22 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>process.2.name</t>
+          <t>process.3.name</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>დანერგვა</t>
+          <t>მხარდაჭერა</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Внедрение</t>
+          <t>Поддержка</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr"/>
@@ -28238,22 +28276,22 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>process.2.desc</t>
+          <t>process.3.desc</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>We build the system in short sprints. You see the first result in 1-2 weeks.</t>
+          <t>The system grows with your business, and growth has no ceiling.</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>ვაწყობთ სისტემას მოკლე სპრინტებით. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
+          <t>სისტემა ბიზნესთან ერთად იზრდება და ზრდას ზღვარი არ აქვს.</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Строим систему короткими спринтами. Первый результат - через 1-2 недели.</t>
+          <t>Система растёт вместе с бизнесом, и у роста нет потолка.</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr"/>
@@ -28276,22 +28314,22 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.1</t>
+          <t>process.3.time</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>System setup and data migration</t>
+          <t>Ongoing · as needed</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>სისტემის აწყობა და მონაცემების გადატანა</t>
+          <t>მუდმივად · საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Настройка системы и перенос данных</t>
+          <t>Постоянно · по необходимости</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr"/>
@@ -28314,22 +28352,22 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.2</t>
+          <t>process.note</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Automations and integrations</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და ინტეგრაციები</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Автоматизации и интеграции</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr"/>
@@ -28352,22 +28390,22 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.3</t>
+          <t>process.cta</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Team training</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>გუნდის ტრენინგი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Обучение команды</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr"/>
@@ -28385,27 +28423,27 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>process.2.time</t>
+          <t>pain.manager.left</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Sprint · 1-2 weeks</t>
+          <t>Ana left the chat</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>სპრინტი · 1-2 კვირა</t>
+          <t>ანამ დატოვა ჩატი</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Спринт · 1-2 недели</t>
+          <t>Анна покинула чат</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr"/>
@@ -28423,27 +28461,27 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>process.3.name</t>
+          <t>pain.owner.note</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Today!!</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>მხარდაჭერა</t>
+          <t>დღეს!!</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Поддержка</t>
+          <t>Сегодня!!</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr"/>
@@ -28461,27 +28499,27 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>process.3.desc</t>
+          <t>pain.chats.more</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>The system keeps working after launch and grows with your business.</t>
+          <t>+11 unanswered</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>სისტემა გაშვების შემდეგაც მუშაობს და იზრდება ბიზნესთან ერთად.</t>
+          <t>+11 უპასუხო</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Система продолжает работать после запуска и растёт вместе с бизнесом.</t>
+          <t>+11 без ответа</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr"/>
@@ -28499,30 +28537,34 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.1</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>Technical support when you need it</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>ტექნიკური მხარდაჭერა, როცა გჭირდება</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>Техническая поддержка, когда она нужна</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr"/>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="inlineStr">
+        <is>
+          <t>AI and process automation for business | Unitty</t>
+        </is>
+      </c>
+      <c r="E200" s="9" t="inlineStr">
+        <is>
+          <t>AI და პროცესების ავტომატიზაცია ბიზნესისთვის | Unitty</t>
+        </is>
+      </c>
+      <c r="F200" s="9" t="inlineStr">
+        <is>
+          <t>AI и автоматизация процессов для бизнеса | Unitty</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -28537,27 +28579,27 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.2</t>
+          <t>pain.ba.before</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Ongoing optimization and improvements</t>
+          <t>Before</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>მუდმივი ოპტიმიზაცია და განვითარება</t>
+          <t>დანერგვამდე</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Постоянная оптимизация и развитие</t>
+          <t>До внедрения</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr"/>
@@ -28575,27 +28617,27 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.3</t>
+          <t>pain.ba.after</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>New tools added as you need them</t>
+          <t>After</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>ახალი ინსტრუმენტების დამატება საჭიროებისამებრ</t>
+          <t>შედეგად</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Новые инструменты - по мере необходимости</t>
+          <t>Результат</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr"/>
@@ -28613,27 +28655,27 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>process.3.time</t>
+          <t>pain.ba.hint</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Ongoing · as needed</t>
+          <t>Switch to see the same situation with a CRM</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>მუდმივად · საჭიროებისამებრ</t>
+          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Постоянно · по необходимости</t>
+          <t>Переключите и посмотрите то же самое с CRM</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr"/>
@@ -28651,27 +28693,27 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>process.note</t>
+          <t>pain.ba.peek</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Pricing is set individually, based on your needs.</t>
+          <t>See the result with CRM</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
+          <t>ნახე შედეგი CRM-ით</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
+          <t>Посмотреть результат с CRM</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr"/>
@@ -28689,27 +28731,27 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>process.cta</t>
+          <t>pain.excel.atitle</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>The client's full history in one search</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Вся история клиента — в одном поиске</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr"/>
@@ -28732,22 +28774,22 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.left</t>
+          <t>pain.owner.atitle</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Ana left the chat</t>
+          <t>The team knows who does what</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>ანამ დატოვა ჩატი</t>
+          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Анна покинула чат</t>
+          <t>Команда знает, кто что делает</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr"/>
@@ -28770,22 +28812,22 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.note</t>
+          <t>pain.chats.atitle</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Today!!</t>
+          <t>Every message in one window</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>დღეს!!</t>
+          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Сегодня!!</t>
+          <t>Все сообщения — в одном окне</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr"/>
@@ -28808,22 +28850,22 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.more</t>
+          <t>pain.z.contacts</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>+11 unanswered</t>
+          <t>Contacts</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>+11 უპასუხო</t>
+          <t>კონტაქტები</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>+11 без ответа</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr"/>
@@ -28841,34 +28883,30 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Seo</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>seo.title</t>
-        </is>
-      </c>
-      <c r="D209" s="9" t="inlineStr">
-        <is>
-          <t>AI and process automation for business | Unitty</t>
-        </is>
-      </c>
-      <c r="E209" s="9" t="inlineStr">
-        <is>
-          <t>AI და პროცესების ავტომატიზაცია ბიზნესისთვის | Unitty</t>
-        </is>
-      </c>
-      <c r="F209" s="9" t="inlineStr">
-        <is>
-          <t>AI и автоматизация процессов для бизнеса | Unitty</t>
-        </is>
-      </c>
-      <c r="G209" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.found</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>1 result</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>1 შედეგი</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>1 результат</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr"/>
       <c r="H209" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -28888,22 +28926,22 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.before</t>
+          <t>pain.z.stage</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Without CRM</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>CRM-ის გარეშე</t>
+          <t>შეთავაზება</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Без CRM</t>
+          <t>Предложение</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr"/>
@@ -28926,22 +28964,22 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.after</t>
+          <t>pain.z.last</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>With Zoho CRM</t>
+          <t>Last purchase</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Zoho CRM-ით</t>
+          <t>ბოლო შეძენა</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>С Zoho CRM</t>
+          <t>Последняя покупка</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr"/>
@@ -28964,22 +29002,22 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.hint</t>
+          <t>pain.z.deals</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Switch to see the same situation with a CRM</t>
+          <t>Deals</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
+          <t>გარიგებები</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Переключите и посмотрите то же самое с CRM</t>
+          <t>Сделки</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr"/>
@@ -29002,22 +29040,22 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.peek</t>
+          <t>pain.z.merged</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>See the result with CRM</t>
+          <t>Duplicate merged</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>ნახე შედეგი CRM-ით</t>
+          <t>დუბლიკატი გაერთიანდა</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Посмотреть результат с CRM</t>
+          <t>Дубликат объединён</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr"/>
@@ -29040,22 +29078,22 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.atitle</t>
+          <t>pain.z.tasks</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>The client's full history in one search</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
+          <t>დავალებები</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Вся история клиента — в одном поиске</t>
+          <t>Задачи</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr"/>
@@ -29078,22 +29116,22 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.atitle</t>
+          <t>pain.z.ontrack</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>The team knows who does what</t>
+          <t>On track</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
+          <t>გეგმაშია</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Команда знает, кто что делает</t>
+          <t>По плану</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr"/>
@@ -29116,22 +29154,22 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.atitle</t>
+          <t>pain.z.t1</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Every message in one window</t>
+          <t>Call the client</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
+          <t>კლიენტთან ზარი</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Все сообщения — в одном окне</t>
+          <t>Звонок клиенту</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr"/>
@@ -29154,22 +29192,22 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>pain.z.contacts</t>
+          <t>pain.z.t2</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Invoice on rs.ge</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>კონტაქტები</t>
+          <t>ინვოისი rs.ge-ზე</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Счёт на rs.ge</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr"/>
@@ -29192,22 +29230,22 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>pain.z.found</t>
+          <t>pain.z.t3</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>1 result</t>
+          <t>Send the price</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>1 შედეგი</t>
+          <t>ფასის გაგზავნა</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>1 результат</t>
+          <t>Отправить цену</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr"/>
@@ -29230,22 +29268,22 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>pain.z.stage</t>
+          <t>pain.z.t4</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Weekly report</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>შეთავაზება</t>
+          <t>კვირის რეპორტი</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Предложение</t>
+          <t>Недельный отчёт</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr"/>
@@ -29268,22 +29306,22 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>pain.z.last</t>
+          <t>pain.z.n1</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Last purchase</t>
+          <t>Nika</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>ბოლო შეძენა</t>
+          <t>ნიკა</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Последняя покупка</t>
+          <t>Ника</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr"/>
@@ -29306,22 +29344,22 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>pain.z.deals</t>
+          <t>pain.z.n2</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Deals</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>გარიგებები</t>
+          <t>ანა</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Сделки</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr"/>
@@ -29344,22 +29382,22 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>pain.z.merged</t>
+          <t>pain.z.n3</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Duplicate merged</t>
+          <t>Luka</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>დუბლიკატი გაერთიანდა</t>
+          <t>ლუკა</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Дубликат объединён</t>
+          <t>Лука</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr"/>
@@ -29382,22 +29420,22 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>pain.z.tasks</t>
+          <t>pain.z.done</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>დავალებები</t>
+          <t>შესრულდა</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Задачи</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr"/>
@@ -29420,22 +29458,22 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>pain.z.ontrack</t>
+          <t>pain.z.auto</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>On track</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>გეგმაშია</t>
+          <t>ავტომატური</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>По плану</t>
+          <t>Авто</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr"/>
@@ -29458,22 +29496,22 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t1</t>
+          <t>pain.z.everymon</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Call the client</t>
+          <t>Every Monday</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>კლიენტთან ზარი</t>
+          <t>ყოველ ორშაბათს</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Звонок клиенту</t>
+          <t>Каждый понедельник</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr"/>
@@ -29496,22 +29534,22 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t2</t>
+          <t>pain.z.reminder</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Invoice on rs.ge</t>
+          <t>Reminder sent to Luka</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>ინვოისი rs.ge-ზე</t>
+          <t>ლუკას შეხსენება გაეგზავნა</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Счёт на rs.ge</t>
+          <t>Луке отправлено напоминание</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr"/>
@@ -29534,22 +29572,22 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t3</t>
+          <t>pain.z.inbox</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Send the price</t>
+          <t>Inbox</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>ფასის გაგზავნა</t>
+          <t>შეტყობინებები</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Отправить цену</t>
+          <t>Сообщения</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr"/>
@@ -29572,22 +29610,22 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t4</t>
+          <t>pain.z.zero</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Weekly report</t>
+          <t>0 unanswered</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>კვირის რეპორტი</t>
+          <t>0 უპასუხო</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Недельный отчёт</t>
+          <t>0 без ответа</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr"/>
@@ -29610,22 +29648,22 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n1</t>
+          <t>pain.z.min</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Nika</t>
+          <t>min</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>ნიკა</t>
+          <t>წთ</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Ника</t>
+          <t>мин</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr"/>
@@ -29648,22 +29686,22 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n2</t>
+          <t>pain.excel.statn</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>1.8 h</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>ანა</t>
+          <t>1.8 სთ</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>1,8 ч</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr"/>
@@ -29686,22 +29724,22 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n3</t>
+          <t>pain.excel.stat</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Luka</t>
+          <t>a day: the average time an employee spends searching for information</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>ლუკა</t>
+          <t>დღეში ხარჯავს საშუალოდ თანამშრომელი საჭირო ინფორმაციის ძებნაში</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Лука</t>
+          <t>в день в среднем тратит сотрудник на поиск нужной информации</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr"/>
@@ -29724,22 +29762,22 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>pain.z.done</t>
+          <t>pain.excel.src</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Source: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>შესრულდა</t>
+          <t>წყარო: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>Источник: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr"/>
@@ -29762,22 +29800,22 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>pain.z.auto</t>
+          <t>pain.owner.statn</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>ავტომატური</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Авто</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr"/>
@@ -29800,22 +29838,22 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>pain.z.everymon</t>
+          <t>pain.owner.stat</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Every Monday</t>
+          <t>of business owners spend over 40% of their time on admin</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>ყოველ ორშაბათს</t>
+          <t>მეწარმეების სამუშაო დროის 40%-ზე მეტს ადმინისტრაციულ საქმეებს ახმარს</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Каждый понедельник</t>
+          <t>предпринимателей тратят на администрирование больше 40% времени</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr"/>
@@ -29838,22 +29876,22 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>pain.z.reminder</t>
+          <t>pain.owner.src</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>Reminder sent to Luka</t>
+          <t>Source: Visma &amp; Kantar, 2,000 business owners, 2024</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>ლუკას შეხსენება გაეგზავნა</t>
+          <t>წყარო: Visma &amp; Kantar, 2 000 მეწარმე, 2024</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Луке отправлено напоминание</t>
+          <t>Источник: Visma &amp; Kantar, 2 000 предпринимателей, 2024</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr"/>
@@ -29876,22 +29914,22 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>pain.z.inbox</t>
+          <t>pain.chats.statn</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Inbox</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>შეტყობინებები</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Сообщения</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr"/>
@@ -29914,22 +29952,22 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>pain.z.zero</t>
+          <t>pain.chats.stat</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>0 unanswered</t>
+          <t>higher chance to qualify a lead when you reply within an hour rather than later</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>0 უპასუხო</t>
+          <t>მეტია ლიდის დაკვალიფიცირების შანსი, თუ 1 საათში უპასუხებ და არა მოგვიანებით</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>0 без ответа</t>
+          <t>выше шанс квалифицировать лид, если ответить в течение часа, а не позже</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr"/>
@@ -29952,22 +29990,22 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>pain.z.min</t>
+          <t>pain.chats.src</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>Source: Harvard Business Review</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>წთ</t>
+          <t>წყარო: Harvard Business Review</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>мин</t>
+          <t>Источник: Harvard Business Review</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr"/>
@@ -29977,10 +30015,200 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>process.0.name</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Where you are today</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>დღევანდელი რეალობა</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>Где вы сейчас</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr"/>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>process.0.desc</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr"/>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>process.0.time</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Starting point</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>საწყისი წერტილი</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>Отправная точка</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr"/>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>process.chart.chaos</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Chaos</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>ქაოსი</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>Хаос</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr"/>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>process.chart.growth</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Growth ∞</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>ზრდა ∞</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Рост ∞</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr"/>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H238"/>
+  <autoFilter ref="A1:H243"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H437" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H442" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29994,7 +30222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -35551,17 +35779,17 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
+          <t>From chaos to steady growth: see the path you'll take with us.</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
+          <t>ქაოსიდან სტაბილურ ზრდამდე: ნახე, რა გზას გაივლი ჩვენთან ერთად.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
+          <t>От хаоса к стабильному росту: посмотрите, какой путь вы пройдёте с нами.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
@@ -35627,17 +35855,17 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>We find the real problem and pick the right tool.</t>
+          <t>Instead of chaos, an exact plan: which tools, what timeline, what budget.</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>ვიგებთ რეალურ პრობლემას და ვარჩევთ სწორ ინსტრუმენტს.</t>
+          <t>ქაოსის ნაცვლად — ზუსტი გეგმა: რა ინსტრუმენტი, რა ვადაში და რა ბიუჯეტით.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Находим реальную проблему и подбираем правильный инструмент.</t>
+          <t>Вместо хаоса — точный план: какие инструменты, сроки и бюджет.</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr"/>
@@ -35660,22 +35888,22 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.1</t>
+          <t>process.1.time</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Review of your processes and current systems</t>
+          <t>First call · 20 min · free</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>პროცესებისა და არსებული სისტემების ანალიზი</t>
+          <t>პირველი ზარი · 20 წთ · უფასო</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Анализ процессов и текущих систем</t>
+          <t>Первый звонок · 20 мин · бесплатно</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr"/>
@@ -35698,22 +35926,22 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.2</t>
+          <t>process.2.name</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>1-3 tools that fit (and what you don't need)</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>1-3 ინსტრუმენტის შერჩევა (და რა არ გჭირდება)</t>
+          <t>დანერგვა</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>1-3 подходящих инструмента (и что вам не нужно)</t>
+          <t>Внедрение</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr"/>
@@ -35736,22 +35964,22 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.3</t>
+          <t>process.2.desc</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Implementation plan, budget and timeline</t>
+          <t>We build the system in short sprints and the business gets stronger. You see first results in 1-2 weeks.</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>დანერგვის გეგმა, ბიუჯეტი და ვადები</t>
+          <t>სისტემას მოკლე სპრინტებით ვაწყობთ და ბიზნესი ძლიერდება. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>План внедрения, бюджет и сроки</t>
+          <t>Мы строим систему короткими спринтами, и бизнес становится сильнее. Первый результат — через 1-2 недели.</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr"/>
@@ -35774,22 +36002,22 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>process.1.time</t>
+          <t>process.2.time</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>First call · 20 min · free</t>
+          <t>Sprint · 1-2 weeks</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>პირველი ზარი · 20 წთ · უფასო</t>
+          <t>სპრინტი · 1-2 კვირა</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Первый звонок · 20 мин · бесплатно</t>
+          <t>Спринт · 1-2 недели</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr"/>
@@ -35812,22 +36040,22 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>process.2.name</t>
+          <t>process.3.name</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>დანერგვა</t>
+          <t>მხარდაჭერა</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Внедрение</t>
+          <t>Поддержка</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr"/>
@@ -35850,22 +36078,22 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>process.2.desc</t>
+          <t>process.3.desc</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>We build the system in short sprints. You see the first result in 1-2 weeks.</t>
+          <t>The system grows with your business, and growth has no ceiling.</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>ვაწყობთ სისტემას მოკლე სპრინტებით. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
+          <t>სისტემა ბიზნესთან ერთად იზრდება და ზრდას ზღვარი არ აქვს.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Строим систему короткими спринтами. Первый результат - через 1-2 недели.</t>
+          <t>Система растёт вместе с бизнесом, и у роста нет потолка.</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr"/>
@@ -35888,22 +36116,22 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.1</t>
+          <t>process.3.time</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>System setup and data migration</t>
+          <t>Ongoing · as needed</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>სისტემის აწყობა და მონაცემების გადატანა</t>
+          <t>მუდმივად · საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Настройка системы и перенос данных</t>
+          <t>Постоянно · по необходимости</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr"/>
@@ -35926,22 +36154,22 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.2</t>
+          <t>process.note</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Automations and integrations</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და ინტეგრაციები</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Автоматизации и интеграции</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr"/>
@@ -35964,22 +36192,22 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.3</t>
+          <t>process.cta</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Team training</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>გუნდის ტრენინგი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Обучение команды</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr"/>
@@ -35997,30 +36225,34 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>process.2.time</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>Sprint · 1-2 weeks</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>სპრინტი · 1-2 კვირა</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t>Спринт · 1-2 недели</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr"/>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>Bank transactions in your CRM: TBC and Bank of Georgia | Unitty</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>ბანკის ტრანზაქციები CRM-ში: TBC და საქართველოს ბანკი | Unitty</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>Банковские транзакции в CRM: TBC и Bank of Georgia | Unitty</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -36040,22 +36272,22 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>process.3.name</t>
+          <t>process.0.name</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Where you are today</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>მხარდაჭერა</t>
+          <t>დღევანდელი რეალობა</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Поддержка</t>
+          <t>Где вы сейчас</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr"/>
@@ -36078,22 +36310,22 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>process.3.desc</t>
+          <t>process.0.desc</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>The system keeps working after launch and grows with your business.</t>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>სისტემა გაშვების შემდეგაც მუშაობს და იზრდება ბიზნესთან ერთად.</t>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Система продолжает работать после запуска и растёт вместе с бизнесом.</t>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr"/>
@@ -36116,22 +36348,22 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.1</t>
+          <t>process.0.time</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Technical support when you need it</t>
+          <t>Starting point</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>ტექნიკური მხარდაჭერა, როცა გჭირდება</t>
+          <t>საწყისი წერტილი</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Техническая поддержка, когда она нужна</t>
+          <t>Отправная точка</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr"/>
@@ -36154,22 +36386,22 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.2</t>
+          <t>process.chart.chaos</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Ongoing optimization and improvements</t>
+          <t>Chaos</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>მუდმივი ოპტიმიზაცია და განვითარება</t>
+          <t>ქაოსი</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Постоянная оптимизация и развитие</t>
+          <t>Хаос</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr"/>
@@ -36192,22 +36424,22 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.3</t>
+          <t>process.chart.growth</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>New tools added as you need them</t>
+          <t>Growth ∞</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>ახალი ინსტრუმენტების დამატება საჭიროებისამებრ</t>
+          <t>ზრდა ∞</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Новые инструменты - по мере необходимости</t>
+          <t>Рост ∞</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr"/>
@@ -36217,166 +36449,10 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>process.3.time</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Ongoing · as needed</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>მუდმივად · საჭიროებისამებრ</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>Постоянно · по необходимости</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr"/>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>process.note</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Pricing is set individually, based on your needs.</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr"/>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>process.cta</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Request a free 20-minute call</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr"/>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>Seo</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>seo.title</t>
-        </is>
-      </c>
-      <c r="D166" s="9" t="inlineStr">
-        <is>
-          <t>Bank transactions in your CRM: TBC and Bank of Georgia | Unitty</t>
-        </is>
-      </c>
-      <c r="E166" s="9" t="inlineStr">
-        <is>
-          <t>ბანკის ტრანზაქციები CRM-ში: TBC და საქართველოს ბანკი | Unitty</t>
-        </is>
-      </c>
-      <c r="F166" s="9" t="inlineStr">
-        <is>
-          <t>Банковские транзакции в CRM: TBC и Bank of Georgia | Unitty</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H166"/>
+  <autoFilter ref="A1:H162"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H365" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H361" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -36390,7 +36466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -41919,17 +41995,17 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>We start with one specific challenge, prove the result, and move on to the next.</t>
+          <t>From chaos to steady growth: see the path you'll take with us.</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>ვიწყებთ კონკრეტული გამოწვევით, ვამოწმებთ შედეგს და გადავდივართ შემდეგზე.</t>
+          <t>ქაოსიდან სტაბილურ ზრდამდე: ნახე, რა გზას გაივლი ჩვენთან ერთად.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Начинаем с конкретной задачи, проверяем результат и переходим к следующей.</t>
+          <t>От хаоса к стабильному росту: посмотрите, какой путь вы пройдёте с нами.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr"/>
@@ -41995,17 +42071,17 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>We find the real problem and pick the right tool.</t>
+          <t>Instead of chaos, an exact plan: which tools, what timeline, what budget.</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>ვიგებთ რეალურ პრობლემას და ვარჩევთ სწორ ინსტრუმენტს.</t>
+          <t>ქაოსის ნაცვლად — ზუსტი გეგმა: რა ინსტრუმენტი, რა ვადაში და რა ბიუჯეტით.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Находим реальную проблему и подбираем правильный инструмент.</t>
+          <t>Вместо хаоса — точный план: какие инструменты, сроки и бюджет.</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr"/>
@@ -42028,22 +42104,22 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.1</t>
+          <t>process.1.time</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Review of your processes and current systems</t>
+          <t>First call · 20 min · free</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>პროცესებისა და არსებული სისტემების ანალიზი</t>
+          <t>პირველი ზარი · 20 წთ · უფასო</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Анализ процессов и текущих систем</t>
+          <t>Первый звонок · 20 мин · бесплатно</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr"/>
@@ -42066,22 +42142,22 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.2</t>
+          <t>process.2.name</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>1-3 tools that fit (and what you don't need)</t>
+          <t>Implementation</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>1-3 ინსტრუმენტის შერჩევა (და რა არ გჭირდება)</t>
+          <t>დანერგვა</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>1-3 подходящих инструмента (и что вам не нужно)</t>
+          <t>Внедрение</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr"/>
@@ -42104,22 +42180,22 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>process.1.item.3</t>
+          <t>process.2.desc</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Implementation plan, budget and timeline</t>
+          <t>We build the system in short sprints and the business gets stronger. You see first results in 1-2 weeks.</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>დანერგვის გეგმა, ბიუჯეტი და ვადები</t>
+          <t>სისტემას მოკლე სპრინტებით ვაწყობთ და ბიზნესი ძლიერდება. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>План внедрения, бюджет и сроки</t>
+          <t>Мы строим систему короткими спринтами, и бизнес становится сильнее. Первый результат — через 1-2 недели.</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr"/>
@@ -42142,22 +42218,22 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>process.1.time</t>
+          <t>process.2.time</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>First call · 20 min · free</t>
+          <t>Sprint · 1-2 weeks</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>პირველი ზარი · 20 წთ · უფასო</t>
+          <t>სპრინტი · 1-2 კვირა</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Первый звонок · 20 мин · бесплатно</t>
+          <t>Спринт · 1-2 недели</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr"/>
@@ -42180,22 +42256,22 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>process.2.name</t>
+          <t>process.3.name</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Implementation</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>დანერგვა</t>
+          <t>მხარდაჭერა</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Внедрение</t>
+          <t>Поддержка</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr"/>
@@ -42218,22 +42294,22 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>process.2.desc</t>
+          <t>process.3.desc</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>We build the system in short sprints. You see the first result in 1-2 weeks.</t>
+          <t>The system grows with your business, and growth has no ceiling.</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>ვაწყობთ სისტემას მოკლე სპრინტებით. პირველ შედეგს 1-2 კვირაში ხედავ.</t>
+          <t>სისტემა ბიზნესთან ერთად იზრდება და ზრდას ზღვარი არ აქვს.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Строим систему короткими спринтами. Первый результат - через 1-2 недели.</t>
+          <t>Система растёт вместе с бизнесом, и у роста нет потолка.</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr"/>
@@ -42256,22 +42332,22 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.1</t>
+          <t>process.3.time</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>System setup and data migration</t>
+          <t>Ongoing · as needed</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>სისტემის აწყობა და მონაცემების გადატანა</t>
+          <t>მუდმივად · საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Настройка системы и перенос данных</t>
+          <t>Постоянно · по необходимости</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr"/>
@@ -42294,22 +42370,22 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.2</t>
+          <t>process.note</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Automations and integrations</t>
+          <t>Pricing is set individually, based on your needs.</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და ინტეგრაციები</t>
+          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Автоматизации и интеграции</t>
+          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr"/>
@@ -42332,22 +42408,22 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>process.2.item.3</t>
+          <t>process.cta</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Team training</t>
+          <t>Request a free 20-minute call</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>გუნდის ტრენინგი</t>
+          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Обучение команды</t>
+          <t>Запросить бесплатный 20-минутный звонок</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr"/>
@@ -42365,30 +42441,34 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>process.2.time</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>Sprint · 1-2 weeks</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>სპრინტი · 1-2 კვირა</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t>Спринт · 1-2 недели</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr"/>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>75+ ready-made CRM, AI and analytics solutions | Unitty</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>75+ მზა გადაწყვეტა CRM-ის, AI-ს და ანალიტიკისთვის | Unitty</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>75+ готовых решений для CRM, AI и аналитики | Unitty</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -42408,22 +42488,22 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>process.3.name</t>
+          <t>process.0.name</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Where you are today</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>მხარდაჭერა</t>
+          <t>დღევანდელი რეალობა</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Поддержка</t>
+          <t>Где вы сейчас</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr"/>
@@ -42446,22 +42526,22 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>process.3.desc</t>
+          <t>process.0.desc</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>The system keeps working after launch and grows with your business.</t>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>სისტემა გაშვების შემდეგაც მუშაობს და იზრდება ბიზნესთან ერთად.</t>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Система продолжает работать после запуска и растёт вместе с бизнесом.</t>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr"/>
@@ -42484,22 +42564,22 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.1</t>
+          <t>process.0.time</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Technical support when you need it</t>
+          <t>Starting point</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>ტექნიკური მხარდაჭერა, როცა გჭირდება</t>
+          <t>საწყისი წერტილი</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Техническая поддержка, когда она нужна</t>
+          <t>Отправная точка</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr"/>
@@ -42522,22 +42602,22 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.2</t>
+          <t>process.chart.chaos</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Ongoing optimization and improvements</t>
+          <t>Chaos</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>მუდმივი ოპტიმიზაცია და განვითარება</t>
+          <t>ქაოსი</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Постоянная оптимизация и развитие</t>
+          <t>Хаос</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr"/>
@@ -42560,22 +42640,22 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>process.3.item.3</t>
+          <t>process.chart.growth</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>New tools added as you need them</t>
+          <t>Growth ∞</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>ახალი ინსტრუმენტების დამატება საჭიროებისამებრ</t>
+          <t>ზრდა ∞</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Новые инструменты - по мере необходимости</t>
+          <t>Рост ∞</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr"/>
@@ -42593,30 +42673,34 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Prod</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>process.3.time</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Ongoing · as needed</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>მუდმივად · საჭიროებისამებრ</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>Постоянно · по необходимости</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr"/>
+          <t>prod.title</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>Our own products</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="inlineStr">
+        <is>
+          <t>ჩვენი პროდუქტები</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>Наши продукты</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -42631,30 +42715,34 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Prod</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>process.note</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Pricing is set individually, based on your needs.</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr"/>
+          <t>prod.sub</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -42669,30 +42757,34 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Prod</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>process.cta</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Request a free 20-minute call</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr"/>
+          <t>prod.cta</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>Request →</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>მოითხოვე →</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>Запросить →</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -42707,27 +42799,27 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Seo</t>
+          <t>Prod</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>seo.title</t>
+          <t>prod.1.desc</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>75+ ready-made CRM, AI and analytics solutions | Unitty</t>
+          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
         </is>
       </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
-          <t>75+ მზა გადაწყვეტა CRM-ის, AI-ს და ანალიტიკისთვის | Unitty</t>
+          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
         </is>
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>75+ готовых решений для CRM, AI и аналитики | Unitty</t>
+          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -42754,22 +42846,22 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>prod.title</t>
+          <t>prod.2.desc</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>Our own products</t>
+          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
         </is>
       </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
-          <t>ჩვენი პროდუქტები</t>
+          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
         </is>
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>Наши продукты</t>
+          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -42796,22 +42888,22 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>prod.sub</t>
+          <t>prod.3.desc</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
+          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
+          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
+          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -42838,22 +42930,22 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>prod.cta</t>
+          <t>prod.4.desc</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Request →</t>
+          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე →</t>
+          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Запросить →</t>
+          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -42880,22 +42972,22 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>prod.1.desc</t>
+          <t>prod.5.desc</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
+          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
+          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
+          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -42922,22 +43014,22 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>prod.2.desc</t>
+          <t>prod.6.desc</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
+          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
         </is>
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
+          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
+          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -42964,22 +43056,22 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>prod.3.desc</t>
+          <t>prod.7.desc</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
+          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
         </is>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
+          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
+          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -43006,22 +43098,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>prod.4.desc</t>
+          <t>prod.8.desc</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
+          <t>Personalised SMS reminders and notifications straight from your CRM - for payments, meetings and bookings.</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
+          <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან — გადახდებზე, შეხვედრებსა და ჯავშნებზე.</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
+          <t>Персональные SMS-напоминания и уведомления прямо из CRM - о платежах, встречах и бронях.</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -43035,178 +43127,10 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>Prod</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>prod.5.desc</t>
-        </is>
-      </c>
-      <c r="D174" s="9" t="inlineStr">
-        <is>
-          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
-        </is>
-      </c>
-      <c r="E174" s="9" t="inlineStr">
-        <is>
-          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
-        </is>
-      </c>
-      <c r="F174" s="9" t="inlineStr">
-        <is>
-          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>Prod</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>prod.6.desc</t>
-        </is>
-      </c>
-      <c r="D175" s="9" t="inlineStr">
-        <is>
-          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
-        </is>
-      </c>
-      <c r="E175" s="9" t="inlineStr">
-        <is>
-          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
-        </is>
-      </c>
-      <c r="F175" s="9" t="inlineStr">
-        <is>
-          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>Prod</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>prod.7.desc</t>
-        </is>
-      </c>
-      <c r="D176" s="9" t="inlineStr">
-        <is>
-          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
-        </is>
-      </c>
-      <c r="E176" s="9" t="inlineStr">
-        <is>
-          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
-        </is>
-      </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>Prod</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>prod.8.desc</t>
-        </is>
-      </c>
-      <c r="D177" s="9" t="inlineStr">
-        <is>
-          <t>Personalised SMS reminders and notifications straight from your CRM - for payments, meetings and bookings.</t>
-        </is>
-      </c>
-      <c r="E177" s="9" t="inlineStr">
-        <is>
-          <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან — გადახდებზე, შეხვედრებსა და ჯავშნებზე.</t>
-        </is>
-      </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>Персональные SMS-напоминания и уведомления прямо из CRM - о платежах, встречах и бронях.</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H177"/>
+  <autoFilter ref="A1:H173"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H376" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H372" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -13,11 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed keys" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$331</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$217</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -5681,10 +5681,48 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>process.go</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Request now</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>მოითხოვე ახლავე</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Запросить сейчас</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H136"/>
+  <autoFilter ref="A1:H137"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H335" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H336" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5698,7 +5736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H331"/>
+  <dimension ref="A1:H333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -9195,17 +9233,17 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Implementation packages have fixed prices: Starter €990 (5 working days), Essentials €2,990 (15 days), Growth €5,990 (25 days), add-ons from €190. VAT (18%) is added. You pay the CRM licence directly to the vendor at its official price. On the 20-minute call we tell you which package you need and what the licence costs.</t>
+          <t>Implementation packages have fixed prices: Starter €990 (5 working days), Essentials €1,999 (instead of €2,499, 20% off; 15 days), Growth €5,990 (25 days), add-ons from €190. VAT (18%) is added. You pay the CRM licence directly to the vendor at its official price. On the 20-minute call we tell you which package you need and what the licence costs.</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>დანერგვის პაკეტები ფიქსირებული ფასისაა: სტარტი €990 (5 სამუშაო დღე), ოპტიმალური €2,990 (15 დღე), ზრდა €5,990 (25 დღე), დამატებები €190-დან. ფასებს ემატება დღგ (18%). CRM-ის ლიცენზიას პირდაპირ მწარმოებელს უხდი მისი ოფიციალური ფასით. 20-წუთიან ზარზე გეტყვით, რომელი პაკეტი გჭირდება და რამდენი დაჯდება ლიცენზია.</t>
+          <t>დანერგვის პაკეტები ფიქსირებული ფასისაა: სტარტი €990 (5 სამუშაო დღე), ოპტიმალური €1,999 (ნაცვლად €2,499, 20% ფასდაკლებით; 15 დღე), ზრდა €5,990 (25 დღე), დამატებები €190-დან. ფასებს ემატება დღგ (18%). CRM-ის ლიცენზიას პირდაპირ მწარმოებელს უხდი მისი ოფიციალური ფასით. 20-წუთიან ზარზე გეტყვით, რომელი პაკეტი გჭირდება და რამდენი დაჯდება ლიცენზია.</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Пакеты внедрения с фиксированной ценой: «Старт» €990 (5 рабочих дней), «Оптимальный» €2,990 (15 дней), «Рост» €5,990 (25 дней), дополнения от €190. Добавляется НДС (18%). Лицензию CRM вы оплачиваете напрямую производителю по официальной цене. На 20-минутном звонке скажем, какой пакет нужен и сколько стоит лицензия.</t>
+          <t>Пакеты внедрения с фиксированной ценой: «Старт» €990 (5 рабочих дней), «Оптимальный» €1,999 (вместо €2,499, скидка 20%; 15 дней), «Рост» €5,990 (25 дней), дополнения от €190. Добавляется НДС (18%). Лицензию CRM вы оплачиваете напрямую производителю по официальной цене. На 20-минутном звонке скажем, какой пакет нужен и сколько стоит лицензия.</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -14063,34 +14101,30 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
-        </is>
-      </c>
-      <c r="D218" s="9" t="inlineStr">
-        <is>
-          <t>Choose where to start</t>
-        </is>
-      </c>
-      <c r="E218" s="9" t="inlineStr">
-        <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
-        </is>
-      </c>
-      <c r="F218" s="9" t="inlineStr">
-        <is>
-          <t>Выберите, с чего начать</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.go</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Request now</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>მოითხოვე ახლავე</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>Запросить сейчас</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr"/>
       <c r="H218" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14110,22 +14144,22 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
+          <t>pk.title</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
+          <t>Choose where to start</t>
         </is>
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
+          <t>აირჩიე, საიდან დაიწყო</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
+          <t>Выберите, с чего начать</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -14152,22 +14186,22 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
+          <t>pk.sub</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>Most popular</t>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
         </is>
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
+          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
         <is>
-          <t>Выбирают чаще всего</t>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -14194,22 +14228,22 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>one-time, + VAT</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>ერთჯერადად, + დღგ</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>разово, + НДС</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -14236,22 +14270,22 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
+          <t>pk.deal</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>working days</t>
+          <t>Discount valid for 1 week from the day the offer is sent.</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>სამუშაო დღე</t>
+          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
         <is>
-          <t>рабочих дней</t>
+          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -14278,22 +14312,22 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>pk.full</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>Everything included</t>
+          <t>one-time, + VAT</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>სრული ჩამონათვალი</t>
+          <t>ერთჯერადად, + დღგ</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>Всё, что входит</t>
+          <t>разово, + НДС</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -14320,22 +14354,22 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>Choose this package</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>ამ პაკეტის არჩევა</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>Выбрать этот пакет</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -14362,22 +14396,22 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>არჩეულია</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>Выбран</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -14404,22 +14438,22 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -14446,22 +14480,22 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>pk.cur</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>ვალუტა</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>Валюта</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -14483,27 +14517,27 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>Extra features</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>დამატებითი ფუნქციები</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>Дополнительные функции</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -14525,27 +14559,27 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>Optional. Add only if you need them</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>Необязательно. Добавьте, если нужно</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -14572,22 +14606,22 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>ao.popular</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>Often added</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>ხშირად ამატებენ</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>Часто добавляют</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -14614,22 +14648,22 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>ao.more</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>All add-ons by category</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
+          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>Все дополнения по категориям</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -14656,22 +14690,22 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -14693,27 +14727,27 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Choose a package</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე პაკეტი</t>
+          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>Выберите пакет</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -14735,27 +14769,27 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>ფუნქცია</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>функц.</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -14782,22 +14816,22 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>+ VAT</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>+ დღგ</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>+ НДС</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -14824,22 +14858,22 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>Request a call</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -14866,22 +14900,22 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>Your selection:</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>შენი არჩევანი:</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>Ваш выбор:</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -14903,27 +14937,27 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>სტარტი</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr">
         <is>
-          <t>Старт</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -14945,27 +14979,27 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.short</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>To move from Excel into a CRM</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>Чтобы перейти с Excel на CRM</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -14992,22 +15026,22 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h1</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>4 core modules</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -15034,22 +15068,22 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h2</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>Email and Facebook inside the CRM</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტა და Facebook CRM-ში</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Почта и Facebook внутри CRM</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -15076,22 +15110,22 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h3</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>Lead form and KPI dashboard</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ფორმა და KPI დაფა</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>Форма лидов и дашборд KPI</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -15118,22 +15152,22 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -15160,22 +15194,22 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -15202,22 +15236,22 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Facebook messages right inside the CRM</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>Сообщения Facebook прямо в CRM</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -15244,22 +15278,22 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>1 web form to capture leads</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>1 веб-форма для приёма лидов</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -15286,22 +15320,22 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>1 sales-pipeline KPI dashboard</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Дашборд KPI воронки продаж</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -15328,22 +15362,22 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>Recorded video instructions for the team</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>Видеоинструкции для команды</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -15370,22 +15404,22 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Essentials</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალური</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>Оптимальный</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -15412,22 +15446,22 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.short</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>For a 5-10 person sales team</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>Для отдела продаж из 5-10 человек</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -15454,22 +15488,22 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter, plus:</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта», плюс:</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -15496,22 +15530,22 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h1</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
+          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта»</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -15538,22 +15572,22 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h2</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads, automatically</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -15580,22 +15614,22 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h3</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Stage rules and lead assignment</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Правила этапов и распределение лидов</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -15622,22 +15656,22 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -15664,22 +15698,22 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -15706,22 +15740,22 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -15748,22 +15782,22 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -15790,22 +15824,22 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -15832,22 +15866,22 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -15874,22 +15908,22 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -15916,22 +15950,22 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -15958,22 +15992,22 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -16000,22 +16034,22 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -16042,22 +16076,22 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.short</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>For a growing 15-25 person team</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
+          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Для растущей команды из 15-25 человек</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -16084,22 +16118,22 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -16126,22 +16160,22 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h1</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი</t>
+          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального»</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -16168,22 +16202,22 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h2</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Telephony and call processing</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია და ზარების დამუშავება</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>Телефония и обработка звонков</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -16210,22 +16244,22 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h3</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Automations and AI (Claude)</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და AI (Claude)</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>Автоматизации и AI (Claude)</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -16252,22 +16286,22 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -16294,22 +16328,22 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -16336,22 +16370,22 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -16378,22 +16412,22 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -16420,22 +16454,22 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -16462,22 +16496,22 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -16504,22 +16538,22 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -16546,22 +16580,22 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -16588,22 +16622,22 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -16625,27 +16659,27 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -16667,27 +16701,27 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -16714,22 +16748,22 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -16756,22 +16790,22 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -16798,22 +16832,22 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>ao.18</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG bank wire deposit matching</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Автосверка переводов TBC/BOG</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -16840,22 +16874,22 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>ao.30</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -16882,22 +16916,22 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>ao.38</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -16924,22 +16958,22 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -16966,22 +17000,22 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -17008,22 +17042,22 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -17050,22 +17084,22 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -17092,22 +17126,22 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -17134,22 +17168,22 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -17176,22 +17210,22 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -17218,22 +17252,22 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -17260,22 +17294,22 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოების აღრიცხვა</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -17302,22 +17336,22 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -17344,22 +17378,22 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>ao.12</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Email + calendar 2-way sync</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+          <t>ბროკერების საკომისიოების აღრიცხვა</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -17386,22 +17420,22 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>ao.13</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Возврат пропущенных звонков и SMS</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -17428,22 +17462,22 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>ao.14</t>
+          <t>ao.12</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>Messaging bot lead capture webhook</t>
+          <t>Email + calendar 2-way sync</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
+          <t>Двусторонняя синхронизация почты и календаря</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -17470,22 +17504,22 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>ao.13</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Missed-call recovery &amp; SMS callback</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Возврат пропущенных звонков и SMS</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -17512,22 +17546,22 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>ao.15</t>
+          <t>ao.14</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Website lead form + webhook</t>
+          <t>Messaging bot lead capture webhook</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + webhook</t>
+          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + webhook</t>
+          <t>Лиды из чат-бота сразу в CRM</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -17554,22 +17588,22 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>ao.16</t>
+          <t>ao.cat.mkt</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
+          <t>Marketing &amp; growth</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
+          <t>მარკეტინგი</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>ROI источников и атрибуция кампаний</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -17596,22 +17630,22 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>ao.17</t>
+          <t>ao.15</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
+          <t>Website lead form + webhook</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+          <t>საიტის ფორმა + webhook</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
+          <t>Форма сайта + webhook</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -17638,22 +17672,22 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>ao.16</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>Lead source ROI &amp; campaign attribution</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>ROI источников и атрибуция кампаний</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -17680,22 +17714,22 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>ao.19</t>
+          <t>ao.17</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+          <t>Email campaigns: account setup &amp; contact sync</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -17722,22 +17756,22 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>ao.20</t>
+          <t>ao.cat.fin</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>NBG daily exchange rate sync</t>
+          <t>Fintech &amp; accounting</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+          <t>ფინანსები და ბანკები</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Ежедневный курс НБГ</t>
+          <t>Финансы и банки</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -17764,22 +17798,22 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>ao.21</t>
+          <t>ao.19</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Ambiguous payment reference fallback queue</t>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>Очередь неопознанных платежей</t>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -17806,22 +17840,22 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>ao.22</t>
+          <t>ao.20</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Dynamic installment payment schedule</t>
+          <t>NBG daily exchange rate sync</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>График рассрочки</t>
+          <t>Ежедневный курс НБГ</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -17848,22 +17882,22 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>ao.23</t>
+          <t>ao.21</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
+          <t>Ambiguous payment reference fallback queue</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>SMS о просроченной задолженности</t>
+          <t>Очередь неопознанных платежей</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -17890,22 +17924,22 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>ao.24</t>
+          <t>ao.22</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>SMS gateway &amp; OTP verification</t>
+          <t>Dynamic installment payment schedule</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+          <t>შიდა განვადების დინამიკური გრაფიკი</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>SMS-шлюз и OTP-верификация</t>
+          <t>График рассрочки</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -17932,22 +17966,22 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>ao.23</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>Overdue debt alert &amp; SMS warning</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>SMS о просроченной задолженности</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -17974,22 +18008,22 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>ao.25</t>
+          <t>ao.24</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
+          <t>SMS gateway &amp; OTP verification</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
+          <t>SMS-шлюз и OTP-верификация</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -18016,22 +18050,22 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>ao.26</t>
+          <t>ao.cat.cx</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Multi-tier SLA escalation matrix</t>
+          <t>Customer experience</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+          <t>მომხმარებლის მომსახურება</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>Матрица эскалации SLA</t>
+          <t>Клиентский сервис</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -18058,22 +18092,22 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>ao.27</t>
+          <t>ao.25</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Оценка NPS/CSAT после тикета</t>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -18100,22 +18134,22 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ao.28</t>
+          <t>ao.26</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Dynamic KYC intake smart form</t>
+          <t>Multi-tier SLA escalation matrix</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Умная KYC-форма</t>
+          <t>Матрица эскалации SLA</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -18142,22 +18176,22 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>ao.29</t>
+          <t>ao.27</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Warranty expiration alerts</t>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
+          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Напоминания об окончании гарантии</t>
+          <t>Оценка NPS/CSAT после тикета</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -18184,22 +18218,22 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.28</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Dynamic KYC intake smart form</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Умная KYC-форма</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -18226,22 +18260,22 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>ao.31</t>
+          <t>ao.29</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Georgian voice meeting transcription</t>
+          <t>Warranty expiration alerts</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+          <t>გარანტიის ვადის შეხსენებები</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Транскрипция встреч на грузинском</t>
+          <t>Напоминания об окончании гарантии</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -18268,22 +18302,22 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ao.32</t>
+          <t>ao.cat.ai</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>Audio call sentiment extractor</t>
+          <t>AI &amp; automation</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>Анализ тональности звонков</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -18310,22 +18344,22 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ind</t>
+          <t>ao.31</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Industry solutions</t>
+          <t>Georgian voice meeting transcription</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>დარგობრივი</t>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Отраслевые</t>
+          <t>Транскрипция встреч на грузинском</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -18352,22 +18386,22 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ao.33</t>
+          <t>ao.32</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
+          <t>Audio call sentiment extractor</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
+          <t>Анализ тональности звонков</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -18394,22 +18428,22 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>ao.34</t>
+          <t>ao.cat.ind</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Client preference proactive matcher</t>
+          <t>Industry solutions</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+          <t>დარგობრივი</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Автоподбор по пожеланиям клиента</t>
+          <t>Отраслевые</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -18436,22 +18470,22 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>ao.35</t>
+          <t>ao.33</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>Reservation expiration timer</t>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Таймер истечения брони</t>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -18478,22 +18512,22 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>ao.36</t>
+          <t>ao.34</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
+          <t>Client preference proactive matcher</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>PDF планировки и предложения</t>
+          <t>Автоподбор по пожеланиям клиента</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -18520,22 +18554,22 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>ao.37</t>
+          <t>ao.35</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Field service visit tracking + approval</t>
+          <t>Reservation expiration timer</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>Учёт выездов и подтверждение</t>
+          <t>Таймер истечения брони</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -18562,22 +18596,22 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.36</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Floor plan &amp; proposal PDF generator</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>PDF планировки и предложения</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -18604,22 +18638,22 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>ao.39</t>
+          <t>ao.37</t>
         </is>
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>Cold storage WMS &amp; automated billing</t>
+          <t>Field service visit tracking + approval</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+          <t>საველე ვიზიტების მართვა და დადასტურება</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>WMS холодного склада и биллинг</t>
+          <t>Учёт выездов и подтверждение</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -18646,22 +18680,22 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>ao.40</t>
+          <t>ao.cat.ops</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>Construction operations &amp; budget tracker</t>
+          <t>Operations &amp; ERP</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+          <t>ოპერაციები და ERP</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>Стройка: операции и бюджет</t>
+          <t>Операции и ERP</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -18688,22 +18722,22 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>ao.41</t>
+          <t>ao.39</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Predictive debtor call queue</t>
+          <t>Cold storage WMS &amp; automated billing</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>Умная очередь звонков должникам</t>
+          <t>WMS холодного склада и биллинг</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -18730,22 +18764,22 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>ao.42</t>
+          <t>ao.40</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Agent attendance tracker</t>
+          <t>Construction operations &amp; budget tracker</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>Учёт посещаемости агентов</t>
+          <t>Стройка: операции и бюджет</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -18772,22 +18806,22 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>ao.43</t>
+          <t>ao.41</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>Round-robin appointment balancing</t>
+          <t>Predictive debtor call queue</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>Равномерное распределение встреч</t>
+          <t>Умная очередь звонков должникам</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -18814,39 +18848,123 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
+          <t>ao.42</t>
+        </is>
+      </c>
+      <c r="D331" s="9" t="inlineStr">
+        <is>
+          <t>Agent attendance tracker</t>
+        </is>
+      </c>
+      <c r="E331" s="9" t="inlineStr">
+        <is>
+          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+        </is>
+      </c>
+      <c r="F331" s="9" t="inlineStr">
+        <is>
+          <t>Учёт посещаемости агентов</t>
+        </is>
+      </c>
+      <c r="G331" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>ao.43</t>
+        </is>
+      </c>
+      <c r="D332" s="9" t="inlineStr">
+        <is>
+          <t>Round-robin appointment balancing</t>
+        </is>
+      </c>
+      <c r="E332" s="9" t="inlineStr">
+        <is>
+          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+        </is>
+      </c>
+      <c r="F332" s="9" t="inlineStr">
+        <is>
+          <t>Равномерное распределение встреч</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H332" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
           <t>ao.44</t>
         </is>
       </c>
-      <c r="D331" s="9" t="inlineStr">
+      <c r="D333" s="9" t="inlineStr">
         <is>
           <t>Discovery call auto-scheduling</t>
         </is>
       </c>
-      <c r="E331" s="9" t="inlineStr">
+      <c r="E333" s="9" t="inlineStr">
         <is>
           <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
-      <c r="F331" s="9" t="inlineStr">
+      <c r="F333" s="9" t="inlineStr">
         <is>
           <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
-      <c r="G331" s="3" t="inlineStr">
+      <c r="G333" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H331" s="3" t="inlineStr">
+      <c r="H333" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H331"/>
+  <autoFilter ref="A1:H333"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H530" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H532" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18860,7 +18978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -27233,10 +27351,48 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>process.go</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Request now</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>მოითხოვე ახლავე</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>Запросить сейчас</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr"/>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H217"/>
+  <autoFilter ref="A1:H218"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H416" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H417" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -27250,7 +27406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -32485,10 +32641,48 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>process.go</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Request now</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>მოითხოვე ახლავე</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Запросить сейчас</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H136"/>
+  <autoFilter ref="A1:H137"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H335" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H336" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -32502,7 +32696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -37721,34 +37915,30 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>prod.title</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>Our own products</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>ჩვენი პროდუქტები</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>Наши продукты</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.go</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Request now</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>მოითხოვე ახლავე</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Запросить сейчас</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -37768,22 +37958,22 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>prod.sub</t>
+          <t>prod.title</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
+          <t>Our own products</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
+          <t>ჩვენი პროდუქტები</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
+          <t>Наши продукты</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -37810,22 +38000,22 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>prod.cta</t>
+          <t>prod.sub</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>Request →</t>
+          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე →</t>
+          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>Запросить →</t>
+          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -37852,22 +38042,22 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>prod.1.desc</t>
+          <t>prod.cta</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
+          <t>Request →</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
+          <t>მოითხოვე →</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
+          <t>Запросить →</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -37894,22 +38084,22 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>prod.2.desc</t>
+          <t>prod.1.desc</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
+          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
+          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
+          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -37936,22 +38126,22 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>prod.3.desc</t>
+          <t>prod.2.desc</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
+          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
+          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
+          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -37978,22 +38168,22 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>prod.4.desc</t>
+          <t>prod.3.desc</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
+          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
+          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr">
         <is>
-          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
+          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -38020,22 +38210,22 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>prod.5.desc</t>
+          <t>prod.4.desc</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
+          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
+          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
+          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -38062,22 +38252,22 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>prod.6.desc</t>
+          <t>prod.5.desc</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
+          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
+          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
+          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -38104,22 +38294,22 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>prod.7.desc</t>
+          <t>prod.6.desc</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
+          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
+          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
+          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -38146,39 +38336,81 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
+          <t>prod.7.desc</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
           <t>prod.8.desc</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr">
+      <c r="D148" s="9" t="inlineStr">
         <is>
           <t>Personalised SMS reminders and notifications straight from your CRM - for payments, meetings and bookings.</t>
         </is>
       </c>
-      <c r="E147" s="9" t="inlineStr">
+      <c r="E148" s="9" t="inlineStr">
         <is>
           <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან — გადახდებზე, შეხვედრებსა და ჯავშნებზე.</t>
         </is>
       </c>
-      <c r="F147" s="9" t="inlineStr">
+      <c r="F148" s="9" t="inlineStr">
         <is>
           <t>Персональные SMS-напоминания и уведомления прямо из CRM - о платежах, встречах и бронях.</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H148" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H147"/>
+  <autoFilter ref="A1:H148"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H346" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H347" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -13,11 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed keys" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$333</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$218</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$331</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -5457,30 +5457,34 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>process.note</t>
+          <t>seo.title</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Pricing is set individually, based on your needs.</t>
+          <t>Unitty - CRM, AI and automation for your business</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
+          <t>Unitty - CRM, AI და ავტომატიზაცია ბიზნესისთვის</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr"/>
+          <t>Unitty - CRM, AI и автоматизация для бизнеса</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -5500,22 +5504,22 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>process.cta</t>
+          <t>process.0.name</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Where you are today</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>დღევანდელი რეალობა</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Где вы сейчас</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr"/>
@@ -5533,34 +5537,30 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Seo</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>seo.title</t>
+          <t>process.0.desc</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Unitty - CRM, AI and automation for your business</t>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Unitty - CRM, AI და ავტომატიზაცია ბიზნესისთვის</t>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Unitty - CRM, AI и автоматизация для бизнеса</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -5580,22 +5580,22 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>process.0.name</t>
+          <t>process.0.time</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Where you are today</t>
+          <t>Starting point</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>დღევანდელი რეალობა</t>
+          <t>საწყისი წერტილი</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Где вы сейчас</t>
+          <t>Отправная точка</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr"/>
@@ -5618,22 +5618,22 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>process.0.desc</t>
+          <t>process.go</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+          <t>Request now</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+          <t>მოითხოვე ახლავე</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+          <t>Запросить сейчас</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
@@ -5643,86 +5643,10 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>process.0.time</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>Starting point</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>საწყისი წერტილი</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>Отправная точка</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr"/>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>process.go</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>Request now</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>მოითხოვე ახლავე</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>Запросить сейчас</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr"/>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H137"/>
+  <autoFilter ref="A1:H135"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H336" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H334" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5736,7 +5660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H333"/>
+  <dimension ref="A1:H331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -12307,34 +12231,30 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>process.note</t>
-        </is>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>Package prices are fixed. We confirm the right one together on the call.</t>
-        </is>
-      </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>პაკეტების ფასი ფიქსირებულია. რომელი გჭირდება, ზარზე ერთად დავაზუსტებთ.</t>
-        </is>
-      </c>
-      <c r="F171" s="9" t="inlineStr">
-        <is>
-          <t>Цены пакетов фиксированы. Какой подходит, уточним вместе на звонке.</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.manager.left</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Ana left the chat</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>ანამ დატოვა ჩატი</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>Анна покинула чат</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr"/>
       <c r="H171" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -12349,27 +12269,27 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>process.cta</t>
+          <t>pain.owner.note</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Today!!</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>დღეს!!</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Сегодня!!</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr"/>
@@ -12392,22 +12312,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.left</t>
+          <t>pain.chats.more</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Ana left the chat</t>
+          <t>+11 unanswered</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>ანამ დატოვა ჩატი</t>
+          <t>+11 უპასუხო</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Анна покинула чат</t>
+          <t>+11 без ответа</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr"/>
@@ -12425,30 +12345,34 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.note</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Today!!</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>დღეს!!</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>Сегодня!!</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr"/>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>CRM selection and implementation in Georgia | Unitty</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>CRM-ის შერჩევა და დანერგვა საქართველოში | Unitty</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>Подбор и внедрение CRM в Грузии | Unitty</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -12468,22 +12392,22 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.more</t>
+          <t>pain.ba.before</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>+11 unanswered</t>
+          <t>Before</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>+11 უპასუხო</t>
+          <t>დანერგვამდე</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>+11 без ответа</t>
+          <t>До внедрения</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr"/>
@@ -12501,34 +12425,30 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Seo</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>seo.title</t>
-        </is>
-      </c>
-      <c r="D176" s="9" t="inlineStr">
-        <is>
-          <t>CRM selection and implementation in Georgia | Unitty</t>
-        </is>
-      </c>
-      <c r="E176" s="9" t="inlineStr">
-        <is>
-          <t>CRM-ის შერჩევა და დანერგვა საქართველოში | Unitty</t>
-        </is>
-      </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>Подбор и внедрение CRM в Грузии | Unitty</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.ba.after</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>შედეგად</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>Результат</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr"/>
       <c r="H176" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -12548,22 +12468,22 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.before</t>
+          <t>pain.ba.hint</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Switch to see the same situation with a CRM</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>დანერგვამდე</t>
+          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>До внедрения</t>
+          <t>Переключите и посмотрите то же самое с CRM</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr"/>
@@ -12586,22 +12506,22 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.after</t>
+          <t>pain.ba.peek</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>See the result with CRM</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>შედეგად</t>
+          <t>ნახე შედეგი CRM-ით</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Результат</t>
+          <t>Посмотреть результат с CRM</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr"/>
@@ -12624,22 +12544,22 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.hint</t>
+          <t>pain.excel.atitle</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Switch to see the same situation with a CRM</t>
+          <t>The client's full history in one search</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
+          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Переключите и посмотрите то же самое с CRM</t>
+          <t>Вся история клиента — в одном поиске</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr"/>
@@ -12662,22 +12582,22 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.peek</t>
+          <t>pain.owner.atitle</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>See the result with CRM</t>
+          <t>The team knows who does what</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>ნახე შედეგი CRM-ით</t>
+          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Посмотреть результат с CRM</t>
+          <t>Команда знает, кто что делает</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr"/>
@@ -12700,22 +12620,22 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.atitle</t>
+          <t>pain.chats.atitle</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>The client's full history in one search</t>
+          <t>Every message in one window</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
+          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Вся история клиента — в одном поиске</t>
+          <t>Все сообщения — в одном окне</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr"/>
@@ -12738,22 +12658,22 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.atitle</t>
+          <t>pain.z.contacts</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>The team knows who does what</t>
+          <t>Contacts</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
+          <t>კონტაქტები</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Команда знает, кто что делает</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr"/>
@@ -12776,22 +12696,22 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.atitle</t>
+          <t>pain.z.found</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Every message in one window</t>
+          <t>1 result</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
+          <t>1 შედეგი</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Все сообщения — в одном окне</t>
+          <t>1 результат</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr"/>
@@ -12814,22 +12734,22 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>pain.z.contacts</t>
+          <t>pain.z.stage</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>კონტაქტები</t>
+          <t>შეთავაზება</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Предложение</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr"/>
@@ -12852,22 +12772,22 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>pain.z.found</t>
+          <t>pain.z.last</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>1 result</t>
+          <t>Last purchase</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>1 შედეგი</t>
+          <t>ბოლო შეძენა</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>1 результат</t>
+          <t>Последняя покупка</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr"/>
@@ -12890,22 +12810,22 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>pain.z.stage</t>
+          <t>pain.z.deals</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Deals</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>შეთავაზება</t>
+          <t>გარიგებები</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Предложение</t>
+          <t>Сделки</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr"/>
@@ -12928,22 +12848,22 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>pain.z.last</t>
+          <t>pain.z.merged</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Last purchase</t>
+          <t>Duplicate merged</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>ბოლო შეძენა</t>
+          <t>დუბლიკატი გაერთიანდა</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Последняя покупка</t>
+          <t>Дубликат объединён</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr"/>
@@ -12966,22 +12886,22 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>pain.z.deals</t>
+          <t>pain.z.tasks</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Deals</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>გარიგებები</t>
+          <t>დავალებები</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Сделки</t>
+          <t>Задачи</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr"/>
@@ -13004,22 +12924,22 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>pain.z.merged</t>
+          <t>pain.z.ontrack</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Duplicate merged</t>
+          <t>On track</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>დუბლიკატი გაერთიანდა</t>
+          <t>გეგმაშია</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Дубликат объединён</t>
+          <t>По плану</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -13042,22 +12962,22 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>pain.z.tasks</t>
+          <t>pain.z.t1</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Call the client</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>დავალებები</t>
+          <t>კლიენტთან ზარი</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Задачи</t>
+          <t>Звонок клиенту</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr"/>
@@ -13080,22 +13000,22 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>pain.z.ontrack</t>
+          <t>pain.z.t2</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>On track</t>
+          <t>Invoice on rs.ge</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>გეგმაშია</t>
+          <t>ინვოისი rs.ge-ზე</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>По плану</t>
+          <t>Счёт на rs.ge</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr"/>
@@ -13118,22 +13038,22 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t1</t>
+          <t>pain.z.t3</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Call the client</t>
+          <t>Send the price</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>კლიენტთან ზარი</t>
+          <t>ფასის გაგზავნა</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Звонок клиенту</t>
+          <t>Отправить цену</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr"/>
@@ -13156,22 +13076,22 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t2</t>
+          <t>pain.z.t4</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Invoice on rs.ge</t>
+          <t>Weekly report</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>ინვოისი rs.ge-ზე</t>
+          <t>კვირის რეპორტი</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Счёт на rs.ge</t>
+          <t>Недельный отчёт</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr"/>
@@ -13194,22 +13114,22 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t3</t>
+          <t>pain.z.n1</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Send the price</t>
+          <t>Nika</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>ფასის გაგზავნა</t>
+          <t>ნიკა</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Отправить цену</t>
+          <t>Ника</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr"/>
@@ -13232,22 +13152,22 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t4</t>
+          <t>pain.z.n2</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Weekly report</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>კვირის რეპორტი</t>
+          <t>ანა</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Недельный отчёт</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr"/>
@@ -13270,22 +13190,22 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n1</t>
+          <t>pain.z.n3</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Nika</t>
+          <t>Luka</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>ნიკა</t>
+          <t>ლუკა</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Ника</t>
+          <t>Лука</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr"/>
@@ -13308,22 +13228,22 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n2</t>
+          <t>pain.z.done</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>ანა</t>
+          <t>შესრულდა</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr"/>
@@ -13346,22 +13266,22 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n3</t>
+          <t>pain.z.auto</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Luka</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>ლუკა</t>
+          <t>ავტომატური</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Лука</t>
+          <t>Авто</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr"/>
@@ -13384,22 +13304,22 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>pain.z.done</t>
+          <t>pain.z.everymon</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Every Monday</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>შესრულდა</t>
+          <t>ყოველ ორშაბათს</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>Каждый понедельник</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr"/>
@@ -13422,22 +13342,22 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>pain.z.auto</t>
+          <t>pain.z.reminder</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Reminder sent to Luka</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>ავტომატური</t>
+          <t>ლუკას შეხსენება გაეგზავნა</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Авто</t>
+          <t>Луке отправлено напоминание</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr"/>
@@ -13460,22 +13380,22 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>pain.z.everymon</t>
+          <t>pain.z.inbox</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Every Monday</t>
+          <t>Inbox</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>ყოველ ორშაბათს</t>
+          <t>შეტყობინებები</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Каждый понедельник</t>
+          <t>Сообщения</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr"/>
@@ -13498,22 +13418,22 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>pain.z.reminder</t>
+          <t>pain.z.zero</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Reminder sent to Luka</t>
+          <t>0 unanswered</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>ლუკას შეხსენება გაეგზავნა</t>
+          <t>0 უპასუხო</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Луке отправлено напоминание</t>
+          <t>0 без ответа</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr"/>
@@ -13536,22 +13456,22 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>pain.z.inbox</t>
+          <t>pain.z.min</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Inbox</t>
+          <t>min</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>შეტყობინებები</t>
+          <t>წთ</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Сообщения</t>
+          <t>мин</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr"/>
@@ -13574,22 +13494,22 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>pain.z.zero</t>
+          <t>pain.excel.statn</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>0 unanswered</t>
+          <t>1.8 h</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>0 უპასუხო</t>
+          <t>1.8 სთ</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>0 без ответа</t>
+          <t>1,8 ч</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr"/>
@@ -13612,22 +13532,22 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>pain.z.min</t>
+          <t>pain.excel.stat</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>a day: the average time an employee spends searching for information</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>წთ</t>
+          <t>დღეში ხარჯავს საშუალოდ თანამშრომელი საჭირო ინფორმაციის ძებნაში</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>мин</t>
+          <t>в день в среднем тратит сотрудник на поиск нужной информации</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr"/>
@@ -13650,22 +13570,22 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.statn</t>
+          <t>pain.excel.src</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>1.8 h</t>
+          <t>Source: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>1.8 სთ</t>
+          <t>წყარო: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>1,8 ч</t>
+          <t>Источник: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr"/>
@@ -13688,22 +13608,22 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.stat</t>
+          <t>pain.owner.statn</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>a day: the average time an employee spends searching for information</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>დღეში ხარჯავს საშუალოდ თანამშრომელი საჭირო ინფორმაციის ძებნაში</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>в день в среднем тратит сотрудник на поиск нужной информации</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr"/>
@@ -13726,22 +13646,22 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.src</t>
+          <t>pain.owner.stat</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Source: McKinsey Global Institute</t>
+          <t>of business owners spend over 40% of their time on admin</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>წყარო: McKinsey Global Institute</t>
+          <t>მეწარმეების სამუშაო დროის 40%-ზე მეტს ადმინისტრაციულ საქმეებს ახმარს</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Источник: McKinsey Global Institute</t>
+          <t>предпринимателей тратят на администрирование больше 40% времени</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr"/>
@@ -13764,22 +13684,22 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.statn</t>
+          <t>pain.owner.src</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>Source: Visma &amp; Kantar, 2,000 business owners, 2024</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>წყარო: Visma &amp; Kantar, 2 000 მეწარმე, 2024</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>Источник: Visma &amp; Kantar, 2 000 предпринимателей, 2024</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr"/>
@@ -13802,22 +13722,22 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.stat</t>
+          <t>pain.chats.statn</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>of business owners spend over 40% of their time on admin</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>მეწარმეების სამუშაო დროის 40%-ზე მეტს ადმინისტრაციულ საქმეებს ახმარს</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>предпринимателей тратят на администрирование больше 40% времени</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr"/>
@@ -13840,22 +13760,22 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.src</t>
+          <t>pain.chats.stat</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Source: Visma &amp; Kantar, 2,000 business owners, 2024</t>
+          <t>higher chance to qualify a lead when you reply within an hour rather than later</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>წყარო: Visma &amp; Kantar, 2 000 მეწარმე, 2024</t>
+          <t>მეტია ლიდის დაკვალიფიცირების შანსი, თუ 1 საათში უპასუხებ და არა მოგვიანებით</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Источник: Visma &amp; Kantar, 2 000 предпринимателей, 2024</t>
+          <t>выше шанс квалифицировать лид, если ответить в течение часа, а не позже</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr"/>
@@ -13878,22 +13798,22 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.statn</t>
+          <t>pain.chats.src</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>7x</t>
+          <t>Source: Harvard Business Review</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>7x</t>
+          <t>წყარო: Harvard Business Review</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>7x</t>
+          <t>Источник: Harvard Business Review</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr"/>
@@ -13911,27 +13831,27 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.stat</t>
+          <t>process.0.name</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>higher chance to qualify a lead when you reply within an hour rather than later</t>
+          <t>Where you are today</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>მეტია ლიდის დაკვალიფიცირების შანსი, თუ 1 საათში უპასუხებ და არა მოგვიანებით</t>
+          <t>დღევანდელი რეალობა</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>выше шанс квалифицировать лид, если ответить в течение часа, а не позже</t>
+          <t>Где вы сейчас</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr"/>
@@ -13949,27 +13869,27 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.src</t>
+          <t>process.0.desc</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Source: Harvard Business Review</t>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>წყარო: Harvard Business Review</t>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Источник: Harvard Business Review</t>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr"/>
@@ -13992,22 +13912,22 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>process.0.name</t>
+          <t>process.0.time</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Where you are today</t>
+          <t>Starting point</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>დღევანდელი რეალობა</t>
+          <t>საწყისი წერტილი</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Где вы сейчас</t>
+          <t>Отправная точка</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr"/>
@@ -14030,22 +13950,22 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>process.0.desc</t>
+          <t>process.go</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+          <t>Request now</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+          <t>მოითხოვე ახლავე</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+          <t>Запросить сейчас</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr"/>
@@ -14063,30 +13983,34 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>process.0.time</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>Starting point</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>საწყისი წერტილი</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
-        <is>
-          <t>Отправная точка</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr"/>
+          <t>pk.title</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>Choose where to start</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
+          <t>აირჩიე, საიდან დაიწყო</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>Выберите, с чего начать</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14101,30 +14025,34 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>process.go</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>Request now</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>მოითხოვე ახლავე</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>Запросить сейчас</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr"/>
+          <t>pk.sub</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="inlineStr">
+        <is>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
+        </is>
+      </c>
+      <c r="E218" s="9" t="inlineStr">
+        <is>
+          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
+        </is>
+      </c>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14144,22 +14072,22 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>Choose where to start</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>Выберите, с чего начать</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -14186,22 +14114,22 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
+          <t>pk.deal</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
+          <t>Discount valid for 1 week from the day the offer is sent.</t>
         </is>
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
+          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
         <is>
-          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
+          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -14228,22 +14156,22 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>Most popular</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
+          <t>ერთჯერადად</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>Выбирают чаще всего</t>
+          <t>разово</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -14270,22 +14198,22 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>pk.deal</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>Discount valid for 1 week from the day the offer is sent.</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
         <is>
-          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -14312,22 +14240,22 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>one-time, + VAT</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>ერთჯერადად, + დღგ</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>разово, + НДС</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -14354,22 +14282,22 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>working days</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>სამუშაო დღე</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>рабочих дней</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -14396,22 +14324,22 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>pk.full</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>Everything included</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>სრული ჩამონათვალი</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>Всё, что входит</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -14438,22 +14366,22 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>Choose this package</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>ამ პაკეტის არჩევა</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>Выбрать этот пакет</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -14480,22 +14408,22 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>არჩეულია</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>Выбран</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -14517,27 +14445,27 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -14559,27 +14487,27 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>pk.cur</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>ვალუტა</t>
+          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>Валюта</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -14606,22 +14534,22 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>Extra features</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>დამატებითი ფუნქციები</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>Дополнительные функции</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -14648,22 +14576,22 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>Optional. Add only if you need them</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
+          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>Необязательно. Добавьте, если нужно</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -14690,22 +14618,22 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>ao.popular</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>Often added</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>ხშირად ამატებენ</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>Часто добавляют</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -14727,27 +14655,27 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>ao.more</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>All add-ons by category</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>Все дополнения по категориям</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -14769,27 +14697,27 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -14816,22 +14744,22 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>Choose a package</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე პაკეტი</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>Выберите пакет</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -14858,22 +14786,22 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>ფუნქცია</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
         <is>
-          <t>функц.</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -14900,22 +14828,22 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>+ VAT</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>+ დღგ</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>+ НДС</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -14937,27 +14865,27 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>Request a call</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -14979,27 +14907,27 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Your selection:</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>შენი არჩევანი:</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>Ваш выбор:</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -15026,22 +14954,22 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>სტარტი</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>Старт</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -15068,22 +14996,22 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.short</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>To move from Excel into a CRM</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Чтобы перейти с Excel на CRM</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -15110,22 +15038,22 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h1</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>4 core modules</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -15152,22 +15080,22 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h2</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Email and Facebook inside the CRM</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტა და Facebook CRM-ში</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Почта и Facebook внутри CRM</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -15194,22 +15122,22 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h3</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>Lead form and KPI dashboard</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ფორმა და KPI დაფა</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>Форма лидов и дашборд KPI</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -15236,22 +15164,22 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -15278,22 +15206,22 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -15320,22 +15248,22 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Facebook messages right inside the CRM</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Сообщения Facebook прямо в CRM</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -15362,22 +15290,22 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>1 web form to capture leads</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>1 веб-форма для приёма лидов</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -15404,22 +15332,22 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>1 sales-pipeline KPI dashboard</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>Дашборд KPI воронки продаж</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -15446,22 +15374,22 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>Recorded video instructions for the team</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>Видеоинструкции для команды</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -15488,22 +15416,22 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Essentials</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალური</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>Оптимальный</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -15530,22 +15458,22 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.short</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>For a 5-10 person sales team</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>Для отдела продаж из 5-10 человек</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -15572,22 +15500,22 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter, plus:</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта», плюс:</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -15614,22 +15542,22 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h1</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта»</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -15656,22 +15584,22 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h2</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads, automatically</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -15698,22 +15626,22 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h3</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>Stage rules and lead assignment</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>Правила этапов и распределение лидов</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -15740,22 +15668,22 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -15782,22 +15710,22 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -15824,22 +15752,22 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -15866,22 +15794,22 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -15908,22 +15836,22 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -15950,22 +15878,22 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -15992,22 +15920,22 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -16034,22 +15962,22 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -16076,22 +16004,22 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -16118,22 +16046,22 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -16160,22 +16088,22 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.short</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>For a growing 15-25 person team</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Для растущей команды из 15-25 человек</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -16202,22 +16130,22 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -16244,22 +16172,22 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h1</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального»</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -16286,22 +16214,22 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h2</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Telephony and call processing</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია და ზარების დამუშავება</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>Телефония и обработка звонков</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -16328,22 +16256,22 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h3</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Automations and AI (Claude)</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და AI (Claude)</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>Автоматизации и AI (Claude)</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -16370,22 +16298,22 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -16412,22 +16340,22 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -16454,22 +16382,22 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -16496,22 +16424,22 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -16538,22 +16466,22 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -16580,22 +16508,22 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -16622,22 +16550,22 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -16659,27 +16587,27 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -16701,27 +16629,27 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -16748,22 +16676,22 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -16790,22 +16718,22 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -16832,22 +16760,22 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -16874,22 +16802,22 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -16916,22 +16844,22 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>ao.18</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG bank wire deposit matching</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Автосверка переводов TBC/BOG</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -16958,22 +16886,22 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>ao.30</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -17000,22 +16928,22 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>ao.38</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -17042,22 +16970,22 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -17084,22 +17012,22 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -17126,22 +17054,22 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -17168,22 +17096,22 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -17210,22 +17138,22 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -17252,22 +17180,22 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -17294,22 +17222,22 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>ბროკერების საკომისიოების აღრიცხვა</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -17336,22 +17264,22 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -17378,22 +17306,22 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>ao.12</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>Email + calendar 2-way sync</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოების აღრიცხვა</t>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>Двусторонняя синхронизация почты и календаря</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -17420,22 +17348,22 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>ao.13</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Missed-call recovery &amp; SMS callback</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Возврат пропущенных звонков и SMS</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -17462,22 +17390,22 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>ao.12</t>
+          <t>ao.14</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>Email + calendar 2-way sync</t>
+          <t>Messaging bot lead capture webhook</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
+          <t>Лиды из чат-бота сразу в CRM</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -17504,22 +17432,22 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>ao.13</t>
+          <t>ao.cat.mkt</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
+          <t>Marketing &amp; growth</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
+          <t>მარკეტინგი</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>Возврат пропущенных звонков и SMS</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -17546,22 +17474,22 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>ao.14</t>
+          <t>ao.15</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Messaging bot lead capture webhook</t>
+          <t>Website lead form + webhook</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
+          <t>საიტის ფორმა + webhook</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
+          <t>Форма сайта + webhook</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -17588,22 +17516,22 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>ao.16</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Lead source ROI &amp; campaign attribution</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>ROI источников и атрибуция кампаний</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -17630,22 +17558,22 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>ao.15</t>
+          <t>ao.17</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Website lead form + webhook</t>
+          <t>Email campaigns: account setup &amp; contact sync</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + webhook</t>
+          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + webhook</t>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -17672,22 +17600,22 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>ao.16</t>
+          <t>ao.cat.fin</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
+          <t>Fintech &amp; accounting</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
+          <t>ფინანსები და ბანკები</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>ROI источников и атрибуция кампаний</t>
+          <t>Финансы и банки</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -17714,22 +17642,22 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>ao.17</t>
+          <t>ao.19</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -17756,22 +17684,22 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>ao.20</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>NBG daily exchange rate sync</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>Ежедневный курс НБГ</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -17798,22 +17726,22 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>ao.19</t>
+          <t>ao.21</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+          <t>Ambiguous payment reference fallback queue</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+          <t>Очередь неопознанных платежей</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -17840,22 +17768,22 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>ao.20</t>
+          <t>ao.22</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>NBG daily exchange rate sync</t>
+          <t>Dynamic installment payment schedule</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+          <t>შიდა განვადების დინამიკური გრაფიკი</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>Ежедневный курс НБГ</t>
+          <t>График рассрочки</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -17882,22 +17810,22 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>ao.21</t>
+          <t>ao.23</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Ambiguous payment reference fallback queue</t>
+          <t>Overdue debt alert &amp; SMS warning</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>Очередь неопознанных платежей</t>
+          <t>SMS о просроченной задолженности</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -17924,22 +17852,22 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>ao.22</t>
+          <t>ao.24</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Dynamic installment payment schedule</t>
+          <t>SMS gateway &amp; OTP verification</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>График рассрочки</t>
+          <t>SMS-шлюз и OTP-верификация</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -17966,22 +17894,22 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>ao.23</t>
+          <t>ao.cat.cx</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
+          <t>Customer experience</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+          <t>მომხმარებლის მომსახურება</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>SMS о просроченной задолженности</t>
+          <t>Клиентский сервис</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -18008,22 +17936,22 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>ao.24</t>
+          <t>ao.25</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>SMS gateway &amp; OTP verification</t>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>SMS-шлюз и OTP-верификация</t>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -18050,22 +17978,22 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>ao.26</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>Multi-tier SLA escalation matrix</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>Матрица эскалации SLA</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -18092,22 +18020,22 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>ao.25</t>
+          <t>ao.27</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
+          <t>Оценка NPS/CSAT после тикета</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -18134,22 +18062,22 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ao.26</t>
+          <t>ao.28</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Multi-tier SLA escalation matrix</t>
+          <t>Dynamic KYC intake smart form</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Матрица эскалации SLA</t>
+          <t>Умная KYC-форма</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -18176,22 +18104,22 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>ao.27</t>
+          <t>ao.29</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
+          <t>Warranty expiration alerts</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+          <t>გარანტიის ვადის შეხსენებები</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Оценка NPS/CSAT после тикета</t>
+          <t>Напоминания об окончании гарантии</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -18218,22 +18146,22 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>ao.28</t>
+          <t>ao.cat.ai</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Dynamic KYC intake smart form</t>
+          <t>AI &amp; automation</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>Умная KYC-форма</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -18260,22 +18188,22 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>ao.29</t>
+          <t>ao.31</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Warranty expiration alerts</t>
+          <t>Georgian voice meeting transcription</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Напоминания об окончании гарантии</t>
+          <t>Транскрипция встреч на грузинском</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -18302,22 +18230,22 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.32</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Audio call sentiment extractor</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Анализ тональности звонков</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -18344,22 +18272,22 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>ao.31</t>
+          <t>ao.cat.ind</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Georgian voice meeting transcription</t>
+          <t>Industry solutions</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+          <t>დარგობრივი</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Транскрипция встреч на грузинском</t>
+          <t>Отраслевые</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -18386,22 +18314,22 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ao.32</t>
+          <t>ao.33</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Audio call sentiment extractor</t>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Анализ тональности звонков</t>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -18428,22 +18356,22 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ind</t>
+          <t>ao.34</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Industry solutions</t>
+          <t>Client preference proactive matcher</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>დარგობრივი</t>
+          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Отраслевые</t>
+          <t>Автоподбор по пожеланиям клиента</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -18470,22 +18398,22 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>ao.33</t>
+          <t>ao.35</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
+          <t>Reservation expiration timer</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
+          <t>Таймер истечения брони</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -18512,22 +18440,22 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>ao.34</t>
+          <t>ao.36</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Client preference proactive matcher</t>
+          <t>Floor plan &amp; proposal PDF generator</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>Автоподбор по пожеланиям клиента</t>
+          <t>PDF планировки и предложения</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -18554,22 +18482,22 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>ao.35</t>
+          <t>ao.37</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Reservation expiration timer</t>
+          <t>Field service visit tracking + approval</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+          <t>საველე ვიზიტების მართვა და დადასტურება</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>Таймер истечения брони</t>
+          <t>Учёт выездов и подтверждение</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -18596,22 +18524,22 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>ao.36</t>
+          <t>ao.cat.ops</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
+          <t>Operations &amp; ERP</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+          <t>ოპერაციები და ERP</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>PDF планировки и предложения</t>
+          <t>Операции и ERP</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -18638,22 +18566,22 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>ao.37</t>
+          <t>ao.39</t>
         </is>
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>Field service visit tracking + approval</t>
+          <t>Cold storage WMS &amp; automated billing</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>Учёт выездов и подтверждение</t>
+          <t>WMS холодного склада и биллинг</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -18680,22 +18608,22 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.40</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Construction operations &amp; budget tracker</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>Стройка: операции и бюджет</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -18722,22 +18650,22 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>ao.39</t>
+          <t>ao.41</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Cold storage WMS &amp; automated billing</t>
+          <t>Predictive debtor call queue</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>WMS холодного склада и биллинг</t>
+          <t>Умная очередь звонков должникам</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -18764,22 +18692,22 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>ao.40</t>
+          <t>ao.42</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Construction operations &amp; budget tracker</t>
+          <t>Agent attendance tracker</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>Стройка: операции и бюджет</t>
+          <t>Учёт посещаемости агентов</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -18806,22 +18734,22 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>ao.41</t>
+          <t>ao.43</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>Predictive debtor call queue</t>
+          <t>Round-robin appointment balancing</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>Умная очередь звонков должникам</t>
+          <t>Равномерное распределение встреч</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -18848,22 +18776,22 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>ao.42</t>
+          <t>ao.44</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>Agent attendance tracker</t>
+          <t>Discovery call auto-scheduling</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+          <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>Учёт посещаемости агентов</t>
+          <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -18877,94 +18805,10 @@
         </is>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C332" s="3" t="inlineStr">
-        <is>
-          <t>ao.43</t>
-        </is>
-      </c>
-      <c r="D332" s="9" t="inlineStr">
-        <is>
-          <t>Round-robin appointment balancing</t>
-        </is>
-      </c>
-      <c r="E332" s="9" t="inlineStr">
-        <is>
-          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
-        </is>
-      </c>
-      <c r="F332" s="9" t="inlineStr">
-        <is>
-          <t>Равномерное распределение встреч</t>
-        </is>
-      </c>
-      <c r="G332" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H332" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B333" s="3" t="inlineStr">
-        <is>
-          <t>Ao</t>
-        </is>
-      </c>
-      <c r="C333" s="3" t="inlineStr">
-        <is>
-          <t>ao.44</t>
-        </is>
-      </c>
-      <c r="D333" s="9" t="inlineStr">
-        <is>
-          <t>Discovery call auto-scheduling</t>
-        </is>
-      </c>
-      <c r="E333" s="9" t="inlineStr">
-        <is>
-          <t>Discovery ზარის ავტომატური დაჯავშნა</t>
-        </is>
-      </c>
-      <c r="F333" s="9" t="inlineStr">
-        <is>
-          <t>Автозапись на discovery-звонок</t>
-        </is>
-      </c>
-      <c r="G333" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H333" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H333"/>
+  <autoFilter ref="A1:H331"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H532" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H530" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18978,7 +18822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -25569,27 +25413,27 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>process.note</t>
+          <t>pain.manager.left</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Pricing is set individually, based on your needs.</t>
+          <t>Ana left the chat</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
+          <t>ანამ დატოვა ჩატი</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
+          <t>Анна покинула чат</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr"/>
@@ -25607,27 +25451,27 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>process.cta</t>
+          <t>pain.owner.note</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Today!!</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>დღეს!!</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Сегодня!!</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr"/>
@@ -25650,22 +25494,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>pain.manager.left</t>
+          <t>pain.chats.more</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Ana left the chat</t>
+          <t>+11 unanswered</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>ანამ დატოვა ჩატი</t>
+          <t>+11 უპასუხო</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Анна покинула чат</t>
+          <t>+11 без ответа</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr"/>
@@ -25683,30 +25527,34 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.note</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Today!!</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>დღეს!!</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>Сегодня!!</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr"/>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>AI and process automation for business | Unitty</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>AI და პროცესების ავტომატიზაცია ბიზნესისთვის | Unitty</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>AI и автоматизация процессов для бизнеса | Unitty</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -25726,22 +25574,22 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.more</t>
+          <t>pain.ba.before</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>+11 unanswered</t>
+          <t>Before</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>+11 უპასუხო</t>
+          <t>დანერგვამდე</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>+11 без ответа</t>
+          <t>До внедрения</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr"/>
@@ -25759,34 +25607,30 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Seo</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>seo.title</t>
-        </is>
-      </c>
-      <c r="D176" s="9" t="inlineStr">
-        <is>
-          <t>AI and process automation for business | Unitty</t>
-        </is>
-      </c>
-      <c r="E176" s="9" t="inlineStr">
-        <is>
-          <t>AI და პროცესების ავტომატიზაცია ბიზნესისთვის | Unitty</t>
-        </is>
-      </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>AI и автоматизация процессов для бизнеса | Unitty</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.ba.after</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>შედეგად</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>Результат</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr"/>
       <c r="H176" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -25806,22 +25650,22 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.before</t>
+          <t>pain.ba.hint</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Switch to see the same situation with a CRM</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>დანერგვამდე</t>
+          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>До внедрения</t>
+          <t>Переключите и посмотрите то же самое с CRM</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr"/>
@@ -25844,22 +25688,22 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.after</t>
+          <t>pain.ba.peek</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>See the result with CRM</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>შედეგად</t>
+          <t>ნახე შედეგი CRM-ით</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Результат</t>
+          <t>Посмотреть результат с CRM</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr"/>
@@ -25882,22 +25726,22 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.hint</t>
+          <t>pain.excel.atitle</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Switch to see the same situation with a CRM</t>
+          <t>The client's full history in one search</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>გადართე და ნახე, როგორ გამოიყურება იგივე CRM-ით</t>
+          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Переключите и посмотрите то же самое с CRM</t>
+          <t>Вся история клиента — в одном поиске</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr"/>
@@ -25920,22 +25764,22 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>pain.ba.peek</t>
+          <t>pain.owner.atitle</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>See the result with CRM</t>
+          <t>The team knows who does what</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>ნახე შედეგი CRM-ით</t>
+          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Посмотреть результат с CRM</t>
+          <t>Команда знает, кто что делает</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr"/>
@@ -25958,22 +25802,22 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.atitle</t>
+          <t>pain.chats.atitle</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>The client's full history in one search</t>
+          <t>Every message in one window</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>კლიენტის მთელი ისტორია — ერთ ძებნაში</t>
+          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Вся история клиента — в одном поиске</t>
+          <t>Все сообщения — в одном окне</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr"/>
@@ -25996,22 +25840,22 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.atitle</t>
+          <t>pain.z.contacts</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>The team knows who does what</t>
+          <t>Contacts</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>გუნდმა იცის, ვინ რას აკეთებს</t>
+          <t>კონტაქტები</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Команда знает, кто что делает</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr"/>
@@ -26034,22 +25878,22 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.atitle</t>
+          <t>pain.z.found</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Every message in one window</t>
+          <t>1 result</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>ყველა შეტყობინება — ერთ ფანჯარაში</t>
+          <t>1 შედეგი</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Все сообщения — в одном окне</t>
+          <t>1 результат</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr"/>
@@ -26072,22 +25916,22 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>pain.z.contacts</t>
+          <t>pain.z.stage</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>კონტაქტები</t>
+          <t>შეთავაზება</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Предложение</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr"/>
@@ -26110,22 +25954,22 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>pain.z.found</t>
+          <t>pain.z.last</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>1 result</t>
+          <t>Last purchase</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>1 შედეგი</t>
+          <t>ბოლო შეძენა</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>1 результат</t>
+          <t>Последняя покупка</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr"/>
@@ -26148,22 +25992,22 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>pain.z.stage</t>
+          <t>pain.z.deals</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Deals</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>შეთავაზება</t>
+          <t>გარიგებები</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Предложение</t>
+          <t>Сделки</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr"/>
@@ -26186,22 +26030,22 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>pain.z.last</t>
+          <t>pain.z.merged</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Last purchase</t>
+          <t>Duplicate merged</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>ბოლო შეძენა</t>
+          <t>დუბლიკატი გაერთიანდა</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Последняя покупка</t>
+          <t>Дубликат объединён</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr"/>
@@ -26224,22 +26068,22 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>pain.z.deals</t>
+          <t>pain.z.tasks</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Deals</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>გარიგებები</t>
+          <t>დავალებები</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Сделки</t>
+          <t>Задачи</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr"/>
@@ -26262,22 +26106,22 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>pain.z.merged</t>
+          <t>pain.z.ontrack</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Duplicate merged</t>
+          <t>On track</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>დუბლიკატი გაერთიანდა</t>
+          <t>გეგმაშია</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Дубликат объединён</t>
+          <t>По плану</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -26300,22 +26144,22 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>pain.z.tasks</t>
+          <t>pain.z.t1</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Call the client</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>დავალებები</t>
+          <t>კლიენტთან ზარი</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Задачи</t>
+          <t>Звонок клиенту</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr"/>
@@ -26338,22 +26182,22 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>pain.z.ontrack</t>
+          <t>pain.z.t2</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>On track</t>
+          <t>Invoice on rs.ge</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>გეგმაშია</t>
+          <t>ინვოისი rs.ge-ზე</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>По плану</t>
+          <t>Счёт на rs.ge</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr"/>
@@ -26376,22 +26220,22 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t1</t>
+          <t>pain.z.t3</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Call the client</t>
+          <t>Send the price</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>კლიენტთან ზარი</t>
+          <t>ფასის გაგზავნა</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Звонок клиенту</t>
+          <t>Отправить цену</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr"/>
@@ -26414,22 +26258,22 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t2</t>
+          <t>pain.z.t4</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Invoice on rs.ge</t>
+          <t>Weekly report</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>ინვოისი rs.ge-ზე</t>
+          <t>კვირის რეპორტი</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Счёт на rs.ge</t>
+          <t>Недельный отчёт</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr"/>
@@ -26452,22 +26296,22 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t3</t>
+          <t>pain.z.n1</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Send the price</t>
+          <t>Nika</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>ფასის გაგზავნა</t>
+          <t>ნიკა</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Отправить цену</t>
+          <t>Ника</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr"/>
@@ -26490,22 +26334,22 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>pain.z.t4</t>
+          <t>pain.z.n2</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Weekly report</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>კვირის რეპორტი</t>
+          <t>ანა</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Недельный отчёт</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr"/>
@@ -26528,22 +26372,22 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n1</t>
+          <t>pain.z.n3</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Nika</t>
+          <t>Luka</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>ნიკა</t>
+          <t>ლუკა</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Ника</t>
+          <t>Лука</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr"/>
@@ -26566,22 +26410,22 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n2</t>
+          <t>pain.z.done</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>ანა</t>
+          <t>შესრულდა</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr"/>
@@ -26604,22 +26448,22 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>pain.z.n3</t>
+          <t>pain.z.auto</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Luka</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>ლუკა</t>
+          <t>ავტომატური</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Лука</t>
+          <t>Авто</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr"/>
@@ -26642,22 +26486,22 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>pain.z.done</t>
+          <t>pain.z.everymon</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Every Monday</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>შესრულდა</t>
+          <t>ყოველ ორშაბათს</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>Каждый понедельник</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr"/>
@@ -26680,22 +26524,22 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>pain.z.auto</t>
+          <t>pain.z.reminder</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Reminder sent to Luka</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>ავტომატური</t>
+          <t>ლუკას შეხსენება გაეგზავნა</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Авто</t>
+          <t>Луке отправлено напоминание</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr"/>
@@ -26718,22 +26562,22 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>pain.z.everymon</t>
+          <t>pain.z.inbox</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Every Monday</t>
+          <t>Inbox</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>ყოველ ორშაბათს</t>
+          <t>შეტყობინებები</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Каждый понедельник</t>
+          <t>Сообщения</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr"/>
@@ -26756,22 +26600,22 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>pain.z.reminder</t>
+          <t>pain.z.zero</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Reminder sent to Luka</t>
+          <t>0 unanswered</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>ლუკას შეხსენება გაეგზავნა</t>
+          <t>0 უპასუხო</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Луке отправлено напоминание</t>
+          <t>0 без ответа</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr"/>
@@ -26794,22 +26638,22 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>pain.z.inbox</t>
+          <t>pain.z.min</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Inbox</t>
+          <t>min</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>შეტყობინებები</t>
+          <t>წთ</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Сообщения</t>
+          <t>мин</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr"/>
@@ -26832,22 +26676,22 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>pain.z.zero</t>
+          <t>pain.excel.statn</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>0 unanswered</t>
+          <t>1.8 h</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>0 უპასუხო</t>
+          <t>1.8 სთ</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>0 без ответа</t>
+          <t>1,8 ч</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr"/>
@@ -26870,22 +26714,22 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>pain.z.min</t>
+          <t>pain.excel.stat</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>a day: the average time an employee spends searching for information</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>წთ</t>
+          <t>დღეში ხარჯავს საშუალოდ თანამშრომელი საჭირო ინფორმაციის ძებნაში</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>мин</t>
+          <t>в день в среднем тратит сотрудник на поиск нужной информации</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr"/>
@@ -26908,22 +26752,22 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.statn</t>
+          <t>pain.excel.src</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>1.8 h</t>
+          <t>Source: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>1.8 სთ</t>
+          <t>წყარო: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>1,8 ч</t>
+          <t>Источник: McKinsey Global Institute</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr"/>
@@ -26946,22 +26790,22 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.stat</t>
+          <t>pain.owner.statn</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>a day: the average time an employee spends searching for information</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>დღეში ხარჯავს საშუალოდ თანამშრომელი საჭირო ინფორმაციის ძებნაში</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>в день в среднем тратит сотрудник на поиск нужной информации</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr"/>
@@ -26984,22 +26828,22 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>pain.excel.src</t>
+          <t>pain.owner.stat</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Source: McKinsey Global Institute</t>
+          <t>of business owners spend over 40% of their time on admin</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>წყარო: McKinsey Global Institute</t>
+          <t>მეწარმეების სამუშაო დროის 40%-ზე მეტს ადმინისტრაციულ საქმეებს ახმარს</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Источник: McKinsey Global Institute</t>
+          <t>предпринимателей тратят на администрирование больше 40% времени</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr"/>
@@ -27022,22 +26866,22 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.statn</t>
+          <t>pain.owner.src</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>Source: Visma &amp; Kantar, 2,000 business owners, 2024</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>წყარო: Visma &amp; Kantar, 2 000 მეწარმე, 2024</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>Источник: Visma &amp; Kantar, 2 000 предпринимателей, 2024</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr"/>
@@ -27060,22 +26904,22 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.stat</t>
+          <t>pain.chats.statn</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>of business owners spend over 40% of their time on admin</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>მეწარმეების სამუშაო დროის 40%-ზე მეტს ადმინისტრაციულ საქმეებს ახმარს</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>предпринимателей тратят на администрирование больше 40% времени</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr"/>
@@ -27098,22 +26942,22 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>pain.owner.src</t>
+          <t>pain.chats.stat</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Source: Visma &amp; Kantar, 2,000 business owners, 2024</t>
+          <t>higher chance to qualify a lead when you reply within an hour rather than later</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>წყარო: Visma &amp; Kantar, 2 000 მეწარმე, 2024</t>
+          <t>მეტია ლიდის დაკვალიფიცირების შანსი, თუ 1 საათში უპასუხებ და არა მოგვიანებით</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Источник: Visma &amp; Kantar, 2 000 предпринимателей, 2024</t>
+          <t>выше шанс квалифицировать лид, если ответить в течение часа, а не позже</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr"/>
@@ -27136,22 +26980,22 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.statn</t>
+          <t>pain.chats.src</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>7x</t>
+          <t>Source: Harvard Business Review</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>7x</t>
+          <t>წყარო: Harvard Business Review</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>7x</t>
+          <t>Источник: Harvard Business Review</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr"/>
@@ -27169,27 +27013,27 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.stat</t>
+          <t>process.0.name</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>higher chance to qualify a lead when you reply within an hour rather than later</t>
+          <t>Where you are today</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>მეტია ლიდის დაკვალიფიცირების შანსი, თუ 1 საათში უპასუხებ და არა მოგვიანებით</t>
+          <t>დღევანდელი რეალობა</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>выше шанс квалифицировать лид, если ответить в течение часа, а не позже</t>
+          <t>Где вы сейчас</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr"/>
@@ -27207,27 +27051,27 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>pain.chats.src</t>
+          <t>process.0.desc</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Source: Harvard Business Review</t>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>წყარო: Harvard Business Review</t>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Источник: Harvard Business Review</t>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr"/>
@@ -27250,22 +27094,22 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>process.0.name</t>
+          <t>process.0.time</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Where you are today</t>
+          <t>Starting point</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>დღევანდელი რეალობა</t>
+          <t>საწყისი წერტილი</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Где вы сейчас</t>
+          <t>Отправная точка</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr"/>
@@ -27288,22 +27132,22 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>process.0.desc</t>
+          <t>process.go</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+          <t>Request now</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+          <t>მოითხოვე ახლავე</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+          <t>Запросить сейчас</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr"/>
@@ -27313,86 +27157,10 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C217" s="3" t="inlineStr">
-        <is>
-          <t>process.0.time</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>Starting point</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>საწყისი წერტილი</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
-        <is>
-          <t>Отправная точка</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr"/>
-      <c r="H217" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C218" s="3" t="inlineStr">
-        <is>
-          <t>process.go</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>Request now</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>მოითხოვე ახლავე</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>Запросить сейчас</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr"/>
-      <c r="H218" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H218"/>
+  <autoFilter ref="A1:H216"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H417" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H415" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -27406,7 +27174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -32417,30 +32185,34 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>process.note</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Pricing is set individually, based on your needs.</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr"/>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>Bank transactions in your CRM: TBC and Bank of Georgia | Unitty</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>ბანკის ტრანზაქციები CRM-ში: TBC და საქართველოს ბანკი | Unitty</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>Банковские транзакции в CRM: TBC и Bank of Georgia | Unitty</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -32460,22 +32232,22 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>process.cta</t>
+          <t>process.0.name</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Where you are today</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>დღევანდელი რეალობა</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Где вы сейчас</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr"/>
@@ -32493,34 +32265,30 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Seo</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>seo.title</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>Bank transactions in your CRM: TBC and Bank of Georgia | Unitty</t>
-        </is>
-      </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>ბანკის ტრანზაქციები CRM-ში: TBC და საქართველოს ბანკი | Unitty</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="inlineStr">
-        <is>
-          <t>Банковские транзакции в CRM: TBC и Bank of Georgia | Unitty</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.0.desc</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -32540,22 +32308,22 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>process.0.name</t>
+          <t>process.0.time</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Where you are today</t>
+          <t>Starting point</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>დღევანდელი რეალობა</t>
+          <t>საწყისი წერტილი</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Где вы сейчас</t>
+          <t>Отправная точка</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr"/>
@@ -32578,22 +32346,22 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>process.0.desc</t>
+          <t>process.go</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+          <t>Request now</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+          <t>მოითხოვე ახლავე</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+          <t>Запросить сейчас</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
@@ -32603,86 +32371,10 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>process.0.time</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>Starting point</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>საწყისი წერტილი</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>Отправная точка</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr"/>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>process.go</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>Request now</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>მოითხოვე ახლავე</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>Запросить сейчас</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr"/>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H137"/>
+  <autoFilter ref="A1:H135"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H336" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H334" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -32696,7 +32388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -37683,30 +37375,34 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Seo</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>process.note</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Pricing is set individually, based on your needs.</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>ღირებულება ინდივიდუალურად განისაზღვრება, საჭიროებებიდან გამომდინარე.</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>Стоимость определяется индивидуально, исходя из ваших потребностей.</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr"/>
+          <t>seo.title</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>75+ ready-made CRM, AI and analytics solutions | Unitty</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>75+ მზა გადაწყვეტა CRM-ის, AI-ს და ანალიტიკისთვის | Unitty</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>75+ готовых решений для CRM, AI и аналитики | Unitty</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -37726,22 +37422,22 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>process.cta</t>
+          <t>process.0.name</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Where you are today</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>დღევანდელი რეალობა</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Где вы сейчас</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr"/>
@@ -37759,34 +37455,30 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Seo</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>seo.title</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>75+ ready-made CRM, AI and analytics solutions | Unitty</t>
-        </is>
-      </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>75+ მზა გადაწყვეტა CRM-ის, AI-ს და ანალიტიკისთვის | Unitty</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="inlineStr">
-        <is>
-          <t>75+ готовых решений для CRM, AI и аналитики | Unitty</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>process.0.desc</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -37806,22 +37498,22 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>process.0.name</t>
+          <t>process.0.time</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Where you are today</t>
+          <t>Starting point</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>დღევანდელი რეალობა</t>
+          <t>საწყისი წერტილი</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Где вы сейчас</t>
+          <t>Отправная точка</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr"/>
@@ -37844,22 +37536,22 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>process.0.desc</t>
+          <t>process.go</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Chaos: spreadsheets, scattered chats, forgotten calls and lost clients.</t>
+          <t>Request now</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>ქაოსი: ცხრილები, მიმოფანტული ჩატები, დავიწყებული ზარები და დაკარგული კლიენტები.</t>
+          <t>მოითხოვე ახლავე</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Хаос: таблицы, разрозненные чаты, забытые звонки и потерянные клиенты.</t>
+          <t>Запросить сейчас</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
@@ -37877,30 +37569,34 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Prod</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>process.0.time</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>Starting point</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>საწყისი წერტილი</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>Отправная точка</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr"/>
+          <t>prod.title</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>Our own products</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>ჩვენი პროდუქტები</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>Наши продукты</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -37915,30 +37611,34 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Prod</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>process.go</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>Request now</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>მოითხოვე ახლავე</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>Запросить сейчас</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr"/>
+          <t>prod.sub</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -37958,22 +37658,22 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>prod.title</t>
+          <t>prod.cta</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Our own products</t>
+          <t>Request →</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>ჩვენი პროდუქტები</t>
+          <t>მოითხოვე →</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>Наши продукты</t>
+          <t>Запросить →</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -38000,22 +37700,22 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>prod.sub</t>
+          <t>prod.1.desc</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
+          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
+          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
+          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -38042,22 +37742,22 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>prod.cta</t>
+          <t>prod.2.desc</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Request →</t>
+          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე →</t>
+          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>Запросить →</t>
+          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -38084,22 +37784,22 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>prod.1.desc</t>
+          <t>prod.3.desc</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
+          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
+          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
+          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -38126,22 +37826,22 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>prod.2.desc</t>
+          <t>prod.4.desc</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
+          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
+          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
+          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -38168,22 +37868,22 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>prod.3.desc</t>
+          <t>prod.5.desc</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
+          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
+          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr">
         <is>
-          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
+          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -38210,22 +37910,22 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>prod.4.desc</t>
+          <t>prod.6.desc</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
+          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
+          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
+          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -38252,22 +37952,22 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>prod.5.desc</t>
+          <t>prod.7.desc</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
+          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
+          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
+          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -38294,22 +37994,22 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>prod.6.desc</t>
+          <t>prod.8.desc</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
+          <t>Personalised SMS reminders and notifications straight from your CRM - for payments, meetings and bookings.</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
+          <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან — გადახდებზე, შეხვედრებსა და ჯავშნებზე.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
+          <t>Персональные SMS-напоминания и уведомления прямо из CRM - о платежах, встречах и бронях.</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -38323,94 +38023,10 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>Prod</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>prod.7.desc</t>
-        </is>
-      </c>
-      <c r="D147" s="9" t="inlineStr">
-        <is>
-          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
-        </is>
-      </c>
-      <c r="E147" s="9" t="inlineStr">
-        <is>
-          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
-        </is>
-      </c>
-      <c r="F147" s="9" t="inlineStr">
-        <is>
-          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
-        </is>
-      </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>Solutions</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>Prod</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>prod.8.desc</t>
-        </is>
-      </c>
-      <c r="D148" s="9" t="inlineStr">
-        <is>
-          <t>Personalised SMS reminders and notifications straight from your CRM - for payments, meetings and bookings.</t>
-        </is>
-      </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან — გადახდებზე, შეხვედრებსა და ჯავშნებზე.</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr">
-        <is>
-          <t>Персональные SMS-напоминания и уведомления прямо из CRM - о платежах, встречах и бронях.</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H148"/>
+  <autoFilter ref="A1:H146"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H347" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H345" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$331</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$251</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
@@ -5660,7 +5660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H331"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -9921,22 +9921,26 @@
           <t>pain.sub</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>We see these situations every day. One call shows you how to fix yours.</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>ასეთ სიტუაციებს ყოველდღე ვხედავთ. ერთი ზარი გაჩვენებს, როგორ მოაგვარო შენი.</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>Мы видим такие ситуации каждый день. Один звонок покажет, как решить вашу.</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr"/>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>A business needs a system people actually work in. Then you can analyse your data and automate your processes.</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>ბიზნესს სჭირდება სისტემა, რომელშიც ადამიანები იმუშავებენ. შედეგად, შეძლებ მონაცემების ანალიზს და პროცესების ავტომატიზაციას.</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Бизнесу нужна система, в которой работают люди. Тогда вы сможете анализировать данные и автоматизировать процессы.</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -13983,34 +13987,30 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
-        </is>
-      </c>
-      <c r="D217" s="9" t="inlineStr">
-        <is>
-          <t>Choose where to start</t>
-        </is>
-      </c>
-      <c r="E217" s="9" t="inlineStr">
-        <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
-        </is>
-      </c>
-      <c r="F217" s="9" t="inlineStr">
-        <is>
-          <t>Выберите, с чего начать</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cx.title</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Excel slows processes, creates risks and holds back growth</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Excel ანელებს პროცესებს, ქმნის რისკებს და აფერხებს ზრდას</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>Excel замедляет процессы, создаёт риски и тормозит рост</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr"/>
       <c r="H217" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14025,34 +14025,30 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
-        </is>
-      </c>
-      <c r="D218" s="9" t="inlineStr">
-        <is>
-          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
-        </is>
-      </c>
-      <c r="E218" s="9" t="inlineStr">
-        <is>
-          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
-        </is>
-      </c>
-      <c r="F218" s="9" t="inlineStr">
-        <is>
-          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cx.body</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Clients spread across files, notebooks and phones.</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>კლიენტები ფაილებში, რვეულებსა და ტელეფონში.</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>Клиенты разбросаны по файлам, блокнотам и телефонам.</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr"/>
       <c r="H218" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14067,34 +14063,30 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
-        </is>
-      </c>
-      <c r="D219" s="9" t="inlineStr">
-        <is>
-          <t>Most popular</t>
-        </is>
-      </c>
-      <c r="E219" s="9" t="inlineStr">
-        <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
-        </is>
-      </c>
-      <c r="F219" s="9" t="inlineStr">
-        <is>
-          <t>Выбирают чаще всего</t>
-        </is>
-      </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cx.statn</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr"/>
       <c r="H219" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14109,34 +14101,30 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>pk.deal</t>
-        </is>
-      </c>
-      <c r="D220" s="9" t="inlineStr">
-        <is>
-          <t>Discount valid for 1 week from the day the offer is sent.</t>
-        </is>
-      </c>
-      <c r="E220" s="9" t="inlineStr">
-        <is>
-          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
-        </is>
-      </c>
-      <c r="F220" s="9" t="inlineStr">
-        <is>
-          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
-        </is>
-      </c>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cx.stat</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>of spreadsheets contain errors</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>ცხრილებში შეცდომებია</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>таблиц содержат ошибки</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr"/>
       <c r="H220" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14151,34 +14139,30 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
-        </is>
-      </c>
-      <c r="D221" s="9" t="inlineStr">
-        <is>
-          <t>one-time</t>
-        </is>
-      </c>
-      <c r="E221" s="9" t="inlineStr">
-        <is>
-          <t>ერთჯერადად</t>
-        </is>
-      </c>
-      <c r="F221" s="9" t="inlineStr">
-        <is>
-          <t>разово</t>
-        </is>
-      </c>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cx.src</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Source: Raymond Panko, University of Hawaii (2008)</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>წყარო: Raymond Panko, ჰავაის უნივერსიტეტი (2008)</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>Источник: Raymond Panko, Гавайский университет (2008)</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr"/>
       <c r="H221" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14193,34 +14177,30 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
-        </is>
-      </c>
-      <c r="D222" s="9" t="inlineStr">
-        <is>
-          <t>working days</t>
-        </is>
-      </c>
-      <c r="E222" s="9" t="inlineStr">
-        <is>
-          <t>სამუშაო დღე</t>
-        </is>
-      </c>
-      <c r="F222" s="9" t="inlineStr">
-        <is>
-          <t>рабочих дней</t>
-        </is>
-      </c>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cx.fix</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>In Zoho CRM every client and deal lives in one system: you see who is at which stage and what is coming in.</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>Zoho CRM-ში ყველა კლიენტი და გარიგება ერთ სისტემაშია: ჩანს, ვინ რა ეტაპზეა და რამდენი შემოდის.</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>В Zoho CRM все клиенты и сделки в одной системе: видно, кто на каком этапе и сколько поступает.</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr"/>
       <c r="H222" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14235,34 +14215,30 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>pk.full</t>
-        </is>
-      </c>
-      <c r="D223" s="9" t="inlineStr">
-        <is>
-          <t>Everything included</t>
-        </is>
-      </c>
-      <c r="E223" s="9" t="inlineStr">
-        <is>
-          <t>სრული ჩამონათვალი</t>
-        </is>
-      </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>Всё, что входит</t>
-        </is>
-      </c>
-      <c r="G223" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cx.atitle</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Every deal in one system</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>ყველა გარიგება — ერთ სისტემაში</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Все сделки — в одной системе</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr"/>
       <c r="H223" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14277,34 +14253,30 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
-        </is>
-      </c>
-      <c r="D224" s="9" t="inlineStr">
-        <is>
-          <t>Choose this package</t>
-        </is>
-      </c>
-      <c r="E224" s="9" t="inlineStr">
-        <is>
-          <t>ამ პაკეტის არჩევა</t>
-        </is>
-      </c>
-      <c r="F224" s="9" t="inlineStr">
-        <is>
-          <t>Выбрать этот пакет</t>
-        </is>
-      </c>
-      <c r="G224" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cc.title</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Unsystematic work creates chaos and unmanageable processes</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>არასისტემური მუშაობა ქმნის ქაოსს და უმართავ პროცესებს</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>Работа без системы создаёт хаос и неуправляемые процессы</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr"/>
       <c r="H224" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14319,34 +14291,30 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
-        </is>
-      </c>
-      <c r="D225" s="9" t="inlineStr">
-        <is>
-          <t>Selected</t>
-        </is>
-      </c>
-      <c r="E225" s="9" t="inlineStr">
-        <is>
-          <t>არჩეულია</t>
-        </is>
-      </c>
-      <c r="F225" s="9" t="inlineStr">
-        <is>
-          <t>Выбран</t>
-        </is>
-      </c>
-      <c r="G225" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cc.body</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Every question lands on you, every task is on your mind.</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>ყველა კითხვა შენთან მოდის, ყველა დავალება შენ გახსოვს.</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>Все вопросы идут к вам, все задачи держите в голове.</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr"/>
       <c r="H225" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14361,34 +14329,30 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
-        </is>
-      </c>
-      <c r="D226" s="9" t="inlineStr">
-        <is>
-          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
-        </is>
-      </c>
-      <c r="E226" s="9" t="inlineStr">
-        <is>
-          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
-        </is>
-      </c>
-      <c r="F226" s="9" t="inlineStr">
-        <is>
-          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cc.statn</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr"/>
       <c r="H226" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14403,34 +14367,30 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>pk.cur</t>
-        </is>
-      </c>
-      <c r="D227" s="9" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E227" s="9" t="inlineStr">
-        <is>
-          <t>ვალუტა</t>
-        </is>
-      </c>
-      <c r="F227" s="9" t="inlineStr">
-        <is>
-          <t>Валюта</t>
-        </is>
-      </c>
-      <c r="G227" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cc.stat</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>of the workday goes on “work about work”: chasing status, clarifying, duplicating</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>სამუშაო დროისა იხარჯება „სამუშაოზე სამუშაოზე“: სტატუსების ძებნა, დაზუსტება, დუბლირება</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>рабочего дня уходит на «работу о работе»: поиск статусов, уточнения, дублирование</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr"/>
       <c r="H227" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14445,34 +14405,30 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
-        </is>
-      </c>
-      <c r="D228" s="9" t="inlineStr">
-        <is>
-          <t>Extra features</t>
-        </is>
-      </c>
-      <c r="E228" s="9" t="inlineStr">
-        <is>
-          <t>დამატებითი ფუნქციები</t>
-        </is>
-      </c>
-      <c r="F228" s="9" t="inlineStr">
-        <is>
-          <t>Дополнительные функции</t>
-        </is>
-      </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cc.src</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Source: Asana Anatomy of Work, 9,615 workers, 2023</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>წყარო: Asana Anatomy of Work, 9 615 თანამშრომელი, 2023</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>Источник: Asana Anatomy of Work, 9 615 сотрудников, 2023</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr"/>
       <c r="H228" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14487,34 +14443,30 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
-        </is>
-      </c>
-      <c r="D229" s="9" t="inlineStr">
-        <is>
-          <t>Optional. Add only if you need them</t>
-        </is>
-      </c>
-      <c r="E229" s="9" t="inlineStr">
-        <is>
-          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
-        </is>
-      </c>
-      <c r="F229" s="9" t="inlineStr">
-        <is>
-          <t>Необязательно. Добавьте, если нужно</t>
-        </is>
-      </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cc.fix</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint walks the team step by step: who does what and when. No stage gets skipped.</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint გუნდს ნაბიჯ-ნაბიჯ მიჰყავს: ვინ, რა და როდის აკეთებს. ვერცერთი ეტაპი ვერ გამოგრჩება.</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint ведёт команду шаг за шагом: кто, что и когда делает. Ни один этап не пропускается.</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr"/>
       <c r="H229" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14529,34 +14481,30 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>ao.popular</t>
-        </is>
-      </c>
-      <c r="D230" s="9" t="inlineStr">
-        <is>
-          <t>Often added</t>
-        </is>
-      </c>
-      <c r="E230" s="9" t="inlineStr">
-        <is>
-          <t>ხშირად ამატებენ</t>
-        </is>
-      </c>
-      <c r="F230" s="9" t="inlineStr">
-        <is>
-          <t>Часто добавляют</t>
-        </is>
-      </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cc.atitle</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Every step follows the rules, in order</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ყველა ნაბიჯი — წესით და თანმიმდევრობით</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>Каждый шаг — по правилам и по порядку</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr"/>
       <c r="H230" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14571,34 +14519,30 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>ao.more</t>
-        </is>
-      </c>
-      <c r="D231" s="9" t="inlineStr">
-        <is>
-          <t>All add-ons by category</t>
-        </is>
-      </c>
-      <c r="E231" s="9" t="inlineStr">
-        <is>
-          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
-        </is>
-      </c>
-      <c r="F231" s="9" t="inlineStr">
-        <is>
-          <t>Все дополнения по категориям</t>
-        </is>
-      </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cd.title</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Scattered data leads to wrong decisions</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>გაფანტული მონაცემებით არასწორ გადაწყვეტილებებს იღებ</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>Разрозненные данные ведут к неверным решениям</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr"/>
       <c r="H231" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14613,34 +14557,30 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
-        </is>
-      </c>
-      <c r="D232" s="9" t="inlineStr">
-        <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
-        </is>
-      </c>
-      <c r="E232" s="9" t="inlineStr">
-        <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
-        </is>
-      </c>
-      <c r="F232" s="9" t="inlineStr">
-        <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cd.body</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Three different numbers for the same question.</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>ერთსა და იმავე კითხვაზე სამი განსხვავებული ციფრი.</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>Три разные цифры на один и тот же вопрос.</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr"/>
       <c r="H232" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14655,34 +14595,30 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
-        </is>
-      </c>
-      <c r="D233" s="9" t="inlineStr">
-        <is>
-          <t>Choose a package</t>
-        </is>
-      </c>
-      <c r="E233" s="9" t="inlineStr">
-        <is>
-          <t>აირჩიე პაკეტი</t>
-        </is>
-      </c>
-      <c r="F233" s="9" t="inlineStr">
-        <is>
-          <t>Выберите пакет</t>
-        </is>
-      </c>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cd.statn</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>$12.9M</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>$12.9 მლნ</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>$12,9 млн</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr"/>
       <c r="H233" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14697,34 +14633,30 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
-        </is>
-      </c>
-      <c r="D234" s="9" t="inlineStr">
-        <is>
-          <t>features</t>
-        </is>
-      </c>
-      <c r="E234" s="9" t="inlineStr">
-        <is>
-          <t>ფუნქცია</t>
-        </is>
-      </c>
-      <c r="F234" s="9" t="inlineStr">
-        <is>
-          <t>функц.</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cd.stat</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>a year: the average cost of poor data quality to an organisation</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>ყოველწლიურად კარგავს საშუალოდ ორგანიზაცია ცუდი ხარისხის მონაცემების გამო</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>в год в среднем теряет организация из-за некачественных данных</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr"/>
       <c r="H234" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14739,34 +14671,30 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
-        </is>
-      </c>
-      <c r="D235" s="9" t="inlineStr">
-        <is>
-          <t>+ VAT</t>
-        </is>
-      </c>
-      <c r="E235" s="9" t="inlineStr">
-        <is>
-          <t>+ დღგ</t>
-        </is>
-      </c>
-      <c r="F235" s="9" t="inlineStr">
-        <is>
-          <t>+ НДС</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cd.src</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Source: Gartner</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>წყარო: Gartner</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>Источник: Gartner</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr"/>
       <c r="H235" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14781,34 +14709,30 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
-        </is>
-      </c>
-      <c r="D236" s="9" t="inlineStr">
-        <is>
-          <t>Request a call</t>
-        </is>
-      </c>
-      <c r="E236" s="9" t="inlineStr">
-        <is>
-          <t>მოითხოვე ზარი</t>
-        </is>
-      </c>
-      <c r="F236" s="9" t="inlineStr">
-        <is>
-          <t>Запросить звонок</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cd.fix</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>All data on one dashboard in real time: you decide based on facts.</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>ყველა მონაცემი ერთ დეშბორდზე, რეალურ დროში: გადაწყვეტილებას ფაქტებზე დაყრდნობით იღებ.</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>Все данные на одном дашборде в реальном времени: решения на основе фактов.</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr"/>
       <c r="H236" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14823,34 +14747,30 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
-        </is>
-      </c>
-      <c r="D237" s="9" t="inlineStr">
-        <is>
-          <t>Your selection:</t>
-        </is>
-      </c>
-      <c r="E237" s="9" t="inlineStr">
-        <is>
-          <t>შენი არჩევანი:</t>
-        </is>
-      </c>
-      <c r="F237" s="9" t="inlineStr">
-        <is>
-          <t>Ваш выбор:</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.cd.atitle</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>Exact numbers on one dashboard</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>ზუსტი ციფრები — ერთ დეშბორდზე</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>Точные цифры — на одном дашборде</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr"/>
       <c r="H237" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14865,34 +14785,30 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
-        </is>
-      </c>
-      <c r="D238" s="9" t="inlineStr">
-        <is>
-          <t>Starter</t>
-        </is>
-      </c>
-      <c r="E238" s="9" t="inlineStr">
-        <is>
-          <t>სტარტი</t>
-        </is>
-      </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>Старт</t>
-        </is>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.data.s1</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Excel · October sales</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>Excel · ოქტომბრის გაყიდვები</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>Excel · продажи за октябрь</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr"/>
       <c r="H238" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14907,34 +14823,30 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.short</t>
-        </is>
-      </c>
-      <c r="D239" s="9" t="inlineStr">
-        <is>
-          <t>To move from Excel into a CRM</t>
-        </is>
-      </c>
-      <c r="E239" s="9" t="inlineStr">
-        <is>
-          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
-        </is>
-      </c>
-      <c r="F239" s="9" t="inlineStr">
-        <is>
-          <t>Чтобы перейти с Excel на CRM</t>
-        </is>
-      </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.data.s2</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Manager · “roughly”</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>მენეჯერი · „დაახლოებით“</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>Менеджер · «примерно»</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr"/>
       <c r="H239" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14949,34 +14861,30 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h1</t>
-        </is>
-      </c>
-      <c r="D240" s="9" t="inlineStr">
-        <is>
-          <t>4 core modules</t>
-        </is>
-      </c>
-      <c r="E240" s="9" t="inlineStr">
-        <is>
-          <t>4 ძირითადი მოდული</t>
-        </is>
-      </c>
-      <c r="F240" s="9" t="inlineStr">
-        <is>
-          <t>4 базовых модуля</t>
-        </is>
-      </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.data.s3</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>ბუღალტერია</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Бухгалтерия</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr"/>
       <c r="H240" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -14991,34 +14899,30 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h2</t>
-        </is>
-      </c>
-      <c r="D241" s="9" t="inlineStr">
-        <is>
-          <t>Email and Facebook inside the CRM</t>
-        </is>
-      </c>
-      <c r="E241" s="9" t="inlineStr">
-        <is>
-          <t>ელფოსტა და Facebook CRM-ში</t>
-        </is>
-      </c>
-      <c r="F241" s="9" t="inlineStr">
-        <is>
-          <t>Почта и Facebook внутри CRM</t>
-        </is>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.k1</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>ახალი</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>Новые</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr"/>
       <c r="H241" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15033,34 +14937,30 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h3</t>
-        </is>
-      </c>
-      <c r="D242" s="9" t="inlineStr">
-        <is>
-          <t>Lead form and KPI dashboard</t>
-        </is>
-      </c>
-      <c r="E242" s="9" t="inlineStr">
-        <is>
-          <t>ლიდების ფორმა და KPI დაფა</t>
-        </is>
-      </c>
-      <c r="F242" s="9" t="inlineStr">
-        <is>
-          <t>Форма лидов и дашборд KPI</t>
-        </is>
-      </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.k2</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>შეთავაზება</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>Предложение</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr"/>
       <c r="H242" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15075,34 +14975,30 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
-        </is>
-      </c>
-      <c r="D243" s="9" t="inlineStr">
-        <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
-        </is>
-      </c>
-      <c r="E243" s="9" t="inlineStr">
-        <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
-        </is>
-      </c>
-      <c r="F243" s="9" t="inlineStr">
-        <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.k3</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>მოგებული</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Выиграно</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr"/>
       <c r="H243" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15117,34 +15013,30 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
-        </is>
-      </c>
-      <c r="D244" s="9" t="inlineStr">
-        <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
-        </is>
-      </c>
-      <c r="E244" s="9" t="inlineStr">
-        <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
-        </is>
-      </c>
-      <c r="F244" s="9" t="inlineStr">
-        <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.bp</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint · sales process</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint · გაყიდვის პროცესი</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint · процесс продаж</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr"/>
       <c r="H244" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15159,34 +15051,30 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
-        </is>
-      </c>
-      <c r="D245" s="9" t="inlineStr">
-        <is>
-          <t>Facebook messages right inside the CRM</t>
-        </is>
-      </c>
-      <c r="E245" s="9" t="inlineStr">
-        <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
-        </is>
-      </c>
-      <c r="F245" s="9" t="inlineStr">
-        <is>
-          <t>Сообщения Facebook прямо в CRM</t>
-        </is>
-      </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.b1</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>New lead</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>ახალი ლიდი</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>Новый лид</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr"/>
       <c r="H245" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15201,34 +15089,30 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
-        </is>
-      </c>
-      <c r="D246" s="9" t="inlineStr">
-        <is>
-          <t>1 web form to capture leads</t>
-        </is>
-      </c>
-      <c r="E246" s="9" t="inlineStr">
-        <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
-        </is>
-      </c>
-      <c r="F246" s="9" t="inlineStr">
-        <is>
-          <t>1 веб-форма для приёма лидов</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.b2</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>კვალიფიკაცია</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>Квалификация</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr"/>
       <c r="H246" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15243,34 +15127,30 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
-        </is>
-      </c>
-      <c r="D247" s="9" t="inlineStr">
-        <is>
-          <t>1 sales-pipeline KPI dashboard</t>
-        </is>
-      </c>
-      <c r="E247" s="9" t="inlineStr">
-        <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
-        </is>
-      </c>
-      <c r="F247" s="9" t="inlineStr">
-        <is>
-          <t>Дашборд KPI воронки продаж</t>
-        </is>
-      </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.b3</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Offer sent</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>შეთავაზება გაიგზავნა</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>Предложение отправлено</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr"/>
       <c r="H247" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15285,34 +15165,30 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
-        </is>
-      </c>
-      <c r="D248" s="9" t="inlineStr">
-        <is>
-          <t>Recorded video instructions for the team</t>
-        </is>
-      </c>
-      <c r="E248" s="9" t="inlineStr">
-        <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
-        </is>
-      </c>
-      <c r="F248" s="9" t="inlineStr">
-        <is>
-          <t>Видеоинструкции для команды</t>
-        </is>
-      </c>
-      <c r="G248" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.b4</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>ხელშეკრულება</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>Договор</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr"/>
       <c r="H248" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15327,34 +15203,30 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
-        </is>
-      </c>
-      <c r="D249" s="9" t="inlineStr">
-        <is>
-          <t>Essentials</t>
-        </is>
-      </c>
-      <c r="E249" s="9" t="inlineStr">
-        <is>
-          <t>ოპტიმალური</t>
-        </is>
-      </c>
-      <c r="F249" s="9" t="inlineStr">
-        <is>
-          <t>Оптимальный</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.an</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Analytics · October</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>ანალიტიკა · ოქტომბერი</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>Аналитика · октябрь</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr"/>
       <c r="H249" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15369,34 +15241,30 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.short</t>
-        </is>
-      </c>
-      <c r="D250" s="9" t="inlineStr">
-        <is>
-          <t>For a 5-10 person sales team</t>
-        </is>
-      </c>
-      <c r="E250" s="9" t="inlineStr">
-        <is>
-          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
-        </is>
-      </c>
-      <c r="F250" s="9" t="inlineStr">
-        <is>
-          <t>Для отдела продаж из 5-10 человек</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.kp1</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>შემოსავალი</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>Выручка</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr"/>
       <c r="H250" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15411,34 +15279,30 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
-        </is>
-      </c>
-      <c r="D251" s="9" t="inlineStr">
-        <is>
-          <t>Everything in Starter, plus:</t>
-        </is>
-      </c>
-      <c r="E251" s="9" t="inlineStr">
-        <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
-        </is>
-      </c>
-      <c r="F251" s="9" t="inlineStr">
-        <is>
-          <t>Всё из «Старта», плюс:</t>
-        </is>
-      </c>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.kp2</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>კონვერსია</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>Конверсия</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr"/>
       <c r="H251" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15458,22 +15322,22 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h1</t>
+          <t>pk.title</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter</t>
+          <t>Choose where to start</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
+          <t>აირჩიე, საიდან დაიწყო</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта»</t>
+          <t>Выберите, с чего начать</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -15500,22 +15364,22 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h2</t>
+          <t>pk.sub</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads, automatically</t>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
+          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически</t>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -15542,22 +15406,22 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h3</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Stage rules and lead assignment</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Правила этапов и распределение лидов</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -15584,22 +15448,22 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>pk.deal</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>Discount valid for 1 week from the day the offer is sent.</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -15626,22 +15490,22 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>ერთჯერადად</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>разово</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -15668,22 +15532,22 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -15710,22 +15574,22 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -15752,22 +15616,22 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -15794,22 +15658,22 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -15836,22 +15700,22 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -15878,22 +15742,22 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -15915,27 +15779,27 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -15957,27 +15821,27 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -15999,27 +15863,27 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.short</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>For a growing 15-25 person team</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Для растущей команды из 15-25 человек</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -16041,27 +15905,27 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
+          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -16083,27 +15947,27 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h1</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального»</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -16125,27 +15989,27 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h2</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Telephony and call processing</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია და ზარების დამუშავება</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>Телефония и обработка звонков</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -16167,27 +16031,27 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h3</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Automations and AI (Claude)</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და AI (Claude)</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>Автоматизации и AI (Claude)</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -16209,27 +16073,27 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -16251,27 +16115,27 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -16293,27 +16157,27 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -16340,22 +16204,22 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -16382,22 +16246,22 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -16424,22 +16288,22 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -16466,22 +16330,22 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -16508,22 +16372,22 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -16550,22 +16414,22 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -16587,27 +16451,27 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -16629,27 +16493,27 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -16671,27 +16535,27 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -16713,27 +16577,27 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -16755,27 +16619,27 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>ao.18</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG bank wire deposit matching</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Автосверка переводов TBC/BOG</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -16797,27 +16661,27 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>ao.30</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -16839,27 +16703,27 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>ao.38</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -16881,27 +16745,27 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -16923,27 +16787,27 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -16965,27 +16829,27 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -17007,27 +16871,27 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -17049,27 +16913,27 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -17091,27 +16955,27 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -17133,27 +16997,27 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -17175,27 +17039,27 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -17217,27 +17081,27 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოების აღრიცხვა</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -17259,27 +17123,27 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -17301,27 +17165,27 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>ao.12</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Email + calendar 2-way sync</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -17343,27 +17207,27 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>ao.13</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Возврат пропущенных звонков и SMS</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -17385,27 +17249,27 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>ao.14</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>Messaging bot lead capture webhook</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
+          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -17427,27 +17291,27 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -17469,27 +17333,27 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>ao.15</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Website lead form + webhook</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + webhook</t>
+          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + webhook</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -17511,27 +17375,27 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>ao.16</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>ROI источников и атрибуция кампаний</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -17553,27 +17417,27 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>ao.17</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -17595,27 +17459,27 @@
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -17637,27 +17501,27 @@
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>ao.19</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -17679,27 +17543,27 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>ao.20</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>NBG daily exchange rate sync</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Ежедневный курс НБГ</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -17721,27 +17585,27 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>ao.21</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Ambiguous payment reference fallback queue</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>Очередь неопознанных платежей</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -17763,27 +17627,27 @@
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>ao.22</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Dynamic installment payment schedule</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>График рассрочки</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -17805,27 +17669,27 @@
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>ao.23</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>SMS о просроченной задолженности</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -17847,27 +17711,27 @@
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>ao.24</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>SMS gateway &amp; OTP verification</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>SMS-шлюз и OTP-верификация</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -17889,27 +17753,27 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -17931,27 +17795,27 @@
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>ao.25</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -17973,27 +17837,27 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>ao.26</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Multi-tier SLA escalation matrix</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>Матрица эскалации SLA</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -18015,27 +17879,27 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>ao.27</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Оценка NPS/CSAT после тикета</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -18062,22 +17926,22 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ao.28</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Dynamic KYC intake smart form</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Умная KYC-форма</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -18104,22 +17968,22 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>ao.29</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Warranty expiration alerts</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Напоминания об окончании гарантии</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -18146,22 +18010,22 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -18188,22 +18052,22 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>ao.31</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Georgian voice meeting transcription</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Транскрипция встреч на грузинском</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -18230,22 +18094,22 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ao.32</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>Audio call sentiment extractor</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>Анализ тональности звонков</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -18272,22 +18136,22 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ind</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Industry solutions</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>დარგობრივი</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Отраслевые</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -18314,22 +18178,22 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ao.33</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -18356,22 +18220,22 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>ao.34</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Client preference proactive matcher</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Автоподбор по пожеланиям клиента</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -18398,22 +18262,22 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>ao.35</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>Reservation expiration timer</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Таймер истечения брони</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -18440,22 +18304,22 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>ao.36</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>PDF планировки и предложения</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -18482,22 +18346,22 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>ao.37</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Field service visit tracking + approval</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>Учёт выездов и подтверждение</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -18524,22 +18388,22 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -18566,22 +18430,22 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>ao.39</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>Cold storage WMS &amp; automated billing</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>WMS холодного склада и биллинг</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -18608,22 +18472,22 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>ao.40</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>Construction operations &amp; budget tracker</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>Стройка: операции и бюджет</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -18650,22 +18514,22 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>ao.41</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Predictive debtor call queue</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>Умная очередь звонков должникам</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -18692,22 +18556,22 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>ao.42</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Agent attendance tracker</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+          <t>ბროკერების საკომისიოების აღრიცხვა</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>Учёт посещаемости агентов</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -18734,22 +18598,22 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>ao.43</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>Round-robin appointment balancing</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>Равномерное распределение встреч</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -18776,39 +18640,1509 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
+          <t>ao.12</t>
+        </is>
+      </c>
+      <c r="D331" s="9" t="inlineStr">
+        <is>
+          <t>Email + calendar 2-way sync</t>
+        </is>
+      </c>
+      <c r="E331" s="9" t="inlineStr">
+        <is>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+        </is>
+      </c>
+      <c r="F331" s="9" t="inlineStr">
+        <is>
+          <t>Двусторонняя синхронизация почты и календаря</t>
+        </is>
+      </c>
+      <c r="G331" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>ao.13</t>
+        </is>
+      </c>
+      <c r="D332" s="9" t="inlineStr">
+        <is>
+          <t>Missed-call recovery &amp; SMS callback</t>
+        </is>
+      </c>
+      <c r="E332" s="9" t="inlineStr">
+        <is>
+          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
+        </is>
+      </c>
+      <c r="F332" s="9" t="inlineStr">
+        <is>
+          <t>Возврат пропущенных звонков и SMS</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H332" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>ao.14</t>
+        </is>
+      </c>
+      <c r="D333" s="9" t="inlineStr">
+        <is>
+          <t>Messaging bot lead capture webhook</t>
+        </is>
+      </c>
+      <c r="E333" s="9" t="inlineStr">
+        <is>
+          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
+        </is>
+      </c>
+      <c r="F333" s="9" t="inlineStr">
+        <is>
+          <t>Лиды из чат-бота сразу в CRM</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H333" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.mkt</t>
+        </is>
+      </c>
+      <c r="D334" s="9" t="inlineStr">
+        <is>
+          <t>Marketing &amp; growth</t>
+        </is>
+      </c>
+      <c r="E334" s="9" t="inlineStr">
+        <is>
+          <t>მარკეტინგი</t>
+        </is>
+      </c>
+      <c r="F334" s="9" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>ao.15</t>
+        </is>
+      </c>
+      <c r="D335" s="9" t="inlineStr">
+        <is>
+          <t>Website lead form + webhook</t>
+        </is>
+      </c>
+      <c r="E335" s="9" t="inlineStr">
+        <is>
+          <t>საიტის ფორმა + webhook</t>
+        </is>
+      </c>
+      <c r="F335" s="9" t="inlineStr">
+        <is>
+          <t>Форма сайта + webhook</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>ao.16</t>
+        </is>
+      </c>
+      <c r="D336" s="9" t="inlineStr">
+        <is>
+          <t>Lead source ROI &amp; campaign attribution</t>
+        </is>
+      </c>
+      <c r="E336" s="9" t="inlineStr">
+        <is>
+          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
+        </is>
+      </c>
+      <c r="F336" s="9" t="inlineStr">
+        <is>
+          <t>ROI источников и атрибуция кампаний</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>ao.17</t>
+        </is>
+      </c>
+      <c r="D337" s="9" t="inlineStr">
+        <is>
+          <t>Email campaigns: account setup &amp; contact sync</t>
+        </is>
+      </c>
+      <c r="E337" s="9" t="inlineStr">
+        <is>
+          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+        </is>
+      </c>
+      <c r="F337" s="9" t="inlineStr">
+        <is>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.fin</t>
+        </is>
+      </c>
+      <c r="D338" s="9" t="inlineStr">
+        <is>
+          <t>Fintech &amp; accounting</t>
+        </is>
+      </c>
+      <c r="E338" s="9" t="inlineStr">
+        <is>
+          <t>ფინანსები და ბანკები</t>
+        </is>
+      </c>
+      <c r="F338" s="9" t="inlineStr">
+        <is>
+          <t>Финансы и банки</t>
+        </is>
+      </c>
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>ao.19</t>
+        </is>
+      </c>
+      <c r="D339" s="9" t="inlineStr">
+        <is>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="E339" s="9" t="inlineStr">
+        <is>
+          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="F339" s="9" t="inlineStr">
+        <is>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H339" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>ao.20</t>
+        </is>
+      </c>
+      <c r="D340" s="9" t="inlineStr">
+        <is>
+          <t>NBG daily exchange rate sync</t>
+        </is>
+      </c>
+      <c r="E340" s="9" t="inlineStr">
+        <is>
+          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+        </is>
+      </c>
+      <c r="F340" s="9" t="inlineStr">
+        <is>
+          <t>Ежедневный курс НБГ</t>
+        </is>
+      </c>
+      <c r="G340" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H340" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>ao.21</t>
+        </is>
+      </c>
+      <c r="D341" s="9" t="inlineStr">
+        <is>
+          <t>Ambiguous payment reference fallback queue</t>
+        </is>
+      </c>
+      <c r="E341" s="9" t="inlineStr">
+        <is>
+          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+        </is>
+      </c>
+      <c r="F341" s="9" t="inlineStr">
+        <is>
+          <t>Очередь неопознанных платежей</t>
+        </is>
+      </c>
+      <c r="G341" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>ao.22</t>
+        </is>
+      </c>
+      <c r="D342" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic installment payment schedule</t>
+        </is>
+      </c>
+      <c r="E342" s="9" t="inlineStr">
+        <is>
+          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+        </is>
+      </c>
+      <c r="F342" s="9" t="inlineStr">
+        <is>
+          <t>График рассрочки</t>
+        </is>
+      </c>
+      <c r="G342" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>ao.23</t>
+        </is>
+      </c>
+      <c r="D343" s="9" t="inlineStr">
+        <is>
+          <t>Overdue debt alert &amp; SMS warning</t>
+        </is>
+      </c>
+      <c r="E343" s="9" t="inlineStr">
+        <is>
+          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+        </is>
+      </c>
+      <c r="F343" s="9" t="inlineStr">
+        <is>
+          <t>SMS о просроченной задолженности</t>
+        </is>
+      </c>
+      <c r="G343" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H343" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>ao.24</t>
+        </is>
+      </c>
+      <c r="D344" s="9" t="inlineStr">
+        <is>
+          <t>SMS gateway &amp; OTP verification</t>
+        </is>
+      </c>
+      <c r="E344" s="9" t="inlineStr">
+        <is>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+        </is>
+      </c>
+      <c r="F344" s="9" t="inlineStr">
+        <is>
+          <t>SMS-шлюз и OTP-верификация</t>
+        </is>
+      </c>
+      <c r="G344" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H344" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.cx</t>
+        </is>
+      </c>
+      <c r="D345" s="9" t="inlineStr">
+        <is>
+          <t>Customer experience</t>
+        </is>
+      </c>
+      <c r="E345" s="9" t="inlineStr">
+        <is>
+          <t>მომხმარებლის მომსახურება</t>
+        </is>
+      </c>
+      <c r="F345" s="9" t="inlineStr">
+        <is>
+          <t>Клиентский сервис</t>
+        </is>
+      </c>
+      <c r="G345" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H345" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>ao.25</t>
+        </is>
+      </c>
+      <c r="D346" s="9" t="inlineStr">
+        <is>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="E346" s="9" t="inlineStr">
+        <is>
+          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="F346" s="9" t="inlineStr">
+        <is>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
+        </is>
+      </c>
+      <c r="G346" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H346" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>ao.26</t>
+        </is>
+      </c>
+      <c r="D347" s="9" t="inlineStr">
+        <is>
+          <t>Multi-tier SLA escalation matrix</t>
+        </is>
+      </c>
+      <c r="E347" s="9" t="inlineStr">
+        <is>
+          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+        </is>
+      </c>
+      <c r="F347" s="9" t="inlineStr">
+        <is>
+          <t>Матрица эскалации SLA</t>
+        </is>
+      </c>
+      <c r="G347" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H347" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>ao.27</t>
+        </is>
+      </c>
+      <c r="D348" s="9" t="inlineStr">
+        <is>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
+        </is>
+      </c>
+      <c r="E348" s="9" t="inlineStr">
+        <is>
+          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+        </is>
+      </c>
+      <c r="F348" s="9" t="inlineStr">
+        <is>
+          <t>Оценка NPS/CSAT после тикета</t>
+        </is>
+      </c>
+      <c r="G348" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H348" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>ao.28</t>
+        </is>
+      </c>
+      <c r="D349" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic KYC intake smart form</t>
+        </is>
+      </c>
+      <c r="E349" s="9" t="inlineStr">
+        <is>
+          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+        </is>
+      </c>
+      <c r="F349" s="9" t="inlineStr">
+        <is>
+          <t>Умная KYC-форма</t>
+        </is>
+      </c>
+      <c r="G349" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H349" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>ao.29</t>
+        </is>
+      </c>
+      <c r="D350" s="9" t="inlineStr">
+        <is>
+          <t>Warranty expiration alerts</t>
+        </is>
+      </c>
+      <c r="E350" s="9" t="inlineStr">
+        <is>
+          <t>გარანტიის ვადის შეხსენებები</t>
+        </is>
+      </c>
+      <c r="F350" s="9" t="inlineStr">
+        <is>
+          <t>Напоминания об окончании гарантии</t>
+        </is>
+      </c>
+      <c r="G350" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H350" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ai</t>
+        </is>
+      </c>
+      <c r="D351" s="9" t="inlineStr">
+        <is>
+          <t>AI &amp; automation</t>
+        </is>
+      </c>
+      <c r="E351" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F351" s="9" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="G351" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H351" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C352" s="3" t="inlineStr">
+        <is>
+          <t>ao.31</t>
+        </is>
+      </c>
+      <c r="D352" s="9" t="inlineStr">
+        <is>
+          <t>Georgian voice meeting transcription</t>
+        </is>
+      </c>
+      <c r="E352" s="9" t="inlineStr">
+        <is>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+        </is>
+      </c>
+      <c r="F352" s="9" t="inlineStr">
+        <is>
+          <t>Транскрипция встреч на грузинском</t>
+        </is>
+      </c>
+      <c r="G352" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H352" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t>ao.32</t>
+        </is>
+      </c>
+      <c r="D353" s="9" t="inlineStr">
+        <is>
+          <t>Audio call sentiment extractor</t>
+        </is>
+      </c>
+      <c r="E353" s="9" t="inlineStr">
+        <is>
+          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+        </is>
+      </c>
+      <c r="F353" s="9" t="inlineStr">
+        <is>
+          <t>Анализ тональности звонков</t>
+        </is>
+      </c>
+      <c r="G353" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H353" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C354" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ind</t>
+        </is>
+      </c>
+      <c r="D354" s="9" t="inlineStr">
+        <is>
+          <t>Industry solutions</t>
+        </is>
+      </c>
+      <c r="E354" s="9" t="inlineStr">
+        <is>
+          <t>დარგობრივი</t>
+        </is>
+      </c>
+      <c r="F354" s="9" t="inlineStr">
+        <is>
+          <t>Отраслевые</t>
+        </is>
+      </c>
+      <c r="G354" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H354" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>ao.33</t>
+        </is>
+      </c>
+      <c r="D355" s="9" t="inlineStr">
+        <is>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
+        </is>
+      </c>
+      <c r="E355" s="9" t="inlineStr">
+        <is>
+          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+        </is>
+      </c>
+      <c r="F355" s="9" t="inlineStr">
+        <is>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
+        </is>
+      </c>
+      <c r="G355" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H355" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C356" s="3" t="inlineStr">
+        <is>
+          <t>ao.34</t>
+        </is>
+      </c>
+      <c r="D356" s="9" t="inlineStr">
+        <is>
+          <t>Client preference proactive matcher</t>
+        </is>
+      </c>
+      <c r="E356" s="9" t="inlineStr">
+        <is>
+          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+        </is>
+      </c>
+      <c r="F356" s="9" t="inlineStr">
+        <is>
+          <t>Автоподбор по пожеланиям клиента</t>
+        </is>
+      </c>
+      <c r="G356" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H356" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>ao.35</t>
+        </is>
+      </c>
+      <c r="D357" s="9" t="inlineStr">
+        <is>
+          <t>Reservation expiration timer</t>
+        </is>
+      </c>
+      <c r="E357" s="9" t="inlineStr">
+        <is>
+          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+        </is>
+      </c>
+      <c r="F357" s="9" t="inlineStr">
+        <is>
+          <t>Таймер истечения брони</t>
+        </is>
+      </c>
+      <c r="G357" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H357" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="inlineStr">
+        <is>
+          <t>ao.36</t>
+        </is>
+      </c>
+      <c r="D358" s="9" t="inlineStr">
+        <is>
+          <t>Floor plan &amp; proposal PDF generator</t>
+        </is>
+      </c>
+      <c r="E358" s="9" t="inlineStr">
+        <is>
+          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+        </is>
+      </c>
+      <c r="F358" s="9" t="inlineStr">
+        <is>
+          <t>PDF планировки и предложения</t>
+        </is>
+      </c>
+      <c r="G358" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H358" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C359" s="3" t="inlineStr">
+        <is>
+          <t>ao.37</t>
+        </is>
+      </c>
+      <c r="D359" s="9" t="inlineStr">
+        <is>
+          <t>Field service visit tracking + approval</t>
+        </is>
+      </c>
+      <c r="E359" s="9" t="inlineStr">
+        <is>
+          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+        </is>
+      </c>
+      <c r="F359" s="9" t="inlineStr">
+        <is>
+          <t>Учёт выездов и подтверждение</t>
+        </is>
+      </c>
+      <c r="G359" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H359" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C360" s="3" t="inlineStr">
+        <is>
+          <t>ao.cat.ops</t>
+        </is>
+      </c>
+      <c r="D360" s="9" t="inlineStr">
+        <is>
+          <t>Operations &amp; ERP</t>
+        </is>
+      </c>
+      <c r="E360" s="9" t="inlineStr">
+        <is>
+          <t>ოპერაციები და ERP</t>
+        </is>
+      </c>
+      <c r="F360" s="9" t="inlineStr">
+        <is>
+          <t>Операции и ERP</t>
+        </is>
+      </c>
+      <c r="G360" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H360" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C361" s="3" t="inlineStr">
+        <is>
+          <t>ao.39</t>
+        </is>
+      </c>
+      <c r="D361" s="9" t="inlineStr">
+        <is>
+          <t>Cold storage WMS &amp; automated billing</t>
+        </is>
+      </c>
+      <c r="E361" s="9" t="inlineStr">
+        <is>
+          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+        </is>
+      </c>
+      <c r="F361" s="9" t="inlineStr">
+        <is>
+          <t>WMS холодного склада и биллинг</t>
+        </is>
+      </c>
+      <c r="G361" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H361" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C362" s="3" t="inlineStr">
+        <is>
+          <t>ao.40</t>
+        </is>
+      </c>
+      <c r="D362" s="9" t="inlineStr">
+        <is>
+          <t>Construction operations &amp; budget tracker</t>
+        </is>
+      </c>
+      <c r="E362" s="9" t="inlineStr">
+        <is>
+          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+        </is>
+      </c>
+      <c r="F362" s="9" t="inlineStr">
+        <is>
+          <t>Стройка: операции и бюджет</t>
+        </is>
+      </c>
+      <c r="G362" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H362" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C363" s="3" t="inlineStr">
+        <is>
+          <t>ao.41</t>
+        </is>
+      </c>
+      <c r="D363" s="9" t="inlineStr">
+        <is>
+          <t>Predictive debtor call queue</t>
+        </is>
+      </c>
+      <c r="E363" s="9" t="inlineStr">
+        <is>
+          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+        </is>
+      </c>
+      <c r="F363" s="9" t="inlineStr">
+        <is>
+          <t>Умная очередь звонков должникам</t>
+        </is>
+      </c>
+      <c r="G363" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H363" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C364" s="3" t="inlineStr">
+        <is>
+          <t>ao.42</t>
+        </is>
+      </c>
+      <c r="D364" s="9" t="inlineStr">
+        <is>
+          <t>Agent attendance tracker</t>
+        </is>
+      </c>
+      <c r="E364" s="9" t="inlineStr">
+        <is>
+          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+        </is>
+      </c>
+      <c r="F364" s="9" t="inlineStr">
+        <is>
+          <t>Учёт посещаемости агентов</t>
+        </is>
+      </c>
+      <c r="G364" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H364" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>ao.43</t>
+        </is>
+      </c>
+      <c r="D365" s="9" t="inlineStr">
+        <is>
+          <t>Round-robin appointment balancing</t>
+        </is>
+      </c>
+      <c r="E365" s="9" t="inlineStr">
+        <is>
+          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+        </is>
+      </c>
+      <c r="F365" s="9" t="inlineStr">
+        <is>
+          <t>Равномерное распределение встреч</t>
+        </is>
+      </c>
+      <c r="G365" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H365" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="inlineStr">
+        <is>
           <t>ao.44</t>
         </is>
       </c>
-      <c r="D331" s="9" t="inlineStr">
+      <c r="D366" s="9" t="inlineStr">
         <is>
           <t>Discovery call auto-scheduling</t>
         </is>
       </c>
-      <c r="E331" s="9" t="inlineStr">
+      <c r="E366" s="9" t="inlineStr">
         <is>
           <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
-      <c r="F331" s="9" t="inlineStr">
+      <c r="F366" s="9" t="inlineStr">
         <is>
           <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
-      <c r="G331" s="3" t="inlineStr">
+      <c r="G366" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H331" s="3" t="inlineStr">
+      <c r="H366" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H331"/>
+  <autoFilter ref="A1:H366"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H530" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H565" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18822,7 +20156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -27157,10 +28491,1340 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>pain.cx.title</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Excel slows processes, creates risks and holds back growth</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Excel ანელებს პროცესებს, ქმნის რისკებს და აფერხებს ზრდას</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>Excel замедляет процессы, создаёт риски и тормозит рост</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr"/>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>pain.cx.body</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Clients spread across files, notebooks and phones.</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>კლიენტები ფაილებში, რვეულებსა და ტელეფონში.</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>Клиенты разбросаны по файлам, блокнотам и телефонам.</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr"/>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>pain.cx.statn</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr"/>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>pain.cx.stat</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>of spreadsheets contain errors</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>ცხრილებში შეცდომებია</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>таблиц содержат ошибки</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr"/>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>pain.cx.src</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Source: Raymond Panko, University of Hawaii (2008)</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>წყარო: Raymond Panko, ჰავაის უნივერსიტეტი (2008)</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>Источник: Raymond Panko, Гавайский университет (2008)</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr"/>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>pain.cx.fix</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>In Zoho CRM every client and deal lives in one system: you see who is at which stage and what is coming in.</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>Zoho CRM-ში ყველა კლიენტი და გარიგება ერთ სისტემაშია: ჩანს, ვინ რა ეტაპზეა და რამდენი შემოდის.</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>В Zoho CRM все клиенты и сделки в одной системе: видно, кто на каком этапе и сколько поступает.</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr"/>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>pain.cx.atitle</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Every deal in one system</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>ყველა გარიგება — ერთ სისტემაში</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Все сделки — в одной системе</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr"/>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>pain.cc.title</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Unsystematic work creates chaos and unmanageable processes</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>არასისტემური მუშაობა ქმნის ქაოსს და უმართავ პროცესებს</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>Работа без системы создаёт хаос и неуправляемые процессы</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr"/>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>pain.cc.body</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Every question lands on you, every task is on your mind.</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>ყველა კითხვა შენთან მოდის, ყველა დავალება შენ გახსოვს.</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>Все вопросы идут к вам, все задачи держите в голове.</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr"/>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>pain.cc.statn</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr"/>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>pain.cc.stat</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>of the workday goes on “work about work”: chasing status, clarifying, duplicating</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>სამუშაო დროისა იხარჯება „სამუშაოზე სამუშაოზე“: სტატუსების ძებნა, დაზუსტება, დუბლირება</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>рабочего дня уходит на «работу о работе»: поиск статусов, уточнения, дублирование</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr"/>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>pain.cc.src</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Source: Asana Anatomy of Work, 9,615 workers, 2023</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>წყარო: Asana Anatomy of Work, 9 615 თანამშრომელი, 2023</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>Источник: Asana Anatomy of Work, 9 615 сотрудников, 2023</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr"/>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>pain.cc.fix</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint walks the team step by step: who does what and when. No stage gets skipped.</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint გუნდს ნაბიჯ-ნაბიჯ მიჰყავს: ვინ, რა და როდის აკეთებს. ვერცერთი ეტაპი ვერ გამოგრჩება.</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint ведёт команду шаг за шагом: кто, что и когда делает. Ни один этап не пропускается.</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr"/>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>pain.cc.atitle</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Every step follows the rules, in order</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ყველა ნაბიჯი — წესით და თანმიმდევრობით</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>Каждый шаг — по правилам и по порядку</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr"/>
+      <c r="H230" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>pain.cd.title</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Scattered data leads to wrong decisions</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>გაფანტული მონაცემებით არასწორ გადაწყვეტილებებს იღებ</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>Разрозненные данные ведут к неверным решениям</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr"/>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>pain.cd.body</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Three different numbers for the same question.</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>ერთსა და იმავე კითხვაზე სამი განსხვავებული ციფრი.</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>Три разные цифры на один и тот же вопрос.</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr"/>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>pain.cd.statn</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>$12.9M</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>$12.9 მლნ</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>$12,9 млн</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr"/>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>pain.cd.stat</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>a year: the average cost of poor data quality to an organisation</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>ყოველწლიურად კარგავს საშუალოდ ორგანიზაცია ცუდი ხარისხის მონაცემების გამო</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>в год в среднем теряет организация из-за некачественных данных</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr"/>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>pain.cd.src</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Source: Gartner</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>წყარო: Gartner</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>Источник: Gartner</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr"/>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>pain.cd.fix</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>All data on one dashboard in real time: you decide based on facts.</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>ყველა მონაცემი ერთ დეშბორდზე, რეალურ დროში: გადაწყვეტილებას ფაქტებზე დაყრდნობით იღებ.</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>Все данные на одном дашборде в реальном времени: решения на основе фактов.</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr"/>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>pain.cd.atitle</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>Exact numbers on one dashboard</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>ზუსტი ციფრები — ერთ დეშბორდზე</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>Точные цифры — на одном дашборде</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr"/>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>pain.data.s1</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Excel · October sales</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>Excel · ოქტომბრის გაყიდვები</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>Excel · продажи за октябрь</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr"/>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>pain.data.s2</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Manager · “roughly”</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>მენეჯერი · „დაახლოებით“</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>Менеджер · «примерно»</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr"/>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>pain.data.s3</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>ბუღალტერია</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Бухгалтерия</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr"/>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.k1</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>ახალი</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>Новые</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr"/>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.k2</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>შეთავაზება</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>Предложение</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr"/>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.k3</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>მოგებული</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Выиграно</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr"/>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.bp</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint · sales process</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint · გაყიდვის პროცესი</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>Blueprint · процесс продаж</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr"/>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.b1</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>New lead</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>ახალი ლიდი</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>Новый лид</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr"/>
+      <c r="H245" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.b2</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>კვალიფიკაცია</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>Квалификация</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr"/>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.b3</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Offer sent</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>შეთავაზება გაიგზავნა</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>Предложение отправлено</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr"/>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.b4</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>ხელშეკრულება</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>Договор</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr"/>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.an</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Analytics · October</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>ანალიტიკა · ოქტომბერი</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>Аналитика · октябрь</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr"/>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.kp1</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>შემოსავალი</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>Выручка</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr"/>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.kp2</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Conversion</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>კონვერსია</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>Конверсия</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr"/>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H216"/>
+  <autoFilter ref="A1:H251"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H415" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H450" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$366</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$253</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
@@ -5660,7 +5660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H366"/>
+  <dimension ref="A1:H368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -5811,17 +5811,17 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Choose the right CRM</t>
+          <t>CRM selection and implementation</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>შეარჩიე სწორი CRM</t>
+          <t>CRM-ის შერჩევა და დანერგვა</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Выберите правильную CRM</t>
+          <t>Подбор и внедрение CRM</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -5853,17 +5853,17 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>and save</t>
+          <t>from 5 days:</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>და დაზოგე</t>
+          <t>5 დღიდან:</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>и сэкономьте</t>
+          <t>от 5 дней:</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -5893,9 +5893,21 @@
           <t>hero.headline.line2.plain</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>every client</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>ყველა კლიენტი</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>все клиенты</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
@@ -5925,17 +5937,17 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>100+ hours</t>
+          <t>in one system</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>100+ საათი</t>
+          <t>ერთ სისტემაში</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>100+ часов</t>
+          <t>в одной системе</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -5997,17 +6009,17 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>With 500+ implementations behind us, in 20 minutes we tell you which CRM fits your sales and what implementation costs. Free if you book now.</t>
+          <t>We pick the CRM that fits your sales, set it up, move your data, train your team and stay on for support. 500+ implementations, fixed price and timeline. The 20-minute call is free if you book now.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>500+ დანერგვის გამოცდილებით, 20 წუთში გეტყვი, რომელი CRM მოერგება შენს გაყიდვებს და რა დაჯდება დანერგვა. უფასოდ - თუ ახლავე დაჯავშნი.</t>
+          <t>ვარჩევთ შენს გაყიდვებზე მორგებულ CRM-ს, ვაწყობთ, გადმოგვაქვს მონაცემები, ვატრენინგებთ გუნდს და ვრჩებით მხარდაჭერისთვის. 500+ დანერგვა, ფიქსირებული ფასი და ვადა. 20-წუთიანი ზარი უფასოა, თუ ახლავე დაჯავშნი.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Опираясь на 500+ внедрений, за 20 минут скажем, какая CRM подойдёт вашим продажам и сколько стоит внедрение. Бесплатно - если бронируете сейчас.</t>
+          <t>Подберём CRM под ваши продажи, настроим, перенесём данные, обучим команду и останемся на поддержке. 500+ внедрений, фиксированные цена и сроки. 20-минутный звонок бесплатный, если забронируете сейчас.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -6075,22 +6087,26 @@
           <t>hero.sub.free</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Free if you book now.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>უფასოდ - თუ ახლავე დაჯავშნი.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Бесплатно - если бронируете сейчас.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>free if you book now.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>უფასოა, თუ ახლავე დაჯავშნი.</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>бесплатный, если забронируете сейчас.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -12401,17 +12417,17 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>დანერგვამდე</t>
+          <t>გამოწვევა</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>До внедрения</t>
+          <t>Проблема</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr"/>
@@ -12439,12 +12455,12 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>შედეგად</t>
+          <t>შედეგი</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -15317,34 +15333,30 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
-        </is>
-      </c>
-      <c r="D252" s="9" t="inlineStr">
-        <is>
-          <t>Choose where to start</t>
-        </is>
-      </c>
-      <c r="E252" s="9" t="inlineStr">
-        <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
-        </is>
-      </c>
-      <c r="F252" s="9" t="inlineStr">
-        <is>
-          <t>Выберите, с чего начать</t>
-        </is>
-      </c>
-      <c r="G252" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.create</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>+ Deal</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>+ გარიგება</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>+ Сделка</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr"/>
       <c r="H252" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15359,34 +15371,30 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
-        </is>
-      </c>
-      <c r="D253" s="9" t="inlineStr">
-        <is>
-          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
-        </is>
-      </c>
-      <c r="E253" s="9" t="inlineStr">
-        <is>
-          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
-        </is>
-      </c>
-      <c r="F253" s="9" t="inlineStr">
-        <is>
-          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
-        </is>
-      </c>
-      <c r="G253" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>pain.z.bnext</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Next step</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>შემდეგი ნაბიჯი</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>Следующий шаг</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr"/>
       <c r="H253" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -15406,22 +15414,22 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
+          <t>pk.title</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Most popular</t>
+          <t>Choose where to start</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
+          <t>აირჩიე, საიდან დაიწყო</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Выбирают чаще всего</t>
+          <t>Выберите, с чего начать</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -15448,22 +15456,22 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>pk.deal</t>
+          <t>pk.sub</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Discount valid for 1 week from the day the offer is sent.</t>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
+          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -15490,22 +15498,22 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>one-time</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>ერთჯერადად</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>разово</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -15532,22 +15540,22 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
+          <t>pk.deal</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>working days</t>
+          <t>Discount valid for 1 week from the day the offer is sent.</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>სამუშაო დღე</t>
+          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>рабочих дней</t>
+          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -15574,22 +15582,22 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>pk.full</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Everything included</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>სრული ჩამონათვალი</t>
+          <t>ერთჯერადად</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Всё, что входит</t>
+          <t>разово</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -15616,22 +15624,22 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Choose this package</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>ამ პაკეტის არჩევა</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Выбрать этот пакет</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -15658,22 +15666,22 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>არჩეულია</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Выбран</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -15700,22 +15708,22 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -15742,22 +15750,22 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>pk.cur</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>ვალუტა</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>Валюта</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -15779,27 +15787,27 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Extra features</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>დამატებითი ფუნქციები</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>Дополнительные функции</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -15821,27 +15829,27 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Optional. Add only if you need them</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>Необязательно. Добавьте, если нужно</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -15868,22 +15876,22 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>ao.popular</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>Often added</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>ხშირად ამატებენ</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Часто добавляют</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -15910,22 +15918,22 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>ao.more</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>All add-ons by category</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
+          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Все дополнения по категориям</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -15952,22 +15960,22 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -15989,27 +15997,27 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Choose a package</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე პაკეტი</t>
+          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>Выберите пакет</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -16031,27 +16039,27 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>ფუნქცია</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>функц.</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -16078,22 +16086,22 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>+ VAT</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>+ დღგ</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>+ НДС</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -16120,22 +16128,22 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Request a call</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -16162,22 +16170,22 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Your selection:</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>შენი არჩევანი:</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>Ваш выбор:</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -16199,27 +16207,27 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>სტარტი</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Старт</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -16241,27 +16249,27 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.short</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>To move from Excel into a CRM</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Чтобы перейти с Excel на CRM</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -16288,22 +16296,22 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h1</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>4 core modules</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -16330,22 +16338,22 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h2</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Email and Facebook inside the CRM</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტა და Facebook CRM-ში</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>Почта и Facebook внутри CRM</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -16372,22 +16380,22 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h3</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Lead form and KPI dashboard</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ფორმა და KPI დაფა</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>Форма лидов и дашборд KPI</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -16414,22 +16422,22 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -16456,22 +16464,22 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -16498,22 +16506,22 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Facebook messages right inside the CRM</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Сообщения Facebook прямо в CRM</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -16540,22 +16548,22 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>1 web form to capture leads</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>1 веб-форма для приёма лидов</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -16582,22 +16590,22 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>1 sales-pipeline KPI dashboard</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Дашборд KPI воронки продаж</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -16624,22 +16632,22 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Recorded video instructions for the team</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Видеоинструкции для команды</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -16666,22 +16674,22 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Essentials</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალური</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>Оптимальный</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -16708,22 +16716,22 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.short</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>For a 5-10 person sales team</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Для отдела продаж из 5-10 человек</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -16750,22 +16758,22 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter, plus:</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта», плюс:</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -16792,22 +16800,22 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h1</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
+          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта»</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -16834,22 +16842,22 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h2</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads, automatically</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -16876,22 +16884,22 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h3</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Stage rules and lead assignment</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Правила этапов и распределение лидов</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -16918,22 +16926,22 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -16960,22 +16968,22 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -17002,22 +17010,22 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -17044,22 +17052,22 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -17086,22 +17094,22 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -17128,22 +17136,22 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -17170,22 +17178,22 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -17212,22 +17220,22 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -17254,22 +17262,22 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -17296,22 +17304,22 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -17338,22 +17346,22 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.short</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>For a growing 15-25 person team</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
+          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>Для растущей команды из 15-25 человек</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -17380,22 +17388,22 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -17422,22 +17430,22 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h1</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი</t>
+          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального»</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -17464,22 +17472,22 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h2</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Telephony and call processing</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია და ზარების დამუშავება</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Телефония и обработка звонков</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -17506,22 +17514,22 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h3</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Automations and AI (Claude)</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და AI (Claude)</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Автоматизации и AI (Claude)</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -17548,22 +17556,22 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -17590,22 +17598,22 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -17632,22 +17640,22 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -17674,22 +17682,22 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -17716,22 +17724,22 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -17758,22 +17766,22 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -17800,22 +17808,22 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -17842,22 +17850,22 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -17884,22 +17892,22 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -17921,27 +17929,27 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -17963,27 +17971,27 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -18010,22 +18018,22 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -18052,22 +18060,22 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -18094,22 +18102,22 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ao.18</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG bank wire deposit matching</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>Автосверка переводов TBC/BOG</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -18136,22 +18144,22 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>ao.30</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -18178,22 +18186,22 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ao.38</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -18220,22 +18228,22 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -18262,22 +18270,22 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -18304,22 +18312,22 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -18346,22 +18354,22 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -18388,22 +18396,22 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -18430,22 +18438,22 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -18472,22 +18480,22 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -18514,22 +18522,22 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -18556,22 +18564,22 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოების აღრიცხვა</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -18598,22 +18606,22 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -18640,22 +18648,22 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>ao.12</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>Email + calendar 2-way sync</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+          <t>ბროკერების საკომისიოების აღრიცხვა</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -18682,22 +18690,22 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>ao.13</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>Возврат пропущенных звонков и SMS</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -18724,22 +18732,22 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>ao.14</t>
+          <t>ao.12</t>
         </is>
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>Messaging bot lead capture webhook</t>
+          <t>Email + calendar 2-way sync</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
+          <t>Двусторонняя синхронизация почты и календаря</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -18766,22 +18774,22 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>ao.13</t>
         </is>
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Missed-call recovery &amp; SMS callback</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Возврат пропущенных звонков и SMS</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -18808,22 +18816,22 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>ao.15</t>
+          <t>ao.14</t>
         </is>
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>Website lead form + webhook</t>
+          <t>Messaging bot lead capture webhook</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + webhook</t>
+          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + webhook</t>
+          <t>Лиды из чат-бота сразу в CRM</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -18850,22 +18858,22 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>ao.16</t>
+          <t>ao.cat.mkt</t>
         </is>
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
+          <t>Marketing &amp; growth</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
+          <t>მარკეტინგი</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>ROI источников и атрибуция кампаний</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -18892,22 +18900,22 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>ao.17</t>
+          <t>ao.15</t>
         </is>
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
+          <t>Website lead form + webhook</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+          <t>საიტის ფორმა + webhook</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
+          <t>Форма сайта + webhook</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -18934,22 +18942,22 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>ao.16</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>Lead source ROI &amp; campaign attribution</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>ROI источников и атрибуция кампаний</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -18976,22 +18984,22 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>ao.19</t>
+          <t>ao.17</t>
         </is>
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+          <t>Email campaigns: account setup &amp; contact sync</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -19018,22 +19026,22 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>ao.20</t>
+          <t>ao.cat.fin</t>
         </is>
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>NBG daily exchange rate sync</t>
+          <t>Fintech &amp; accounting</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+          <t>ფინანსები და ბანკები</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>Ежедневный курс НБГ</t>
+          <t>Финансы и банки</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -19060,22 +19068,22 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>ao.21</t>
+          <t>ao.19</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>Ambiguous payment reference fallback queue</t>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>Очередь неопознанных платежей</t>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -19102,22 +19110,22 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>ao.22</t>
+          <t>ao.20</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>Dynamic installment payment schedule</t>
+          <t>NBG daily exchange rate sync</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>График рассрочки</t>
+          <t>Ежедневный курс НБГ</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -19144,22 +19152,22 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>ao.23</t>
+          <t>ao.21</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
+          <t>Ambiguous payment reference fallback queue</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>SMS о просроченной задолженности</t>
+          <t>Очередь неопознанных платежей</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -19186,22 +19194,22 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>ao.24</t>
+          <t>ao.22</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>SMS gateway &amp; OTP verification</t>
+          <t>Dynamic installment payment schedule</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+          <t>შიდა განვადების დინამიკური გრაფიკი</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>SMS-шлюз и OTP-верификация</t>
+          <t>График рассрочки</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -19228,22 +19236,22 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>ao.23</t>
         </is>
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>Overdue debt alert &amp; SMS warning</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>SMS о просроченной задолженности</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -19270,22 +19278,22 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>ao.25</t>
+          <t>ao.24</t>
         </is>
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
+          <t>SMS gateway &amp; OTP verification</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
+          <t>SMS-шлюз и OTP-верификация</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -19312,22 +19320,22 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>ao.26</t>
+          <t>ao.cat.cx</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>Multi-tier SLA escalation matrix</t>
+          <t>Customer experience</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+          <t>მომხმარებლის მომსახურება</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>Матрица эскалации SLA</t>
+          <t>Клиентский сервис</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -19354,22 +19362,22 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>ao.27</t>
+          <t>ao.25</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>Оценка NPS/CSAT после тикета</t>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -19396,22 +19404,22 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>ao.28</t>
+          <t>ao.26</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>Dynamic KYC intake smart form</t>
+          <t>Multi-tier SLA escalation matrix</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>Умная KYC-форма</t>
+          <t>Матрица эскалации SLA</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -19438,22 +19446,22 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>ao.29</t>
+          <t>ao.27</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>Warranty expiration alerts</t>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
+          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>Напоминания об окончании гарантии</t>
+          <t>Оценка NPS/CSAT после тикета</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -19480,22 +19488,22 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.28</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Dynamic KYC intake smart form</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Умная KYC-форма</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -19522,22 +19530,22 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>ao.31</t>
+          <t>ao.29</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>Georgian voice meeting transcription</t>
+          <t>Warranty expiration alerts</t>
         </is>
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+          <t>გარანტიის ვადის შეხსენებები</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>Транскрипция встреч на грузинском</t>
+          <t>Напоминания об окончании гарантии</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -19564,22 +19572,22 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>ao.32</t>
+          <t>ao.cat.ai</t>
         </is>
       </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
-          <t>Audio call sentiment extractor</t>
+          <t>AI &amp; automation</t>
         </is>
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>Анализ тональности звонков</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -19606,22 +19614,22 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ind</t>
+          <t>ao.31</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>Industry solutions</t>
+          <t>Georgian voice meeting transcription</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>დარგობრივი</t>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>Отраслевые</t>
+          <t>Транскрипция встреч на грузинском</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -19648,22 +19656,22 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>ao.33</t>
+          <t>ao.32</t>
         </is>
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
+          <t>Audio call sentiment extractor</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
+          <t>Анализ тональности звонков</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -19690,22 +19698,22 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>ao.34</t>
+          <t>ao.cat.ind</t>
         </is>
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>Client preference proactive matcher</t>
+          <t>Industry solutions</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+          <t>დარგობრივი</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>Автоподбор по пожеланиям клиента</t>
+          <t>Отраслевые</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -19732,22 +19740,22 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>ao.35</t>
+          <t>ao.33</t>
         </is>
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>Reservation expiration timer</t>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>Таймер истечения брони</t>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -19774,22 +19782,22 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>ao.36</t>
+          <t>ao.34</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
+          <t>Client preference proactive matcher</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>PDF планировки и предложения</t>
+          <t>Автоподбор по пожеланиям клиента</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -19816,22 +19824,22 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>ao.37</t>
+          <t>ao.35</t>
         </is>
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>Field service visit tracking + approval</t>
+          <t>Reservation expiration timer</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>Учёт выездов и подтверждение</t>
+          <t>Таймер истечения брони</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -19858,22 +19866,22 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.36</t>
         </is>
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Floor plan &amp; proposal PDF generator</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>PDF планировки и предложения</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -19900,22 +19908,22 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>ao.39</t>
+          <t>ao.37</t>
         </is>
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>Cold storage WMS &amp; automated billing</t>
+          <t>Field service visit tracking + approval</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+          <t>საველე ვიზიტების მართვა და დადასტურება</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>WMS холодного склада и биллинг</t>
+          <t>Учёт выездов и подтверждение</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -19942,22 +19950,22 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>ao.40</t>
+          <t>ao.cat.ops</t>
         </is>
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>Construction operations &amp; budget tracker</t>
+          <t>Operations &amp; ERP</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+          <t>ოპერაციები და ERP</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>Стройка: операции и бюджет</t>
+          <t>Операции и ERP</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -19984,22 +19992,22 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>ao.41</t>
+          <t>ao.39</t>
         </is>
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>Predictive debtor call queue</t>
+          <t>Cold storage WMS &amp; automated billing</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>Умная очередь звонков должникам</t>
+          <t>WMS холодного склада и биллинг</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -20026,22 +20034,22 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>ao.42</t>
+          <t>ao.40</t>
         </is>
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>Agent attendance tracker</t>
+          <t>Construction operations &amp; budget tracker</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>Учёт посещаемости агентов</t>
+          <t>Стройка: операции и бюджет</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -20068,22 +20076,22 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>ao.43</t>
+          <t>ao.41</t>
         </is>
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>Round-robin appointment balancing</t>
+          <t>Predictive debtor call queue</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>Равномерное распределение встреч</t>
+          <t>Умная очередь звонков должникам</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
@@ -20110,39 +20118,123 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
+          <t>ao.42</t>
+        </is>
+      </c>
+      <c r="D366" s="9" t="inlineStr">
+        <is>
+          <t>Agent attendance tracker</t>
+        </is>
+      </c>
+      <c r="E366" s="9" t="inlineStr">
+        <is>
+          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+        </is>
+      </c>
+      <c r="F366" s="9" t="inlineStr">
+        <is>
+          <t>Учёт посещаемости агентов</t>
+        </is>
+      </c>
+      <c r="G366" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H366" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C367" s="3" t="inlineStr">
+        <is>
+          <t>ao.43</t>
+        </is>
+      </c>
+      <c r="D367" s="9" t="inlineStr">
+        <is>
+          <t>Round-robin appointment balancing</t>
+        </is>
+      </c>
+      <c r="E367" s="9" t="inlineStr">
+        <is>
+          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+        </is>
+      </c>
+      <c r="F367" s="9" t="inlineStr">
+        <is>
+          <t>Равномерное распределение встреч</t>
+        </is>
+      </c>
+      <c r="G367" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H367" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C368" s="3" t="inlineStr">
+        <is>
           <t>ao.44</t>
         </is>
       </c>
-      <c r="D366" s="9" t="inlineStr">
+      <c r="D368" s="9" t="inlineStr">
         <is>
           <t>Discovery call auto-scheduling</t>
         </is>
       </c>
-      <c r="E366" s="9" t="inlineStr">
+      <c r="E368" s="9" t="inlineStr">
         <is>
           <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
-      <c r="F366" s="9" t="inlineStr">
+      <c r="F368" s="9" t="inlineStr">
         <is>
           <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
-      <c r="G366" s="3" t="inlineStr">
+      <c r="G368" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H366" s="3" t="inlineStr">
+      <c r="H368" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H366"/>
+  <autoFilter ref="A1:H368"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H565" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H567" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20156,7 +20248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -26913,17 +27005,17 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>დანერგვამდე</t>
+          <t>გამოწვევა</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>До внедрения</t>
+          <t>Проблема</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr"/>
@@ -26951,12 +27043,12 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>შედეგად</t>
+          <t>შედეგი</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -29821,10 +29913,86 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.create</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>+ Deal</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>+ გარიგება</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>+ Сделка</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr"/>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>pain.z.bnext</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Next step</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>შემდეგი ნაბიჯი</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>Следующий шаг</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr"/>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H251"/>
+  <autoFilter ref="A1:H253"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H450" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H452" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -6989,17 +6989,17 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>CRM selection and implementation</t>
+          <t>We'll choose and implement</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>CRM-ის შერჩევა და დანერგვა</t>
+          <t>შეგირჩევთ და დაგინერგავთ</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Подбор и внедрение CRM</t>
+          <t>Подберём и внедрим</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>from 5 days:</t>
+          <t>your CRM system</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>5 დღიდან:</t>
+          <t>CRM სისტემას</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>от 5 дней:</t>
+          <t>вашу CRM-систему</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -7071,21 +7071,9 @@
           <t>hero.headline.line2.plain</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>every client</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>ყველა კლიენტი</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>все клиенты</t>
-        </is>
-      </c>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
@@ -7113,21 +7101,9 @@
           <t>hero.headline.line3.underline</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>in one system</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>ერთ სისტემაში</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>в одной системе</t>
-        </is>
-      </c>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
@@ -7187,17 +7163,17 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>We pick the CRM that fits your sales, set it up, move your data, train your team and stay on for support. 500+ implementations, fixed price and timeline. The 20-minute call is free if you book now.</t>
+          <t>We implement the right CRM, train your team and provide technical support. Request a free 20-minute consultation and I'll tell you exactly which CRM you need. Full service: selection → implementation → training → support.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>ვარჩევთ შენს გაყიდვებზე მორგებულ CRM-ს, ვაწყობთ, გადმოგვაქვს მონაცემები, ვატრენინგებთ გუნდს და ვრჩებით მხარდაჭერისთვის. 500+ დანერგვა, ფიქსირებული ფასი და ვადა. 20-წუთიანი ზარი უფასოა, თუ ახლავე დაჯავშნი.</t>
+          <t>დაგინერგავთ სწორ CRM სისტემას, დავატრეინინგებთ შენს გუნდს და გაგიწევთ ტექნიკურ მხარდაჭერას. მოითხოვე 20-წუთიანი უფასო კონსულტაცია და გეტყვი, კონკრეტულად რომელი CRM გჭირდება. სრული სერვისი: შერჩევა → დანერგვა → სწავლება → მხარდაჭერა.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Подберём CRM под ваши продажи, настроим, перенесём данные, обучим команду и останемся на поддержке. 500+ внедрений, фиксированные цена и сроки. 20-минутный звонок бесплатный, если забронируете сейчас.</t>
+          <t>Внедрим правильную CRM, обучим вашу команду и обеспечим техническую поддержку. Запросите бесплатную 20-минутную консультацию, и я скажу, какая именно CRM вам нужна. Полный сервис: подбор → внедрение → обучение → поддержка.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -7267,17 +7243,17 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>free if you book now.</t>
+          <t>free 20-minute consultation</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>უფასოა, თუ ახლავე დაჯავშნი.</t>
+          <t>20-წუთიანი უფასო კონსულტაცია</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>бесплатный, если забронируете сейчас.</t>
+          <t>бесплатную 20-минутную консультацию</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -7163,17 +7163,17 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>We implement the right CRM, train your team and provide technical support. Request a free 20-minute consultation and I'll tell you exactly which CRM you need. Full service: selection → implementation → training → support.</t>
+          <t>Request a free 20-minute consultation and I'll tell you exactly which CRM you need. AI services and full process management: selection → implementation → training → support included.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>დაგინერგავთ სწორ CRM სისტემას, დავატრეინინგებთ შენს გუნდს და გაგიწევთ ტექნიკურ მხარდაჭერას. მოითხოვე 20-წუთიანი უფასო კონსულტაცია და გეტყვი, კონკრეტულად რომელი CRM გჭირდება. სრული სერვისი: შერჩევა → დანერგვა → სწავლება → მხარდაჭერა.</t>
+          <t>მოითხოვე 20-წუთიანი უფასო კონსულტაცია და გეტყვი, კონკრეტულად რომელი CRM გჭირდება. AI სერვისები და სრული პროცესის მართვა: შერჩევა → დანერგვა → სწავლება → მხარდაჭერის ჩათვლით.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Внедрим правильную CRM, обучим вашу команду и обеспечим техническую поддержку. Запросите бесплатную 20-минутную консультацию, и я скажу, какая именно CRM вам нужна. Полный сервис: подбор → внедрение → обучение → поддержка.</t>
+          <t>Запросите бесплатную 20-минутную консультацию, и я скажу, какая именно CRM вам нужна. AI-сервисы и управление всем процессом: подбор → внедрение → обучение → поддержка включительно.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">

--- a/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
+++ b/Claude outputs/Unitty Solutions — Translations (EN_KA_RU).xlsx
@@ -13,11 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed keys" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$291</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$284</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Start'!$A$1:$H$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CRM'!$A$1:$H$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AI'!$A$1:$H$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Banks'!$A$1:$H$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Solutions'!$A$1:$H$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Thank-you'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>კვლევას და ძიებას</t>
+          <t>კვლევას</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -945,17 +945,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4365,17 +4365,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -5353,17 +5353,17 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>დარეკვა</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Позвонить</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr"/>
@@ -6759,17 +6759,17 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr"/>
@@ -6821,10 +6821,48 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Nav</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>nav.cta</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Free call</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>უფასო ზარი</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>Бесплатный звонок</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr"/>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H166"/>
+  <autoFilter ref="A1:H167"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H365" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H366" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6838,7 +6876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -7285,17 +7323,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -10709,17 +10747,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -11777,17 +11815,17 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>დარეკვა</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Позвонить</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr"/>
@@ -13231,17 +13269,17 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr"/>
@@ -13301,34 +13339,30 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Nav</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>process.go</t>
-        </is>
-      </c>
-      <c r="D167" s="9" t="inlineStr">
-        <is>
-          <t>Request now</t>
-        </is>
-      </c>
-      <c r="E167" s="9" t="inlineStr">
-        <is>
-          <t>მოითხოვე ახლავე</t>
-        </is>
-      </c>
-      <c r="F167" s="9" t="inlineStr">
-        <is>
-          <t>Запросить сейчас</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>nav.cta</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Free call</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>უფასო ზარი</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>Бесплатный звонок</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr"/>
       <c r="H167" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -13343,27 +13377,27 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Cp</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>cp.cx.p</t>
+          <t>process.go</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Excel slows sales down and creates risks</t>
+          <t>Request now</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>Excel ანელებს გაყიდვებს და ქმნის რისკებს</t>
+          <t>მოითხოვე ახლავე</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>Excel тормозит продажи и создаёт риски</t>
+          <t>Запросить сейчас</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -13390,22 +13424,22 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>cp.cx.s</t>
+          <t>cp.cx.p</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Zoho CRM: every deal in one system</t>
+          <t>Excel slows sales down and creates risks</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>Zoho CRM: ყველა გარიგება ერთ სისტემაში</t>
+          <t>Excel ანელებს გაყიდვებს და ქმნის რისკებს</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Zoho CRM: все сделки в одной системе</t>
+          <t>Excel тормозит продажи и создаёт риски</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -13432,22 +13466,22 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>cp.cc.p</t>
+          <t>cp.cx.s</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>Work without a system creates chaos</t>
+          <t>Zoho CRM: every deal in one system</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>არასისტემური მუშაობა ქაოსს ქმნის</t>
+          <t>Zoho CRM: ყველა გარიგება ერთ სისტემაში</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>Работа без системы создаёт хаос</t>
+          <t>Zoho CRM: все сделки в одной системе</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -13474,22 +13508,22 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>cp.cc.s</t>
+          <t>cp.cc.p</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Blueprint: every step by the rules, in order</t>
+          <t>Work without a system creates chaos</t>
         </is>
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>Blueprint: ყველა ნაბიჯი წესით და თანმიმდევრობით</t>
+          <t>არასისტემური მუშაობა ქაოსს ქმნის</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>Blueprint: каждый шаг по правилам и по порядку</t>
+          <t>Работа без системы создаёт хаос</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -13516,22 +13550,22 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>cp.cd.p</t>
+          <t>cp.cc.s</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>Scattered data, wrong decisions</t>
+          <t>Blueprint: every step by the rules, in order</t>
         </is>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>გაფანტული მონაცემები — არასწორი გადაწყვეტილებები</t>
+          <t>Blueprint: ყველა ნაბიჯი წესით და თანმიმდევრობით</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>Разрозненные данные — неверные решения</t>
+          <t>Blueprint: каждый шаг по правилам и по порядку</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -13558,22 +13592,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>cp.cd.s</t>
+          <t>cp.cd.p</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Analytics: exact numbers on one dashboard</t>
+          <t>Scattered data, wrong decisions</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>ანალიტიკა: ზუსტი ციფრები ერთ დეშბორდზე</t>
+          <t>გაფანტული მონაცემები — არასწორი გადაწყვეტილებები</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>Аналитика: точные цифры на одном дашборде</t>
+          <t>Разрозненные данные — неверные решения</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -13595,27 +13629,27 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Cp</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>pk.title</t>
+          <t>cp.cd.s</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>Choose where to start</t>
+          <t>Analytics: exact numbers on one dashboard</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე, საიდან დაიწყო</t>
+          <t>ანალიტიკა: ზუსტი ციფრები ერთ დეშბორდზე</t>
         </is>
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>Выберите, с чего начать</t>
+          <t>Аналитика: точные цифры на одном дашборде</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -13642,22 +13676,22 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>pk.sub</t>
+          <t>pk.title</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
+          <t>Choose where to start</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
+          <t>აირჩიე, საიდან დაიწყო</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
+          <t>Выберите, с чего начать</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -13684,22 +13718,22 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>pk.popular</t>
+          <t>pk.sub</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>Most popular</t>
+          <t>Fixed price, fixed timeline. Start small and add the rest later.</t>
         </is>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>ყველაზე ხშირად ირჩევენ</t>
+          <t>ფიქსირებული ფასი და მკაფიო ვადები. დაიწყე მცირე პაკეტით, დანარჩენს მოგვიანებით დაამატებ.</t>
         </is>
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>Выбирают чаще всего</t>
+          <t>Фиксированная цена и срок. Начните с малого, остальное добавите потом.</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -13726,22 +13760,22 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>pk.deal</t>
+          <t>pk.popular</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>Discount valid for 1 week from the day the offer is sent.</t>
+          <t>Most popular</t>
         </is>
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
-          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
+          <t>ყველაზე ხშირად ირჩევენ</t>
         </is>
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
+          <t>Выбирают чаще всего</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -13768,22 +13802,22 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>pk.once</t>
+          <t>pk.deal</t>
         </is>
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>one-time</t>
+          <t>Discount valid for 1 week from the day the offer is sent.</t>
         </is>
       </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
-          <t>ერთჯერადად</t>
+          <t>ფასდაკლება მოქმედებს ოფერის გაგზავნიდან 1 კვირის განმავლობაში.</t>
         </is>
       </c>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>разово</t>
+          <t>Скидка действует 1 неделю с момента отправки предложения.</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -13810,22 +13844,22 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>pk.days</t>
+          <t>pk.once</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>working days</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
-          <t>სამუშაო დღე</t>
+          <t>ერთჯერადად</t>
         </is>
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>рабочих дней</t>
+          <t>разово</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -13852,22 +13886,22 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>pk.full</t>
+          <t>pk.days</t>
         </is>
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>Everything included</t>
+          <t>working days</t>
         </is>
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
-          <t>სრული ჩამონათვალი</t>
+          <t>სამუშაო დღე</t>
         </is>
       </c>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>Всё, что входит</t>
+          <t>рабочих дней</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -13894,22 +13928,22 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>pk.choose</t>
+          <t>pk.full</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>Choose this package</t>
+          <t>Everything included</t>
         </is>
       </c>
       <c r="E181" s="9" t="inlineStr">
         <is>
-          <t>ამ პაკეტის არჩევა</t>
+          <t>სრული ჩამონათვალი</t>
         </is>
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>Выбрать этот пакет</t>
+          <t>Всё, что входит</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -13936,22 +13970,22 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>pk.chosen</t>
+          <t>pk.choose</t>
         </is>
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Choose this package</t>
         </is>
       </c>
       <c r="E182" s="9" t="inlineStr">
         <is>
-          <t>არჩეულია</t>
+          <t>ამ პაკეტის არჩევა</t>
         </is>
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>Выбран</t>
+          <t>Выбрать этот пакет</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -13978,22 +14012,22 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>pk.note</t>
+          <t>pk.chosen</t>
         </is>
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E183" s="9" t="inlineStr">
         <is>
-          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
+          <t>არჩეულია</t>
         </is>
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
+          <t>Выбран</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -14020,22 +14054,22 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>pk.cur</t>
+          <t>pk.note</t>
         </is>
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>VAT (18%) is added. The CRM licence is paid separately, directly to the vendor.</t>
         </is>
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
-          <t>ვალუტა</t>
+          <t>ფასს ემატება დღგ (18%). CRM-ის ლიცენზიას ცალკე, პირდაპირ მწარმოებელს უხდი.</t>
         </is>
       </c>
       <c r="F184" s="9" t="inlineStr">
         <is>
-          <t>Валюта</t>
+          <t>Добавляется НДС (18%). Лицензия CRM оплачивается отдельно, напрямую производителю.</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -14057,27 +14091,27 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>ao.title</t>
+          <t>pk.cur</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>Extra features</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>დამატებითი ფუნქციები</t>
+          <t>ვალუტა</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>Дополнительные функции</t>
+          <t>Валюта</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -14104,22 +14138,22 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>ao.sub</t>
+          <t>ao.title</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>Optional. Add only if you need them</t>
+          <t>Extra features</t>
         </is>
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
+          <t>დამატებითი ფუნქციები</t>
         </is>
       </c>
       <c r="F186" s="9" t="inlineStr">
         <is>
-          <t>Необязательно. Добавьте, если нужно</t>
+          <t>Дополнительные функции</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -14146,22 +14180,22 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>ao.popular</t>
+          <t>ao.sub</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>Often added</t>
+          <t>Optional. Add only if you need them</t>
         </is>
       </c>
       <c r="E187" s="9" t="inlineStr">
         <is>
-          <t>ხშირად ამატებენ</t>
+          <t>არასავალდებულოა. დაამატე მხოლოდ საჭიროებისამებრ</t>
         </is>
       </c>
       <c r="F187" s="9" t="inlineStr">
         <is>
-          <t>Часто добавляют</t>
+          <t>Необязательно. Добавьте, если нужно</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -14188,22 +14222,22 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>ao.more</t>
+          <t>ao.popular</t>
         </is>
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>All add-ons by category</t>
+          <t>Often added</t>
         </is>
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
+          <t>ხშირად ამატებენ</t>
         </is>
       </c>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>Все дополнения по категориям</t>
+          <t>Часто добавляют</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -14230,22 +14264,22 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>ao.catalog</t>
+          <t>ao.more</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>We show the full catalog (75+ solutions) on the call.</t>
+          <t>All add-ons by category</t>
         </is>
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
+          <t>ყველა დამატებითი ფუნქცია კატეგორიების მიხედვით</t>
         </is>
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>Полный каталог (75+ решений) покажем на звонке.</t>
+          <t>Все дополнения по категориям</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -14267,27 +14301,27 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Sum</t>
+          <t>Ao</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>sum.empty</t>
+          <t>ao.catalog</t>
         </is>
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>Choose a package</t>
+          <t>We show the full catalog (75+ solutions) on the call.</t>
         </is>
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
-          <t>აირჩიე პაკეტი</t>
+          <t>სრულ კატალოგს (75+ გადაწყვეტა) ზარზე გაჩვენებთ.</t>
         </is>
       </c>
       <c r="F190" s="9" t="inlineStr">
         <is>
-          <t>Выберите пакет</t>
+          <t>Полный каталог (75+ решений) покажем на звонке.</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -14314,22 +14348,22 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>sum.addons</t>
+          <t>sum.empty</t>
         </is>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>Choose a package</t>
         </is>
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
-          <t>ფუნქცია</t>
+          <t>აირჩიე პაკეტი</t>
         </is>
       </c>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>функц.</t>
+          <t>Выберите пакет</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -14356,22 +14390,22 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>sum.vat</t>
+          <t>sum.addons</t>
         </is>
       </c>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>+ VAT</t>
+          <t>features</t>
         </is>
       </c>
       <c r="E192" s="9" t="inlineStr">
         <is>
-          <t>+ დღგ</t>
+          <t>ფუნქცია</t>
         </is>
       </c>
       <c r="F192" s="9" t="inlineStr">
         <is>
-          <t>+ НДС</t>
+          <t>функц.</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -14398,22 +14432,22 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>sum.cta</t>
+          <t>sum.vat</t>
         </is>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>Request a call</t>
+          <t>+ VAT</t>
         </is>
       </c>
       <c r="E193" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე ზარი</t>
+          <t>+ დღგ</t>
         </is>
       </c>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>Запросить звонок</t>
+          <t>+ НДС</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -14440,22 +14474,22 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>sum.picked</t>
+          <t>sum.cta</t>
         </is>
       </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>Your selection:</t>
+          <t>Request a call</t>
         </is>
       </c>
       <c r="E194" s="9" t="inlineStr">
         <is>
-          <t>შენი არჩევანი:</t>
+          <t>მოითხოვე ზარი</t>
         </is>
       </c>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>Ваш выбор:</t>
+          <t>Запросить звонок</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -14477,27 +14511,27 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Pk</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.name</t>
+          <t>sum.picked</t>
         </is>
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>Your selection:</t>
         </is>
       </c>
       <c r="E195" s="9" t="inlineStr">
         <is>
-          <t>სტარტი</t>
+          <t>შენი არჩევანი:</t>
         </is>
       </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>Старт</t>
+          <t>Ваш выбор:</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -14524,22 +14558,22 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.short</t>
+          <t>pk.starter.name</t>
         </is>
       </c>
       <c r="D196" s="9" t="inlineStr">
         <is>
-          <t>To move from Excel into a CRM</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="E196" s="9" t="inlineStr">
         <is>
-          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
+          <t>სტარტი</t>
         </is>
       </c>
       <c r="F196" s="9" t="inlineStr">
         <is>
-          <t>Чтобы перейти с Excel на CRM</t>
+          <t>Старт</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -14566,22 +14600,22 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.out</t>
+          <t>pk.starter.short</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>You move from Excel to a CRM: every client and lead in one system.</t>
+          <t>To move from Excel into a CRM</t>
         </is>
       </c>
       <c r="E197" s="9" t="inlineStr">
         <is>
-          <t>Excel-იდან CRM-ზე გადახვალ: ყველა კლიენტი და ლიდი ერთ სისტემაშია.</t>
+          <t>Excel-იდან CRM-ზე გადასასვლელად</t>
         </is>
       </c>
       <c r="F197" s="9" t="inlineStr">
         <is>
-          <t>Переходите с Excel на CRM: все клиенты и лиды в одной системе.</t>
+          <t>Чтобы перейти с Excel на CRM</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -14608,22 +14642,22 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h1</t>
+          <t>pk.starter.out</t>
         </is>
       </c>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>4 core modules</t>
+          <t>You move from Excel to a CRM: every client and lead in one system.</t>
         </is>
       </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული</t>
+          <t>Excel-იდან CRM-ზე გადახვალ: ყველა კლიენტი და ლიდი ერთ სისტემაშია.</t>
         </is>
       </c>
       <c r="F198" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля</t>
+          <t>Переходите с Excel на CRM: все клиенты и лиды в одной системе.</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -14650,22 +14684,22 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h2</t>
+          <t>pk.starter.h1</t>
         </is>
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>Email and Facebook inside the CRM</t>
+          <t>4 core modules</t>
         </is>
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტა და Facebook CRM-ში</t>
+          <t>4 ძირითადი მოდული</t>
         </is>
       </c>
       <c r="F199" s="9" t="inlineStr">
         <is>
-          <t>Почта и Facebook внутри CRM</t>
+          <t>4 базовых модуля</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -14692,22 +14726,22 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.h3</t>
+          <t>pk.starter.h2</t>
         </is>
       </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>Lead form and KPI dashboard</t>
+          <t>Email and Facebook inside the CRM</t>
         </is>
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ფორმა და KPI დაფა</t>
+          <t>ელფოსტა და Facebook CRM-ში</t>
         </is>
       </c>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>Форма лидов и дашборд KPI</t>
+          <t>Почта и Facebook внутри CRM</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -14734,22 +14768,22 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i1</t>
+          <t>pk.starter.h3</t>
         </is>
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
+          <t>Lead form and KPI dashboard</t>
         </is>
       </c>
       <c r="E201" s="9" t="inlineStr">
         <is>
-          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
+          <t>ლიდების ფორმა და KPI დაფა</t>
         </is>
       </c>
       <c r="F201" s="9" t="inlineStr">
         <is>
-          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
+          <t>Форма лидов и дашборд KPI</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -14776,22 +14810,22 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i2</t>
+          <t>pk.starter.i1</t>
         </is>
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>2-way email sync (Google or Microsoft 365)</t>
+          <t>4 core modules: Leads, Contacts, Accounts, Deals</t>
         </is>
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
+          <t>4 ძირითადი მოდული: ლიდები, კონტაქტები, კომპანიები, გარიგებები</t>
         </is>
       </c>
       <c r="F202" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
+          <t>4 базовых модуля: лиды, контакты, компании, сделки</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -14818,22 +14852,22 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i3</t>
+          <t>pk.starter.i2</t>
         </is>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>Facebook messages right inside the CRM</t>
+          <t>2-way email sync (Google or Microsoft 365)</t>
         </is>
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
+          <t>ელფოსტის ორმხრივი სინქრონიზაცია (Google ან Microsoft 365)</t>
         </is>
       </c>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>Сообщения Facebook прямо в CRM</t>
+          <t>Двусторонняя синхронизация почты (Google или Microsoft 365)</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -14860,22 +14894,22 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i4</t>
+          <t>pk.starter.i3</t>
         </is>
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>1 web form to capture leads</t>
+          <t>Facebook messages right inside the CRM</t>
         </is>
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>1 ვებფორმა ლიდების მისაღებად</t>
+          <t>Facebook-ის შეტყობინებები პირდაპირ CRM-ში</t>
         </is>
       </c>
       <c r="F204" s="9" t="inlineStr">
         <is>
-          <t>1 веб-форма для приёма лидов</t>
+          <t>Сообщения Facebook прямо в CRM</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -14902,22 +14936,22 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i5</t>
+          <t>pk.starter.i4</t>
         </is>
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>1 sales-pipeline KPI dashboard</t>
+          <t>1 web form to capture leads</t>
         </is>
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ძაბრის KPI დაფა</t>
+          <t>1 ვებფორმა ლიდების მისაღებად</t>
         </is>
       </c>
       <c r="F205" s="9" t="inlineStr">
         <is>
-          <t>Дашборд KPI воронки продаж</t>
+          <t>1 веб-форма для приёма лидов</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -14944,22 +14978,22 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>pk.starter.i6</t>
+          <t>pk.starter.i5</t>
         </is>
       </c>
       <c r="D206" s="9" t="inlineStr">
         <is>
-          <t>Recorded video instructions for the team</t>
+          <t>1 sales-pipeline KPI dashboard</t>
         </is>
       </c>
       <c r="E206" s="9" t="inlineStr">
         <is>
-          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
+          <t>გაყიდვების ძაბრის KPI დაფა</t>
         </is>
       </c>
       <c r="F206" s="9" t="inlineStr">
         <is>
-          <t>Видеоинструкции для команды</t>
+          <t>Дашборд KPI воронки продаж</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14986,22 +15020,22 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.name</t>
+          <t>pk.starter.i6</t>
         </is>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>Essentials</t>
+          <t>Recorded video instructions for the team</t>
         </is>
       </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალური</t>
+          <t>ჩაწერილი ვიდეო ინსტრუქციები გუნდისთვის</t>
         </is>
       </c>
       <c r="F207" s="9" t="inlineStr">
         <is>
-          <t>Оптимальный</t>
+          <t>Видеоинструкции для команды</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -15028,22 +15062,22 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.short</t>
+          <t>pk.essentials.name</t>
         </is>
       </c>
       <c r="D208" s="9" t="inlineStr">
         <is>
-          <t>For a 5-10 person sales team</t>
+          <t>Essentials</t>
         </is>
       </c>
       <c r="E208" s="9" t="inlineStr">
         <is>
-          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
+          <t>ოპტიმალური</t>
         </is>
       </c>
       <c r="F208" s="9" t="inlineStr">
         <is>
-          <t>Для отдела продаж из 5-10 человек</t>
+          <t>Оптимальный</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -15070,22 +15104,22 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.base</t>
+          <t>pk.essentials.short</t>
         </is>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter, plus:</t>
+          <t>For a 5-10 person sales team</t>
         </is>
       </c>
       <c r="E209" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
+          <t>5-10-წევრიანი გაყიდვების გუნდისთვის</t>
         </is>
       </c>
       <c r="F209" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта», плюс:</t>
+          <t>Для отдела продаж из 5-10 человек</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -15112,22 +15146,22 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.out</t>
+          <t>pk.essentials.base</t>
         </is>
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>Sales in order: leads come in automatically and go to the right people.</t>
+          <t>Everything in Starter, plus:</t>
         </is>
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>მოწესრიგებული გაყიდვები: ლიდები ავტომატურად შემოდის და გუნდზე სწორად ნაწილდება.</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
-          <t>Продажи в порядке: лиды приходят автоматически и правильно распределяются по команде.</t>
+          <t>Всё из «Старта», плюс:</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -15154,22 +15188,22 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h1</t>
+          <t>pk.essentials.out</t>
         </is>
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>Everything in Starter</t>
+          <t>Sales in order: leads come in automatically and go to the right people.</t>
         </is>
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
+          <t>მოწესრიგებული გაყიდვები: ლიდები ავტომატურად შემოდის და გუნდზე სწორად ნაწილდება.</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Старта»</t>
+          <t>Продажи в порядке: лиды приходят автоматически и правильно распределяются по команде.</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -15196,22 +15230,22 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h2</t>
+          <t>pk.essentials.h1</t>
         </is>
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads, automatically</t>
+          <t>Everything in Starter</t>
         </is>
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
+          <t>სტარტ პაკეტის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически</t>
+          <t>Всё из «Старта»</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -15238,22 +15272,22 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.h3</t>
+          <t>pk.essentials.h2</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>Stage rules and lead assignment</t>
+          <t>Meta and Google Ads leads, automatically</t>
         </is>
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
+          <t>Meta და Google Ads-ის ლიდები ავტომატურად</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>Правила этапов и распределение лидов</t>
+          <t>Лиды из Meta и Google Ads автоматически</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -15280,22 +15314,22 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i1</t>
+          <t>pk.essentials.h3</t>
         </is>
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>Up to 15 custom fields</t>
+          <t>Stage rules and lead assignment</t>
         </is>
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>15-მდე დამატებითი ველი</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით და ლიდების განაწილება</t>
         </is>
       </c>
       <c r="F214" s="9" t="inlineStr">
         <is>
-          <t>До 15 дополнительных полей</t>
+          <t>Правила этапов и распределение лидов</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -15322,22 +15356,22 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i2</t>
+          <t>pk.essentials.i1</t>
         </is>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>Products and invoices, with your invoice template</t>
+          <t>Up to 15 custom fields</t>
         </is>
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
+          <t>15-მდე დამატებითი ველი</t>
         </is>
       </c>
       <c r="F215" s="9" t="inlineStr">
         <is>
-          <t>Товары и счета с вашим шаблоном счёта</t>
+          <t>До 15 дополнительных полей</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -15364,22 +15398,22 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i3</t>
+          <t>pk.essentials.i2</t>
         </is>
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
-          <t>Sales stages with rules: no skipped steps</t>
+          <t>Products and invoices, with your invoice template</t>
         </is>
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
+          <t>პროდუქტები და ინვოისები, შენი ინვოისის შაბლონით</t>
         </is>
       </c>
       <c r="F216" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами: этап не пропустить</t>
+          <t>Товары и счета с вашим шаблоном счёта</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -15406,22 +15440,22 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i4</t>
+          <t>pk.essentials.i3</t>
         </is>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>Phone validation (+995) and deduplication</t>
+          <t>Sales stages with rules: no skipped steps</t>
         </is>
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>გაყიდვის ეტაპები მკაფიო წესებით: ეტაპს ვერ გამოტოვებ</t>
         </is>
       </c>
       <c r="F217" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и удаление дублей</t>
+          <t>Этапы продаж с правилами: этап не пропустить</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -15448,22 +15482,22 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i5</t>
+          <t>pk.essentials.i4</t>
         </is>
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>Meta and Google Ads leads synced automatically</t>
+          <t>Phone validation (+995) and deduplication</t>
         </is>
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
-          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F218" s="9" t="inlineStr">
         <is>
-          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
+          <t>Проверка номеров (+995) и удаление дублей</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -15490,22 +15524,22 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i6</t>
+          <t>pk.essentials.i5</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>Automatic lead assignment across managers</t>
+          <t>Meta and Google Ads leads synced automatically</t>
         </is>
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
+          <t>Meta-სა და Google Ads-ის ლიდები ავტომატურად CRM-ში</t>
         </is>
       </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>Автоматическое распределение лидов по менеджерам</t>
+          <t>Лиды из Meta и Google Ads автоматически в CRM</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -15532,22 +15566,22 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i7</t>
+          <t>pk.essentials.i6</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders</t>
+          <t>Automatic lead assignment across managers</t>
         </is>
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები</t>
+          <t>ლიდების ავტომატური განაწილება მენეჯერებზე</t>
         </is>
       </c>
       <c r="F220" s="9" t="inlineStr">
         <is>
-          <t>Напоминания о follow-up</t>
+          <t>Автоматическое распределение лидов по менеджерам</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15574,22 +15608,22 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i8</t>
+          <t>pk.essentials.i7</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>Contacts and products migration</t>
+          <t>Follow-up reminders</t>
         </is>
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
+          <t>follow-up შეხსენებები</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>Перенос контактов и товаров</t>
+          <t>Напоминания о follow-up</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15616,22 +15650,22 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>pk.essentials.i9</t>
+          <t>pk.essentials.i8</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>30-minute training, recorded</t>
+          <t>Contacts and products migration</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>კონტაქტებისა და პროდუქტების გადმოტანა</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
         <is>
-          <t>30-минутное обучение с записью</t>
+          <t>Перенос контактов и товаров</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -15658,22 +15692,22 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.name</t>
+          <t>pk.essentials.i9</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>30-minute training, recorded</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>ზრდა</t>
+          <t>30-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>Рост</t>
+          <t>30-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -15700,22 +15734,22 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.short</t>
+          <t>pk.growth.name</t>
         </is>
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>For a growing 15-25 person team</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
+          <t>ზრდა</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>Для растущей команды из 15-25 человек</t>
+          <t>Рост</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15742,22 +15776,22 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.base</t>
+          <t>pk.growth.short</t>
         </is>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials, plus:</t>
+          <t>For a growing 15-25 person team</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
+          <t>15-25-წევრიანი მზარდი გუნდისთვის</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального», плюс:</t>
+          <t>Для растущей команды из 15-25 человек</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -15784,22 +15818,22 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.out</t>
+          <t>pk.growth.base</t>
         </is>
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>A complete sales system: calls, automations and AI in one place.</t>
+          <t>Everything in Essentials, plus:</t>
         </is>
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების სრული სისტემა: ზარები, ავტომატიზაციები და AI ერთ სივრცეში.</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი, პლუს:</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>Полная система продаж: звонки, автоматизации и AI в одном месте.</t>
+          <t>Всё из «Оптимального», плюс:</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15826,22 +15860,22 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h1</t>
+          <t>pk.growth.out</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>Everything in Essentials</t>
+          <t>A complete sales system: calls, automations and AI in one place.</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>ოპტიმალურის სრული ფუნქციონალი</t>
+          <t>გაყიდვების სრული სისტემა: ზარები, ავტომატიზაციები და AI ერთ სივრცეში.</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>Всё из «Оптимального»</t>
+          <t>Полная система продаж: звонки, автоматизации и AI в одном месте.</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -15868,22 +15902,22 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h2</t>
+          <t>pk.growth.h1</t>
         </is>
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>Telephony and call processing</t>
+          <t>Everything in Essentials</t>
         </is>
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია და ზარების დამუშავება</t>
+          <t>ოპტიმალურის სრული ფუნქციონალი</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>Телефония и обработка звонков</t>
+          <t>Всё из «Оптимального»</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -15910,22 +15944,22 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.h3</t>
+          <t>pk.growth.h2</t>
         </is>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>Automations and AI (Claude)</t>
+          <t>Telephony and call processing</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>ავტომატიზაციები და AI (Claude)</t>
+          <t>ტელეფონია და ზარების დამუშავება</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>Автоматизации и AI (Claude)</t>
+          <t>Телефония и обработка звонков</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -15952,22 +15986,22 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i1</t>
+          <t>pk.growth.h3</t>
         </is>
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 additional modules</t>
+          <t>Automations and AI (Claude)</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>3-მდე დამატებითი მოდული</t>
+          <t>ავტომატიზაციები და AI (Claude)</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>До 3 дополнительных модулей</t>
+          <t>Автоматизации и AI (Claude)</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15994,22 +16028,22 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i2</t>
+          <t>pk.growth.i1</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>Up to 5 no-code automations</t>
+          <t>Up to 3 additional modules</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>5-მდე ავტომატიზაცია</t>
+          <t>3-მდე დამატებითი მოდული</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>До 5 автоматизаций</t>
+          <t>До 3 дополнительных модулей</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -16036,22 +16070,22 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i3</t>
+          <t>pk.growth.i2</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>Up to 3 automations with custom functions</t>
+          <t>Up to 5 no-code automations</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
+          <t>5-მდე ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>До 3 автоматизаций с custom-функциями</t>
+          <t>До 5 автоматизаций</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -16078,22 +16112,22 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i4</t>
+          <t>pk.growth.i3</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Telephony: GEONET or another cloud PBX</t>
+          <t>Up to 3 automations with custom functions</t>
         </is>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
+          <t>3-მდე ავტომატიზაცია custom ფუნქციებით</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>Телефония: GEONET или другая облачная АТС</t>
+          <t>До 3 автоматизаций с custom-функциями</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -16120,22 +16154,22 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i5</t>
+          <t>pk.growth.i4</t>
         </is>
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>Call processing workflow in the CRM</t>
+          <t>Telephony: GEONET or another cloud PBX</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>ზარების დამუშავება CRM-ში</t>
+          <t>ტელეფონია: GEONET ან სხვა cloud PBX</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>Обработка звонков в CRM</t>
+          <t>Телефония: GEONET или другая облачная АТС</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -16162,22 +16196,22 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i6</t>
+          <t>pk.growth.i5</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>Website form + secure webhook</t>
+          <t>Call processing workflow in the CRM</t>
         </is>
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + დაცული webhook</t>
+          <t>ზარების დამუშავება CRM-ში</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + защищённый webhook</t>
+          <t>Обработка звонков в CRM</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -16204,22 +16238,22 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i7</t>
+          <t>pk.growth.i6</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>Up to 10 reports</t>
+          <t>Website form + secure webhook</t>
         </is>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>10-მდე რეპორტი</t>
+          <t>საიტის ფორმა + დაცული webhook</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
         <is>
-          <t>До 10 отчётов</t>
+          <t>Форма сайта + защищённый webhook</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -16246,22 +16280,22 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i8</t>
+          <t>pk.growth.i7</t>
         </is>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude connected to your CRM</t>
+          <t>Up to 10 reports</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
+          <t>10-მდე რეპორტი</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>AI: Claude, подключённый к вашей CRM</t>
+          <t>До 10 отчётов</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16288,22 +16322,22 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>pk.growth.i9</t>
+          <t>pk.growth.i8</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>60-minute training, recorded</t>
+          <t>AI: Claude connected to your CRM</t>
         </is>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
+          <t>AI: Claude დაკავშირებული შენს CRM-თან</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr">
         <is>
-          <t>60-минутное обучение с записью</t>
+          <t>AI: Claude, подключённый к вашей CRM</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16325,27 +16359,27 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Ao</t>
+          <t>Pk</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>ao.4</t>
+          <t>pk.growth.i9</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Automated lead routing (round-robin)</t>
+          <t>60-minute training, recorded</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
+          <t>60-წუთიანი ტრენინგი (ჩანაწერით)</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>Автораспределение лидов (round-robin)</t>
+          <t>60-минутное обучение с записью</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -16372,22 +16406,22 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>ao.5</t>
+          <t>ao.4</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>Enforced sales stage blueprint</t>
+          <t>Automated lead routing (round-robin)</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
+          <t>ლიდების ავტომატური განაწილება (round-robin)</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>Этапы продаж с правилами (Blueprint)</t>
+          <t>Автораспределение лидов (round-robin)</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16414,22 +16448,22 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>ao.10</t>
+          <t>ao.5</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>Cloud telephony integration (GEONET)</t>
+          <t>Enforced sales stage blueprint</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
+          <t>გაყიდვის ეტაპები წესებით (Blueprint)</t>
         </is>
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Интеграция телефонии (GEONET)</t>
+          <t>Этапы продаж с правилами (Blueprint)</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16456,22 +16490,22 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>ao.11</t>
+          <t>ao.10</t>
         </is>
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business integration</t>
+          <t>Cloud telephony integration (GEONET)</t>
         </is>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business-ის ინტეგრაცია</t>
+          <t>ტელეფონიის ინტეგრაცია (GEONET)</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>Интеграция WhatsApp Business</t>
+          <t>Интеграция телефонии (GEONET)</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16498,22 +16532,22 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>ao.18</t>
+          <t>ao.11</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG bank wire deposit matching</t>
+          <t>WhatsApp Business integration</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
+          <t>WhatsApp Business-ის ინტეგრაცია</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>Автосверка переводов TBC/BOG</t>
+          <t>Интеграция WhatsApp Business</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -16540,22 +16574,22 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>ao.30</t>
+          <t>ao.18</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>Autonomous web chat assistant (Unitty AI)</t>
+          <t>TBC/BOG bank wire deposit matching</t>
         </is>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
+          <t>TBC/BOG გადარიცხვების ავტომატური შეჯერება</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>AI чат-ассистент на сайте (Unitty AI)</t>
+          <t>Автосверка переводов TBC/BOG</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -16582,22 +16616,22 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>ao.38</t>
+          <t>ao.30</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
+          <t>Autonomous web chat assistant (Unitty AI)</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
+          <t>AI ჩატ-ასისტენტი საიტზე (Unitty AI)</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
+          <t>AI чат-ассистент на сайте (Unitty AI)</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16624,22 +16658,22 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.data</t>
+          <t>ao.38</t>
         </is>
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>Data foundation</t>
+          <t>Enterprise ERP sync (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>მონაცემები</t>
+          <t>ERP სინქრონიზაცია (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>Данные</t>
+          <t>Синхронизация с ERP (1C / FINA / SAP)</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -16666,22 +16700,22 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>ao.1</t>
+          <t>ao.cat.data</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Georgian phone validation &amp; deduplication (+995)</t>
+          <t>Data foundation</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
+          <t>მონაცემები</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Проверка номеров (+995) и дубли</t>
+          <t>Данные</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16708,22 +16742,22 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>ao.2</t>
+          <t>ao.1</t>
         </is>
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreadsheet → CRM migration</t>
+          <t>Georgian phone validation &amp; deduplication (+995)</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
+          <t>ტელეფონის ნომრების ვალიდაცია (+995) და დუბლიკატების გასუფთავება</t>
         </is>
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблиц Excel в CRM</t>
+          <t>Проверка номеров (+995) и дубли</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -16750,22 +16784,22 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>ao.3</t>
+          <t>ao.2</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Property stock database migration</t>
+          <t>Legacy spreadsheet → CRM migration</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
+          <t>Excel-ის ცხრილების გადმოტანა CRM-ში</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>Перенос базы объектов недвижимости</t>
+          <t>Перенос таблиц Excel в CRM</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -16792,22 +16826,22 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.sales</t>
+          <t>ao.3</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>Sales automation</t>
+          <t>Property stock database migration</t>
         </is>
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>გაყიდვების ავტომატიზაცია</t>
+          <t>უძრავი ქონების / ობიექტების ბაზის მიგრაცია</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>Автоматизация продаж</t>
+          <t>Перенос базы объектов недвижимости</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16834,22 +16868,22 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>ao.6</t>
+          <t>ao.cat.sales</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Follow-up reminders &amp; alerts</t>
+          <t>Sales automation</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>follow-up შეხსენებები და შეტყობინებები</t>
+          <t>გაყიდვების ავტომატიზაცია</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>Напоминания и уведомления о follow-up</t>
+          <t>Автоматизация продаж</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -16876,22 +16910,22 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>ao.7</t>
+          <t>ao.6</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>One-click agreement PDF generator</t>
+          <t>Follow-up reminders &amp; alerts</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
+          <t>follow-up შეხსენებები და შეტყობინებები</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>PDF договора в один клик</t>
+          <t>Напоминания и уведомления о follow-up</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -16918,22 +16952,22 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>ao.8</t>
+          <t>ao.7</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>First-response SLA tracker</t>
+          <t>One-click agreement PDF generator</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
+          <t>ხელშეკრულების PDF ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>Контроль времени первого ответа (SLA)</t>
+          <t>PDF договора в один клик</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -16960,22 +16994,22 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>ao.9</t>
+          <t>ao.8</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Broker commission tracking</t>
+          <t>First-response SLA tracker</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>ბროკერების საკომისიოების აღრიცხვა</t>
+          <t>პირველი პასუხის დროის (SLA) კონტროლი</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Учёт комиссий брокеров</t>
+          <t>Контроль времени первого ответа (SLA)</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -17002,22 +17036,22 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.comms</t>
+          <t>ao.9</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Broker commission tracking</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>კომუნიკაცია</t>
+          <t>ბროკერების საკომისიოების აღრიცხვა</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>Коммуникации</t>
+          <t>Учёт комиссий брокеров</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -17044,22 +17078,22 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>ao.12</t>
+          <t>ao.cat.comms</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>Email + calendar 2-way sync</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
+          <t>კომუნიკაცია</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>Двусторонняя синхронизация почты и календаря</t>
+          <t>Коммуникации</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -17086,22 +17120,22 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>ao.13</t>
+          <t>ao.12</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>Missed-call recovery &amp; SMS callback</t>
+          <t>Email + calendar 2-way sync</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
+          <t>ელფოსტისა და კალენდრის ორმხრივი სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>Возврат пропущенных звонков и SMS</t>
+          <t>Двусторонняя синхронизация почты и календаря</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -17128,22 +17162,22 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>ao.14</t>
+          <t>ao.13</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Messaging bot lead capture webhook</t>
+          <t>Missed-call recovery &amp; SMS callback</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
+          <t>გამოტოვებული ზარების დამუშავება და ავტომატური SMS</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>Лиды из чат-бота сразу в CRM</t>
+          <t>Возврат пропущенных звонков и SMS</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -17170,22 +17204,22 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.mkt</t>
+          <t>ao.14</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Marketing &amp; growth</t>
+          <t>Messaging bot lead capture webhook</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>მარკეტინგი</t>
+          <t>ჩატბოტის ლიდების პირდაპირი ინტეგრაცია CRM-ში</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Лиды из чат-бота сразу в CRM</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -17212,22 +17246,22 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>ao.15</t>
+          <t>ao.cat.mkt</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Website lead form + webhook</t>
+          <t>Marketing &amp; growth</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>საიტის ფორმა + webhook</t>
+          <t>მარკეტინგი</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Форма сайта + webhook</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17254,22 +17288,22 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>ao.16</t>
+          <t>ao.15</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Lead source ROI &amp; campaign attribution</t>
+          <t>Website lead form + webhook</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
+          <t>საიტის ფორმა + webhook</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>ROI источников и атрибуция кампаний</t>
+          <t>Форма сайта + webhook</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -17296,22 +17330,22 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>ao.17</t>
+          <t>ao.16</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Email campaigns: account setup &amp; contact sync</t>
+          <t>Lead source ROI &amp; campaign attribution</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
+          <t>ლიდების წყაროების ROI და კამპანიების ატრიბუცია</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>Email-рассылки: настройка и синхронизация контактов</t>
+          <t>ROI источников и атрибуция кампаний</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -17338,22 +17372,22 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.fin</t>
+          <t>ao.17</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Fintech &amp; accounting</t>
+          <t>Email campaigns: account setup &amp; contact sync</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>ფინანსები და ბანკები</t>
+          <t>იმეილ კამპანიები: ანგარიშის გამართვა და კონტაქტების სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>Финансы и банки</t>
+          <t>Email-рассылки: настройка и синхронизация контактов</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -17380,22 +17414,22 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>ao.19</t>
+          <t>ao.cat.fin</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
+          <t>Fintech &amp; accounting</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
+          <t>ფინანსები და ბანკები</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
+          <t>Финансы и банки</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -17422,22 +17456,22 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>ao.20</t>
+          <t>ao.19</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>NBG daily exchange rate sync</t>
+          <t>Multi-currency reconciliation (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
+          <t>მრავალვალუტიანი ავტომატური შეჯერება (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Ежедневный курс НБГ</t>
+          <t>Мультивалютная сверка (GEL/USD/EUR)</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -17464,22 +17498,22 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>ao.21</t>
+          <t>ao.20</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Ambiguous payment reference fallback queue</t>
+          <t>NBG daily exchange rate sync</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
+          <t>ეროვნული ბანკის (NBG) კურსის ყოველდღიური სინქრონიზაცია</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Очередь неопознанных платежей</t>
+          <t>Ежедневный курс НБГ</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17506,22 +17540,22 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>ao.22</t>
+          <t>ao.21</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Dynamic installment payment schedule</t>
+          <t>Ambiguous payment reference fallback queue</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>შიდა განვადების დინამიკური გრაფიკი</t>
+          <t>დაუზუსტებელი გადარიცხვების დამუშავების რიგი</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>График рассрочки</t>
+          <t>Очередь неопознанных платежей</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -17548,22 +17582,22 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>ao.23</t>
+          <t>ao.22</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Overdue debt alert &amp; SMS warning</t>
+          <t>Dynamic installment payment schedule</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
+          <t>შიდა განვადების დინამიკური გრაფიკი</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>SMS о просроченной задолженности</t>
+          <t>График рассрочки</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -17590,22 +17624,22 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>ao.24</t>
+          <t>ao.23</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>SMS gateway &amp; OTP verification</t>
+          <t>Overdue debt alert &amp; SMS warning</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
+          <t>ვადაგადაცილებული დავალიანების SMS შეხსენება</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>SMS-шлюз и OTP-верификация</t>
+          <t>SMS о просроченной задолженности</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -17632,22 +17666,22 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.cx</t>
+          <t>ao.24</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Customer experience</t>
+          <t>SMS gateway &amp; OTP verification</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>მომხმარებლის მომსახურება</t>
+          <t>SMS გეითვეი და OTP ვერიფიკაცია</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>Клиентский сервис</t>
+          <t>SMS-шлюз и OTP-верификация</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -17674,22 +17708,22 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>ao.25</t>
+          <t>ao.cat.cx</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Omnichannel support ticketing (Zoho Desk)</t>
+          <t>Customer experience</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
+          <t>მომხმარებლის მომსახურება</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>Омниканальные тикеты (Zoho Desk)</t>
+          <t>Клиентский сервис</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -17716,22 +17750,22 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>ao.26</t>
+          <t>ao.25</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Multi-tier SLA escalation matrix</t>
+          <t>Omnichannel support ticketing (Zoho Desk)</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
+          <t>ომნიარხული (Omnichannel) მხარდაჭერის ტიკეტები (Zoho Desk)</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>Матрица эскалации SLA</t>
+          <t>Омниканальные тикеты (Zoho Desk)</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -17758,22 +17792,22 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>ao.27</t>
+          <t>ao.26</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Post-ticket NPS/CSAT feedback loop</t>
+          <t>Multi-tier SLA escalation matrix</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
+          <t>მრავალდონიანი SLA-ს ესკალაციის მატრიცა</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>Оценка NPS/CSAT после тикета</t>
+          <t>Матрица эскалации SLA</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -17800,22 +17834,22 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>ao.28</t>
+          <t>ao.27</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Dynamic KYC intake smart form</t>
+          <t>Post-ticket NPS/CSAT feedback loop</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
+          <t>NPS/CSAT კმაყოფილების შეფასება ტიკეტის დახურვის შემდეგ</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Умная KYC-форма</t>
+          <t>Оценка NPS/CSAT после тикета</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -17842,22 +17876,22 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>ao.29</t>
+          <t>ao.28</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Warranty expiration alerts</t>
+          <t>Dynamic KYC intake smart form</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>გარანტიის ვადის შეხსენებები</t>
+          <t>KYC-ის დინამიკური ჭკვიანი ფორმა</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Напоминания об окончании гарантии</t>
+          <t>Умная KYC-форма</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -17884,22 +17918,22 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ai</t>
+          <t>ao.29</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>AI &amp; automation</t>
+          <t>Warranty expiration alerts</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>გარანტიის ვადის შეხსენებები</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Напоминания об окончании гарантии</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -17926,22 +17960,22 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>ao.31</t>
+          <t>ao.cat.ai</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Georgian voice meeting transcription</t>
+          <t>AI &amp; automation</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>Транскрипция встреч на грузинском</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -17968,22 +18002,22 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>ao.32</t>
+          <t>ao.31</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Audio call sentiment extractor</t>
+          <t>Georgian voice meeting transcription</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
+          <t>ქართული შეხვედრების ტრანსკრიფცია</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>Анализ тональности звонков</t>
+          <t>Транскрипция встреч на грузинском</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -18010,22 +18044,22 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ind</t>
+          <t>ao.32</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Industry solutions</t>
+          <t>Audio call sentiment extractor</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>დარგობრივი</t>
+          <t>სატელეფონო ზარის ემოციური განწყობის (Sentiment) ანალიზი</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Отраслевые</t>
+          <t>Анализ тональности звонков</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -18052,22 +18086,22 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>ao.33</t>
+          <t>ao.cat.ind</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Real estate unit inventory &amp; anti-double-booking</t>
+          <t>Industry solutions</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
+          <t>დარგობრივი</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Недвижимость: учёт квартир без двойной брони</t>
+          <t>Отраслевые</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -18094,22 +18128,22 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>ao.34</t>
+          <t>ao.33</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Client preference proactive matcher</t>
+          <t>Real estate unit inventory &amp; anti-double-booking</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
+          <t>უძრავი ქონება: ბინების ინვენტარიზაცია ორმაგი ჯავშნების პრევენციით</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Автоподбор по пожеланиям клиента</t>
+          <t>Недвижимость: учёт квартир без двойной брони</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -18136,22 +18170,22 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>ao.35</t>
+          <t>ao.34</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Reservation expiration timer</t>
+          <t>Client preference proactive matcher</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
+          <t>კლიენტის მოთხოვნებთან ობიექტების ავტომატური შეთავსება (Matching)</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Таймер истечения брони</t>
+          <t>Автоподбор по пожеланиям клиента</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -18178,22 +18212,22 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>ao.36</t>
+          <t>ao.35</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Floor plan &amp; proposal PDF generator</t>
+          <t>Reservation expiration timer</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
+          <t>ჯავშნის ვადის ავტომატური ტაიმერი</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>PDF планировки и предложения</t>
+          <t>Таймер истечения брони</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -18220,22 +18254,22 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>ao.37</t>
+          <t>ao.36</t>
         </is>
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Field service visit tracking + approval</t>
+          <t>Floor plan &amp; proposal PDF generator</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>საველე ვიზიტების მართვა და დადასტურება</t>
+          <t>გეგმარებისა და შეთავაზების PDF-ის გენერირება ერთი დაჭერით</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>Учёт выездов и подтверждение</t>
+          <t>PDF планировки и предложения</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -18262,22 +18296,22 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>ao.cat.ops</t>
+          <t>ao.37</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Operations &amp; ERP</t>
+          <t>Field service visit tracking + approval</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>ოპერაციები და ERP</t>
+          <t>საველე ვიზიტების მართვა და დადასტურება</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Операции и ERP</t>
+          <t>Учёт выездов и подтверждение</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -18304,22 +18338,22 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>ao.39</t>
+          <t>ao.cat.ops</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Cold storage WMS &amp; automated billing</t>
+          <t>Operations &amp; ERP</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
+          <t>ოპერაციები და ERP</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>WMS холодного склада и биллинг</t>
+          <t>Операции и ERP</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -18346,22 +18380,22 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>ao.40</t>
+          <t>ao.39</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Construction operations &amp; budget tracker</t>
+          <t>Cold storage WMS &amp; automated billing</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
+          <t>სამაცივრე საწყობის WMS სისტემა და ავტომატური ბილინგი</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Стройка: операции и бюджет</t>
+          <t>WMS холодного склада и биллинг</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -18388,22 +18422,22 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>ao.41</t>
+          <t>ao.40</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Predictive debtor call queue</t>
+          <t>Construction operations &amp; budget tracker</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
+          <t>სამშენებლო ოპერაციებისა და ბიუჯეტის მართვა</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Умная очередь звонков должникам</t>
+          <t>Стройка: операции и бюджет</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -18430,22 +18464,22 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>ao.42</t>
+          <t>ao.41</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Agent attendance tracker</t>
+          <t>Predictive debtor call queue</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
+          <t>მოვალეებთან დაკავშირების ჭკვიანი რიგი (Predictive Queue)</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Учёт посещаемости агентов</t>
+          <t>Умная очередь звонков должникам</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -18472,22 +18506,22 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>ao.43</t>
+          <t>ao.42</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Round-robin appointment balancing</t>
+          <t>Agent attendance tracker</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+          <t>აგენტების/თანამშრომლების დასწრების აღრიცხვა</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>Равномерное распределение встреч</t>
+          <t>Учёт посещаемости агентов</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -18514,39 +18548,81 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
+          <t>ao.43</t>
+        </is>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
+        <is>
+          <t>Round-robin appointment balancing</t>
+        </is>
+      </c>
+      <c r="E291" s="9" t="inlineStr">
+        <is>
+          <t>შეხვედრების თანაბარი როტაციული განაწილება (Round-robin)</t>
+        </is>
+      </c>
+      <c r="F291" s="9" t="inlineStr">
+        <is>
+          <t>Равномерное распределение встреч</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>Ao</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
           <t>ao.44</t>
         </is>
       </c>
-      <c r="D291" s="9" t="inlineStr">
+      <c r="D292" s="9" t="inlineStr">
         <is>
           <t>Discovery call auto-scheduling</t>
         </is>
       </c>
-      <c r="E291" s="9" t="inlineStr">
+      <c r="E292" s="9" t="inlineStr">
         <is>
           <t>Discovery ზარის ავტომატური დაჯავშნა</t>
         </is>
       </c>
-      <c r="F291" s="9" t="inlineStr">
+      <c r="F292" s="9" t="inlineStr">
         <is>
           <t>Автозапись на discovery-звонок</t>
         </is>
       </c>
-      <c r="G291" s="3" t="inlineStr">
+      <c r="G292" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H291" s="3" t="inlineStr">
+      <c r="H292" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H291"/>
+  <autoFilter ref="A1:H292"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H490" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H491" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18560,7 +18636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H284"/>
+  <dimension ref="A1:H285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -19031,17 +19107,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -22459,17 +22535,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -23527,17 +23603,17 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>დარეკვა</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Позвонить</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr"/>
@@ -23793,17 +23869,17 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr"/>
@@ -26457,17 +26533,17 @@
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr"/>
@@ -29483,10 +29559,48 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>Nav</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>nav.cta</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>Free call</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>უფასო ზარი</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>Бесплатный звонок</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr"/>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H284"/>
+  <autoFilter ref="A1:H285"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H483" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H484" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29500,7 +29614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -29971,17 +30085,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -33399,17 +33513,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -34411,17 +34525,17 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>დარეკვა</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Позвонить</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr"/>
@@ -35817,17 +35931,17 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr"/>
@@ -35879,10 +35993,48 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Nav</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>nav.cta</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Free call</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>უფასო ზარი</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>Бесплатный звонок</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr"/>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H166"/>
+  <autoFilter ref="A1:H167"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H365" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H366" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -35896,7 +36048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.630000000000001" customWidth="1" style="6" min="2" max="2"/>
@@ -36208,7 +36360,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>კვლევას და ძიებას</t>
+          <t>კვლევას</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -36363,17 +36515,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -39783,17 +39935,17 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr"/>
@@ -40779,17 +40931,17 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>დარეკვა</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Позвонить</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr"/>
@@ -42185,17 +42337,17 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Request a free 20-minute call</t>
+          <t>Request a free call</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>მოითხოვე 20-წუთიანი უფასო ზარი</t>
+          <t>მოითხოვე უფასო ზარი</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Запросить бесплатный 20-минутный звонок</t>
+          <t>Запросить бесплатный звонок</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr"/>
@@ -42255,34 +42407,30 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Nav</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>prod.title</t>
-        </is>
-      </c>
-      <c r="D167" s="9" t="inlineStr">
-        <is>
-          <t>Our own products</t>
-        </is>
-      </c>
-      <c r="E167" s="9" t="inlineStr">
-        <is>
-          <t>ჩვენი პროდუქტები</t>
-        </is>
-      </c>
-      <c r="F167" s="9" t="inlineStr">
-        <is>
-          <t>Наши продукты</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>Only on this landing</t>
-        </is>
-      </c>
+          <t>nav.cta</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Free call</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>უფასო ზარი</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>Бесплатный звонок</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr"/>
       <c r="H167" s="3" t="inlineStr">
         <is>
           <t>New</t>
@@ -42302,22 +42450,22 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>prod.sub</t>
+          <t>prod.title</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
+          <t>Our own products</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
+          <t>ჩვენი პროდუქტები</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
+          <t>Наши продукты</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -42344,22 +42492,22 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>prod.cta</t>
+          <t>prod.sub</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Request →</t>
+          <t>Ready-made services we built ourselves, quick to plug into your system.</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>მოითხოვე →</t>
+          <t>ჩვენ მიერ შექმნილი მზა გადაწყვეტები, რომლებიც სწრაფად და მარტივად ინტეგრირდება შენს სისტემაში.</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Запросить →</t>
+          <t>Готовые сервисы, которые мы создали сами и быстро подключаем к вашей системе.</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -42386,22 +42534,22 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>prod.1.desc</t>
+          <t>prod.cta</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
+          <t>Request →</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
+          <t>მოითხოვე →</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
+          <t>Запросить →</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -42428,22 +42576,22 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>prod.2.desc</t>
+          <t>prod.1.desc</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
+          <t>Bank transactions (TBC, Bank of Georgia) flow into your CRM automatically - with payment matching and in-house installment schedules.</t>
         </is>
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
+          <t>საბანკო ტრანზაქციები (TBC, საქართველოს ბანკი) ავტომატურად ისახება CRM-ში — გადახდების შეჯერებითა და შიდა განვადების გრაფიკით.</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
+          <t>Транзакции банков (TBC, Банк Грузии) автоматически попадают в CRM - с привязкой платежей и графиком внутренней рассрочки.</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -42470,22 +42618,22 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>prod.3.desc</t>
+          <t>prod.2.desc</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
+          <t>An AI chat assistant on your website: answers questions 24/7 and writes leads straight into your CRM.</t>
         </is>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
+          <t>AI ჩატ-ასისტენტი შენს საიტზე: 24/7 პასუხობს შეკითხვებს და ლიდებს პირდაპირ CRM-ში აღრიცხავს.</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
+          <t>AI-чат-ассистент на вашем сайте: отвечает на вопросы 24/7 и записывает лиды прямо в CRM.</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -42512,22 +42660,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>prod.4.desc</t>
+          <t>prod.3.desc</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
+          <t>Transcription of Georgian-language meetings, a short summary and next steps - automatically.</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
+          <t>ქართულენოვანი შეხვედრების ტრანსკრიფცია, მოკლე შეჯამება და სამოქმედო ნაბიჯები — სრულად ავტომატურად.</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
+          <t>Расшифровка встреч на грузинском, краткое резюме и следующие шаги - автоматически.</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -42554,22 +42702,22 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>prod.5.desc</t>
+          <t>prod.4.desc</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
+          <t>Claude connected to your data: ask in plain language and get answers in numbers.</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
+          <t>Claude დაკავშირებული შენს მონაცემებთან: დასვი კითხვა მარტივ ენაზე და მიიღე ზუსტი პასუხები ციფრებში.</t>
         </is>
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
+          <t>Claude, подключённый к вашим данным: спрашивайте обычным языком и получайте ответы в цифрах.</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -42596,22 +42744,22 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>prod.6.desc</t>
+          <t>prod.5.desc</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
+          <t>Calls, recordings and click-to-call right inside your CRM - with routing to the right manager.</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
+          <t>ზარები, აუდიოჩანაწერები და click-to-call პირდაპირ CRM-ში — ზარის შესაბამის მენეჯერზე ჭკვიანი გადამისამართებით.</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
+          <t>Звонки, записи и click-to-call прямо в CRM - с маршрутизацией на нужного менеджера.</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -42638,22 +42786,22 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>prod.7.desc</t>
+          <t>prod.6.desc</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
+          <t>Every new lead is processed automatically: contact created, duplicates found, owner assigned.</t>
         </is>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
+          <t>ყოველი ახალი ლიდი მუშავდება ავტომატურად: კონტაქტის შექმნა, დუბლიკატების პრევენცია და პასუხისმგებელი მენეჯერის მინიჭება.</t>
         </is>
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
+          <t>Каждый новый лид обрабатывается автоматически: создание контакта, поиск дублей, назначение менеджера.</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -42680,39 +42828,81 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
+          <t>prod.7.desc</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>Partners submit leads in one place and see their status, while you get the full history of every referral.</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr">
+        <is>
+          <t>პარტნიორები ლიდებს ერთიან პორტალში აგზავნიან და ხედავენ სტატუსებს, შენ კი იღებ თითოეული რეკომენდაციის სრულ ისტორიას.</t>
+        </is>
+      </c>
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>Партнёры отправляют лиды в одном месте и видят их статус, а вы - полную историю каждой рекомендации.</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>Only on this landing</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
           <t>prod.8.desc</t>
         </is>
       </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>Personalised SMS reminders and notifications straight from your CRM - for payments, meetings and bookings.</t>
         </is>
       </c>
-      <c r="E177" s="9" t="inlineStr">
+      <c r="E178" s="9" t="inlineStr">
         <is>
           <t>პერსონალიზებული SMS შეხსენებები და შეტყობინებები პირდაპირ CRM-იდან — გადახდებზე, შეხვედრებსა და ჯავშნებზე.</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
+      <c r="F178" s="9" t="inlineStr">
         <is>
           <t>Персональные SMS-напоминания и уведомления прямо из CRM - о платежах, встречах и бронях.</t>
         </is>
       </c>
-      <c r="G177" s="3" t="inlineStr">
+      <c r="G178" s="3" t="inlineStr">
         <is>
           <t>Only on this landing</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr">
+      <c r="H178" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H177"/>
+  <autoFilter ref="A1:H178"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H376" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H377" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Updated,New,Changed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -43793,17 +43983,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Call</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>დარეკვა</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Позвонить</t>
+          <t>+995 32 205 50 60</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
